--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Apr-2026  16:34:55    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 18-Apr-2026  15:25:28    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Apr-2026  16:34:55</t>
+          <t>18-Apr-2026  15:25:28</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2054.36</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2233.92</v>
+        <v>2232.3</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1444.68</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1416.95</v>
+        <v>1416.09</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>7457.55</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7351.3</v>
+        <v>7349.09</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2355.08</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2464.01</v>
+        <v>2464.69</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1288.16</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1235.62</v>
+        <v>1235.05</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9393.49</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9083.559999999999</v>
+        <v>9091.73</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>913.67</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.8200000000001</v>
+        <v>937.48</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1841.62</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1938.66</v>
+        <v>1938.37</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>433.01</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>404.3</v>
+        <v>404.27</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>320.62</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>325.78</v>
+        <v>325.51</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1887.89</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1925.31</v>
+        <v>1925.65</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5752.92</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.68</v>
+        <v>5748.51</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1289.63</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1410.99</v>
+        <v>1410.71</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>437.83</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>403.13</v>
+        <v>402.8</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1253.57</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1256.33</v>
+        <v>1256.37</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7170.73</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6801.94</v>
+        <v>6800.95</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2720.86</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2738.24</v>
+        <v>2737.15</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1441.8</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1527.54</v>
+        <v>1527.65</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>841.04</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>912.49</v>
+        <v>911.92</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>652.3200000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>706.34</v>
+        <v>706.09</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5369.65</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5194.7</v>
+        <v>5194.83</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>935.13</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>838</v>
+        <v>838.11</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>2147.26</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2207.13</v>
+        <v>2207.14</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2329.18</v>
+        <v>2330.64</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1316.68</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1352.83</v>
+        <v>1352.77</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>311.39</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>356.61</v>
+        <v>356.63</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>851.02</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.53</v>
+        <v>852.52</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1351.55</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1482.92</v>
+        <v>1482.26</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1187.67</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1136.65</v>
+        <v>1136.16</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>388.68</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>405.63</v>
+        <v>405.81</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3871.36</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3826.73</v>
+        <v>3823.79</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3260.2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3357.33</v>
+        <v>3359.06</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13813.29</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14361.38</v>
+        <v>14357.9</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>371.26</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>347.16</v>
+        <v>346.95</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1241.82</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1226.99</v>
+        <v>1227.76</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>271.73</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.42</v>
+        <v>250.09</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>294.1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>282.55</v>
+        <v>282.49</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1389.87</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1415.8</v>
+        <v>1415.34</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1938.58</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1897.22</v>
+        <v>1897.45</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>985.01</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>858.24</v>
+        <v>857.48</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1071.75</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>976.66</v>
+        <v>976.2</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1727.68</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1711.62</v>
+        <v>1711.14</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2620.03</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2962.37</v>
+        <v>2959.51</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1099.81</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1112.69</v>
+        <v>1113.06</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>197.64</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>179.46</v>
+        <v>179.35</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1456.26</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1503.48</v>
+        <v>1502.6</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4199.9</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3907.42</v>
+        <v>3907.55</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>3827.65</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4427.7</v>
+        <v>4424.35</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11666.98</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11882.77</v>
+        <v>11876.59</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>207.88</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>231.6</v>
+        <v>231.39</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-Apr-2026  15:25:28    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 19-Apr-2026  15:25:28    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-Apr-2026  15:25:28</t>
+          <t>19-Apr-2026  15:25:28</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2054.36</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2232.3</v>
+        <v>2227.78</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1444.68</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1416.09</v>
+        <v>1415.21</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>7457.55</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7349.09</v>
+        <v>7346.71</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2355.08</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2464.69</v>
+        <v>2463.41</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -918,9 +918,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
@@ -950,7 +950,7 @@
         <v>1288.16</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1235.05</v>
+        <v>1234.13</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9393.49</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9091.73</v>
+        <v>9088.67</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>913.67</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.48</v>
+        <v>937.53</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1841.62</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1938.37</v>
+        <v>1938.85</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>433.01</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>404.27</v>
+        <v>403.82</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>320.62</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>325.51</v>
+        <v>325.41</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1887.89</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1925.65</v>
+        <v>1926.03</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5752.92</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5748.51</v>
+        <v>5749.07</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1289.63</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1410.71</v>
+        <v>1409.87</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>437.83</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>402.8</v>
+        <v>402.66</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1253.57</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1256.37</v>
+        <v>1255.62</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7170.73</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6800.95</v>
+        <v>6797.43</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2720.86</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2737.15</v>
+        <v>2735.13</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1441.8</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1527.65</v>
+        <v>1530.17</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>841.04</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>911.92</v>
+        <v>911.6900000000001</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>652.3200000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>706.09</v>
+        <v>705.9299999999999</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5369.65</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5194.83</v>
+        <v>5194.04</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>935.13</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>838.11</v>
+        <v>837.47</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>2207.14</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2330.64</v>
+        <v>2330.92</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1316.68</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1352.77</v>
+        <v>1352.23</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>311.39</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>356.63</v>
+        <v>356.42</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>851.02</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.52</v>
+        <v>850.63</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1351.55</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1482.26</v>
+        <v>1484.37</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1187.67</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1136.16</v>
+        <v>1136.56</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>388.68</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>405.81</v>
+        <v>405.52</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3871.36</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3823.79</v>
+        <v>3824.15</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3260.2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3359.06</v>
+        <v>3357.6</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13813.29</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14357.9</v>
+        <v>14353.16</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>371.26</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>346.95</v>
+        <v>346.44</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1241.82</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1227.76</v>
+        <v>1227.58</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>271.73</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.09</v>
+        <v>250.08</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>294.1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>282.49</v>
+        <v>282.26</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1389.87</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1415.34</v>
+        <v>1414.78</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1938.58</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1897.45</v>
+        <v>1897.88</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>985.01</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>857.48</v>
+        <v>856.1900000000001</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1071.75</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>976.2</v>
+        <v>975.47</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1727.68</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1711.14</v>
+        <v>1709.35</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2620.03</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2959.51</v>
+        <v>2968.92</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1099.81</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1113.06</v>
+        <v>1113.17</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>197.64</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>179.35</v>
+        <v>179.24</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1456.26</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1502.6</v>
+        <v>1505.27</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4199.9</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3907.55</v>
+        <v>3905.51</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>3827.65</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4424.35</v>
+        <v>4422.71</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11666.98</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11876.59</v>
+        <v>11859.45</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>207.88</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>231.39</v>
+        <v>231.73</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -163,10 +163,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-Apr-2026  15:25:28    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 20-Apr-2026  16:49:47    |    Closing Price Date: 20-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-Apr-2026  15:25:28</t>
+          <t>20-Apr-2026  16:49:47</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 90.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 88.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 45 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 44 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2218.3</v>
+        <v>2229.6</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2030.93</v>
+        <v>2049.85</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2054.36</v>
+        <v>2061.23</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2227.78</v>
+        <v>2221.27</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1573.4</v>
+        <v>1578.4</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1447.25</v>
+        <v>1459.74</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1444.68</v>
+        <v>1449.92</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1415.21</v>
+        <v>1414.86</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7699</v>
+        <v>7657</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7501.12</v>
+        <v>7515.97</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7457.55</v>
+        <v>7465.38</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7346.71</v>
+        <v>7341.21</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2464</v>
+        <v>2516.8</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2307.68</v>
+        <v>2327.6</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2355.08</v>
+        <v>2361.42</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2463.41</v>
+        <v>2461</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1359.1</v>
+        <v>1354.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1292.78</v>
+        <v>1298.68</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1288.16</v>
+        <v>1290.77</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1234.13</v>
+        <v>1235.71</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9773.5</v>
+        <v>9803</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9417.610000000001</v>
+        <v>9454.309999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9393.49</v>
+        <v>9409.549999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9088.67</v>
+        <v>9088.629999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>908.25</v>
+        <v>917.75</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>889.0700000000001</v>
+        <v>891.8</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>913.67</v>
+        <v>913.83</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.53</v>
+        <v>936.73</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1838.9</v>
+        <v>1830.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1777.84</v>
+        <v>1782.87</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1841.62</v>
+        <v>1841.19</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1938.85</v>
+        <v>1936.59</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>462.75</v>
+        <v>457.55</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>437.43</v>
+        <v>439.35</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>433.01</v>
+        <v>433.98</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>403.82</v>
+        <v>403.87</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>312.1</v>
+        <v>316.05</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>301.9</v>
+        <v>303.24</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>320.62</v>
+        <v>320.44</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>325.41</v>
+        <v>324.82</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>BPCL</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1846.9</v>
+        <v>1846.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1844.6</v>
+        <v>1844.75</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1887.89</v>
+        <v>1886.25</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1926.03</v>
+        <v>1924.42</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5735.5</v>
+        <v>5700</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5633.78</v>
+        <v>5640.08</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5752.92</v>
+        <v>5750.84</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5749.07</v>
+        <v>5748.06</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>BRITANNIA</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1240.8</v>
+        <v>1229.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1239.02</v>
+        <v>1238.11</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1289.63</v>
+        <v>1287.27</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1409.87</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+        <v>1406.79</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -1333,22 +1333,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>438.75</v>
+        <v>441.75</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>444.56</v>
+        <v>444.29</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>437.83</v>
+        <v>437.99</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>402.66</v>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
+        <v>402.82</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1363,7 +1363,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1235.7</v>
+        <v>1232.6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1240.5</v>
+        <v>1239.75</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1253.57</v>
+        <v>1252.75</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1255.62</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
+        <v>1254.56</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7189.5</v>
+        <v>7243</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7054.81</v>
+        <v>7072.73</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7170.73</v>
+        <v>7173.56</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6797.43</v>
+        <v>6796.71</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2720.5</v>
+        <v>2760.1</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2687.91</v>
+        <v>2694.79</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2720.86</v>
+        <v>2722.4</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2735.13</v>
+        <v>2732.07</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1442.3</v>
+        <v>1428.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1415.56</v>
+        <v>1416.78</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1441.8</v>
+        <v>1441.27</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1530.17</v>
+        <v>1528.92</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>799.9</v>
+        <v>795.45</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>799.65</v>
+        <v>799.25</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>841.04</v>
+        <v>839.25</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>911.6900000000001</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
+        <v>909.97</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>616.45</v>
+        <v>609.75</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>617.75</v>
+        <v>616.99</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>652.3200000000001</v>
+        <v>650.65</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>705.9299999999999</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
+        <v>704.59</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -1641,27 +1641,27 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5230.5</v>
+        <v>5282.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5258.01</v>
+        <v>5260.34</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5369.65</v>
+        <v>5366.24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5194.04</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
+        <v>5191.69</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1671,7 +1671,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>HEROMOTOCO</t>
         </is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1039</v>
+        <v>1015.25</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>958.64</v>
+        <v>964.03</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>935.13</v>
+        <v>938.27</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>837.47</v>
+        <v>838.77</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2240.8</v>
+        <v>2231.5</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2147.26</v>
+        <v>2155.28</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2207.14</v>
+        <v>2208.09</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2330.92</v>
+        <v>2330.32</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,12 +1754,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1346.8</v>
+        <v>1356.2</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1298.37</v>
+        <v>1303.88</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1316.68</v>
+        <v>1318.23</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1352.23</v>
+        <v>1351.39</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1798,12 +1798,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>306.8</v>
+        <v>305</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>301.51</v>
+        <v>301.84</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>311.39</v>
+        <v>311.14</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>356.42</v>
+        <v>355.67</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>853.9</v>
+        <v>851.95</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>828.3200000000001</v>
+        <v>830.5700000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>851.02</v>
+        <v>851.0599999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>850.63</v>
+        <v>850.8200000000001</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1318.7</v>
+        <v>1312.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1302.7</v>
+        <v>1303.64</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1351.55</v>
+        <v>1350.02</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1484.37</v>
+        <v>1482.46</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1240.3</v>
+        <v>1274.5</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1187.96</v>
+        <v>1196.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1187.67</v>
+        <v>1191.08</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1136.56</v>
+        <v>1137.22</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>383.6</v>
+        <v>379.2</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>375.45</v>
+        <v>375.81</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>388.68</v>
+        <v>388.31</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>405.52</v>
+        <v>405.1</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4096.1</v>
+        <v>4051</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3854.22</v>
+        <v>3872.96</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3871.36</v>
+        <v>3878.41</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3824.15</v>
+        <v>3823.3</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3200.2</v>
+        <v>3221.6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3162.24</v>
+        <v>3167.89</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3260.2</v>
+        <v>3258.68</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3357.6</v>
+        <v>3352.21</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13453</v>
+        <v>13450</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13214.7</v>
+        <v>13237.11</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13813.29</v>
+        <v>13799.04</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14353.16</v>
+        <v>14338.41</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>393.6</v>
+        <v>398</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>379.52</v>
+        <v>381.28</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>371.26</v>
+        <v>372.31</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>346.44</v>
+        <v>346.53</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1285.6</v>
+        <v>1286.4</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1231.22</v>
+        <v>1236.48</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1241.82</v>
+        <v>1243.57</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1227.58</v>
+        <v>1227.94</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>284.05</v>
+        <v>283.35</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>280.92</v>
+        <v>281.15</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>271.73</v>
+        <v>272.18</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.08</v>
+        <v>250.12</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>318.1</v>
+        <v>319.7</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>301.52</v>
+        <v>303.25</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>294.1</v>
+        <v>295.11</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>282.26</v>
+        <v>282.12</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1365</v>
+        <v>1363.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1358.03</v>
+        <v>1358.54</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1389.87</v>
+        <v>1388.83</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1414.78</v>
+        <v>1414.18</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1970.9</v>
+        <v>1982.5</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1909.66</v>
+        <v>1916.6</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1938.58</v>
+        <v>1940.3</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1897.88</v>
+        <v>1898.25</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1036.95</v>
+        <v>1045.15</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>986.09</v>
+        <v>991.71</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>985.01</v>
+        <v>987.37</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>856.1900000000001</v>
+        <v>857.6</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1080.25</v>
+        <v>1107.85</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1061.75</v>
+        <v>1066.14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1071.75</v>
+        <v>1073.17</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>975.47</v>
+        <v>976.1900000000001</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1675.5</v>
+        <v>1668.6</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1717.22</v>
+        <v>1712.59</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1727.68</v>
+        <v>1725.36</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1709.35</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
+        <v>1707.31</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2581.5</v>
+        <v>2579.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2512.83</v>
+        <v>2519.19</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2620.03</v>
+        <v>2618.45</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2968.92</v>
+        <v>2966.11</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1113.2</v>
+        <v>1120.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1080.11</v>
+        <v>1083.95</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1099.81</v>
+        <v>1100.62</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1113.17</v>
+        <v>1112.93</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>360.1</v>
+        <v>355.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>334.37</v>
+        <v>336.4</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>341.04</v>
+        <v>341.62</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.94</v>
+        <v>364.85</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2678,12 +2678,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>212.12</v>
+        <v>211.72</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>201.77</v>
+        <v>202.72</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>197.64</v>
+        <v>198.19</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>179.24</v>
+        <v>179.37</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1511.4</v>
+        <v>1504.4</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1440.8</v>
+        <v>1446.86</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1456.26</v>
+        <v>1458.15</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1505.27</v>
+        <v>1503.31</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4525.9</v>
+        <v>4513</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4297.35</v>
+        <v>4317.88</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4199.9</v>
+        <v>4212.18</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3905.51</v>
+        <v>3909.04</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4107.7</v>
+        <v>4242.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3800</v>
+        <v>3842.18</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3827.65</v>
+        <v>3843.92</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4422.71</v>
+        <v>4405.2</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11886</v>
+        <v>11917</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11428.36</v>
+        <v>11474.89</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11666.98</v>
+        <v>11676.78</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11859.45</v>
+        <v>11849.16</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>204.32</v>
+        <v>202.48</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.16</v>
+        <v>201.28</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>207.88</v>
+        <v>207.67</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>231.73</v>
+        <v>231.08</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 20-Apr-2026  16:49:47    |    Closing Price Date: 20-Apr-2026</t>
+          <t>Scan Run: 22-Apr-2026  04:49:52    |    Closing Price Date: 22-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>56</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>20-Apr-2026  16:49:47</t>
+          <t>22-Apr-2026  04:49:52</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 88.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 82.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 44 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 41 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2229.6</v>
+        <v>2233.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2049.85</v>
+        <v>2082.5</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2061.23</v>
+        <v>2074.19</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2221.27</v>
+        <v>2221.44</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1578.4</v>
+        <v>1586.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1459.74</v>
+        <v>1483.42</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1449.92</v>
+        <v>1460.72</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1414.86</v>
+        <v>1418.33</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7657</v>
+        <v>7740</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7515.97</v>
+        <v>7556.95</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7465.38</v>
+        <v>7486.64</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7341.21</v>
+        <v>7349.15</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2516.8</v>
+        <v>2540.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2327.6</v>
+        <v>2366.45</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2361.42</v>
+        <v>2375.29</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2461</v>
+        <v>2462.6</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1354.7</v>
+        <v>1370.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1298.68</v>
+        <v>1312.36</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1290.77</v>
+        <v>1297.19</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1235.71</v>
+        <v>1238.45</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9803</v>
+        <v>9746</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9454.309999999999</v>
+        <v>9511.280000000001</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9409.549999999999</v>
+        <v>9437.190000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9088.629999999999</v>
+        <v>9102.110000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>917.75</v>
+        <v>931.95</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>891.8</v>
+        <v>899.6799999999999</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>913.83</v>
+        <v>915.48</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.73</v>
+        <v>936.71</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1830.6</v>
+        <v>1840.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1782.87</v>
+        <v>1794.22</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1841.19</v>
+        <v>1841.53</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1936.59</v>
+        <v>1934.79</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>457.55</v>
+        <v>445.15</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>439.35</v>
+        <v>440.95</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>433.98</v>
+        <v>435.07</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>403.87</v>
+        <v>404.75</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>316.05</v>
+        <v>316.15</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>303.24</v>
+        <v>305.75</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>320.44</v>
+        <v>320.18</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.82</v>
+        <v>324.67</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1846.1</v>
+        <v>1836.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1844.75</v>
+        <v>1844.81</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1886.25</v>
+        <v>1883.11</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1924.42</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1922.86</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1245,34 +1245,34 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5700</v>
+        <v>5763</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5640.08</v>
+        <v>5668.8</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5750.84</v>
+        <v>5754.58</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5748.06</v>
+        <v>5749.09</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1229.5</v>
+        <v>1226.8</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1238.11</v>
+        <v>1236.55</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1287.27</v>
+        <v>1282.83</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1406.79</v>
+        <v>1403.28</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>441.75</v>
+        <v>446.75</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>444.29</v>
+        <v>444.43</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>437.99</v>
+        <v>438.52</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>402.82</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>403.65</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1232.6</v>
+        <v>1213.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1239.75</v>
+        <v>1235.59</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1252.75</v>
+        <v>1249.99</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1254.56</v>
+        <v>1253.81</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7243</v>
+        <v>7163</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7072.73</v>
+        <v>7095.79</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7173.56</v>
+        <v>7175.67</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6796.71</v>
+        <v>6804.73</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2760.1</v>
+        <v>2769.9</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2694.79</v>
+        <v>2709.08</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2722.4</v>
+        <v>2726.34</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2732.07</v>
+        <v>2732.9</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,24 +1509,24 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1428.3</v>
+        <v>1302.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1416.78</v>
+        <v>1408.04</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1441.27</v>
+        <v>1435.84</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1528.92</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1525.81</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -1553,24 +1553,24 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>795.45</v>
+        <v>804</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>799.25</v>
+        <v>800.78</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>839.25</v>
+        <v>836.83</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>909.97</v>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>907.95</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>609.75</v>
+        <v>607.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>616.99</v>
+        <v>615.8200000000001</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>650.65</v>
+        <v>647.5700000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>704.59</v>
+        <v>702.73</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5282.5</v>
+        <v>5265</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5260.34</v>
+        <v>5260.67</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5366.24</v>
+        <v>5358.22</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5191.69</v>
+        <v>5193.08</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1015.25</v>
+        <v>1030.75</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>964.03</v>
+        <v>975.35</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>938.27</v>
+        <v>945.04</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>838.77</v>
+        <v>842.48</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2231.5</v>
+        <v>2350</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2155.28</v>
+        <v>2187.22</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2208.09</v>
+        <v>2217.52</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>2330.32</v>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1356.2</v>
+        <v>1369.3</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1303.88</v>
+        <v>1317.39</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1318.23</v>
+        <v>1322.88</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.39</v>
+        <v>1351.94</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>305</v>
+        <v>306.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>301.84</v>
+        <v>302.94</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>311.14</v>
+        <v>310.89</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>355.67</v>
+        <v>354.72</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>851.95</v>
+        <v>858.3</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>830.5700000000001</v>
+        <v>835.4299999999999</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>851.0599999999999</v>
+        <v>851.54</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>850.8200000000001</v>
+        <v>850.95</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,24 +1905,24 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1312.6</v>
+        <v>1263.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1303.64</v>
+        <v>1300.68</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1350.02</v>
+        <v>1345.26</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1482.46</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1478.61</v>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1274.5</v>
+        <v>1266.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1196.2</v>
+        <v>1210.11</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1191.08</v>
+        <v>1197.38</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1137.22</v>
+        <v>1139.91</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>379.2</v>
+        <v>378.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>375.81</v>
+        <v>376.63</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>388.31</v>
+        <v>387.7</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>405.1</v>
+        <v>404.61</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4051</v>
+        <v>4035</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3872.96</v>
+        <v>3905.84</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3878.41</v>
+        <v>3891.97</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3823.3</v>
+        <v>3827.89</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3221.6</v>
+        <v>3201.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3167.89</v>
+        <v>3177.91</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3258.68</v>
+        <v>3256</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3352.21</v>
+        <v>3349.67</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13450</v>
+        <v>13366</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13237.11</v>
+        <v>13268.68</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13799.04</v>
+        <v>13769.32</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14338.41</v>
+        <v>14320.09</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>398</v>
+        <v>403.2</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>381.28</v>
+        <v>384.65</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>372.31</v>
+        <v>374.42</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>346.53</v>
+        <v>347.58</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1286.4</v>
+        <v>1413.7</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1236.48</v>
+        <v>1265.71</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1243.57</v>
+        <v>1255.38</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1227.94</v>
+        <v>1231.29</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>283.35</v>
+        <v>284.2</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>281.15</v>
+        <v>281.61</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>272.18</v>
+        <v>273.07</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.12</v>
+        <v>250.78</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.7</v>
+        <v>319.15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>303.25</v>
+        <v>306.15</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>295.11</v>
+        <v>296.96</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>282.12</v>
+        <v>282.86</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1363.3</v>
+        <v>1359.4</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1358.54</v>
+        <v>1358.17</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1388.83</v>
+        <v>1386.34</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1414.18</v>
+        <v>1413.04</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1982.5</v>
+        <v>1890</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1916.6</v>
+        <v>1913.64</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1940.3</v>
+        <v>1937.24</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1898.25</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1898.3</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1045.15</v>
+        <v>1030</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>991.71</v>
+        <v>999.98</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>987.37</v>
+        <v>991.22</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>857.6</v>
+        <v>861.17</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1107.85</v>
+        <v>1104</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1066.14</v>
+        <v>1073.68</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1073.17</v>
+        <v>1075.84</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>976.1900000000001</v>
+        <v>978.8</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1668.6</v>
+        <v>1657.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1712.59</v>
+        <v>1703.26</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1725.36</v>
+        <v>1720.43</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1707.31</v>
+        <v>1706.4</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2579.6</v>
+        <v>2561.5</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2519.19</v>
+        <v>2531.08</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2618.45</v>
+        <v>2615.92</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2966.11</v>
+        <v>2958.58</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1120.4</v>
+        <v>1165.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1083.95</v>
+        <v>1096.72</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1100.62</v>
+        <v>1104.72</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1112.93</v>
+        <v>1113.74</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>355.7</v>
+        <v>360.05</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>336.4</v>
+        <v>340.33</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>341.62</v>
+        <v>342.88</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.85</v>
+        <v>364.72</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>211.72</v>
+        <v>212.58</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>202.72</v>
+        <v>204.46</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>198.19</v>
+        <v>199.28</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>179.37</v>
+        <v>180.02</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,34 +2741,34 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1504.4</v>
+        <v>1440.8</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1446.86</v>
+        <v>1450.93</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1458.15</v>
+        <v>1459.07</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1503.31</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1502.66</v>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4513</v>
+        <v>4461.2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4317.88</v>
+        <v>4345.48</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4212.18</v>
+        <v>4232.03</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3909.04</v>
+        <v>3920.16</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4242.8</v>
+        <v>4346.2</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3842.18</v>
+        <v>3937.43</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3843.92</v>
+        <v>3884.22</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4405.2</v>
+        <v>4404.47</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11917</v>
+        <v>12016</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11474.89</v>
+        <v>11575.03</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11676.78</v>
+        <v>11703.73</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11849.16</v>
+        <v>11852.69</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>202.48</v>
+        <v>203.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.28</v>
+        <v>201.83</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>207.67</v>
+        <v>207.41</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>231.08</v>
+        <v>230.55</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Apr-2026  04:49:52    |    Closing Price Date: 22-Apr-2026</t>
+          <t>Scan Run: 22-Apr-2026  16:45:54    |    Closing Price Date: 22-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -598,20 +598,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>58</v>
+        <v>76</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>62</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026  04:49:52</t>
+          <t>22-Apr-2026  16:45:54</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 82.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 76.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 41 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 38 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2233.3</v>
+        <v>2260.8</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2082.5</v>
+        <v>2085.12</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2074.19</v>
+        <v>2075.27</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2221.44</v>
+        <v>2221.71</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1586.8</v>
+        <v>1588.6</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1483.42</v>
+        <v>1483.59</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1460.72</v>
+        <v>1460.79</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1418.33</v>
+        <v>1418.35</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7740</v>
+        <v>7662</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7556.95</v>
+        <v>7549.53</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7486.64</v>
+        <v>7483.58</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7349.15</v>
+        <v>7348.37</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2540.1</v>
+        <v>2562.9</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2366.45</v>
+        <v>2368.62</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2375.29</v>
+        <v>2376.19</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.6</v>
+        <v>2462.83</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1370.8</v>
+        <v>1379.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1312.36</v>
+        <v>1313.2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1297.19</v>
+        <v>1297.53</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1238.45</v>
+        <v>1238.54</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -985,16 +985,16 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9746</v>
+        <v>9602</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9511.280000000001</v>
+        <v>9497.559999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9437.190000000001</v>
+        <v>9431.540000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9102.110000000001</v>
+        <v>9100.67</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>931.95</v>
+        <v>934.75</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>899.6799999999999</v>
+        <v>899.95</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>915.48</v>
+        <v>915.59</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.71</v>
+        <v>936.74</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1073,25 +1073,25 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1840.1</v>
+        <v>1842.9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1794.22</v>
+        <v>1794.49</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1841.53</v>
+        <v>1841.64</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1934.79</v>
+        <v>1934.81</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>445.15</v>
+        <v>448.7</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>440.95</v>
+        <v>441.28</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.07</v>
+        <v>435.21</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>404.75</v>
+        <v>404.78</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>316.15</v>
+        <v>314.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>305.75</v>
+        <v>305.58</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>320.18</v>
+        <v>320.11</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.67</v>
+        <v>324.65</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1836.2</v>
+        <v>1829</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1844.81</v>
+        <v>1844.13</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1883.11</v>
+        <v>1882.83</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1922.86</v>
+        <v>1922.79</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1249,30 +1249,30 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5763</v>
+        <v>5729.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5668.8</v>
+        <v>5665.61</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5754.58</v>
+        <v>5753.27</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5749.09</v>
+        <v>5748.75</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1226.8</v>
+        <v>1236.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1236.55</v>
+        <v>1237.46</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1282.83</v>
+        <v>1283.21</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1403.28</v>
+        <v>1403.38</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1337,20 +1337,20 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>446.75</v>
+        <v>444.15</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>444.43</v>
+        <v>444.18</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>438.52</v>
+        <v>438.42</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>403.65</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>403.63</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1213.4</v>
+        <v>1217</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1235.59</v>
+        <v>1235.93</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1249.99</v>
+        <v>1250.14</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1253.81</v>
+        <v>1253.85</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7163</v>
+        <v>7230</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7095.79</v>
+        <v>7102.17</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7175.67</v>
+        <v>7178.3</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6804.73</v>
+        <v>6805.4</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2769.9</v>
+        <v>2776.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2709.08</v>
+        <v>2709.72</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2726.34</v>
+        <v>2726.61</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2732.9</v>
+        <v>2732.96</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1302.9</v>
+        <v>1285.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1408.04</v>
+        <v>1406.36</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1435.84</v>
+        <v>1435.15</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1525.81</v>
+        <v>1525.63</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1557,20 +1557,20 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>804</v>
+        <v>799.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>800.78</v>
+        <v>800.39</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>836.83</v>
+        <v>836.67</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>907.95</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>907.91</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>607.2</v>
+        <v>604.05</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>615.8200000000001</v>
+        <v>615.52</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>647.5700000000001</v>
+        <v>647.45</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>702.73</v>
+        <v>702.7</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1645,20 +1645,20 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5265</v>
+        <v>5189</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5260.67</v>
+        <v>5253.43</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5358.22</v>
+        <v>5355.24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5193.08</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5192.32</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -1666,9 +1666,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1030.75</v>
+        <v>1039.9</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>975.35</v>
+        <v>976.22</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>945.04</v>
+        <v>945.4</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>842.48</v>
+        <v>842.5700000000001</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2350</v>
+        <v>2368.8</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2187.22</v>
+        <v>2189.01</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2217.52</v>
+        <v>2218.26</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2330.32</v>
+        <v>2330.51</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1777,16 +1777,16 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1369.3</v>
+        <v>1367.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1317.39</v>
+        <v>1317.23</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1322.88</v>
+        <v>1322.81</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.94</v>
+        <v>1351.92</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>306.3</v>
+        <v>305.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>302.94</v>
+        <v>302.86</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.89</v>
+        <v>310.86</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>354.72</v>
+        <v>354.71</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>858.3</v>
+        <v>870.1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>835.4299999999999</v>
+        <v>836.5599999999999</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>851.54</v>
+        <v>852.01</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>850.95</v>
+        <v>851.0700000000001</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1263.9</v>
+        <v>1268.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1300.68</v>
+        <v>1301.13</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1345.26</v>
+        <v>1345.44</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1478.61</v>
+        <v>1478.66</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1266.8</v>
+        <v>1263.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1210.11</v>
+        <v>1209.79</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1197.38</v>
+        <v>1197.25</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1139.91</v>
+        <v>1139.87</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>378.7</v>
+        <v>376.85</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>376.63</v>
+        <v>376.45</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>387.7</v>
+        <v>387.63</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.61</v>
+        <v>404.59</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4035</v>
+        <v>4021.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3905.84</v>
+        <v>3904.52</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3891.97</v>
+        <v>3891.42</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3827.89</v>
+        <v>3827.75</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2085,20 +2085,20 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3201.3</v>
+        <v>3149.7</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3177.91</v>
+        <v>3173</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3256</v>
+        <v>3253.98</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3349.67</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3349.16</v>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13366</v>
+        <v>13337</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13268.68</v>
+        <v>13265.92</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13769.32</v>
+        <v>13768.18</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14320.09</v>
+        <v>14319.8</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>403.2</v>
+        <v>405.4</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>384.65</v>
+        <v>384.86</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>374.42</v>
+        <v>374.51</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>347.58</v>
+        <v>347.6</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1413.7</v>
+        <v>1395.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1265.71</v>
+        <v>1264.01</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1255.38</v>
+        <v>1254.68</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1231.29</v>
+        <v>1231.11</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>284.2</v>
+        <v>283.65</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>281.61</v>
+        <v>281.56</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>273.07</v>
+        <v>273.05</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.78</v>
+        <v>250.77</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.15</v>
+        <v>319.75</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>306.15</v>
+        <v>306.21</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>296.96</v>
+        <v>296.99</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>282.86</v>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1359.4</v>
+        <v>1362.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1358.17</v>
+        <v>1358.42</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1386.34</v>
+        <v>1386.44</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1413.04</v>
+        <v>1413.06</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1890</v>
+        <v>1884.8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1913.64</v>
+        <v>1913.14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1937.24</v>
+        <v>1937.04</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1898.3</v>
+        <v>1898.24</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1030</v>
+        <v>1044.55</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>999.98</v>
+        <v>1001.36</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>991.22</v>
+        <v>991.79</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>861.17</v>
+        <v>861.3099999999999</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1104</v>
+        <v>1103.3</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1073.68</v>
+        <v>1073.62</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1075.84</v>
+        <v>1075.81</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>978.8</v>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1657.5</v>
+        <v>1669.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1703.26</v>
+        <v>1704.43</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1720.43</v>
+        <v>1720.91</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1706.4</v>
+        <v>1706.52</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2561.5</v>
+        <v>2538.5</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2531.08</v>
+        <v>2528.89</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2615.92</v>
+        <v>2615.01</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2958.58</v>
+        <v>2958.35</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1165.5</v>
+        <v>1178.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1096.72</v>
+        <v>1097.96</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1104.72</v>
+        <v>1105.23</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1113.74</v>
+        <v>1113.87</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>360.05</v>
+        <v>361.85</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>340.33</v>
+        <v>340.5</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>342.88</v>
+        <v>342.95</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.72</v>
+        <v>364.73</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>212.58</v>
+        <v>213.03</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>204.46</v>
+        <v>204.5</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>199.28</v>
+        <v>199.29</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.02</v>
+        <v>180.03</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1440.8</v>
+        <v>1462.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1450.93</v>
+        <v>1453.01</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1459.07</v>
+        <v>1459.93</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1502.66</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1502.88</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4461.2</v>
+        <v>4454.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4345.48</v>
+        <v>4344.85</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4232.03</v>
+        <v>4231.77</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3920.16</v>
+        <v>3920.1</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4346.2</v>
+        <v>4434.5</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3937.43</v>
+        <v>3945.84</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3884.22</v>
+        <v>3887.68</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4404.47</v>
+        <v>4405.35</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>12016</v>
+        <v>12193</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11575.03</v>
+        <v>11591.89</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11703.73</v>
+        <v>11710.67</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11852.69</v>
+        <v>11854.45</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>203.7</v>
+        <v>204</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.83</v>
+        <v>201.86</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>207.41</v>
+        <v>207.42</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>230.55</v>
+        <v>230.56</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Apr-2026  16:45:54    |    Closing Price Date: 22-Apr-2026</t>
+          <t>Scan Run: 23-Apr-2026  17:59:29    |    Closing Price Date: 23-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026  16:45:54</t>
+          <t>23-Apr-2026  17:59:29</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 76.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 38 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2260.8</v>
+        <v>2300</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2085.12</v>
+        <v>2105.58</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2075.27</v>
+        <v>2084.08</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2221.71</v>
+        <v>2229.15</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1588.6</v>
+        <v>1602.9</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1483.59</v>
+        <v>1494.96</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1460.79</v>
+        <v>1466.37</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1418.35</v>
+        <v>1422.34</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7662</v>
+        <v>7781</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7549.53</v>
+        <v>7571.57</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7483.58</v>
+        <v>7495.25</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7348.37</v>
+        <v>7347.01</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2562.9</v>
+        <v>2521.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2368.62</v>
+        <v>2383.17</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2376.19</v>
+        <v>2381.88</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.83</v>
+        <v>2462.87</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1379.6</v>
+        <v>1369.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1313.2</v>
+        <v>1318.57</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1297.53</v>
+        <v>1300.36</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1238.54</v>
+        <v>1239.94</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9602</v>
+        <v>9550.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9497.559999999999</v>
+        <v>9502.610000000001</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9431.540000000001</v>
+        <v>9436.209999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9100.67</v>
+        <v>9105.77</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>934.75</v>
+        <v>918.35</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>899.95</v>
+        <v>901.7</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>915.59</v>
+        <v>915.7</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.74</v>
+        <v>937.34</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1842.9</v>
+        <v>1792.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1794.49</v>
+        <v>1794.31</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1841.64</v>
+        <v>1839.72</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1934.81</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1935.08</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>448.7</v>
+        <v>449.95</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>441.28</v>
+        <v>442.11</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.21</v>
+        <v>435.79</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>404.78</v>
+        <v>405.67</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>314.4</v>
+        <v>309.8</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>305.58</v>
+        <v>305.98</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>320.11</v>
+        <v>319.71</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.65</v>
+        <v>324.7</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1829</v>
+        <v>1841.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1844.13</v>
+        <v>1843.85</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1882.83</v>
+        <v>1881.19</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1922.79</v>
+        <v>1922.1</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5729.5</v>
+        <v>5671.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5665.61</v>
+        <v>5666.17</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5753.27</v>
+        <v>5750.06</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5748.75</v>
+        <v>5745.25</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,29 +1289,29 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1236.3</v>
+        <v>1305.9</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1237.46</v>
+        <v>1243.98</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1283.21</v>
+        <v>1284.1</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1403.38</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1402.77</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>444.15</v>
+        <v>450.65</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>444.18</v>
+        <v>444.8</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>438.42</v>
+        <v>438.9</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>403.63</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>404.35</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,34 +1377,34 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1217</v>
+        <v>1331</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1235.93</v>
+        <v>1244.99</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1250.14</v>
+        <v>1253.31</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1253.85</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1254.72</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7230</v>
+        <v>7092.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7102.17</v>
+        <v>7101.25</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7178.3</v>
+        <v>7174.93</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6805.4</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6812.08</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2776.6</v>
+        <v>2735</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2709.72</v>
+        <v>2712.13</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2726.61</v>
+        <v>2726.94</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2732.96</v>
+        <v>2733.94</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1285.3</v>
+        <v>1277.6</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1406.36</v>
+        <v>1394.1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1435.15</v>
+        <v>1428.97</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1525.63</v>
+        <v>1515.96</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>799.9</v>
+        <v>784.35</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>800.39</v>
+        <v>798.86</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>836.67</v>
+        <v>834.62</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>907.91</v>
+        <v>907.01</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>604.05</v>
+        <v>598.65</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>615.52</v>
+        <v>613.91</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>647.45</v>
+        <v>645.54</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>702.7</v>
+        <v>701.6900000000001</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5189</v>
+        <v>5032</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5253.43</v>
+        <v>5232.34</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5355.24</v>
+        <v>5342.57</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5192.32</v>
+        <v>5193.11</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1039.9</v>
+        <v>1041.35</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>976.22</v>
+        <v>982.4299999999999</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>945.4</v>
+        <v>949.16</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>842.5700000000001</v>
+        <v>845.71</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2368.8</v>
+        <v>2366.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2189.01</v>
+        <v>2205.9</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2218.26</v>
+        <v>2224.07</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2330.51</v>
+        <v>2327.37</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1367.6</v>
+        <v>1348</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1317.23</v>
+        <v>1320.16</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1322.81</v>
+        <v>1323.8</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.92</v>
+        <v>1352.33</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1798,9 +1798,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>305.5</v>
+        <v>305.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>302.86</v>
+        <v>303.09</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.86</v>
+        <v>310.64</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>354.71</v>
+        <v>354.12</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>870.1</v>
+        <v>860.35</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>836.5599999999999</v>
+        <v>838.8200000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>852.01</v>
+        <v>852.33</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>851.0700000000001</v>
+        <v>852.04</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1268.6</v>
+        <v>1240.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1301.13</v>
+        <v>1295.36</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1345.44</v>
+        <v>1341.33</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1478.66</v>
+        <v>1475.37</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1263.4</v>
+        <v>1257</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1209.79</v>
+        <v>1214.28</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1197.25</v>
+        <v>1199.59</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1139.87</v>
+        <v>1141.99</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>376.85</v>
+        <v>370.4</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>376.45</v>
+        <v>375.88</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>387.63</v>
+        <v>386.95</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.59</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>404.36</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4021.1</v>
+        <v>4054.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3904.52</v>
+        <v>3918.76</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3891.42</v>
+        <v>3897.8</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3827.75</v>
+        <v>3829.93</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3149.7</v>
+        <v>3047.7</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3173</v>
+        <v>3161.07</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3253.98</v>
+        <v>3245.89</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3349.16</v>
+        <v>3348.28</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13337</v>
+        <v>13160</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13265.92</v>
+        <v>13255.83</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13768.18</v>
+        <v>13744.33</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14319.8</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>14318.58</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>405.4</v>
+        <v>402.25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>384.86</v>
+        <v>386.52</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>374.51</v>
+        <v>375.59</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>347.6</v>
+        <v>348.65</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1395.8</v>
+        <v>1410.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1264.01</v>
+        <v>1277.96</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1254.68</v>
+        <v>1260.79</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1231.11</v>
+        <v>1232.51</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>283.65</v>
+        <v>286.25</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>281.56</v>
+        <v>282</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>273.05</v>
+        <v>273.56</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>250.77</v>
+        <v>251.31</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.75</v>
+        <v>319.15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>306.21</v>
+        <v>307.44</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>296.99</v>
+        <v>297.86</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>282.86</v>
+        <v>283.33</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,24 +2345,24 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1362.1</v>
+        <v>1343.4</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1358.42</v>
+        <v>1356.99</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1386.44</v>
+        <v>1384.75</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1413.06</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1412.32</v>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1884.8</v>
+        <v>1828.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1913.14</v>
+        <v>1905.04</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1937.04</v>
+        <v>1932.77</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1898.24</v>
+        <v>1898.91</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1044.55</v>
+        <v>1009.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1001.36</v>
+        <v>1002.12</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>991.79</v>
+        <v>992.48</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>861.3099999999999</v>
+        <v>863.75</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1103.3</v>
+        <v>1094.25</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1073.62</v>
+        <v>1075.58</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1075.81</v>
+        <v>1076.53</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>978.8</v>
+        <v>980.73</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1669.8</v>
+        <v>1680.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1704.43</v>
+        <v>1702.11</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1720.91</v>
+        <v>1719.31</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1706.52</v>
+        <v>1707.27</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,24 +2565,24 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2538.5</v>
+        <v>2521.8</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2528.89</v>
+        <v>2528.22</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2615.01</v>
+        <v>2611.36</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2958.35</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2951.64</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1178.6</v>
+        <v>1184.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1097.96</v>
+        <v>1106.2</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1105.23</v>
+        <v>1108.34</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1113.87</v>
+        <v>1114.47</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>361.85</v>
+        <v>351.95</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>340.5</v>
+        <v>341.59</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>342.95</v>
+        <v>343.3</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.73</v>
+        <v>364.61</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>213.03</v>
+        <v>210.91</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>204.5</v>
+        <v>205.11</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>199.29</v>
+        <v>199.75</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.03</v>
+        <v>180.5</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1462.6</v>
+        <v>1421.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1453.01</v>
+        <v>1450.01</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1459.93</v>
+        <v>1458.42</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1502.88</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1501.56</v>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4454.6</v>
+        <v>4456.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4344.85</v>
+        <v>4355.48</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4231.77</v>
+        <v>4240.58</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3920.1</v>
+        <v>3922.86</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4434.5</v>
+        <v>4251.4</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3945.84</v>
+        <v>3974.94</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3887.68</v>
+        <v>3901.94</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4405.35</v>
+        <v>4401.11</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>12193</v>
+        <v>12167</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11591.89</v>
+        <v>11646.66</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11710.67</v>
+        <v>11728.57</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11854.45</v>
+        <v>11851.96</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>204</v>
+        <v>202.76</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.86</v>
+        <v>201.95</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>207.42</v>
+        <v>207.24</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>230.56</v>
+        <v>230.32</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 23-Apr-2026  17:59:29    |    Closing Price Date: 23-Apr-2026</t>
+          <t>Scan Run: 24-Apr-2026  16:41:29    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>23-Apr-2026  17:59:29</t>
+          <t>24-Apr-2026  16:41:29</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2300</v>
+        <v>2287.6</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2105.58</v>
+        <v>2122.92</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2084.08</v>
+        <v>2092.06</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2229.15</v>
+        <v>2230.06</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1602.9</v>
+        <v>1585.1</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1494.96</v>
+        <v>1503.54</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1466.37</v>
+        <v>1471.02</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1422.34</v>
+        <v>1424.46</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7781</v>
+        <v>7732.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7571.57</v>
+        <v>7586.9</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7495.25</v>
+        <v>7504.55</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7347.01</v>
+        <v>7350.2</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2521.4</v>
+        <v>2485.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2383.17</v>
+        <v>2392.88</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2381.88</v>
+        <v>2385.93</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.87</v>
+        <v>2462.66</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1369.6</v>
+        <v>1365.9</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1318.57</v>
+        <v>1323.08</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1300.36</v>
+        <v>1302.93</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.94</v>
+        <v>1240.13</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9550.5</v>
+        <v>9576</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9502.610000000001</v>
+        <v>9509.6</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9436.209999999999</v>
+        <v>9441.690000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9105.77</v>
+        <v>9109.059999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>918.35</v>
+        <v>921.55</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>901.7</v>
+        <v>903.59</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>915.7</v>
+        <v>915.9299999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.34</v>
+        <v>936.51</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1792.6</v>
+        <v>1770.7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1794.31</v>
+        <v>1792.06</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1839.72</v>
+        <v>1837.01</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1935.08</v>
+        <v>1931.66</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>449.95</v>
+        <v>444.45</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>442.11</v>
+        <v>442.33</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.79</v>
+        <v>436.13</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>405.67</v>
+        <v>405.97</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>309.8</v>
+        <v>308.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>305.98</v>
+        <v>306.19</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>319.71</v>
+        <v>319.25</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.7</v>
+        <v>324.41</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1841.2</v>
+        <v>1814.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1843.85</v>
+        <v>1841.05</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1881.19</v>
+        <v>1878.58</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1922.1</v>
+        <v>1921.34</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5671.5</v>
+        <v>5730.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5666.17</v>
+        <v>5672.3</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5750.06</v>
+        <v>5749.3</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.25</v>
+        <v>5745.72</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1305.9</v>
+        <v>1295</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1243.98</v>
+        <v>1248.83</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1284.1</v>
+        <v>1284.52</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1402.77</v>
+        <v>1401.67</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>450.65</v>
+        <v>456</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>444.8</v>
+        <v>445.86</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>438.9</v>
+        <v>439.57</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>404.35</v>
+        <v>405.07</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1331</v>
+        <v>1317.1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1244.99</v>
+        <v>1251.86</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1253.31</v>
+        <v>1255.81</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1254.72</v>
+        <v>1255.33</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7092.5</v>
+        <v>7111.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7101.25</v>
+        <v>7102.22</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7174.93</v>
+        <v>7172.45</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6812.08</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>6817.27</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2735</v>
+        <v>2739.3</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2712.13</v>
+        <v>2714.72</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2726.94</v>
+        <v>2727.42</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2733.94</v>
+        <v>2734.29</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1277.6</v>
+        <v>1203.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1394.1</v>
+        <v>1352.22</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1428.97</v>
+        <v>1394.33</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1515.96</v>
+        <v>1485.14</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>784.35</v>
+        <v>784.85</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>798.86</v>
+        <v>797.53</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>834.62</v>
+        <v>832.67</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>907.01</v>
+        <v>905.72</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>598.65</v>
+        <v>588.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>613.91</v>
+        <v>611.46</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>645.54</v>
+        <v>643.29</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>701.6900000000001</v>
+        <v>700.29</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5032</v>
+        <v>4961.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5232.34</v>
+        <v>5206.55</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5342.57</v>
+        <v>5327.62</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5193.11</v>
+        <v>5191.18</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1041.35</v>
+        <v>1048.35</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>982.4299999999999</v>
+        <v>988.7</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>949.16</v>
+        <v>953.05</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>845.71</v>
+        <v>847.75</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2366.4</v>
+        <v>2327.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2205.9</v>
+        <v>2217.47</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2224.07</v>
+        <v>2228.12</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2327.37</v>
+        <v>2327.58</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1348</v>
+        <v>1326.2</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1320.16</v>
+        <v>1320.74</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1323.8</v>
+        <v>1323.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1352.33</v>
+        <v>1351.98</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,24 +1817,24 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>305.3</v>
+        <v>301.6</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>303.09</v>
+        <v>302.95</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.64</v>
+        <v>310.29</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>354.12</v>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>353.63</v>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
@@ -1861,34 +1861,34 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>860.35</v>
+        <v>847.95</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>838.8200000000001</v>
+        <v>839.6900000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>852.33</v>
+        <v>852.16</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.04</v>
+        <v>852.01</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1240.6</v>
+        <v>1154.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1295.36</v>
+        <v>1281.96</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1341.33</v>
+        <v>1334.01</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1475.37</v>
+        <v>1472.58</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1257</v>
+        <v>1255.7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1214.28</v>
+        <v>1218.23</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1199.59</v>
+        <v>1201.79</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1141.99</v>
+        <v>1143.04</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,17 +1993,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>370.4</v>
+        <v>370.85</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>375.88</v>
+        <v>375.4</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>386.95</v>
+        <v>386.32</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>404.36</v>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4054.1</v>
+        <v>4014.3</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3918.76</v>
+        <v>3927.86</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3897.8</v>
+        <v>3902.37</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3829.93</v>
+        <v>3833.41</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3047.7</v>
+        <v>3038.4</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3161.07</v>
+        <v>3149.38</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3245.89</v>
+        <v>3237.75</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3348.28</v>
+        <v>3341.4</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13160</v>
+        <v>13048</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13255.83</v>
+        <v>13236.04</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13744.33</v>
+        <v>13717.03</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14318.58</v>
+        <v>14314.68</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>402.25</v>
+        <v>401.85</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>386.52</v>
+        <v>387.98</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>375.59</v>
+        <v>376.62</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>348.65</v>
+        <v>349.64</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1410.5</v>
+        <v>1421.3</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1277.96</v>
+        <v>1291.61</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1260.79</v>
+        <v>1267.08</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1232.51</v>
+        <v>1233.98</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>286.25</v>
+        <v>284.8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>282</v>
+        <v>282.27</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>273.56</v>
+        <v>274</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>251.31</v>
+        <v>251.56</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.15</v>
+        <v>316.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>307.44</v>
+        <v>308.3</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>297.86</v>
+        <v>298.58</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>283.33</v>
+        <v>284.01</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1343.4</v>
+        <v>1327.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1356.99</v>
+        <v>1354.21</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1384.75</v>
+        <v>1382.52</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.32</v>
+        <v>1412.06</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1828.1</v>
+        <v>1768.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1905.04</v>
+        <v>1892.08</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1932.77</v>
+        <v>1926.34</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1898.91</v>
+        <v>1896.48</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1009.3</v>
+        <v>1011.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1002.12</v>
+        <v>1002.99</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>992.48</v>
+        <v>993.22</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>863.75</v>
+        <v>864.76</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1094.25</v>
+        <v>1101.1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1075.58</v>
+        <v>1078.01</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1076.53</v>
+        <v>1077.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>980.73</v>
+        <v>982.16</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1680.1</v>
+        <v>1620.4</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1702.11</v>
+        <v>1694.33</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1719.31</v>
+        <v>1715.43</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1707.27</v>
+        <v>1705.82</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2521.8</v>
+        <v>2396.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2528.22</v>
+        <v>2515.71</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2611.36</v>
+        <v>2602.95</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2951.64</v>
+        <v>2946.8</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1184.4</v>
+        <v>1174</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1106.2</v>
+        <v>1112.65</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1108.34</v>
+        <v>1110.91</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1114.47</v>
+        <v>1114.74</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>351.95</v>
+        <v>350.5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>341.59</v>
+        <v>342.44</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>343.3</v>
+        <v>343.58</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.61</v>
+        <v>364.47</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.91</v>
+        <v>210.07</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>205.11</v>
+        <v>205.58</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>199.75</v>
+        <v>200.15</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.5</v>
+        <v>180.78</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1421.5</v>
+        <v>1358.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1450.01</v>
+        <v>1441.29</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1458.42</v>
+        <v>1454.5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1501.56</v>
+        <v>1501.32</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4456.5</v>
+        <v>4410</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4355.48</v>
+        <v>4360.67</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4240.58</v>
+        <v>4247.22</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3922.86</v>
+        <v>3927.75</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4251.4</v>
+        <v>4297.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3974.94</v>
+        <v>4005.64</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3901.94</v>
+        <v>3917.45</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4401.11</v>
+        <v>4409.89</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>12167</v>
+        <v>11998</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11646.66</v>
+        <v>11680.12</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11728.57</v>
+        <v>11739.13</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11851.96</v>
+        <v>11855.03</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,24 +2917,24 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>202.76</v>
+        <v>199.36</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.95</v>
+        <v>201.7</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>207.24</v>
+        <v>206.93</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>230.32</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>230</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 24-Apr-2026  16:41:29    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 25-Apr-2026  15:56:54    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026  16:41:29</t>
+          <t>25-Apr-2026  15:56:54</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2092.06</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2230.06</v>
+        <v>2231.77</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1471.02</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1424.46</v>
+        <v>1425.4</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>7504.55</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7350.2</v>
+        <v>7354.42</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2385.93</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.66</v>
+        <v>2462.05</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1302.93</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1240.13</v>
+        <v>1240.62</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9441.690000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9109.059999999999</v>
+        <v>9109.23</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>915.9299999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.51</v>
+        <v>936.86</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1837.01</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1931.66</v>
+        <v>1932.77</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>436.13</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>405.97</v>
+        <v>406.32</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>319.25</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.41</v>
+        <v>324.4</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1878.58</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1921.34</v>
+        <v>1922.32</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5749.3</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.72</v>
+        <v>5744.33</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1284.52</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1401.67</v>
+        <v>1401.52</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>439.57</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>405.07</v>
+        <v>405.24</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1255.81</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1255.33</v>
+        <v>1253.84</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7172.45</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6817.27</v>
+        <v>6815.82</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2727.42</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2734.29</v>
+        <v>2735.72</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1394.33</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1485.14</v>
+        <v>1483.78</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>832.67</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>905.72</v>
+        <v>905.91</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>643.29</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>700.29</v>
+        <v>702.33</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5327.62</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5191.18</v>
+        <v>5189.64</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>953.05</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>847.75</v>
+        <v>848.23</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>2228.12</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2327.58</v>
+        <v>2326.39</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1786,7 +1786,7 @@
         <v>1323.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.98</v>
+        <v>1352.45</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>310.29</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>353.63</v>
+        <v>353.45</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>852.16</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.01</v>
+        <v>852.5700000000001</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1334.01</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1472.58</v>
+        <v>1471.69</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1201.79</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1143.04</v>
+        <v>1143.16</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>386.32</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.36</v>
+        <v>404.49</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3902.37</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3833.41</v>
+        <v>3833.69</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3237.75</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3341.4</v>
+        <v>3342.27</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13717.03</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14314.68</v>
+        <v>14320.88</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>376.62</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>349.64</v>
+        <v>349.81</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1267.08</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1233.98</v>
+        <v>1233.33</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>274</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>251.56</v>
+        <v>251.76</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>298.58</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>284.01</v>
+        <v>283.97</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1382.52</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.06</v>
+        <v>1412.67</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1926.34</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1896.48</v>
+        <v>1898.24</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>993.22</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>864.76</v>
+        <v>865.34</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1077.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>982.16</v>
+        <v>982.6900000000001</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1715.43</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1705.82</v>
+        <v>1706.09</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2602.95</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2946.8</v>
+        <v>2945.02</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1110.91</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1114.74</v>
+        <v>1113.97</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>200.15</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.78</v>
+        <v>180.84</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1454.5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1501.32</v>
+        <v>1501.82</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4247.22</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3927.75</v>
+        <v>3927.46</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>3917.45</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4409.89</v>
+        <v>4402.16</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11739.13</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11855.03</v>
+        <v>11859.96</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>206.93</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>230</v>
+        <v>229.82</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Apr-2026  15:56:54    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 26-Apr-2026  15:59:46    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Apr-2026  15:56:54</t>
+          <t>26-Apr-2026  15:59:46</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2092.06</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2231.77</v>
+        <v>2230.55</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1471.02</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1425.4</v>
+        <v>1425.96</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>7504.55</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7354.42</v>
+        <v>7356.1</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2385.93</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.05</v>
+        <v>2464.02</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1302.93</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1240.62</v>
+        <v>1238.57</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9441.690000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9109.23</v>
+        <v>9109.209999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>915.9299999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.86</v>
+        <v>936.53</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1837.01</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1932.77</v>
+        <v>1932.04</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>436.13</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>406.32</v>
+        <v>406.58</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>319.25</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.4</v>
+        <v>324.67</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1878.58</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1922.32</v>
+        <v>1922.2</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5749.3</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5744.33</v>
+        <v>5744.76</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1284.52</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1401.52</v>
+        <v>1401.46</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>439.57</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>405.24</v>
+        <v>405.59</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1255.81</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1253.84</v>
+        <v>1254.13</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7172.45</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6815.82</v>
+        <v>6814.29</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2727.42</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2735.72</v>
+        <v>2736.82</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1394.33</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1483.78</v>
+        <v>1484.39</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>832.67</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>905.91</v>
+        <v>905.58</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>643.29</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>702.33</v>
+        <v>702.37</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5327.62</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5189.64</v>
+        <v>5190.62</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>953.05</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>848.23</v>
+        <v>848.85</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>2228.12</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2326.39</v>
+        <v>2326.78</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1323.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1352.45</v>
+        <v>1351.42</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>310.29</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>353.45</v>
+        <v>353.75</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>852.16</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.5700000000001</v>
+        <v>852.38</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1334.01</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1471.69</v>
+        <v>1466.89</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1201.79</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1143.16</v>
+        <v>1143.23</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>386.32</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.49</v>
+        <v>404.08</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3902.37</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3833.69</v>
+        <v>3836.32</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3237.75</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3342.27</v>
+        <v>3339.53</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13717.03</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14320.88</v>
+        <v>14322.79</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>376.62</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>349.81</v>
+        <v>349.84</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1267.08</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1233.33</v>
+        <v>1234.36</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>274</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>251.76</v>
+        <v>251.9</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>298.58</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>283.97</v>
+        <v>284.17</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1382.52</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.67</v>
+        <v>1414.23</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1926.34</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1898.24</v>
+        <v>1899.41</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>993.22</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>865.34</v>
+        <v>864.47</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1077.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>982.6900000000001</v>
+        <v>982.6</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1715.43</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1706.09</v>
+        <v>1707.09</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2602.95</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2945.02</v>
+        <v>2944.76</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1110.91</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1113.97</v>
+        <v>1114.7</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>200.15</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.84</v>
+        <v>180.94</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1454.5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1501.82</v>
+        <v>1500.65</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4247.22</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3927.46</v>
+        <v>3929.23</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>3917.45</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4402.16</v>
+        <v>4402.38</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11739.13</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11859.96</v>
+        <v>11857.51</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>206.93</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>229.82</v>
+        <v>229.57</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 26-Apr-2026  15:59:46    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 27-Apr-2026  17:52:47    |    Closing Price Date: 27-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>26-Apr-2026  15:59:46</t>
+          <t>27-Apr-2026  17:52:47</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 70.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 35 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2287.6</v>
+        <v>2321.8</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2122.92</v>
+        <v>2141.86</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2092.06</v>
+        <v>2101.07</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2230.55</v>
+        <v>2233.33</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1585.1</v>
+        <v>1628.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1503.54</v>
+        <v>1515.44</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1471.02</v>
+        <v>1477.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1425.96</v>
+        <v>1427.33</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7732.5</v>
+        <v>7825</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7586.9</v>
+        <v>7609.57</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7504.55</v>
+        <v>7517.12</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7356.1</v>
+        <v>7358.7</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2485.1</v>
+        <v>2485.2</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2392.88</v>
+        <v>2401.67</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2385.93</v>
+        <v>2389.82</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2464.02</v>
+        <v>2465.07</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1365.9</v>
+        <v>1324.2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1323.08</v>
+        <v>1323.18</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1302.93</v>
+        <v>1303.76</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1238.57</v>
+        <v>1239.29</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9576</v>
+        <v>9662</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9509.6</v>
+        <v>9524.110000000001</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9441.690000000001</v>
+        <v>9450.33</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9109.209999999999</v>
+        <v>9113.129999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>921.55</v>
+        <v>921.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>903.59</v>
+        <v>905.3200000000001</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>915.9299999999999</v>
+        <v>916.16</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.53</v>
+        <v>937.5</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1770.7</v>
+        <v>1772.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1792.06</v>
+        <v>1790.17</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1837.01</v>
+        <v>1834.47</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1932.04</v>
+        <v>1932.83</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,29 +1113,29 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>444.45</v>
+        <v>435.6</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>442.33</v>
+        <v>441.69</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>436.13</v>
+        <v>436.11</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>406.58</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>407.03</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>308.1</v>
+        <v>312.65</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>306.19</v>
+        <v>306.8</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>319.25</v>
+        <v>319</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.67</v>
+        <v>324.7</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1814.5</v>
+        <v>1820.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1841.05</v>
+        <v>1839.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1878.58</v>
+        <v>1876.28</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1922.2</v>
+        <v>1921.78</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5730.5</v>
+        <v>5717.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5672.3</v>
+        <v>5676.6</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5749.3</v>
+        <v>5748.05</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5744.76</v>
+        <v>5745.83</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1295</v>
+        <v>1317.2</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1248.83</v>
+        <v>1255.35</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1284.52</v>
+        <v>1285.81</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1401.46</v>
+        <v>1400.76</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>456</v>
+        <v>452.5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>445.86</v>
+        <v>446.5</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>439.57</v>
+        <v>440.08</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>405.59</v>
+        <v>406.04</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1317.1</v>
+        <v>1334.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1251.86</v>
+        <v>1259.73</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1255.81</v>
+        <v>1258.89</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1254.13</v>
+        <v>1254.63</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7111.5</v>
+        <v>7174</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7102.22</v>
+        <v>7109.06</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7172.45</v>
+        <v>7172.51</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6814.29</v>
+        <v>6818.06</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2739.3</v>
+        <v>2778.2</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2714.72</v>
+        <v>2720.76</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2727.42</v>
+        <v>2729.41</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2736.82</v>
+        <v>2738.37</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1203.2</v>
+        <v>1228.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1352.22</v>
+        <v>1340.41</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1394.33</v>
+        <v>1387.81</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1484.39</v>
+        <v>1482.14</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>784.85</v>
+        <v>789.8</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>797.53</v>
+        <v>796.79</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>832.67</v>
+        <v>830.99</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>905.58</v>
+        <v>904.74</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>588.2</v>
+        <v>597.3</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>611.46</v>
+        <v>610.11</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>643.29</v>
+        <v>641.48</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>702.37</v>
+        <v>700.97</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4961.5</v>
+        <v>5043</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5206.55</v>
+        <v>5190.97</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5327.62</v>
+        <v>5316.46</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5190.62</v>
+        <v>5188.91</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1048.35</v>
+        <v>1061.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>988.7</v>
+        <v>995.67</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>953.05</v>
+        <v>957.3099999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>848.85</v>
+        <v>851.02</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2327.3</v>
+        <v>2328.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2217.47</v>
+        <v>2228.02</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2228.12</v>
+        <v>2232.05</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2326.78</v>
+        <v>2326.42</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1326.2</v>
+        <v>1314.1</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1320.74</v>
+        <v>1320.11</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1323.9</v>
+        <v>1323.51</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.42</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1351.38</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -1817,24 +1817,24 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>301.6</v>
+        <v>303.85</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>302.95</v>
+        <v>303.04</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.29</v>
+        <v>310.04</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>353.75</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>353.15</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
@@ -1861,34 +1861,34 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>847.95</v>
+        <v>900.15</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>839.6900000000001</v>
+        <v>845.45</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>852.16</v>
+        <v>854.04</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.38</v>
+        <v>852.84</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1154.6</v>
+        <v>1170.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1281.96</v>
+        <v>1271.32</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1334.01</v>
+        <v>1327.59</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1466.89</v>
+        <v>1463.85</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1255.7</v>
+        <v>1282.7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1218.23</v>
+        <v>1224.37</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1201.79</v>
+        <v>1204.97</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1143.23</v>
+        <v>1145.08</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>370.85</v>
+        <v>376.8</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>375.4</v>
+        <v>375.53</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>386.32</v>
+        <v>385.95</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.08</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>405.23</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4014.3</v>
+        <v>4053.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3927.86</v>
+        <v>3939.84</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3902.37</v>
+        <v>3908.3</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3836.32</v>
+        <v>3839.54</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3038.4</v>
+        <v>3102.4</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3149.38</v>
+        <v>3144.91</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3237.75</v>
+        <v>3232.45</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3339.53</v>
+        <v>3335.9</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13048</v>
+        <v>13222</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13236.04</v>
+        <v>13234.7</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13717.03</v>
+        <v>13697.61</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14322.79</v>
+        <v>14306.81</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>401.85</v>
+        <v>410.2</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>387.98</v>
+        <v>390.1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>376.62</v>
+        <v>377.94</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>349.84</v>
+        <v>350.86</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1421.3</v>
+        <v>1417.3</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1291.61</v>
+        <v>1303.58</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1267.08</v>
+        <v>1272.97</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1234.36</v>
+        <v>1236.11</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>284.8</v>
+        <v>285.9</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>282.27</v>
+        <v>282.61</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>274</v>
+        <v>274.47</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>251.9</v>
+        <v>252.35</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>316.4</v>
+        <v>320.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>308.3</v>
+        <v>309.5</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>298.58</v>
+        <v>299.46</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>284.17</v>
+        <v>284.69</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,24 +2345,24 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1327.8</v>
+        <v>1365.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1354.21</v>
+        <v>1355.32</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1382.52</v>
+        <v>1381.87</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1414.23</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1413.89</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1768.9</v>
+        <v>1815.4</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1892.08</v>
+        <v>1884.77</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1926.34</v>
+        <v>1921.99</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1899.41</v>
+        <v>1896.8</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,29 +2433,29 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1011.3</v>
+        <v>974.65</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1002.99</v>
+        <v>1000.29</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>993.22</v>
+        <v>992.49</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>864.47</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>865.14</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1101.1</v>
+        <v>1111.85</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1078.01</v>
+        <v>1081.24</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1077.5</v>
+        <v>1078.84</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>982.6</v>
+        <v>984.53</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,34 +2521,34 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1620.4</v>
+        <v>1733.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1694.33</v>
+        <v>1698.06</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1715.43</v>
+        <v>1716.14</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1707.09</v>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1707</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2396.9</v>
+        <v>2447.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2515.71</v>
+        <v>2509.22</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2602.95</v>
+        <v>2596.86</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2944.76</v>
+        <v>2937.85</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1174</v>
+        <v>1160.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1112.65</v>
+        <v>1117.21</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1110.91</v>
+        <v>1112.86</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1114.7</v>
+        <v>1115.41</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>350.5</v>
+        <v>354.35</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>342.44</v>
+        <v>343.58</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>343.58</v>
+        <v>344.01</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.47</v>
+        <v>364.37</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.07</v>
+        <v>213.27</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>205.58</v>
+        <v>206.32</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>200.15</v>
+        <v>200.67</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>180.94</v>
+        <v>181.32</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1358.5</v>
+        <v>1396.1</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1441.29</v>
+        <v>1436.99</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1454.5</v>
+        <v>1452.21</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1500.65</v>
+        <v>1500.22</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4410</v>
+        <v>4441.8</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4360.67</v>
+        <v>4368.4</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4247.22</v>
+        <v>4254.85</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3929.23</v>
+        <v>3935.41</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4297.3</v>
+        <v>4260.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4005.64</v>
+        <v>4029.94</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3917.45</v>
+        <v>3930.91</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4402.38</v>
+        <v>4395.44</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11998</v>
+        <v>12010</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11680.12</v>
+        <v>11711.54</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11739.13</v>
+        <v>11749.75</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11857.51</v>
+        <v>11860.96</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,24 +2917,24 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>199.36</v>
+        <v>205.05</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.7</v>
+        <v>202.02</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>206.93</v>
+        <v>206.86</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>229.57</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>230.07</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 27-Apr-2026  17:52:47    |    Closing Price Date: 27-Apr-2026</t>
+          <t>Scan Run: 28-Apr-2026  19:11:38    |    Closing Price Date: 27-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026  17:52:47</t>
+          <t>28-Apr-2026  19:11:38</t>
         </is>
       </c>
     </row>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>354.35</v>
+        <v>350.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>343.58</v>
+        <v>344.26</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>344.01</v>
+        <v>344.27</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.37</v>
+        <v>364.23</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-Apr-2026  19:11:38    |    Closing Price Date: 27-Apr-2026</t>
+          <t>Scan Run: 30-Apr-2026  16:10:03    |    Closing Price Date: 30-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-Apr-2026  19:11:38</t>
+          <t>30-Apr-2026  16:10:03</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 70.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 35 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 28 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2321.8</v>
+        <v>2408.4</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2141.86</v>
+        <v>2212.81</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2101.07</v>
+        <v>2136.63</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2233.33</v>
+        <v>2236.21</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1628.5</v>
+        <v>1657.3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1515.44</v>
+        <v>1551.03</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1477.2</v>
+        <v>1497</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1427.33</v>
+        <v>1432.16</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7825</v>
+        <v>7636.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7609.57</v>
+        <v>7631.89</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7517.12</v>
+        <v>7537.57</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7358.7</v>
+        <v>7374.67</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2485.2</v>
+        <v>2444.5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2401.67</v>
+        <v>2414.43</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2389.82</v>
+        <v>2396.77</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2465.07</v>
+        <v>2463.81</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -918,9 +918,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
@@ -937,29 +937,29 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1324.2</v>
+        <v>1268.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1323.18</v>
+        <v>1312.98</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1303.76</v>
+        <v>1301.56</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.29</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1239.86</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9662</v>
+        <v>9994</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9524.110000000001</v>
+        <v>9568.299999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9450.33</v>
+        <v>9476.799999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9113.129999999999</v>
+        <v>9126.690000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>921.8</v>
+        <v>937</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>905.3200000000001</v>
+        <v>911.9</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>916.16</v>
+        <v>917.77</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.5</v>
+        <v>936.65</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1772.2</v>
+        <v>1747.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1790.17</v>
+        <v>1782.97</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1834.47</v>
+        <v>1826.39</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1932.83</v>
+        <v>1927.04</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>435.6</v>
+        <v>431.3</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>441.69</v>
+        <v>439.88</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>436.11</v>
+        <v>435.96</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>407.03</v>
+        <v>407.56</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>312.65</v>
+        <v>300.45</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>306.8</v>
+        <v>306.02</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>319</v>
+        <v>317.29</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.7</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>324.2</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1820.1</v>
+        <v>1886.8</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1839.06</v>
+        <v>1848.2</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1876.28</v>
+        <v>1875.97</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1921.78</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1919.7</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5717.5</v>
+        <v>5726</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5676.6</v>
+        <v>5682.96</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5748.05</v>
+        <v>5742.6</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.83</v>
+        <v>5745.23</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1317.2</v>
+        <v>1309.6</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1255.35</v>
+        <v>1269.87</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1285.81</v>
+        <v>1288.69</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1400.76</v>
+        <v>1397.38</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>452.5</v>
+        <v>481.45</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>446.5</v>
+        <v>454.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>440.08</v>
+        <v>444.18</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>406.04</v>
+        <v>407.89</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1334.5</v>
+        <v>1322.9</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1259.73</v>
+        <v>1279.18</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1258.89</v>
+        <v>1267.54</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1254.63</v>
+        <v>1256.42</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7174</v>
+        <v>7109</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7109.06</v>
+        <v>7113.06</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7172.51</v>
+        <v>7167</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6818.06</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6825.1</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2778.2</v>
+        <v>2794.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2720.76</v>
+        <v>2739.74</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2729.41</v>
+        <v>2736.68</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2738.37</v>
+        <v>2738.53</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1228.2</v>
+        <v>1199.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1340.41</v>
+        <v>1303.61</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1387.81</v>
+        <v>1366.4</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1482.14</v>
+        <v>1474.01</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>789.8</v>
+        <v>771.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>796.79</v>
+        <v>791.76</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>830.99</v>
+        <v>824.95</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>904.74</v>
+        <v>900.8</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>597.3</v>
+        <v>586.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>610.11</v>
+        <v>604.99</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>641.48</v>
+        <v>635.71</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>700.97</v>
+        <v>697.27</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5043</v>
+        <v>5099</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5190.97</v>
+        <v>5166.04</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5316.46</v>
+        <v>5291.33</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5188.91</v>
+        <v>5183.39</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1061.8</v>
+        <v>1038</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>995.67</v>
+        <v>1011.99</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>957.3099999999999</v>
+        <v>968.85</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>851.02</v>
+        <v>857.05</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2328.3</v>
+        <v>2250.9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2228.02</v>
+        <v>2242.44</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2232.05</v>
+        <v>2237.97</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2326.42</v>
+        <v>2324.99</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1314.1</v>
+        <v>1263.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1320.11</v>
+        <v>1309.14</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1323.51</v>
+        <v>1318.41</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1351.38</v>
+        <v>1347.66</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,29 +1817,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>303.85</v>
+        <v>314.9</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>303.04</v>
+        <v>305.42</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.04</v>
+        <v>310.26</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>353.15</v>
+        <v>351.92</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>900.15</v>
+        <v>916.05</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>845.45</v>
+        <v>861.1900000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>854.04</v>
+        <v>859.86</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>852.84</v>
+        <v>853.95</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1170.3</v>
+        <v>1181.8</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1271.32</v>
+        <v>1244.56</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1327.59</v>
+        <v>1309.48</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1463.85</v>
+        <v>1454.56</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1282.7</v>
+        <v>1264.5</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1224.37</v>
+        <v>1237.42</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1204.97</v>
+        <v>1212.89</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1145.08</v>
+        <v>1149.26</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>376.8</v>
+        <v>383.3</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>375.53</v>
+        <v>377.02</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>385.95</v>
+        <v>385.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>405.23</v>
+        <v>404.28</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4053.6</v>
+        <v>4014</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3939.84</v>
+        <v>3967.99</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3908.3</v>
+        <v>3924.21</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3839.54</v>
+        <v>3843.53</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3102.4</v>
+        <v>3097.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3144.91</v>
+        <v>3136.6</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3232.45</v>
+        <v>3218.91</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3335.9</v>
+        <v>3326.47</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13222</v>
+        <v>13314</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13234.7</v>
+        <v>13217.46</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13697.61</v>
+        <v>13636.81</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14306.81</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>14267.01</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>410.2</v>
+        <v>399.15</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>390.1</v>
+        <v>393.23</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>377.94</v>
+        <v>380.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>350.86</v>
+        <v>351.89</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1417.3</v>
+        <v>1458.6</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1303.58</v>
+        <v>1342.94</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1272.97</v>
+        <v>1293.56</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1236.11</v>
+        <v>1242.2</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>285.9</v>
+        <v>299.55</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>282.61</v>
+        <v>287.3</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>274.47</v>
+        <v>277.44</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>252.35</v>
+        <v>253.64</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>320.9</v>
+        <v>318.35</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>309.5</v>
+        <v>312.02</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>299.46</v>
+        <v>301.69</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>284.69</v>
+        <v>285.55</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,34 +2345,34 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1365.8</v>
+        <v>1430.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1355.32</v>
+        <v>1371.16</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1381.87</v>
+        <v>1385.68</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1413.89</v>
+        <v>1412.57</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1815.4</v>
+        <v>1819</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1884.77</v>
+        <v>1866.64</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1921.99</v>
+        <v>1909.85</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1896.8</v>
+        <v>1892.95</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>974.65</v>
+        <v>937.35</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1000.29</v>
+        <v>986.89</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>992.49</v>
+        <v>987.5599999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>865.14</v>
+        <v>867.78</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,29 +2477,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1111.85</v>
+        <v>1068.45</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1081.24</v>
+        <v>1081.29</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1078.84</v>
+        <v>1079.19</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>984.53</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>986.5700000000001</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1733.5</v>
+        <v>1808.3</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1698.06</v>
+        <v>1719.35</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1716.14</v>
+        <v>1723.24</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1707</v>
+        <v>1708.45</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2447.6</v>
+        <v>2473.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2509.22</v>
+        <v>2497.85</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2596.86</v>
+        <v>2581.92</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2937.85</v>
+        <v>2922.13</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1160.5</v>
+        <v>1144.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1117.21</v>
+        <v>1126.57</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1112.86</v>
+        <v>1117.44</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1115.41</v>
+        <v>1117.03</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,29 +2653,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>350.8</v>
+        <v>341.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>344.26</v>
+        <v>344.73</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>344.27</v>
+        <v>344.48</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>364.23</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>363.89</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>213.27</v>
+        <v>211.36</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>206.32</v>
+        <v>208.3</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>200.67</v>
+        <v>202.18</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>181.32</v>
+        <v>182.21</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1396.1</v>
+        <v>1473.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1436.99</v>
+        <v>1440.18</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1452.21</v>
+        <v>1451.74</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1500.22</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1497.24</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4441.8</v>
+        <v>4385.2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4368.4</v>
+        <v>4379.94</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4254.85</v>
+        <v>4272.8</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3935.41</v>
+        <v>3948.32</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4260.8</v>
+        <v>4144.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4029.94</v>
+        <v>4075.41</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3930.91</v>
+        <v>3962.19</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4395.44</v>
+        <v>4374.8</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,34 +2873,34 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>12010</v>
+        <v>11586</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11711.54</v>
+        <v>11718.27</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11749.75</v>
+        <v>11748.9</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11860.96</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11859.37</v>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>205.05</v>
+        <v>200.65</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>202.02</v>
+        <v>201.74</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>206.86</v>
+        <v>206.19</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>230.07</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>229.14</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 30-Apr-2026  16:10:03    |    Closing Price Date: 30-Apr-2026</t>
+          <t>Scan Run: 01-May-2026  14:39:59    |    Closing Price Date: 30-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>30-Apr-2026  16:10:03</t>
+          <t>01-May-2026  14:39:59</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2136.63</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2236.21</v>
+        <v>2235.88</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1497</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1432.16</v>
+        <v>1431.99</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>7537.57</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7374.67</v>
+        <v>7373.53</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2396.77</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2463.81</v>
+        <v>2463.89</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1301.56</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.86</v>
+        <v>1239.39</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9476.799999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9126.690000000001</v>
+        <v>9126.370000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>917.77</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.65</v>
+        <v>937.11</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>1826.39</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1927.04</v>
+        <v>1928.18</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>435.96</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>407.56</v>
+        <v>407.19</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>317.29</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.2</v>
+        <v>324.1</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1875.97</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1919.7</v>
+        <v>1919.94</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5742.6</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.23</v>
+        <v>5747.49</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1288.69</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1397.38</v>
+        <v>1397.86</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>444.18</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>407.89</v>
+        <v>407.8</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1267.54</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1256.42</v>
+        <v>1256.76</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7167</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6825.1</v>
+        <v>6826.8</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2736.68</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2738.53</v>
+        <v>2739.42</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1366.4</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1474.01</v>
+        <v>1475.05</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>824.95</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>900.8</v>
+        <v>901.3099999999999</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>635.71</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>697.27</v>
+        <v>697.02</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5291.33</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5183.39</v>
+        <v>5184.65</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>968.85</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>857.05</v>
+        <v>856.99</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>2237.97</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2324.99</v>
+        <v>2325.09</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1318.41</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1347.66</v>
+        <v>1347.85</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>310.26</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>351.92</v>
+        <v>351.9</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>859.86</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>853.95</v>
+        <v>854.4</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
         <v>1244.56</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1309.48</v>
+        <v>1309.49</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1454.56</v>
+        <v>1456.9</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1212.89</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1149.26</v>
+        <v>1148.94</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>385.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.28</v>
+        <v>404.49</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3924.21</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3843.53</v>
+        <v>3842.55</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3218.91</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3326.47</v>
+        <v>3326.69</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13636.81</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14267.01</v>
+        <v>14272.86</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>380.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>351.89</v>
+        <v>351.81</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1293.56</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1242.2</v>
+        <v>1242.45</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>277.44</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>253.64</v>
+        <v>253.57</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>301.69</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>285.55</v>
+        <v>285.35</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1385.68</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.57</v>
+        <v>1412.72</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1909.85</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1892.95</v>
+        <v>1892.67</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>987.5599999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>867.78</v>
+        <v>867.7</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1079.19</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>986.5700000000001</v>
+        <v>986.33</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1723.24</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1708.45</v>
+        <v>1709.99</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2581.92</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2922.13</v>
+        <v>2927.18</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1117.44</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1117.03</v>
+        <v>1116.83</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>202.18</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>182.21</v>
+        <v>182.17</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1451.74</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1497.24</v>
+        <v>1499.07</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4272.8</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3948.32</v>
+        <v>3948.45</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>3962.19</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4374.8</v>
+        <v>4370.02</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11748.9</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11859.37</v>
+        <v>11860.48</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>206.19</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>229.14</v>
+        <v>229.57</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-May-2026  14:39:59    |    Closing Price Date: 30-Apr-2026</t>
+          <t>Scan Run: 04-May-2026  17:15:51    |    Closing Price Date: 04-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-May-2026  14:39:59</t>
+          <t>04-May-2026  17:15:51</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 28 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2408.4</v>
+        <v>2485.7</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2212.81</v>
+        <v>2238.8</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2136.63</v>
+        <v>2150.32</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2235.88</v>
+        <v>2233.23</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1657.3</v>
+        <v>1742.6</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1551.03</v>
+        <v>1569.27</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1497</v>
+        <v>1506.63</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1431.99</v>
+        <v>1434.19</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7636.5</v>
+        <v>7737.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7631.89</v>
+        <v>7641.95</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7537.57</v>
+        <v>7545.41</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7373.53</v>
+        <v>7368.53</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2444.5</v>
+        <v>2448.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2414.43</v>
+        <v>2417.64</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2396.77</v>
+        <v>2398.78</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2463.89</v>
+        <v>2463.26</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1268.3</v>
+        <v>1275.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1312.98</v>
+        <v>1309.38</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1301.56</v>
+        <v>1300.52</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.39</v>
+        <v>1239.26</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9994</v>
+        <v>10132</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9568.299999999999</v>
+        <v>9621.99</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9476.799999999999</v>
+        <v>9502.49</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9126.370000000001</v>
+        <v>9133.139999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>937</v>
+        <v>950.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>911.9</v>
+        <v>915.54</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>917.77</v>
+        <v>919.04</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.11</v>
+        <v>936.79</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1747.2</v>
+        <v>1770.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1782.97</v>
+        <v>1781.77</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1826.39</v>
+        <v>1824.2</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1928.18</v>
+        <v>1925.22</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>431.3</v>
+        <v>433.55</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>439.88</v>
+        <v>439.28</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.96</v>
+        <v>435.87</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>407.19</v>
+        <v>407.13</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>300.45</v>
+        <v>301.7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>306.02</v>
+        <v>305.61</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>317.29</v>
+        <v>316.68</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>324.1</v>
+        <v>323.22</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1886.8</v>
+        <v>1827.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1848.2</v>
+        <v>1846.19</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1875.97</v>
+        <v>1874.05</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1919.94</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1917.73</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1245,34 +1245,34 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5726</v>
+        <v>5792.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5682.96</v>
+        <v>5693.39</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5742.6</v>
+        <v>5744.56</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5747.49</v>
+        <v>5757.42</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1309.6</v>
+        <v>1335</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1269.87</v>
+        <v>1276.07</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1288.69</v>
+        <v>1290.5</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1397.86</v>
+        <v>1395.35</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>481.45</v>
+        <v>479.95</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>454.3</v>
+        <v>456.74</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>444.18</v>
+        <v>445.58</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>407.8</v>
+        <v>408.37</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1322.9</v>
+        <v>1287.2</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1279.18</v>
+        <v>1279.94</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1267.54</v>
+        <v>1268.31</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1256.76</v>
+        <v>1252.78</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7109</v>
+        <v>7329</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7113.06</v>
+        <v>7133.62</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7167</v>
+        <v>7173.35</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6826.8</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>6837.54</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2794.5</v>
+        <v>2856</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2739.74</v>
+        <v>2750.81</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2736.68</v>
+        <v>2741.36</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2739.42</v>
+        <v>2743.58</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1199.1</v>
+        <v>1200.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1303.61</v>
+        <v>1293.79</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1366.4</v>
+        <v>1359.89</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1475.05</v>
+        <v>1467.49</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>771.7</v>
+        <v>779.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>791.76</v>
+        <v>790.58</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>824.95</v>
+        <v>823.16</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>901.3099999999999</v>
+        <v>899.3099999999999</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>586.9</v>
+        <v>588.35</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>604.99</v>
+        <v>603.41</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>635.71</v>
+        <v>633.85</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>697.02</v>
+        <v>695.58</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5099</v>
+        <v>5066.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5166.04</v>
+        <v>5156.56</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5291.33</v>
+        <v>5282.51</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5184.65</v>
+        <v>5181.8</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1038</v>
+        <v>1042.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1011.99</v>
+        <v>1014.92</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>968.85</v>
+        <v>971.75</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>856.99</v>
+        <v>857.6799999999999</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2250.9</v>
+        <v>2309.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2242.44</v>
+        <v>2248.8</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2237.97</v>
+        <v>2240.76</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2325.09</v>
+        <v>2327.1</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1263.4</v>
+        <v>1270.8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1309.14</v>
+        <v>1305.49</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1318.41</v>
+        <v>1316.54</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1347.85</v>
+        <v>1348.28</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>314.9</v>
+        <v>311.1</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>305.42</v>
+        <v>305.96</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.26</v>
+        <v>310.29</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>351.9</v>
+        <v>351.62</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>916.05</v>
+        <v>913.9</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>861.1900000000001</v>
+        <v>866.21</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>859.86</v>
+        <v>861.98</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>854.4</v>
+        <v>853.04</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1181.8</v>
+        <v>1168.4</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1244.56</v>
+        <v>1237.3</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1309.49</v>
+        <v>1303.95</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1456.9</v>
+        <v>1452.54</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1264.5</v>
+        <v>1266.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1237.42</v>
+        <v>1240.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1212.89</v>
+        <v>1215</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1148.94</v>
+        <v>1150.09</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>383.3</v>
+        <v>371.65</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>377.02</v>
+        <v>376.51</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>385.41</v>
+        <v>384.87</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>404.49</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>403.85</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4014</v>
+        <v>4100.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3967.99</v>
+        <v>3980.64</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3924.21</v>
+        <v>3931.13</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3842.55</v>
+        <v>3842.5</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3097.5</v>
+        <v>3106.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3136.6</v>
+        <v>3133.74</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3218.91</v>
+        <v>3214.5</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3326.69</v>
+        <v>3324.71</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13314</v>
+        <v>13580</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13217.46</v>
+        <v>13251.98</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13636.81</v>
+        <v>13634.58</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14272.86</v>
+        <v>14264.82</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>399.15</v>
+        <v>400.05</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>393.23</v>
+        <v>393.88</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>380.7</v>
+        <v>381.46</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>351.81</v>
+        <v>352.28</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1458.6</v>
+        <v>1457.1</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1342.94</v>
+        <v>1353.81</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1293.56</v>
+        <v>1299.97</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1242.45</v>
+        <v>1243.87</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>299.55</v>
+        <v>292.9</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>287.3</v>
+        <v>287.84</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>277.44</v>
+        <v>278.05</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>253.57</v>
+        <v>253.42</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>318.35</v>
+        <v>319.05</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>312.02</v>
+        <v>312.69</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>301.69</v>
+        <v>302.37</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>285.35</v>
+        <v>285.25</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1430.8</v>
+        <v>1463.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1371.16</v>
+        <v>1379.92</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1385.68</v>
+        <v>1388.72</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.72</v>
+        <v>1411.14</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1819</v>
+        <v>1820.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1866.64</v>
+        <v>1862.21</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1909.85</v>
+        <v>1906.33</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1892.67</v>
+        <v>1890.4</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>937.35</v>
+        <v>960.45</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>986.89</v>
+        <v>984.37</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>987.5599999999999</v>
+        <v>986.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>867.7</v>
+        <v>868.3099999999999</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1068.45</v>
+        <v>1068.4</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1081.29</v>
+        <v>1080.06</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1079.19</v>
+        <v>1078.77</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>986.33</v>
+        <v>986.97</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1808.3</v>
+        <v>1823.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1719.35</v>
+        <v>1729.27</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1723.24</v>
+        <v>1727.17</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1709.99</v>
+        <v>1710.57</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2473.9</v>
+        <v>2431.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2497.85</v>
+        <v>2491.52</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2581.92</v>
+        <v>2576.02</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2927.18</v>
+        <v>2918.35</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1144.6</v>
+        <v>1160.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1126.57</v>
+        <v>1129.79</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1117.44</v>
+        <v>1119.13</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1116.83</v>
+        <v>1117.18</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>341.55</v>
+        <v>343.05</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>344.73</v>
+        <v>344.57</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>344.48</v>
+        <v>344.43</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>363.89</v>
+        <v>363.68</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>211.36</v>
+        <v>212.24</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>208.3</v>
+        <v>208.68</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>202.18</v>
+        <v>202.58</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>182.17</v>
+        <v>182.36</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1473.5</v>
+        <v>1471.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1440.18</v>
+        <v>1443.17</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1451.74</v>
+        <v>1452.52</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1499.07</v>
+        <v>1497.47</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,24 +2785,24 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4385.2</v>
+        <v>4363</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4379.94</v>
+        <v>4378.33</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4272.8</v>
+        <v>4276.34</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3948.45</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3950.91</v>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4144.6</v>
+        <v>4158.5</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4075.41</v>
+        <v>4083.32</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3962.19</v>
+        <v>3969.88</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4370.02</v>
+        <v>4358.5</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,29 +2873,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11586</v>
+        <v>11758</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11718.27</v>
+        <v>11722.06</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11748.9</v>
+        <v>11749.26</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11860.48</v>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>11882.84</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>200.65</v>
+        <v>200.75</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.74</v>
+        <v>201.65</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>206.19</v>
+        <v>205.98</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>229.57</v>
+        <v>229.23</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 04-May-2026  17:15:51    |    Closing Price Date: 04-May-2026</t>
+          <t>Scan Run: 05-May-2026  16:30:03    |    Closing Price Date: 05-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>04-May-2026  17:15:51</t>
+          <t>05-May-2026  16:30:03</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 29 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2485.7</v>
+        <v>2462</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2238.8</v>
+        <v>2260.06</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2150.32</v>
+        <v>2162.54</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2233.23</v>
+        <v>2235.51</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1742.6</v>
+        <v>1725</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1569.27</v>
+        <v>1592.39</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1506.63</v>
+        <v>1521</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1434.19</v>
+        <v>1439.29</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7737.5</v>
+        <v>7772</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7641.95</v>
+        <v>7654.33</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7545.41</v>
+        <v>7554.29</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7368.53</v>
+        <v>7372.54</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2448.1</v>
+        <v>2430</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2417.64</v>
+        <v>2418.82</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2398.78</v>
+        <v>2400.01</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2463.26</v>
+        <v>2462.93</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1275.1</v>
+        <v>1259.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1309.38</v>
+        <v>1304.64</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1300.52</v>
+        <v>1298.92</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.26</v>
+        <v>1239.46</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10132</v>
+        <v>10046</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9621.99</v>
+        <v>9662.370000000001</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9502.49</v>
+        <v>9523.799999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9133.139999999999</v>
+        <v>9142.23</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>950.2</v>
+        <v>958.6</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>915.54</v>
+        <v>921.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>919.04</v>
+        <v>921.29</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>936.79</v>
+        <v>937.01</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1770.4</v>
+        <v>1794.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1781.77</v>
+        <v>1782.99</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1824.2</v>
+        <v>1823.03</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1925.22</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1923.92</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>433.55</v>
+        <v>433.35</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>439.28</v>
+        <v>438.04</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.87</v>
+        <v>435.6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>407.13</v>
+        <v>407.63</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>301.7</v>
+        <v>298.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>305.61</v>
+        <v>304.5</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>316.68</v>
+        <v>315.36</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>323.22</v>
+        <v>322.75</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1827.1</v>
+        <v>1806.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1846.19</v>
+        <v>1845.38</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1874.05</v>
+        <v>1871.78</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1917.73</v>
+        <v>1916.31</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5792.5</v>
+        <v>5834.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5693.39</v>
+        <v>5706.83</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5744.56</v>
+        <v>5748.08</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5757.42</v>
+        <v>5758.18</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1335</v>
+        <v>1333.7</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1276.07</v>
+        <v>1281.56</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1290.5</v>
+        <v>1292.2</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.35</v>
+        <v>1394.74</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>479.95</v>
+        <v>472.6</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>456.74</v>
+        <v>460.37</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>445.58</v>
+        <v>447.99</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>408.37</v>
+        <v>409.73</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1287.2</v>
+        <v>1271.2</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1279.94</v>
+        <v>1282.52</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1268.31</v>
+        <v>1270.43</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1252.78</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1253.65</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7329</v>
+        <v>7301.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7133.62</v>
+        <v>7149.29</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7173.35</v>
+        <v>7176.28</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6837.54</v>
+        <v>6844.86</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2856</v>
+        <v>2871.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2750.81</v>
+        <v>2766.58</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2741.36</v>
+        <v>2748.56</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2743.58</v>
+        <v>2745.36</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1200.5</v>
+        <v>1200.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1293.79</v>
+        <v>1276.73</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1359.89</v>
+        <v>1347.57</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1467.49</v>
+        <v>1462.19</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>779.4</v>
+        <v>772.3</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>790.58</v>
+        <v>787.28</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>823.16</v>
+        <v>819.24</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>899.3099999999999</v>
+        <v>896.79</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>588.35</v>
+        <v>594.1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>603.41</v>
+        <v>601.11</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>633.85</v>
+        <v>630.53</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>695.58</v>
+        <v>693.5</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5066.5</v>
+        <v>5109</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5156.56</v>
+        <v>5152.03</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5282.51</v>
+        <v>5275.71</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5181.8</v>
+        <v>5181.07</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1042.7</v>
+        <v>1054.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1014.92</v>
+        <v>1020.73</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>971.75</v>
+        <v>977.51</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>857.6799999999999</v>
+        <v>861.41</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2309.3</v>
+        <v>2327.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2248.8</v>
+        <v>2256.95</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2240.76</v>
+        <v>2244.63</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2327.1</v>
+        <v>2326.35</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1270.8</v>
+        <v>1251.3</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1305.49</v>
+        <v>1296.76</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1316.54</v>
+        <v>1311.99</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1348.28</v>
+        <v>1346.48</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>311.1</v>
+        <v>311.45</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>305.96</v>
+        <v>307.22</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>310.29</v>
+        <v>310.51</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>351.62</v>
+        <v>350.86</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>913.9</v>
+        <v>910.7</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>866.21</v>
+        <v>874.72</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>861.98</v>
+        <v>865.9299999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>853.04</v>
+        <v>854.23</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1168.4</v>
+        <v>1178.1</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1237.3</v>
+        <v>1226.77</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1303.95</v>
+        <v>1294.39</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1452.54</v>
+        <v>1447.14</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1266.6</v>
+        <v>1252.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1240.2</v>
+        <v>1241.36</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1215</v>
+        <v>1216.46</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1150.09</v>
+        <v>1151.11</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>371.65</v>
+        <v>371.35</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>376.51</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>384.87</v>
+        <v>384.26</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>403.85</v>
+        <v>403.32</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4100.8</v>
+        <v>4054.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3980.64</v>
+        <v>3991.26</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3931.13</v>
+        <v>3939.22</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3842.5</v>
+        <v>3846.31</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,29 +2081,29 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3106.5</v>
+        <v>3210.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3133.74</v>
+        <v>3138.03</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3214.5</v>
+        <v>3209.96</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3324.71</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3321.34</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13580</v>
+        <v>13426</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13251.98</v>
+        <v>13276.08</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13634.58</v>
+        <v>13614.71</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14264.82</v>
+        <v>14247.13</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>400.05</v>
+        <v>398.65</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>393.88</v>
+        <v>394.8</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>381.46</v>
+        <v>382.8</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>352.28</v>
+        <v>353.21</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1457.1</v>
+        <v>1477.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1353.81</v>
+        <v>1365.62</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1299.97</v>
+        <v>1306.94</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1243.87</v>
+        <v>1246.19</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>292.9</v>
+        <v>289.95</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>287.84</v>
+        <v>288.04</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>278.05</v>
+        <v>278.51</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>253.42</v>
+        <v>253.78</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.05</v>
+        <v>319.45</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>312.69</v>
+        <v>313.82</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>302.37</v>
+        <v>303.65</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>285.25</v>
+        <v>285.91</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1463.1</v>
+        <v>1463.6</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1379.92</v>
+        <v>1392.54</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1388.72</v>
+        <v>1393.29</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1411.14</v>
+        <v>1411.85</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1820.1</v>
+        <v>1821.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1862.21</v>
+        <v>1858.3</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1906.33</v>
+        <v>1902.99</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1890.4</v>
+        <v>1889.71</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>960.45</v>
+        <v>964.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>984.37</v>
+        <v>978.61</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>986.5</v>
+        <v>983.8099999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>868.3099999999999</v>
+        <v>869.95</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1068.4</v>
+        <v>1059.9</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1080.06</v>
+        <v>1078.14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1078.77</v>
+        <v>1078.03</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>986.97</v>
+        <v>987.7</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1823.5</v>
+        <v>1820.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1729.27</v>
+        <v>1737.98</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1727.17</v>
+        <v>1730.84</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1710.57</v>
+        <v>1711.67</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2431.3</v>
+        <v>2427.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2491.52</v>
+        <v>2483.53</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2576.02</v>
+        <v>2566.27</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2918.35</v>
+        <v>2909.08</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1160.4</v>
+        <v>1153.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1129.79</v>
+        <v>1133.46</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1119.13</v>
+        <v>1121.46</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1117.18</v>
+        <v>1117.81</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>343.05</v>
+        <v>340.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>344.57</v>
+        <v>344.15</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>344.43</v>
+        <v>344.26</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>363.68</v>
+        <v>363.45</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>212.24</v>
+        <v>211.32</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>208.68</v>
+        <v>209.17</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>202.58</v>
+        <v>203.25</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>182.36</v>
+        <v>182.94</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1471.6</v>
+        <v>1452.2</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1443.17</v>
+        <v>1444.03</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1452.52</v>
+        <v>1452.5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1497.47</v>
+        <v>1497.02</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4363</v>
+        <v>4373.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4378.33</v>
+        <v>4378.29</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4276.34</v>
+        <v>4284.22</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3950.91</v>
+        <v>3959.39</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4158.5</v>
+        <v>4135.4</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4083.32</v>
+        <v>4088.28</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3969.88</v>
+        <v>3976.37</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4358.5</v>
+        <v>4356.28</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11758</v>
+        <v>11963</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11722.06</v>
+        <v>11745</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11749.26</v>
+        <v>11757.64</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11882.84</v>
+        <v>11883.64</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2898,9 +2898,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>200.75</v>
+        <v>199.78</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.65</v>
+        <v>201.38</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>205.98</v>
+        <v>205.53</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>229.23</v>
+        <v>228.65</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 05-May-2026  16:30:03    |    Closing Price Date: 05-May-2026</t>
+          <t>Scan Run: 06-May-2026  16:24:49    |    Closing Price Date: 06-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>58</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>05-May-2026  16:30:03</t>
+          <t>06-May-2026  16:24:49</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 82.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 74.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 41 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 37 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2462</v>
+        <v>2540.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2260.06</v>
+        <v>2300.54</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2162.54</v>
+        <v>2186.81</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2235.51</v>
+        <v>2240.26</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1725</v>
+        <v>1748.3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1592.39</v>
+        <v>1607.24</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1521</v>
+        <v>1529.91</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1439.29</v>
+        <v>1442.37</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>7772</v>
+        <v>7760.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7654.33</v>
+        <v>7664.77</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7554.29</v>
+        <v>7565.82</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7372.54</v>
+        <v>7379.02</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2430</v>
+        <v>2519</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2418.82</v>
+        <v>2428.36</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2400.01</v>
+        <v>2404.67</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2462.93</v>
+        <v>2463.49</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -918,9 +918,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1259.7</v>
+        <v>1294.2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1304.64</v>
+        <v>1300.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1298.92</v>
+        <v>1297.58</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1239.46</v>
+        <v>1240.29</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10046</v>
+        <v>10319</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9662.370000000001</v>
+        <v>9724.91</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9523.799999999999</v>
+        <v>9554.99</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9142.23</v>
+        <v>9153.940000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>958.6</v>
+        <v>980.75</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>921.6</v>
+        <v>927.23</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>921.29</v>
+        <v>923.62</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.01</v>
+        <v>937.4400000000001</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1794.6</v>
+        <v>1836.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1782.99</v>
+        <v>1788.05</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1823.03</v>
+        <v>1823.55</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1923.92</v>
+        <v>1923.04</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,29 +1113,29 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>433.35</v>
+        <v>438.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>438.04</v>
+        <v>438.06</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.6</v>
+        <v>435.7</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>407.63</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>407.93</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>298.5</v>
+        <v>314.05</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>304.5</v>
+        <v>305.41</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>315.36</v>
+        <v>315.31</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>322.75</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>322.67</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1806.1</v>
+        <v>1833.7</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1845.38</v>
+        <v>1844.27</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1871.78</v>
+        <v>1870.28</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1916.31</v>
+        <v>1915.49</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5834.5</v>
+        <v>5783</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5706.83</v>
+        <v>5714.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5748.08</v>
+        <v>5749.45</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5758.18</v>
+        <v>5758.43</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1333.7</v>
+        <v>1364.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1281.56</v>
+        <v>1289.45</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1292.2</v>
+        <v>1295.03</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1394.74</v>
+        <v>1394.44</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472.6</v>
+        <v>470.2</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>460.37</v>
+        <v>461.31</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>447.99</v>
+        <v>448.86</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>409.73</v>
+        <v>410.33</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1271.2</v>
+        <v>1311</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1282.52</v>
+        <v>1285.23</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1270.43</v>
+        <v>1272.02</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1253.65</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1254.22</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7301.5</v>
+        <v>7310.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7149.29</v>
+        <v>7164.65</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7176.28</v>
+        <v>7181.54</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6844.86</v>
+        <v>6849.49</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2871.5</v>
+        <v>2914.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2766.58</v>
+        <v>2780.69</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2748.56</v>
+        <v>2755.08</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2745.36</v>
+        <v>2747.04</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1200.2</v>
+        <v>1189.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1276.73</v>
+        <v>1268.38</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1347.57</v>
+        <v>1341.36</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1462.19</v>
+        <v>1459.47</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,24 +1553,24 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>772.3</v>
+        <v>796.55</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>787.28</v>
+        <v>788.16</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>819.24</v>
+        <v>818.35</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>896.79</v>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>895.79</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -1597,24 +1597,24 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>594.1</v>
+        <v>606.35</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>601.11</v>
+        <v>601.61</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>630.53</v>
+        <v>629.58</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>693.5</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>692.64</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5109</v>
+        <v>5170</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5152.03</v>
+        <v>5149.01</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5275.71</v>
+        <v>5264.87</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5181.07</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5180.15</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1054.7</v>
+        <v>1045.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1020.73</v>
+        <v>1023.12</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>977.51</v>
+        <v>980.1799999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>861.41</v>
+        <v>863.25</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2327.4</v>
+        <v>2317.1</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2256.95</v>
+        <v>2262.68</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2244.63</v>
+        <v>2247.47</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2326.35</v>
+        <v>2326.26</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,9 +1754,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1251.3</v>
+        <v>1279.5</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1296.76</v>
+        <v>1295.12</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1311.99</v>
+        <v>1310.72</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1346.48</v>
+        <v>1345.81</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>311.45</v>
+        <v>310.7</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>307.22</v>
+        <v>307.55</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>310.51</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>350.86</v>
+        <v>350.46</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>910.7</v>
+        <v>946.75</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>874.72</v>
+        <v>881.58</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>865.9299999999999</v>
+        <v>869.1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>854.23</v>
+        <v>855.15</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1178.1</v>
+        <v>1167.2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1226.77</v>
+        <v>1221.1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1294.39</v>
+        <v>1289.41</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1447.14</v>
+        <v>1444.35</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1252.4</v>
+        <v>1273.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1241.36</v>
+        <v>1246.31</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1216.46</v>
+        <v>1220.49</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1151.11</v>
+        <v>1153.44</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>371.35</v>
+        <v>376.6</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>376.51</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>384.26</v>
+        <v>383.96</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>403.32</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>403.06</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4054.5</v>
+        <v>4008.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3991.26</v>
+        <v>3992.9</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3939.22</v>
+        <v>3941.94</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3846.31</v>
+        <v>3847.92</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3210.8</v>
+        <v>3300.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3138.03</v>
+        <v>3153.53</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3209.96</v>
+        <v>3213.52</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3321.34</v>
+        <v>3321.13</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13426</v>
+        <v>13722</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13276.08</v>
+        <v>13318.55</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13614.71</v>
+        <v>13618.92</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14247.13</v>
+        <v>14241.91</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>398.65</v>
+        <v>394.85</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>394.8</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>382.8</v>
+        <v>383.27</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>353.21</v>
+        <v>353.62</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1477.8</v>
+        <v>1486.1</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1365.62</v>
+        <v>1385.25</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1306.94</v>
+        <v>1319.71</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1246.19</v>
+        <v>1250.68</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,24 +2257,24 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>289.95</v>
+        <v>280.8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>288.04</v>
+        <v>288.21</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>278.51</v>
+        <v>279.37</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>253.78</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>254.5</v>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>319.45</v>
+        <v>315.95</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>313.82</v>
+        <v>314.03</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>303.65</v>
+        <v>304.13</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>285.91</v>
+        <v>286.21</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1463.6</v>
+        <v>1437.9</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1392.54</v>
+        <v>1396.86</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1393.29</v>
+        <v>1395.03</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1411.85</v>
+        <v>1412.11</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,24 +2389,24 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1821.2</v>
+        <v>1859</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1858.3</v>
+        <v>1858.37</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1902.99</v>
+        <v>1901.27</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1889.71</v>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1889.4</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2433,29 +2433,29 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>964.4</v>
+        <v>1004.1</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>978.61</v>
+        <v>981.03</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>983.8099999999999</v>
+        <v>984.61</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>869.95</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>871.29</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -2477,29 +2477,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1059.9</v>
+        <v>1096</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1078.14</v>
+        <v>1078.94</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1078.03</v>
+        <v>1078.36</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>987.7</v>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>989.5700000000001</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1820.8</v>
+        <v>1850.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1737.98</v>
+        <v>1748.67</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1730.84</v>
+        <v>1735.53</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1711.67</v>
+        <v>1713.05</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2427.3</v>
+        <v>2435.4</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2483.53</v>
+        <v>2478.95</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2566.27</v>
+        <v>2561.14</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2909.08</v>
+        <v>2904.36</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1153.5</v>
+        <v>1152.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1133.46</v>
+        <v>1135.24</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1121.46</v>
+        <v>1122.66</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1117.81</v>
+        <v>1118.15</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,29 +2653,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>340.15</v>
+        <v>358.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>344.15</v>
+        <v>345.48</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>344.26</v>
+        <v>344.8</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>363.45</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>363.4</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>211.32</v>
+        <v>215.47</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>209.17</v>
+        <v>209.77</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>203.25</v>
+        <v>203.73</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>182.94</v>
+        <v>183.26</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1452.2</v>
+        <v>1466.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1444.03</v>
+        <v>1448.54</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1452.5</v>
+        <v>1453.82</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1497.02</v>
+        <v>1496.49</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4373.6</v>
+        <v>4359.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4378.29</v>
+        <v>4376.51</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4284.22</v>
+        <v>4287.18</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3959.39</v>
+        <v>3963.37</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4135.4</v>
+        <v>4289.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4088.28</v>
+        <v>4112.36</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3976.37</v>
+        <v>3995.01</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4356.28</v>
+        <v>4353.53</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11963</v>
+        <v>12093</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11745</v>
+        <v>11768.82</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11757.64</v>
+        <v>11765.13</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11883.64</v>
+        <v>11882.84</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>199.78</v>
+        <v>199.12</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.38</v>
+        <v>201.17</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>205.53</v>
+        <v>205.28</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>228.65</v>
+        <v>228.36</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 07-May-2026  17:25:24    |    Closing Price Date: 07-May-2026</t>
+          <t>Scan Run: 08-May-2026  16:05:28    |    Closing Price Date: 08-May-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07-May-2026  17:25:24</t>
+          <t>08-May-2026  16:05:28</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 76.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 72.0% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 38 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 36 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 33 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 30 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2513.7</v>
+        <v>2505.9</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2320.84</v>
+        <v>2338.47</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2199.63</v>
+        <v>2211.64</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2244.11</v>
+        <v>2248.1</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1732.8</v>
+        <v>1760.4</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1619.2</v>
+        <v>1632.64</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1537.87</v>
+        <v>1546.59</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1445.2</v>
+        <v>1449.03</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>7837</v>
+        <v>8097</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7681.17</v>
+        <v>7720.77</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7576.46</v>
+        <v>7596.87</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7384.16</v>
+        <v>7394.47</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2530.6</v>
+        <v>2599.9</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2440.01</v>
+        <v>2455.24</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2411.21</v>
+        <v>2418.6</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2463.57</v>
+        <v>2464.13</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1292.7</v>
+        <v>1268.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1299.76</v>
+        <v>1296.76</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1297.39</v>
+        <v>1296.25</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1242.34</v>
+        <v>1242.58</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10605</v>
+        <v>10711.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>9835.889999999999</v>
+        <v>9919.280000000001</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9613.450000000001</v>
+        <v>9656.51</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9177.280000000001</v>
+        <v>9202.049999999999</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>972.75</v>
+        <v>955.35</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>931.5700000000001</v>
+        <v>933.83</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>925.55</v>
+        <v>926.72</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>939.12</v>
+        <v>939.9299999999999</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,29 +1061,29 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1824.5</v>
+        <v>1818.3</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1791.52</v>
+        <v>1794.07</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1823.58</v>
+        <v>1823.38</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1924.54</v>
+        <v>1924.42</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>439.45</v>
+        <v>439.7</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>438.19</v>
+        <v>438.34</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>435.85</v>
+        <v>436</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>408.05</v>
+        <v>408.74</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,24 +1149,24 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>307.6</v>
+        <v>302.75</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>305.62</v>
+        <v>305.34</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>315</v>
+        <v>314.52</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>322.39</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>322.35</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1826.6</v>
+        <v>1834.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1842.59</v>
+        <v>1841.82</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1868.57</v>
+        <v>1867.23</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1915.27</v>
+        <v>1913.71</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5814</v>
+        <v>5520</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5723.6</v>
+        <v>5704.21</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5751.98</v>
+        <v>5742.89</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5754.05</v>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5750.71</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1362.3</v>
+        <v>1347</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1298.92</v>
+        <v>1303.5</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1298.36</v>
+        <v>1300.27</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394.33</v>
+        <v>1394</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,24 +1325,24 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>466.65</v>
+        <v>456.4</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>461.82</v>
+        <v>461.3</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>449.56</v>
+        <v>449.82</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>410.69</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>411.49</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1307.6</v>
+        <v>1293.9</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1287.36</v>
+        <v>1287.98</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1273.41</v>
+        <v>1274.22</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1254.05</v>
+        <v>1254.44</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>7327.5</v>
+        <v>7302.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7180.16</v>
+        <v>7191.81</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7187.27</v>
+        <v>7191.79</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6852.59</v>
+        <v>6860.35</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2960.6</v>
+        <v>2968.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2797.83</v>
+        <v>2814.09</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2763.14</v>
+        <v>2771.2</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2747.17</v>
+        <v>2751.19</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1183.4</v>
+        <v>1198.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1260.29</v>
+        <v>1254.4</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1335.16</v>
+        <v>1329.8</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1455.96</v>
+        <v>1454.45</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1545,24 +1545,24 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>796.05</v>
+        <v>780.85</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>788.91</v>
+        <v>788.14</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>817.48</v>
+        <v>816.04</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>895.66</v>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>894.66</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>625.4</v>
+        <v>621.7</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>603.88</v>
+        <v>605.5700000000001</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>629.42</v>
+        <v>629.11</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>692.03</v>
+        <v>692.04</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5343</v>
+        <v>5322</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5167.49</v>
+        <v>5182.2</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5267.94</v>
+        <v>5270.06</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5182.19</v>
+        <v>5185.45</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1055.7</v>
+        <v>1044.4</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1026.22</v>
+        <v>1027.95</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>983.15</v>
+        <v>985.55</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>864.61</v>
+        <v>866.83</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2272.2</v>
+        <v>2287.7</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2263.58</v>
+        <v>2265.88</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2248.44</v>
+        <v>2249.98</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2325.56</v>
+        <v>2324.97</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1279</v>
+        <v>1264.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1293.59</v>
+        <v>1290.84</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1309.48</v>
+        <v>1307.72</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1345.96</v>
+        <v>1345.35</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>307.4</v>
+        <v>307.45</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>307.54</v>
+        <v>307.53</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>310.39</v>
+        <v>310.28</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>349.84</v>
+        <v>349.34</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>946.95</v>
+        <v>950.75</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>887.8099999999999</v>
+        <v>893.8</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>872.15</v>
+        <v>875.23</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>856.4</v>
+        <v>857.9400000000001</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1162.7</v>
+        <v>1179.2</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1215.54</v>
+        <v>1212.08</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1284.44</v>
+        <v>1280.31</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1441.87</v>
+        <v>1441.4</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1283.4</v>
+        <v>1277.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1249.84</v>
+        <v>1252.51</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1222.95</v>
+        <v>1225.11</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1154.6</v>
+        <v>1156.74</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>379.4</v>
+        <v>380.8</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>376.79</v>
+        <v>377.17</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.78</v>
+        <v>383.66</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>402.88</v>
+        <v>402.94</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,24 +2029,24 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>4023</v>
+        <v>3974.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3995.77</v>
+        <v>3993.75</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3945.12</v>
+        <v>3946.27</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3847.81</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3850.59</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3370.7</v>
+        <v>3330.4</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3174.21</v>
+        <v>3189.09</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3219.69</v>
+        <v>3224.03</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3323.28</v>
+        <v>3325.64</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13361.55</v>
+        <v>13396.26</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13624.85</v>
+        <v>13628.81</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14242.72</v>
+        <v>14231.39</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>400.35</v>
+        <v>402.15</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>395.33</v>
+        <v>395.98</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>383.94</v>
+        <v>384.66</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>353.92</v>
+        <v>354.53</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1476</v>
+        <v>1482.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1393.9</v>
+        <v>1402.33</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1325.84</v>
+        <v>1331.98</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1252.53</v>
+        <v>1255.33</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,29 +2249,29 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>283.9</v>
+        <v>279.2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>287.8</v>
+        <v>286.98</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>279.55</v>
+        <v>279.54</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>254.71</v>
+        <v>255.06</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>313.8</v>
+        <v>313.95</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>314</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.51</v>
+        <v>304.88</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>286.36</v>
+        <v>286.79</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1436.2</v>
+        <v>1435.2</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1400.6</v>
+        <v>1403.9</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1396.65</v>
+        <v>1398.16</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1412.57</v>
+        <v>1412.84</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1872.2</v>
+        <v>1872.1</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1856.64</v>
+        <v>1858.12</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1897.09</v>
+        <v>1896.11</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1888.33</v>
+        <v>1889.94</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>1015.65</v>
+        <v>1007.75</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>984.33</v>
+        <v>986.5599999999999</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>985.83</v>
+        <v>986.6900000000001</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>873.5</v>
+        <v>875.83</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,29 +2469,29 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>1092</v>
+        <v>1019.3</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1080.18</v>
+        <v>1074.38</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1078.89</v>
+        <v>1076.56</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>990.72</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>991.26</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1834.4</v>
+        <v>1847.9</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1756.84</v>
+        <v>1770.65</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1739.4</v>
+        <v>1746.39</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1710.79</v>
+        <v>1714.38</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2401.4</v>
+        <v>2394.4</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2471.56</v>
+        <v>2464.21</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2554.88</v>
+        <v>2548.58</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2898.33</v>
+        <v>2895.78</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1151.7</v>
+        <v>1176.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1136.81</v>
+        <v>1140.56</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1123.8</v>
+        <v>1125.86</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1118.29</v>
+        <v>1118.84</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>359.25</v>
+        <v>355.45</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>346.8</v>
+        <v>347.62</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>345.37</v>
+        <v>345.77</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>363.36</v>
+        <v>363.28</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>217.09</v>
+        <v>214.49</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>210.46</v>
+        <v>210.85</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>204.25</v>
+        <v>204.66</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>183.69</v>
+        <v>184.09</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,29 +2733,29 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1448.2</v>
+        <v>1463</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1448.51</v>
+        <v>1449.89</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1453.6</v>
+        <v>1453.97</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1495.78</v>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1496.82</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4307.5</v>
+        <v>4509</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4369.94</v>
+        <v>4383.18</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4287.98</v>
+        <v>4296.64</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3967.07</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3974.38</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4294.1</v>
+        <v>4242.3</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4129.67</v>
+        <v>4140.39</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4006.74</v>
+        <v>4015.98</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4354.76</v>
+        <v>4359.72</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>12146</v>
+        <v>11950</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11804.74</v>
+        <v>11818.57</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11780.07</v>
+        <v>11786.73</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11887.88</v>
+        <v>11899.08</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>197.36</v>
+        <v>197.91</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>200.81</v>
+        <v>200.53</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>204.97</v>
+        <v>204.69</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>228.12</v>
+        <v>228.18</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,13 +157,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-May-2026  16:05:28    |    Closing Price Date: 08-May-2026</t>
+          <t>Scan Run: 11-May-2026  18:03:33    |    Closing Price Date: 11-May-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-May-2026  16:05:28</t>
+          <t>11-May-2026  18:03:33</t>
         </is>
       </c>
     </row>
@@ -617,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -645,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 27 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 33 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 27 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2505.9</v>
+        <v>2500.2</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2338.47</v>
+        <v>2353.87</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2211.64</v>
+        <v>2222.96</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2248.1</v>
+        <v>2248.53</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1760.4</v>
+        <v>1767.3</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1632.64</v>
+        <v>1645.47</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1546.59</v>
+        <v>1555.25</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1449.03</v>
+        <v>1451.65</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8097</v>
+        <v>8082</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7720.77</v>
+        <v>7755.18</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7596.87</v>
+        <v>7615.89</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7394.47</v>
+        <v>7403.75</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2599.9</v>
+        <v>2566.1</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2455.24</v>
+        <v>2465.8</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2418.6</v>
+        <v>2424.39</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2464.13</v>
+        <v>2470.64</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1268.3</v>
+        <v>1272.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1296.76</v>
+        <v>1294.43</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1296.25</v>
+        <v>1295.31</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1242.58</v>
+        <v>1243.52</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10711.5</v>
+        <v>10595.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>9919.280000000001</v>
+        <v>9983.68</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9656.51</v>
+        <v>9693.34</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9202.049999999999</v>
+        <v>9238.35</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>955.35</v>
+        <v>936.05</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>933.83</v>
+        <v>934.05</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>926.72</v>
+        <v>927.08</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>939.9299999999999</v>
+        <v>940.9299999999999</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1042,9 +1047,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1061,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1818.3</v>
+        <v>1794.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1794.07</v>
+        <v>1792.22</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1823.38</v>
+        <v>1819.79</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1924.42</v>
+        <v>1919.86</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,29 +1110,29 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>439.7</v>
+        <v>431.95</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>438.34</v>
+        <v>437.73</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>436</v>
+        <v>435.84</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>408.74</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>409.59</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1149,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>302.75</v>
+        <v>294.45</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>305.34</v>
+        <v>304.31</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>314.52</v>
+        <v>313.74</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>322.35</v>
+        <v>322.02</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1193,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1834.5</v>
+        <v>1759.8</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1841.82</v>
+        <v>1834.01</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1867.23</v>
+        <v>1863.02</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1913.71</v>
+        <v>1913.14</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5520</v>
+        <v>5410.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5704.21</v>
+        <v>5678.49</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5742.89</v>
+        <v>5729.34</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5750.71</v>
+        <v>5754.12</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1281,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1347</v>
+        <v>1304.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1303.5</v>
+        <v>1303.63</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1300.27</v>
+        <v>1300.45</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394</v>
+        <v>1393.75</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,24 +1330,24 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>456.4</v>
+        <v>464.45</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>461.3</v>
+        <v>461.6</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>449.82</v>
+        <v>450.4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>411.49</v>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>412.47</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1369,24 +1374,24 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1293.9</v>
+        <v>1279.9</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1287.98</v>
+        <v>1287.21</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1274.22</v>
+        <v>1274.44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1254.44</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1255.71</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1413,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>7302.5</v>
+        <v>7202.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7191.81</v>
+        <v>7192.83</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7191.79</v>
+        <v>7192.21</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6860.35</v>
+        <v>6872.7</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1457,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2968.6</v>
+        <v>2984.2</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2814.09</v>
+        <v>2830.29</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2771.2</v>
+        <v>2779.55</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2751.19</v>
+        <v>2752.9</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1198.4</v>
+        <v>1194.9</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1254.4</v>
+        <v>1248.73</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1329.8</v>
+        <v>1324.51</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1454.45</v>
+        <v>1450.83</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1545,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>780.85</v>
+        <v>763.65</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>788.14</v>
+        <v>785.8099999999999</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>816.04</v>
+        <v>813.99</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>894.66</v>
+        <v>893.64</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1589,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>621.7</v>
+        <v>622.7</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>605.5700000000001</v>
+        <v>607.2</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>629.11</v>
+        <v>628.86</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>692.04</v>
+        <v>691.22</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,29 +1638,29 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5322</v>
+        <v>5228.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5182.2</v>
+        <v>5186.61</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5270.06</v>
+        <v>5268.43</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5185.45</v>
+        <v>5199.31</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -1677,24 +1682,24 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1044.4</v>
+        <v>1023.5</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1027.95</v>
+        <v>1027.53</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>985.55</v>
+        <v>987.04</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>866.83</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>868.49</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -1721,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2287.7</v>
+        <v>2307.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2265.88</v>
+        <v>2269.82</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2249.98</v>
+        <v>2252.23</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2324.97</v>
+        <v>2329.99</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1264.8</v>
+        <v>1266.4</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1290.84</v>
+        <v>1288.52</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1307.72</v>
+        <v>1306.1</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1345.35</v>
+        <v>1344.73</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>307.45</v>
+        <v>305.85</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>307.53</v>
+        <v>307.37</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>310.28</v>
+        <v>310.1</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>349.34</v>
+        <v>350.11</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>950.75</v>
+        <v>922.3</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>893.8</v>
+        <v>896.52</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>875.23</v>
+        <v>877.08</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>857.9400000000001</v>
+        <v>861.23</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1179.2</v>
+        <v>1177</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1212.08</v>
+        <v>1208.74</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1280.31</v>
+        <v>1276.26</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1441.4</v>
+        <v>1437.51</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1941,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1277.8</v>
+        <v>1262.6</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1252.51</v>
+        <v>1253.47</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1225.11</v>
+        <v>1226.58</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1156.74</v>
+        <v>1157.64</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>380.8</v>
+        <v>381.05</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>377.17</v>
+        <v>377.54</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.66</v>
+        <v>383.56</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>402.94</v>
+        <v>402.57</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,29 +2034,29 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3974.5</v>
+        <v>3940.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3993.75</v>
+        <v>3988.65</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3946.27</v>
+        <v>3946.03</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3850.59</v>
+        <v>3851.35</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2073,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3330.4</v>
+        <v>3245.9</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3189.09</v>
+        <v>3194.5</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3224.03</v>
+        <v>3224.89</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3325.64</v>
+        <v>3331.41</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2098,9 +2103,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
@@ -2117,29 +2122,29 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13726</v>
+        <v>13483</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13396.26</v>
+        <v>13404.52</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13628.81</v>
+        <v>13623.1</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14231.39</v>
+        <v>14264.39</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -2161,24 +2166,24 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>402.15</v>
+        <v>392.95</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>395.98</v>
+        <v>395.69</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>384.66</v>
+        <v>384.98</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>354.53</v>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>354.86</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2205,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1482.4</v>
+        <v>1481.9</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1402.33</v>
+        <v>1409.9</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1331.98</v>
+        <v>1337.86</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1255.33</v>
+        <v>1260.7</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,29 +2254,29 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>279.2</v>
+        <v>281</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>286.98</v>
+        <v>286.41</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>279.54</v>
+        <v>279.59</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>255.06</v>
+        <v>255.56</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -2293,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>313.95</v>
+        <v>310.9</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>314</v>
+        <v>313.7</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.88</v>
+        <v>305.12</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>286.79</v>
+        <v>287.11</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2337,34 +2342,34 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1435.2</v>
+        <v>1388.2</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1403.9</v>
+        <v>1402.4</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1398.16</v>
+        <v>1397.77</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1412.84</v>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1413.84</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -2381,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1872.1</v>
+        <v>1884.4</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1858.12</v>
+        <v>1860.62</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1896.11</v>
+        <v>1895.65</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1889.94</v>
+        <v>1889.58</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,29 +2430,29 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>1007.75</v>
+        <v>975.95</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>986.5599999999999</v>
+        <v>985.55</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>986.6900000000001</v>
+        <v>986.27</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>875.83</v>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>876</v>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -2469,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>1019.3</v>
+        <v>973.6</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1074.38</v>
+        <v>1064.78</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1076.56</v>
+        <v>1072.52</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>991.26</v>
+        <v>991.4</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2494,9 +2499,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -2513,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1847.9</v>
+        <v>1872.7</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1770.65</v>
+        <v>1780.36</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1746.39</v>
+        <v>1751.34</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1714.38</v>
+        <v>1716.25</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2394.4</v>
+        <v>2392.9</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2464.21</v>
+        <v>2457.42</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2548.58</v>
+        <v>2542.48</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2895.78</v>
+        <v>2889.65</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2601,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1176.2</v>
+        <v>1271</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1140.56</v>
+        <v>1152.98</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1125.86</v>
+        <v>1131.55</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1118.84</v>
+        <v>1125.07</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,24 +2650,24 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>355.45</v>
+        <v>346</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>347.62</v>
+        <v>347.47</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>345.77</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>363.28</v>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>363.11</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -2689,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>214.49</v>
+        <v>212.08</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>210.85</v>
+        <v>210.97</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>204.66</v>
+        <v>204.95</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>184.09</v>
+        <v>184.46</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1463</v>
+        <v>1457.4</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1449.89</v>
+        <v>1450.6</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1453.97</v>
+        <v>1454.1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1496.82</v>
+        <v>1494.96</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,29 +2782,29 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4509</v>
+        <v>4205.6</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4383.18</v>
+        <v>4366.27</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4296.64</v>
+        <v>4293.07</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3974.38</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3984.53</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2821,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4242.3</v>
+        <v>4181.1</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4140.39</v>
+        <v>4144.27</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4015.98</v>
+        <v>4022.46</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4359.72</v>
+        <v>4383.79</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11950</v>
+        <v>11866</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11818.57</v>
+        <v>11823.09</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11786.73</v>
+        <v>11789.84</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11899.08</v>
+        <v>11886.39</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2890,9 +2895,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
@@ -2909,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>197.91</v>
+        <v>196.68</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>200.53</v>
+        <v>200.16</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>204.69</v>
+        <v>204.38</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>228.18</v>
+        <v>227.55</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 12-May-2026  18:20:05    |    Closing Price Date: 12-May-2026</t>
+          <t>Scan Run: 13-May-2026  18:21:17    |    Closing Price Date: 13-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>38</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>12-May-2026  18:20:05</t>
+          <t>13-May-2026  18:21:17</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2405.2</v>
+        <v>2498</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2358.76</v>
+        <v>2372.02</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2230.1</v>
+        <v>2240.61</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2249.73</v>
+        <v>2252.2</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1688.2</v>
+        <v>1737.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1649.54</v>
+        <v>1657.94</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1560.46</v>
+        <v>1567.42</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1454.03</v>
+        <v>1456.86</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8022.5</v>
+        <v>8004.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7780.64</v>
+        <v>7801.96</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7631.84</v>
+        <v>7646.45</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7408.06</v>
+        <v>7413.99</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2505.5</v>
+        <v>2617.6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2469.58</v>
+        <v>2483.68</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2427.57</v>
+        <v>2435.02</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2468.44</v>
+        <v>2469.92</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1260.1</v>
+        <v>1255.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1291.16</v>
+        <v>1287.78</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1293.93</v>
+        <v>1292.43</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1243.3</v>
+        <v>1243.42</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10397</v>
+        <v>10262</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10023.05</v>
+        <v>10045.81</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9720.93</v>
+        <v>9742.15</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9240.120000000001</v>
+        <v>9250.290000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>904.2</v>
+        <v>896.15</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>931.2</v>
+        <v>927.86</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>926.1799999999999</v>
+        <v>925.01</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>942.41</v>
+        <v>941.95</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1744.8</v>
+        <v>1728.9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1787.7</v>
+        <v>1782.1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1816.85</v>
+        <v>1813.4</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1919.9</v>
+        <v>1918</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>416.5</v>
+        <v>428.25</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>435.71</v>
+        <v>435</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>435.08</v>
+        <v>434.82</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.32</v>
+        <v>409.51</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>287.85</v>
+        <v>297.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>302.74</v>
+        <v>302.2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>312.72</v>
+        <v>312.11</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>321.43</v>
+        <v>321.18</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1756.8</v>
+        <v>1789.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1826.65</v>
+        <v>1823.09</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1858.86</v>
+        <v>1856.12</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1912.84</v>
+        <v>1911.61</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5645.68</v>
+        <v>5616.19</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5713.84</v>
+        <v>5699.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5745.81</v>
+        <v>5741.73</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,29 +1289,29 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1292.3</v>
+        <v>1327.6</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1302.55</v>
+        <v>1304.94</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1300.13</v>
+        <v>1301.21</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1391.92</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1391.28</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>463.05</v>
+        <v>462.25</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>461.74</v>
+        <v>461.79</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>450.89</v>
+        <v>451.34</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>412.52</v>
+        <v>413.01</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1270</v>
+        <v>1265.3</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1285.57</v>
+        <v>1283.64</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1274.27</v>
+        <v>1273.91</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1255.8</v>
+        <v>1255.9</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7126</v>
+        <v>6971.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7186.46</v>
+        <v>7165.99</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7189.61</v>
+        <v>7181.06</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6879.32</v>
+        <v>6880.24</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2903</v>
+        <v>2945.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2837.22</v>
+        <v>2847.54</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2784.39</v>
+        <v>2790.71</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2755.83</v>
+        <v>2757.72</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1145.8</v>
+        <v>1143.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1238.93</v>
+        <v>1229.81</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1317.5</v>
+        <v>1310.67</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1447.71</v>
+        <v>1444.68</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>750.45</v>
+        <v>749.6</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>782.4400000000001</v>
+        <v>779.3200000000001</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>811.5</v>
+        <v>809.0700000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>891.9400000000001</v>
+        <v>890.52</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>601.8</v>
+        <v>602.8</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>606.6900000000001</v>
+        <v>606.3200000000001</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>627.8</v>
+        <v>626.8200000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>690.15</v>
+        <v>689.29</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5082.5</v>
+        <v>4995</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5176.7</v>
+        <v>5159.39</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5261.14</v>
+        <v>5250.7</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5193.39</v>
+        <v>5191.41</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1041.4</v>
+        <v>1073.1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1028.85</v>
+        <v>1033.07</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>989.17</v>
+        <v>992.46</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>869.67</v>
+        <v>871.6900000000001</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2262</v>
+        <v>2267.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2269.07</v>
+        <v>2268.9</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2252.61</v>
+        <v>2253.19</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2326.56</v>
+        <v>2325.97</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1240.3</v>
+        <v>1235.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1283.92</v>
+        <v>1279.32</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1303.52</v>
+        <v>1300.86</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1343.58</v>
+        <v>1342.51</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>300.7</v>
+        <v>304.45</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>306.73</v>
+        <v>306.52</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>309.73</v>
+        <v>309.53</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>349.27</v>
+        <v>348.83</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>892.85</v>
+        <v>892.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>896.17</v>
+        <v>895.8200000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>877.7</v>
+        <v>878.28</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>861.6900000000001</v>
+        <v>862</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1140.3</v>
+        <v>1123.1</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1202.22</v>
+        <v>1194.68</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1270.93</v>
+        <v>1265.13</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1435.06</v>
+        <v>1431.96</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,24 +1949,24 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1252.3</v>
+        <v>1274.9</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1253.36</v>
+        <v>1255.41</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1227.58</v>
+        <v>1229.44</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1158.57</v>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1159.73</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>377.39</v>
+        <v>377.42</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.27</v>
+        <v>383.05</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>402.14</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>401.9</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3856.5</v>
+        <v>3915.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3976.06</v>
+        <v>3970.32</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3942.52</v>
+        <v>3941.47</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3844.54</v>
+        <v>3845.25</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3176</v>
+        <v>3111.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3192.74</v>
+        <v>3185.03</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3222.97</v>
+        <v>3218.61</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3334.05</v>
+        <v>3331.83</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13172</v>
+        <v>13103</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13382.37</v>
+        <v>13355.77</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13605.41</v>
+        <v>13585.71</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14263.18</v>
+        <v>14251.64</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>392.7</v>
+        <v>390.45</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>395.41</v>
+        <v>394.93</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>385.28</v>
+        <v>385.49</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>354.96</v>
+        <v>355.32</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1468.6</v>
+        <v>1468.9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1415.49</v>
+        <v>1420.58</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1342.99</v>
+        <v>1347.92</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1262.55</v>
+        <v>1264.6</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>294.5</v>
+        <v>297.15</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>287.18</v>
+        <v>288.13</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>280.18</v>
+        <v>280.84</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>255.6</v>
+        <v>256.01</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,29 +2301,29 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>306.3</v>
+        <v>301.5</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>313</v>
+        <v>311.9</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>305.16</v>
+        <v>305.02</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.05</v>
+        <v>287.19</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1364</v>
+        <v>1358.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1398.75</v>
+        <v>1394.94</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1396.45</v>
+        <v>1394.97</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1412.53</v>
+        <v>1412</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1833.9</v>
+        <v>1837.5</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1858.08</v>
+        <v>1856.12</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1893.23</v>
+        <v>1891.05</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1889.27</v>
+        <v>1888.76</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>930.45</v>
+        <v>920.55</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>980.3</v>
+        <v>974.61</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>984.08</v>
+        <v>981.59</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>877.17</v>
+        <v>877.6</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>974.6</v>
+        <v>970.1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1056.2</v>
+        <v>1048</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1068.68</v>
+        <v>1064.81</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>991.02</v>
+        <v>990.8099999999999</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1845.7</v>
+        <v>1824.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1786.59</v>
+        <v>1790.23</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1755.04</v>
+        <v>1757.78</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1717.47</v>
+        <v>1718.53</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2300.3</v>
+        <v>2272.8</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2442.46</v>
+        <v>2426.3</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2532.98</v>
+        <v>2522.78</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2883.59</v>
+        <v>2877.51</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1162.51</v>
+        <v>1169.41</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1136.31</v>
+        <v>1140.18</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.88</v>
+        <v>1125.98</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
         <v>336.85</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>346.45</v>
+        <v>345.54</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>345.42</v>
+        <v>345.09</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>362.84</v>
+        <v>362.59</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>212</v>
+        <v>219.62</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.06</v>
+        <v>211.88</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>205.22</v>
+        <v>205.79</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>184.68</v>
+        <v>185.03</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1392.9</v>
+        <v>1375</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1445.11</v>
+        <v>1438.43</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1451.7</v>
+        <v>1448.69</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1494.29</v>
+        <v>1493.11</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4055.3</v>
+        <v>4090.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4336.65</v>
+        <v>4313.23</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4283.75</v>
+        <v>4276.18</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3986.47</v>
+        <v>3987.51</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4050.6</v>
+        <v>4084.5</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4135.35</v>
+        <v>4130.51</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4023.56</v>
+        <v>4025.95</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4378.1</v>
+        <v>4375.18</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11516</v>
+        <v>11573</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11793.84</v>
+        <v>11772.81</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11779.1</v>
+        <v>11771.02</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11879.04</v>
+        <v>11875.99</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>13-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>189.57</v>
+        <v>187.8</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>199.15</v>
+        <v>198.07</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>203.8</v>
+        <v>203.17</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>227.54</v>
+        <v>227.15</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 14-May-2026  17:26:45    |    Closing Price Date: 14-May-2026</t>
+          <t>Scan Run: 15-May-2026  17:12:12    |    Closing Price Date: 15-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,14 +591,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>50</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>14-May-2026  17:26:45</t>
+          <t>15-May-2026  17:12:12</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,14 +650,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 24 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2712.9</v>
+        <v>2716</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2404.49</v>
+        <v>2434.15</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2259.13</v>
+        <v>2277.05</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2258.5</v>
+        <v>2264.06</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1773.4</v>
+        <v>1795.1</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1668.94</v>
+        <v>1680.95</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1575.49</v>
+        <v>1584.11</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1461.74</v>
+        <v>1465.88</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8119</v>
+        <v>8082.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7832.15</v>
+        <v>7855.99</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7664.99</v>
+        <v>7681.36</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7420.73</v>
+        <v>7433.89</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2622.2</v>
+        <v>2605.6</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2496.87</v>
+        <v>2507.22</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2442.36</v>
+        <v>2448.76</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2474.1</v>
+        <v>2472.01</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1254.6</v>
+        <v>1244.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1284.62</v>
+        <v>1280.83</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1290.94</v>
+        <v>1289.14</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.66</v>
+        <v>1244.57</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10451</v>
+        <v>10377.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10084.4</v>
+        <v>10112.31</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9769.950000000001</v>
+        <v>9793.77</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9261.59</v>
+        <v>9273.389999999999</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>912.15</v>
+        <v>910.45</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>926.37</v>
+        <v>924.85</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>924.5</v>
+        <v>923.95</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>941.87</v>
+        <v>941.7</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1740.2</v>
+        <v>1728.1</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1778.11</v>
+        <v>1773.35</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1810.53</v>
+        <v>1807.3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1917.03</v>
+        <v>1914.43</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>428.85</v>
+        <v>423.65</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>434.41</v>
+        <v>433.39</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>434.58</v>
+        <v>434.15</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>410.15</v>
+        <v>410.47</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>295</v>
+        <v>284.45</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>301.52</v>
+        <v>299.89</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>311.44</v>
+        <v>310.38</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>321.18</v>
+        <v>321.03</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1883.5</v>
+        <v>1905.4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1828.84</v>
+        <v>1836.13</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1857.2</v>
+        <v>1859.09</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1911.73</v>
+        <v>1911.62</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5372.5</v>
+        <v>5406</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5592.98</v>
+        <v>5575.17</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5686.21</v>
+        <v>5675.23</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5734.76</v>
+        <v>5727.4</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1436.7</v>
+        <v>1432.1</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1317.49</v>
+        <v>1328.4</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1306.52</v>
+        <v>1311.45</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1392.95</v>
+        <v>1392.82</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,24 +1330,24 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>454.05</v>
+        <v>462.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>461.05</v>
+        <v>461.16</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>451.45</v>
+        <v>451.87</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>413.52</v>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>414.26</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1303.6</v>
+        <v>1336.7</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1285.54</v>
+        <v>1290.42</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1275.08</v>
+        <v>1277.5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1257.06</v>
+        <v>1258.18</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>7034</v>
+        <v>7014.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7153.42</v>
+        <v>7140.19</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7175.29</v>
+        <v>7168.98</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6880.27</v>
+        <v>6880.2</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2938.7</v>
+        <v>2933.8</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2856.22</v>
+        <v>2863.61</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2796.52</v>
+        <v>2801.9</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2759.99</v>
+        <v>2761.95</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1124</v>
+        <v>1132.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1219.73</v>
+        <v>1211.43</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1303.35</v>
+        <v>1296.65</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1443.15</v>
+        <v>1439.26</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>769.55</v>
+        <v>767.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>778.39</v>
+        <v>777.35</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>807.52</v>
+        <v>805.95</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>890.24</v>
+        <v>889.37</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>612.55</v>
+        <v>608.7</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>606.91</v>
+        <v>607.08</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>626.26</v>
+        <v>625.5700000000001</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>688.72</v>
+        <v>688</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5077</v>
+        <v>5064.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5151.54</v>
+        <v>5143.25</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5243.89</v>
+        <v>5236.85</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5188.25</v>
+        <v>5188.38</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1103.3</v>
+        <v>1067.5</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1039.75</v>
+        <v>1042.4</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>996.8099999999999</v>
+        <v>999.58</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>874.42</v>
+        <v>877.0599999999999</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2248.7</v>
+        <v>2272.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2266.98</v>
+        <v>2267.48</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2253.01</v>
+        <v>2253.76</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2325.04</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2322.52</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1246</v>
+        <v>1244.5</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1276.15</v>
+        <v>1273.13</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1298.71</v>
+        <v>1296.58</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1342.2</v>
+        <v>1341.21</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>307.2</v>
+        <v>309.45</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>306.58</v>
+        <v>306.85</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>309.44</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>348.45</v>
+        <v>347.77</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>907.9</v>
+        <v>886.4</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>896.97</v>
+        <v>895.96</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>879.4400000000001</v>
+        <v>879.71</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>863.95</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>864.78</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1095</v>
+        <v>1119</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1185.19</v>
+        <v>1178.89</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1258.46</v>
+        <v>1252.99</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1430.1</v>
+        <v>1426.93</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1296.9</v>
+        <v>1278.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1259.36</v>
+        <v>1261.21</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1232.09</v>
+        <v>1233.92</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1161.54</v>
+        <v>1162.95</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>383.2</v>
+        <v>387.05</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>377.97</v>
+        <v>378.83</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.05</v>
+        <v>383.21</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>402.09</v>
+        <v>401.8</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3940.4</v>
+        <v>3909</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3967.47</v>
+        <v>3961.9</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3941.43</v>
+        <v>3940.16</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3852.63</v>
+        <v>3850.79</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3173.9</v>
+        <v>3123.1</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3183.97</v>
+        <v>3178.17</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3216.86</v>
+        <v>3213.18</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3330.94</v>
+        <v>3328.43</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13075</v>
+        <v>13221</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13329.03</v>
+        <v>13318.74</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13565.68</v>
+        <v>13552.16</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14238.64</v>
+        <v>14227.53</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>396.3</v>
+        <v>395.25</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>395.06</v>
+        <v>395.08</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>385.91</v>
+        <v>386.28</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>356.05</v>
+        <v>356.47</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1459.6</v>
+        <v>1430.5</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1424.3</v>
+        <v>1424.89</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1352.3</v>
+        <v>1355.37</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1266.17</v>
+        <v>1266.73</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>300.9</v>
+        <v>299.35</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>289.35</v>
+        <v>290.3</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>281.63</v>
+        <v>282.32</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>256.67</v>
+        <v>257.4</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,29 +2298,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>301.75</v>
+        <v>305.85</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>310.94</v>
+        <v>310.45</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.89</v>
+        <v>304.93</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.41</v>
+        <v>287.58</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1361.8</v>
+        <v>1336.4</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1391.79</v>
+        <v>1386.51</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1393.67</v>
+        <v>1391.42</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1413.19</v>
+        <v>1412.13</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1866.7</v>
+        <v>1864.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1857.12</v>
+        <v>1857.83</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1890.09</v>
+        <v>1889.09</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1889.08</v>
+        <v>1888.69</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>935.1</v>
+        <v>937.9</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>970.85</v>
+        <v>967.71</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>979.76</v>
+        <v>978.12</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>879.48</v>
+        <v>879.83</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>979.9</v>
+        <v>963.2</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1041.51</v>
+        <v>1017.37</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1061.48</v>
+        <v>1039.57</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>991.48</v>
+        <v>973.27</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1863.2</v>
+        <v>1878.2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1797.18</v>
+        <v>1804.89</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1761.91</v>
+        <v>1766.47</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1721.02</v>
+        <v>1722.05</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2246</v>
+        <v>2264</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2409.13</v>
+        <v>2395.31</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2511.92</v>
+        <v>2502.2</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2872.84</v>
+        <v>2866.11</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1228.3</v>
+        <v>1234</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1175.02</v>
+        <v>1180.64</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1143.64</v>
+        <v>1147.18</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1126.91</v>
+        <v>1127.16</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,29 +2650,29 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>338.75</v>
+        <v>356.55</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>344.89</v>
+        <v>346</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>344.84</v>
+        <v>345.3</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.35</v>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>362.29</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>221.13</v>
+        <v>216.84</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>212.76</v>
+        <v>213.15</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>206.39</v>
+        <v>206.8</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>185.46</v>
+        <v>185.81</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1343.4</v>
+        <v>1370.5</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1429.38</v>
+        <v>1423.77</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1444.56</v>
+        <v>1441.66</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1491.8</v>
+        <v>1490.67</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4135.2</v>
+        <v>4169.1</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4296.27</v>
+        <v>4284.16</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4270.65</v>
+        <v>4266.67</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3989.73</v>
+        <v>3986.9</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,24 +2826,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4132.4</v>
+        <v>4101.3</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4130.69</v>
+        <v>4127.89</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4030.12</v>
+        <v>4032.91</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4356.12</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4353.57</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11692</v>
+        <v>11487</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11765.11</v>
+        <v>11738.63</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11767.92</v>
+        <v>11756.9</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11888.98</v>
+        <v>11887.84</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>188.3</v>
+        <v>190</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>197.14</v>
+        <v>196.46</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>202.59</v>
+        <v>202.09</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>226.87</v>
+        <v>226.54</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 15-May-2026  17:12:12    |    Closing Price Date: 15-May-2026</t>
+          <t>Scan Run: 18-May-2026  18:14:12    |    Closing Price Date: 18-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,14 +591,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>50</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>15-May-2026  17:12:12</t>
+          <t>18-May-2026  18:14:12</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,14 +650,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 23 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2716</v>
+        <v>2689.8</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2434.15</v>
+        <v>2458.5</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2277.05</v>
+        <v>2293.23</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2264.06</v>
+        <v>2266.8</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1795.1</v>
+        <v>1787.7</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1680.95</v>
+        <v>1691.12</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1584.11</v>
+        <v>1592.09</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1465.88</v>
+        <v>1469.07</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8082.5</v>
+        <v>8020.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7855.99</v>
+        <v>7871.66</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7681.36</v>
+        <v>7694.66</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7433.89</v>
+        <v>7431.76</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2605.6</v>
+        <v>2614</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2507.22</v>
+        <v>2517.39</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2448.76</v>
+        <v>2455.24</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2472.01</v>
+        <v>2473.21</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1244.8</v>
+        <v>1237.9</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1280.83</v>
+        <v>1276.74</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1289.14</v>
+        <v>1287.13</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.57</v>
+        <v>1244.43</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -959,9 +959,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10377.5</v>
+        <v>10198.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10112.31</v>
+        <v>10120.52</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9793.77</v>
+        <v>9809.639999999999</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9273.389999999999</v>
+        <v>9280.57</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>910.45</v>
+        <v>921.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>924.85</v>
+        <v>924.49</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>923.95</v>
+        <v>923.84</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>941.7</v>
+        <v>940.52</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1728.1</v>
+        <v>1753.1</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1773.35</v>
+        <v>1771.42</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1807.3</v>
+        <v>1805.17</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1914.43</v>
+        <v>1912.64</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>423.65</v>
+        <v>426.6</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>433.39</v>
+        <v>432.74</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>434.15</v>
+        <v>433.86</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>410.47</v>
+        <v>409.97</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>284.45</v>
+        <v>280.8</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>299.89</v>
+        <v>298.07</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>310.38</v>
+        <v>309.22</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>321.03</v>
+        <v>320.57</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1905.4</v>
+        <v>1938.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1836.13</v>
+        <v>1845.84</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1859.09</v>
+        <v>1862.19</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1911.62</v>
+        <v>1913.32</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1223,9 +1223,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5406</v>
+        <v>5380.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5575.17</v>
+        <v>5556.63</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5675.23</v>
+        <v>5663.67</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5727.4</v>
+        <v>5722.96</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1432.1</v>
+        <v>1426.2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1328.4</v>
+        <v>1337.72</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1311.45</v>
+        <v>1315.95</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1392.82</v>
+        <v>1394.08</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>462.2</v>
+        <v>462.1</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>461.16</v>
+        <v>461.25</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>451.87</v>
+        <v>452.27</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>414.26</v>
+        <v>414.23</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1336.7</v>
+        <v>1331.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1290.42</v>
+        <v>1294.3</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1277.5</v>
+        <v>1279.6</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1258.18</v>
+        <v>1258.61</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>7014.5</v>
+        <v>6913</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7140.19</v>
+        <v>7118.55</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7168.98</v>
+        <v>7158.95</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6880.2</v>
+        <v>6877.01</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2933.8</v>
+        <v>2943.8</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2863.61</v>
+        <v>2871.25</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2801.9</v>
+        <v>2807.46</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2761.95</v>
+        <v>2763.02</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1132.6</v>
+        <v>1146.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1211.43</v>
+        <v>1205.26</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1296.65</v>
+        <v>1290.77</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1439.26</v>
+        <v>1437.21</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>767.5</v>
+        <v>768.65</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>777.35</v>
+        <v>776.52</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>805.95</v>
+        <v>804.49</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>889.37</v>
+        <v>887.6900000000001</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>608.7</v>
+        <v>604.95</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>607.08</v>
+        <v>606.88</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>625.5700000000001</v>
+        <v>624.76</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>688</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>687.52</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5064.5</v>
+        <v>4957</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5143.25</v>
+        <v>5125.52</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5236.85</v>
+        <v>5225.88</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5188.38</v>
+        <v>5183.02</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1067.5</v>
+        <v>1053.1</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1042.4</v>
+        <v>1043.42</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>999.58</v>
+        <v>1001.68</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>877.0599999999999</v>
+        <v>878.61</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,24 +1726,24 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2272.2</v>
+        <v>2254.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2267.48</v>
+        <v>2266.21</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2253.76</v>
+        <v>2253.78</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2322.52</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2320.57</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1244.5</v>
+        <v>1251.1</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1273.13</v>
+        <v>1271.04</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1296.58</v>
+        <v>1294.8</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1341.21</v>
+        <v>1340.09</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>309.45</v>
+        <v>310.15</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>306.85</v>
+        <v>307.17</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>309.44</v>
+        <v>309.46</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>347.77</v>
+        <v>346.53</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>886.4</v>
+        <v>892.15</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>895.96</v>
+        <v>895.6</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>879.71</v>
+        <v>880.2</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>864.78</v>
+        <v>865.34</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1119</v>
+        <v>1142.5</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1178.89</v>
+        <v>1175.42</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1252.99</v>
+        <v>1248.66</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1426.93</v>
+        <v>1423.37</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1278.8</v>
+        <v>1292.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1261.21</v>
+        <v>1264.22</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1233.92</v>
+        <v>1236.23</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1162.95</v>
+        <v>1164.63</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>387.05</v>
+        <v>391.8</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>378.83</v>
+        <v>380.07</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.21</v>
+        <v>383.55</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>401.8</v>
+        <v>402.13</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3909</v>
+        <v>3917.8</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3961.9</v>
+        <v>3957.7</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3940.16</v>
+        <v>3939.28</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3850.79</v>
+        <v>3849.1</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3123.1</v>
+        <v>3083.7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3178.17</v>
+        <v>3169.17</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3213.18</v>
+        <v>3208.1</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3328.43</v>
+        <v>3324.18</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13221</v>
+        <v>13016</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13318.74</v>
+        <v>13289.91</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13552.16</v>
+        <v>13531.13</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14227.53</v>
+        <v>14207.37</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,24 +2166,24 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>395.25</v>
+        <v>388.3</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>395.08</v>
+        <v>394.44</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>386.28</v>
+        <v>386.36</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>356.47</v>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>356.39</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1430.5</v>
+        <v>1431.7</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1424.89</v>
+        <v>1425.54</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1355.37</v>
+        <v>1358.36</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1266.73</v>
+        <v>1268.08</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>299.35</v>
+        <v>297.2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>290.3</v>
+        <v>290.96</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>282.32</v>
+        <v>282.91</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>257.4</v>
+        <v>257.21</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,29 +2298,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>305.85</v>
+        <v>296.55</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>310.45</v>
+        <v>309.13</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.93</v>
+        <v>304.6</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.58</v>
+        <v>287.11</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1336.4</v>
+        <v>1335.9</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1386.51</v>
+        <v>1381.69</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1391.42</v>
+        <v>1389.25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1412.13</v>
+        <v>1410.29</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1864.5</v>
+        <v>1860.4</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1857.83</v>
+        <v>1858.07</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1889.09</v>
+        <v>1887.96</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1888.69</v>
+        <v>1887.49</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>937.9</v>
+        <v>933.7</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>967.71</v>
+        <v>964.47</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>978.12</v>
+        <v>976.38</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>879.83</v>
+        <v>879.91</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>963.2</v>
+        <v>939.4</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1017.37</v>
+        <v>1009.94</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1039.57</v>
+        <v>1035.64</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>973.27</v>
+        <v>971.7</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1878.2</v>
+        <v>1905.8</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1804.89</v>
+        <v>1814.5</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1766.47</v>
+        <v>1771.94</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1722.05</v>
+        <v>1723.44</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2264</v>
+        <v>2283.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2395.31</v>
+        <v>2384.63</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2502.2</v>
+        <v>2493.61</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2866.11</v>
+        <v>2858.03</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1180.64</v>
+        <v>1185.43</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1147.18</v>
+        <v>1150.47</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1127.16</v>
+        <v>1128.72</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>356.55</v>
+        <v>353.15</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>346</v>
+        <v>346.68</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>345.3</v>
+        <v>345.61</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.29</v>
+        <v>362.2</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,24 +2694,24 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>216.84</v>
+        <v>209.71</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>213.15</v>
+        <v>212.82</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>206.8</v>
+        <v>206.91</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>185.81</v>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>186.03</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -2738,24 +2738,24 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1370.5</v>
+        <v>1430</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1423.77</v>
+        <v>1424.37</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1441.66</v>
+        <v>1441.2</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1490.67</v>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1491.69</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4169.1</v>
+        <v>4169.7</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4284.16</v>
+        <v>4273.26</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4266.67</v>
+        <v>4262.87</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3986.9</v>
+        <v>3981.59</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,29 +2826,29 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4101.3</v>
+        <v>4032.3</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4127.89</v>
+        <v>4118.78</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4032.91</v>
+        <v>4032.89</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4353.57</v>
+        <v>4326.3</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11487</v>
+        <v>11561</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11738.63</v>
+        <v>11721.71</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11756.9</v>
+        <v>11749.22</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11887.84</v>
+        <v>11882.27</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>190</v>
+        <v>192.17</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>196.46</v>
+        <v>196.05</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>202.09</v>
+        <v>201.71</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>226.54</v>
+        <v>226.28</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-May-2026  18:14:12    |    Closing Price Date: 18-May-2026</t>
+          <t>Scan Run: 19-May-2026  13:54:25    |    Closing Price Date: 19-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,11 +591,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>46</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-May-2026  18:14:12</t>
+          <t>19-May-2026  13:54:25</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2689.8</v>
+        <v>2725</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2458.5</v>
+        <v>2483.88</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2293.23</v>
+        <v>2310.16</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2266.8</v>
+        <v>2271.36</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1787.7</v>
+        <v>1762.8</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1691.12</v>
+        <v>1697.95</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1592.09</v>
+        <v>1598.78</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1469.07</v>
+        <v>1471.99</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8020.5</v>
+        <v>8026</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7871.66</v>
+        <v>7886.36</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7694.66</v>
+        <v>7707.65</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7431.76</v>
+        <v>7437.67</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2614</v>
+        <v>2600.7</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2517.39</v>
+        <v>2525.33</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2455.24</v>
+        <v>2460.95</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2473.21</v>
+        <v>2474.48</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1237.9</v>
+        <v>1238.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1276.74</v>
+        <v>1273.08</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1287.13</v>
+        <v>1285.21</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.43</v>
+        <v>1244.37</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10198.5</v>
+        <v>10205</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10120.52</v>
+        <v>10128.56</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9809.639999999999</v>
+        <v>9825.15</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9280.57</v>
+        <v>9289.77</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>921.1</v>
+        <v>923.55</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>924.49</v>
+        <v>924.4</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>923.84</v>
+        <v>923.83</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>940.52</v>
+        <v>940.35</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1753.1</v>
+        <v>1749.8</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1771.42</v>
+        <v>1769.36</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1805.17</v>
+        <v>1803</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1912.64</v>
+        <v>1911.02</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>426.6</v>
+        <v>422.95</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>432.74</v>
+        <v>431.81</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>433.86</v>
+        <v>433.43</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>409.97</v>
+        <v>410.1</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>280.8</v>
+        <v>286.45</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>298.07</v>
+        <v>296.97</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>309.22</v>
+        <v>308.33</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>320.57</v>
+        <v>320.24</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,17 +1198,17 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1938.1</v>
+        <v>1913.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1845.84</v>
+        <v>1852.29</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1862.19</v>
+        <v>1864.2</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>1913.32</v>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5380.5</v>
+        <v>5416.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5556.63</v>
+        <v>5543.28</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5663.67</v>
+        <v>5653.97</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5722.96</v>
+        <v>5719.91</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1426.2</v>
+        <v>1409.8</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1337.72</v>
+        <v>1344.58</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1315.95</v>
+        <v>1319.63</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394.08</v>
+        <v>1394.24</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,24 +1330,24 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>462.1</v>
+        <v>456.95</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>461.25</v>
+        <v>460.84</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>452.27</v>
+        <v>452.45</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>414.23</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>414.66</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1331.2</v>
+        <v>1335.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1294.3</v>
+        <v>1298.2</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1279.6</v>
+        <v>1281.78</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1258.61</v>
+        <v>1259.37</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>6913</v>
+        <v>6882.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7118.55</v>
+        <v>7096.07</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7158.95</v>
+        <v>7148.1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6877.01</v>
+        <v>6877.06</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2943.8</v>
+        <v>2935.2</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2871.25</v>
+        <v>2877.34</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2807.46</v>
+        <v>2812.47</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2763.02</v>
+        <v>2764.73</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1146.6</v>
+        <v>1179.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1205.26</v>
+        <v>1202.8</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1290.77</v>
+        <v>1286.4</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1437.21</v>
+        <v>1434.65</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>768.65</v>
+        <v>762.45</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>776.52</v>
+        <v>775.1799999999999</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>804.49</v>
+        <v>802.84</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>887.6900000000001</v>
+        <v>886.45</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>604.95</v>
+        <v>610.4</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>606.88</v>
+        <v>607.22</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>624.76</v>
+        <v>624.2</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>687.52</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>686.75</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4957</v>
+        <v>5007.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5125.52</v>
+        <v>5114.28</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5225.88</v>
+        <v>5217.32</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5183.02</v>
+        <v>5181.27</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1053.1</v>
+        <v>1048.3</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1043.42</v>
+        <v>1043.88</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1001.68</v>
+        <v>1003.51</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>878.61</v>
+        <v>880.3</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2254.2</v>
+        <v>2232.9</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2266.21</v>
+        <v>2263.04</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2253.78</v>
+        <v>2252.96</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2320.57</v>
+        <v>2319.7</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1251.1</v>
+        <v>1240.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1271.04</v>
+        <v>1268.16</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1294.8</v>
+        <v>1292.68</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1340.09</v>
+        <v>1339.1</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>310.15</v>
+        <v>310.3</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>307.17</v>
+        <v>307.47</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>309.46</v>
+        <v>309.5</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>346.53</v>
+        <v>346.17</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>892.15</v>
+        <v>895.25</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>895.6</v>
+        <v>895.5700000000001</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>880.2</v>
+        <v>880.79</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>865.34</v>
+        <v>865.64</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1902,24 +1902,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1142.5</v>
+        <v>1196.9</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1175.42</v>
+        <v>1177.47</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1248.66</v>
+        <v>1246.63</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1423.37</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1421.12</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1292.8</v>
+        <v>1285.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1264.22</v>
+        <v>1266.22</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1236.23</v>
+        <v>1238.15</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1164.63</v>
+        <v>1165.83</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,29 +1990,29 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>391.8</v>
+        <v>381.95</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>380.07</v>
+        <v>380.25</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.55</v>
+        <v>383.48</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>402.13</v>
+        <v>401.92</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3917.8</v>
+        <v>3921</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3957.7</v>
+        <v>3954.21</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3939.28</v>
+        <v>3938.56</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3849.1</v>
+        <v>3849.82</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3083.7</v>
+        <v>3092.3</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3169.17</v>
+        <v>3161.85</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3208.1</v>
+        <v>3203.56</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3324.18</v>
+        <v>3321.88</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13016</v>
+        <v>12956</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13289.91</v>
+        <v>13258.11</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13531.13</v>
+        <v>13508.58</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14207.37</v>
+        <v>14194.92</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>388.3</v>
+        <v>389.4</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>394.44</v>
+        <v>393.96</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>386.36</v>
+        <v>386.48</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>356.39</v>
+        <v>356.72</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1431.7</v>
+        <v>1431.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1425.54</v>
+        <v>1426.09</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1358.36</v>
+        <v>1361.23</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1268.08</v>
+        <v>1269.7</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>297.2</v>
+        <v>296.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>290.96</v>
+        <v>291.49</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>282.91</v>
+        <v>283.44</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>257.21</v>
+        <v>257.6</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>296.55</v>
+        <v>298.6</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>309.13</v>
+        <v>308.13</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.6</v>
+        <v>304.36</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.11</v>
+        <v>287.22</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1335.9</v>
+        <v>1322.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1381.69</v>
+        <v>1376.07</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1389.25</v>
+        <v>1386.64</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1410.29</v>
+        <v>1409.42</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1860.4</v>
+        <v>1881.4</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1858.07</v>
+        <v>1860.29</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1887.96</v>
+        <v>1887.7</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1887.49</v>
+        <v>1887.43</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>933.7</v>
+        <v>927.35</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>964.47</v>
+        <v>960.9400000000001</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>976.38</v>
+        <v>974.46</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>879.91</v>
+        <v>880.39</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>939.4</v>
+        <v>948.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1009.94</v>
+        <v>1004.12</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1035.64</v>
+        <v>1032.24</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>971.7</v>
+        <v>971.48</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1905.8</v>
+        <v>1882.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1814.5</v>
+        <v>1820.96</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1771.94</v>
+        <v>1776.26</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1723.44</v>
+        <v>1725.02</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2283.2</v>
+        <v>2327.1</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2384.63</v>
+        <v>2379.15</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2493.61</v>
+        <v>2487.08</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2858.03</v>
+        <v>2852.75</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1231</v>
+        <v>1210.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1185.43</v>
+        <v>1187.86</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1150.47</v>
+        <v>1152.84</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1128.72</v>
+        <v>1129.54</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>353.15</v>
+        <v>361.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>346.68</v>
+        <v>348.07</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>345.61</v>
+        <v>346.22</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.2</v>
+        <v>362.19</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>209.71</v>
+        <v>209.29</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>212.82</v>
+        <v>212.48</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>206.91</v>
+        <v>207.01</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>186.03</v>
+        <v>186.26</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2738,29 +2738,29 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1430</v>
+        <v>1467.1</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1424.37</v>
+        <v>1428.44</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1441.2</v>
+        <v>1442.22</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1491.69</v>
+        <v>1491.44</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4169.7</v>
+        <v>4102</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4273.26</v>
+        <v>4256.95</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4262.87</v>
+        <v>4256.56</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3981.59</v>
+        <v>3982.79</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,29 +2826,29 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4032.3</v>
+        <v>4069.6</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4118.78</v>
+        <v>4114.1</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4032.89</v>
+        <v>4034.33</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4326.3</v>
+        <v>4323.75</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11561</v>
+        <v>11368</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11721.71</v>
+        <v>11688.02</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11749.22</v>
+        <v>11734.27</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11882.27</v>
+        <v>11877.15</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>18-May-2026</t>
+          <t>19-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>192.17</v>
+        <v>195.17</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>196.05</v>
+        <v>195.97</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>201.71</v>
+        <v>201.45</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>226.28</v>
+        <v>225.97</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-May-2026  13:54:25    |    Closing Price Date: 19-May-2026</t>
+          <t>Scan Run: 20-May-2026  13:37:11    |    Closing Price Date: 20-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-May-2026  13:54:25</t>
+          <t>20-May-2026  13:37:11</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 21 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2725</v>
+        <v>2704.8</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2483.88</v>
+        <v>2504.92</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2310.16</v>
+        <v>2325.64</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2271.36</v>
+        <v>2275.67</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1762.8</v>
+        <v>1772.6</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1697.95</v>
+        <v>1705.06</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1598.78</v>
+        <v>1605.6</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1471.99</v>
+        <v>1474.98</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8026</v>
+        <v>8078.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7886.36</v>
+        <v>7904.66</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7707.65</v>
+        <v>7722.19</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7437.67</v>
+        <v>7444.05</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2600.7</v>
+        <v>2598.6</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2525.33</v>
+        <v>2532.31</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2460.95</v>
+        <v>2466.35</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2474.48</v>
+        <v>2475.72</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1238.3</v>
+        <v>1249.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1273.08</v>
+        <v>1270.86</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1285.21</v>
+        <v>1283.82</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.37</v>
+        <v>1244.42</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -959,9 +959,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10205</v>
+        <v>10462.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10128.56</v>
+        <v>10160.37</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9825.15</v>
+        <v>9850.139999999999</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9289.77</v>
+        <v>9301.440000000001</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>923.55</v>
+        <v>923.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>924.4</v>
+        <v>924.28</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>923.83</v>
+        <v>923.8</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>940.35</v>
+        <v>940.1799999999999</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1749.8</v>
+        <v>1772</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1769.36</v>
+        <v>1769.61</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1803</v>
+        <v>1801.78</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1911.02</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1909.63</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>422.95</v>
+        <v>413.3</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>431.81</v>
+        <v>430.04</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>433.43</v>
+        <v>432.64</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>410.1</v>
+        <v>410.13</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>286.45</v>
+        <v>293.75</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>296.97</v>
+        <v>296.66</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>308.33</v>
+        <v>307.76</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>320.24</v>
+        <v>319.97</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1913.5</v>
+        <v>1904.9</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1852.29</v>
+        <v>1857.3</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1864.2</v>
+        <v>1865.8</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1913.32</v>
+        <v>1913.24</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1223,9 +1223,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5416.5</v>
+        <v>5344.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5543.28</v>
+        <v>5524.35</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5653.97</v>
+        <v>5641.84</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5719.91</v>
+        <v>5716.18</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1409.8</v>
+        <v>1399.5</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1344.58</v>
+        <v>1349.81</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1319.63</v>
+        <v>1322.76</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394.24</v>
+        <v>1394.29</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>456.95</v>
+        <v>458.7</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>460.84</v>
+        <v>460.64</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>452.45</v>
+        <v>452.7</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>414.66</v>
+        <v>415.09</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1335.2</v>
+        <v>1321.9</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1298.2</v>
+        <v>1300.45</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1281.78</v>
+        <v>1283.36</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1259.37</v>
+        <v>1259.99</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>6882.5</v>
+        <v>6849.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7096.07</v>
+        <v>7072.59</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7148.1</v>
+        <v>7136.39</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6877.06</v>
+        <v>6876.79</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1443,9 +1443,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2935.2</v>
+        <v>2971.1</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2877.34</v>
+        <v>2886.27</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2812.47</v>
+        <v>2818.69</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2764.73</v>
+        <v>2766.79</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1179.4</v>
+        <v>1169.8</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1202.8</v>
+        <v>1199.65</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1286.4</v>
+        <v>1281.83</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1434.65</v>
+        <v>1432.01</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>762.45</v>
+        <v>759.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>775.1799999999999</v>
+        <v>773.6900000000001</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>802.84</v>
+        <v>801.14</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>886.45</v>
+        <v>885.1799999999999</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>610.4</v>
+        <v>605.1</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>607.22</v>
+        <v>607.01</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>624.2</v>
+        <v>623.45</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>686.75</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>685.9400000000001</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5007.5</v>
+        <v>4968</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5114.28</v>
+        <v>5100.35</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5217.32</v>
+        <v>5207.54</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5181.27</v>
+        <v>5179.15</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1048.3</v>
+        <v>1085.5</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1043.88</v>
+        <v>1047.84</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1003.51</v>
+        <v>1006.72</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>880.3</v>
+        <v>882.34</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2232.9</v>
+        <v>2209.3</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2263.04</v>
+        <v>2257.92</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2252.96</v>
+        <v>2251.25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2319.7</v>
+        <v>2318.6</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1240.8</v>
+        <v>1237.3</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1268.16</v>
+        <v>1265.22</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1292.68</v>
+        <v>1290.51</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1339.1</v>
+        <v>1338.09</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>310.3</v>
+        <v>307.55</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>307.47</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>309.5</v>
+        <v>309.42</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>346.17</v>
+        <v>345.79</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>895.25</v>
+        <v>897.15</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>895.5700000000001</v>
+        <v>895.72</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>880.79</v>
+        <v>881.4299999999999</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>865.64</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>865.95</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1196.9</v>
+        <v>1193.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1177.47</v>
+        <v>1179.01</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1246.63</v>
+        <v>1244.55</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1421.12</v>
+        <v>1418.85</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1285.2</v>
+        <v>1283.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1266.22</v>
+        <v>1267.84</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1238.15</v>
+        <v>1239.91</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1165.83</v>
+        <v>1167</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>381.95</v>
+        <v>383.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>380.25</v>
+        <v>380.53</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.48</v>
+        <v>383.47</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>401.92</v>
+        <v>401.74</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3921</v>
+        <v>3910.7</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3954.21</v>
+        <v>3950.06</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3938.56</v>
+        <v>3937.47</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3849.82</v>
+        <v>3850.42</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3092.3</v>
+        <v>3122.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3161.85</v>
+        <v>3158.08</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3203.56</v>
+        <v>3200.37</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3321.88</v>
+        <v>3319.89</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>12956</v>
+        <v>13003</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13258.11</v>
+        <v>13233.81</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13508.58</v>
+        <v>13488.75</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14194.92</v>
+        <v>14183.06</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>389.4</v>
+        <v>392.45</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>393.96</v>
+        <v>393.81</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>386.48</v>
+        <v>386.71</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>356.72</v>
+        <v>357.08</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,24 +2210,24 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1431.4</v>
+        <v>1420.1</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1426.09</v>
+        <v>1425.52</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1361.23</v>
+        <v>1363.54</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1269.7</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1271.2</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>296.5</v>
+        <v>298.3</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>291.49</v>
+        <v>292.13</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>283.44</v>
+        <v>284.02</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>257.6</v>
+        <v>258</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>298.6</v>
+        <v>299.9</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>308.13</v>
+        <v>307.34</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.36</v>
+        <v>304.19</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.22</v>
+        <v>287.35</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1322.7</v>
+        <v>1359.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1376.07</v>
+        <v>1374.51</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1386.64</v>
+        <v>1385.58</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1409.42</v>
+        <v>1408.93</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1881.4</v>
+        <v>1864.2</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1860.29</v>
+        <v>1860.67</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1887.7</v>
+        <v>1886.78</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1887.43</v>
+        <v>1887.2</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>927.35</v>
+        <v>923.45</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>960.9400000000001</v>
+        <v>957.37</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>974.46</v>
+        <v>972.46</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>880.39</v>
+        <v>880.8099999999999</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>948.8</v>
+        <v>950.9</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1004.12</v>
+        <v>999.05</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1032.24</v>
+        <v>1029.05</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>971.48</v>
+        <v>971.27</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1882.3</v>
+        <v>1880.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1820.96</v>
+        <v>1826.61</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1776.26</v>
+        <v>1780.34</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1725.02</v>
+        <v>1726.56</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2327.1</v>
+        <v>2327.4</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2379.15</v>
+        <v>2374.22</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2487.08</v>
+        <v>2480.82</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2852.75</v>
+        <v>2847.52</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1210.9</v>
+        <v>1208.7</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1187.86</v>
+        <v>1189.84</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1152.84</v>
+        <v>1155.03</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1129.54</v>
+        <v>1130.33</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>361.2</v>
+        <v>361.25</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>348.07</v>
+        <v>349.32</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>346.22</v>
+        <v>346.81</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.19</v>
+        <v>362.18</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>209.29</v>
+        <v>207.01</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>212.48</v>
+        <v>211.96</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>207.01</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>186.26</v>
+        <v>186.47</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2738,29 +2738,29 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1467.1</v>
+        <v>1439</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1428.44</v>
+        <v>1429.44</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1442.22</v>
+        <v>1442.09</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1491.44</v>
+        <v>1490.92</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4102</v>
+        <v>4106.4</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4256.95</v>
+        <v>4242.61</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4256.56</v>
+        <v>4250.67</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3982.79</v>
+        <v>3984.02</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4069.6</v>
+        <v>4099.9</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4114.1</v>
+        <v>4112.75</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4034.33</v>
+        <v>4036.9</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4323.75</v>
+        <v>4321.52</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11368</v>
+        <v>11409</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11688.02</v>
+        <v>11661.45</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11734.27</v>
+        <v>11721.51</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11877.15</v>
+        <v>11872.49</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,24 +2914,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>19-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>195.17</v>
+        <v>197.12</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>195.97</v>
+        <v>196.08</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>201.45</v>
+        <v>201.28</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>225.97</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>225.68</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 20-May-2026  13:37:11    |    Closing Price Date: 20-May-2026</t>
+          <t>Scan Run: 21-May-2026  14:12:41    |    Closing Price Date: 21-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>42</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>20-May-2026  13:37:11</t>
+          <t>21-May-2026  14:12:41</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2704.8</v>
+        <v>2697.6</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2504.92</v>
+        <v>2523.27</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2325.64</v>
+        <v>2340.23</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2275.67</v>
+        <v>2281.21</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1772.6</v>
+        <v>1793.3</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1705.06</v>
+        <v>1713.46</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1605.6</v>
+        <v>1612.96</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1474.98</v>
+        <v>1477.98</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8078.5</v>
+        <v>8308.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7904.66</v>
+        <v>7943.12</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7722.19</v>
+        <v>7745.19</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7444.05</v>
+        <v>7433.51</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2598.6</v>
+        <v>2598.8</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2532.31</v>
+        <v>2538.64</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2466.35</v>
+        <v>2471.54</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2475.72</v>
+        <v>2475.69</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1249.8</v>
+        <v>1253.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1270.86</v>
+        <v>1269.19</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1283.82</v>
+        <v>1282.63</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.42</v>
+        <v>1244.32</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10462.5</v>
+        <v>10667</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10160.37</v>
+        <v>10208.62</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9850.139999999999</v>
+        <v>9882.17</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9301.440000000001</v>
+        <v>9310.02</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>923.1</v>
+        <v>907.65</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>924.28</v>
+        <v>922.7</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>923.8</v>
+        <v>923.17</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>940.1799999999999</v>
+        <v>939.45</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1772</v>
+        <v>1752.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1769.61</v>
+        <v>1767.95</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1801.78</v>
+        <v>1799.84</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1909.63</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1906.01</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>413.3</v>
+        <v>420.4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>430.04</v>
+        <v>429.13</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>432.64</v>
+        <v>432.16</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>410.13</v>
+        <v>409.87</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>293.75</v>
+        <v>296.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>296.66</v>
+        <v>296.63</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>307.76</v>
+        <v>307.31</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>319.97</v>
+        <v>319.54</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1904.9</v>
+        <v>1885.3</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1857.3</v>
+        <v>1859.96</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1865.8</v>
+        <v>1866.56</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1913.24</v>
+        <v>1913.12</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5344.5</v>
+        <v>5333</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5524.35</v>
+        <v>5506.13</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5641.84</v>
+        <v>5629.73</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5716.18</v>
+        <v>5712.13</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1399.5</v>
+        <v>1401.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1349.81</v>
+        <v>1354.77</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1322.76</v>
+        <v>1325.87</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394.29</v>
+        <v>1394.12</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>458.7</v>
+        <v>460.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>460.64</v>
+        <v>460.59</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>452.7</v>
+        <v>452.99</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>415.09</v>
+        <v>415.08</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1321.9</v>
+        <v>1318.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1300.45</v>
+        <v>1302.17</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1283.36</v>
+        <v>1284.73</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1259.99</v>
+        <v>1260.1</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>6849.5</v>
+        <v>6892</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7072.59</v>
+        <v>7055.39</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7136.39</v>
+        <v>7126.81</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6876.79</v>
+        <v>6861.43</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1443,9 +1443,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2971.1</v>
+        <v>3154.5</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2886.27</v>
+        <v>2911.81</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2818.69</v>
+        <v>2831.86</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2766.79</v>
+        <v>2771.43</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1169.8</v>
+        <v>1168.2</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1199.65</v>
+        <v>1196.66</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1281.83</v>
+        <v>1277.37</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1432.01</v>
+        <v>1428.95</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>759.5</v>
+        <v>759.15</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>773.6900000000001</v>
+        <v>772.3</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>801.14</v>
+        <v>799.49</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>885.1799999999999</v>
+        <v>883.62</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>605.1</v>
+        <v>614.35</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>607.01</v>
+        <v>607.71</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>623.45</v>
+        <v>623.09</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>685.9400000000001</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>684.49</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4968</v>
+        <v>4969.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5100.35</v>
+        <v>5087.88</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5207.54</v>
+        <v>5198.2</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5179.15</v>
+        <v>5172.54</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1085.5</v>
+        <v>1099.3</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1047.84</v>
+        <v>1052.75</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1006.72</v>
+        <v>1010.35</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>882.34</v>
+        <v>884.49</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2209.3</v>
+        <v>2179</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2257.92</v>
+        <v>2250.41</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2251.25</v>
+        <v>2248.41</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2318.6</v>
+        <v>2315.25</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1237.3</v>
+        <v>1242.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1265.22</v>
+        <v>1263.08</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1290.51</v>
+        <v>1288.64</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1338.09</v>
+        <v>1336.72</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>307.55</v>
+        <v>308.05</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>307.47</v>
+        <v>307.53</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>309.42</v>
+        <v>309.37</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>345.79</v>
+        <v>345.05</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>897.15</v>
+        <v>899.95</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>895.72</v>
+        <v>896.12</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>881.4299999999999</v>
+        <v>882.16</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>865.95</v>
+        <v>865.6900000000001</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1193.7</v>
+        <v>1181.2</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1179.01</v>
+        <v>1179.22</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1244.55</v>
+        <v>1242.07</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1418.85</v>
+        <v>1416.29</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1283.2</v>
+        <v>1281.3</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1267.84</v>
+        <v>1269.12</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1239.91</v>
+        <v>1241.54</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1167</v>
+        <v>1167.94</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>383.2</v>
+        <v>380.85</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>380.53</v>
+        <v>380.56</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.47</v>
+        <v>383.37</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>401.74</v>
+        <v>401.17</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3910.7</v>
+        <v>3928.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3950.06</v>
+        <v>3948.01</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3937.47</v>
+        <v>3937.12</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3850.42</v>
+        <v>3847.38</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3122.2</v>
+        <v>3099</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3158.08</v>
+        <v>3152.45</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3200.37</v>
+        <v>3196.4</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3319.89</v>
+        <v>3315.49</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13003</v>
+        <v>13010</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13233.81</v>
+        <v>13212.49</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13488.75</v>
+        <v>13469.98</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14183.06</v>
+        <v>14163.83</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>392.45</v>
+        <v>388.8</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>393.81</v>
+        <v>393.34</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>386.71</v>
+        <v>386.79</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>357.08</v>
+        <v>357.19</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1420.1</v>
+        <v>1406.5</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1425.52</v>
+        <v>1423.71</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1363.54</v>
+        <v>1365.22</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1271.2</v>
+        <v>1272</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>298.3</v>
+        <v>295.85</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>292.13</v>
+        <v>292.49</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>284.02</v>
+        <v>284.49</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>258</v>
+        <v>258.24</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>299.9</v>
+        <v>299.55</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>307.34</v>
+        <v>306.6</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.19</v>
+        <v>304.01</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.35</v>
+        <v>287.16</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1359.7</v>
+        <v>1349.6</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1374.51</v>
+        <v>1372.14</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1385.58</v>
+        <v>1384.17</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1408.93</v>
+        <v>1407.53</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1864.2</v>
+        <v>1859.9</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1860.67</v>
+        <v>1860.59</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1886.78</v>
+        <v>1885.73</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1887.2</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1885.66</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>923.45</v>
+        <v>914.75</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>957.37</v>
+        <v>953.3099999999999</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>972.46</v>
+        <v>970.1900000000001</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>880.8099999999999</v>
+        <v>880.2</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
         <v>950.9</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>999.05</v>
+        <v>994.47</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1029.05</v>
+        <v>1025.98</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>971.27</v>
+        <v>970.83</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1880.3</v>
+        <v>1891.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1826.61</v>
+        <v>1832.77</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1780.34</v>
+        <v>1784.69</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1726.56</v>
+        <v>1726.81</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2327.4</v>
+        <v>2327.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2374.22</v>
+        <v>2369.74</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2480.82</v>
+        <v>2474.8</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2847.52</v>
+        <v>2839.27</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1208.7</v>
+        <v>1194.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1189.84</v>
+        <v>1190.33</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1155.03</v>
+        <v>1156.59</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1130.33</v>
+        <v>1130.38</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>361.25</v>
+        <v>361.35</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>349.32</v>
+        <v>350.47</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>346.81</v>
+        <v>347.38</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.18</v>
+        <v>362.17</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>207.01</v>
+        <v>208.58</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>211.96</v>
+        <v>211.64</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>207.01</v>
+        <v>207.07</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>186.47</v>
+        <v>186.52</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2738,24 +2738,24 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1439</v>
+        <v>1420</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1429.44</v>
+        <v>1428.54</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1442.09</v>
+        <v>1441.23</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1490.92</v>
-      </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1488.95</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4106.4</v>
+        <v>4083.1</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4242.61</v>
+        <v>4227.42</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4250.67</v>
+        <v>4244.1</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3984.02</v>
+        <v>3983.03</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,24 +2826,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4099.9</v>
+        <v>4170.4</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4112.75</v>
+        <v>4118.24</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4036.9</v>
+        <v>4042.13</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4321.52</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4321.38</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11409</v>
+        <v>11474</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11661.45</v>
+        <v>11643.6</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11721.51</v>
+        <v>11711.81</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11872.49</v>
+        <v>11858.54</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>20-May-2026</t>
+          <t>21-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>197.12</v>
+        <v>199.74</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>196.08</v>
+        <v>196.43</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>201.28</v>
+        <v>201.22</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>225.68</v>
+        <v>225.17</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 21-May-2026  14:12:41    |    Closing Price Date: 21-May-2026</t>
+          <t>Scan Run: 22-May-2026  13:28:50    |    Closing Price Date: 22-May-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>21-May-2026  14:12:41</t>
+          <t>22-May-2026  13:28:50</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2697.6</v>
+        <v>2717.3</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2523.27</v>
+        <v>2541.75</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2340.23</v>
+        <v>2355.01</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2281.21</v>
+        <v>2286.92</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>1793.3</v>
+        <v>1786.9</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1713.46</v>
+        <v>1720.46</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1612.96</v>
+        <v>1619.78</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1477.98</v>
+        <v>1480.57</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8308.5</v>
+        <v>8362.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>7943.12</v>
+        <v>7983.06</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7745.19</v>
+        <v>7769.39</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7433.51</v>
+        <v>7445.22</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2598.8</v>
+        <v>2639.8</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>2538.64</v>
+        <v>2548.27</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2471.54</v>
+        <v>2478.14</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2475.69</v>
+        <v>2476.78</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,29 +934,29 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1253.3</v>
+        <v>1285.4</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1269.19</v>
+        <v>1270.73</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1282.63</v>
+        <v>1282.73</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1244.32</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1244.71</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>10667</v>
+        <v>10549.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10208.62</v>
+        <v>10241.08</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9882.17</v>
+        <v>9908.34</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>9310.02</v>
+        <v>9320.219999999999</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>907.65</v>
+        <v>916.55</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>922.7</v>
+        <v>922.11</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>923.17</v>
+        <v>922.91</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>939.45</v>
+        <v>939.3200000000001</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1752.2</v>
+        <v>1766</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1767.95</v>
+        <v>1767.77</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1799.84</v>
+        <v>1798.51</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1906.01</v>
+        <v>1906.51</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>420.4</v>
+        <v>416.55</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>429.13</v>
+        <v>427.93</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>432.16</v>
+        <v>431.55</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>409.87</v>
+        <v>409.68</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>296.4</v>
+        <v>295.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>296.63</v>
+        <v>296.54</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>307.31</v>
+        <v>306.85</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>319.54</v>
+        <v>319.32</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1885.3</v>
+        <v>1871.4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1859.96</v>
+        <v>1861.05</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1866.56</v>
+        <v>1866.75</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1913.12</v>
+        <v>1913.34</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5333</v>
+        <v>5331.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5506.13</v>
+        <v>5489.5</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>5629.73</v>
+        <v>5618.03</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5712.13</v>
+        <v>5708.95</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1401.9</v>
+        <v>1399.2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1354.77</v>
+        <v>1359</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1325.87</v>
+        <v>1328.74</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1394.12</v>
+        <v>1394.01</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>460.2</v>
+        <v>456.55</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>460.59</v>
+        <v>460.21</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>452.99</v>
+        <v>453.13</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>415.08</v>
+        <v>415.55</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1318.5</v>
+        <v>1307.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1302.17</v>
+        <v>1302.65</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1284.73</v>
+        <v>1285.61</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1260.1</v>
+        <v>1260.83</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>6892</v>
+        <v>6981.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>7055.39</v>
+        <v>7048.35</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>7126.81</v>
+        <v>7121.11</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>6861.43</v>
+        <v>6857.37</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>3154.5</v>
+        <v>3155.3</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2911.81</v>
+        <v>2935</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2831.86</v>
+        <v>2844.55</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2771.43</v>
+        <v>2774.97</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1168.2</v>
+        <v>1164</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1196.66</v>
+        <v>1193.55</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1277.37</v>
+        <v>1272.93</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1428.95</v>
+        <v>1426.07</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>759.15</v>
+        <v>766.8</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>772.3</v>
+        <v>771.78</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>799.49</v>
+        <v>798.21</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>883.62</v>
+        <v>882.58</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>614.35</v>
+        <v>616.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>607.71</v>
+        <v>608.5599999999999</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>623.09</v>
+        <v>622.84</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>684.49</v>
+        <v>684.27</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4969.5</v>
+        <v>4966</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5087.88</v>
+        <v>5076.28</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>5198.2</v>
+        <v>5189.1</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5172.54</v>
+        <v>5171.74</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1099.3</v>
+        <v>1109.2</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1052.75</v>
+        <v>1058.12</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1010.35</v>
+        <v>1014.23</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>884.49</v>
+        <v>886.86</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>2179</v>
+        <v>2203.6</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2250.41</v>
+        <v>2245.95</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2248.41</v>
+        <v>2246.66</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2315.25</v>
+        <v>2314.87</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1770,24 +1770,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1242.8</v>
+        <v>1264.3</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1263.08</v>
+        <v>1263.2</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1288.64</v>
+        <v>1287.68</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1336.72</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1335.96</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>308.05</v>
+        <v>301.7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>307.53</v>
+        <v>306.97</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>309.37</v>
+        <v>309.07</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>345.05</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>344.54</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>899.95</v>
+        <v>910.15</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>896.12</v>
+        <v>897.46</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>882.16</v>
+        <v>883.26</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>865.6900000000001</v>
+        <v>865.5</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,24 +1902,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1181.2</v>
+        <v>1174.5</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1179.22</v>
+        <v>1178.77</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1242.07</v>
+        <v>1239.42</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>1416.29</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1413.36</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1281.3</v>
+        <v>1285.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1269.12</v>
+        <v>1270.68</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1241.54</v>
+        <v>1243.26</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1167.94</v>
+        <v>1169.19</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,29 +1990,29 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>380.85</v>
+        <v>384.15</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>380.56</v>
+        <v>380.9</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>383.37</v>
+        <v>383.4</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>401.17</v>
+        <v>401.22</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -2034,29 +2034,29 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>3928.5</v>
+        <v>3926.6</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3948.01</v>
+        <v>3911.42</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3937.12</v>
+        <v>3900.12</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3847.38</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3813.45</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3099</v>
+        <v>3081.3</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3152.45</v>
+        <v>3145.67</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3196.4</v>
+        <v>3191.88</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>3315.49</v>
+        <v>3308.92</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>13010</v>
+        <v>12987</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>13212.49</v>
+        <v>13191.02</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>13469.98</v>
+        <v>13451.04</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>14163.83</v>
+        <v>14149.17</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>388.8</v>
+        <v>388.65</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>393.34</v>
+        <v>392.89</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>386.79</v>
+        <v>386.86</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>357.19</v>
+        <v>357.53</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1406.5</v>
+        <v>1423.1</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1423.71</v>
+        <v>1423.65</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1365.22</v>
+        <v>1367.49</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1272</v>
+        <v>1273.46</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,24 +2254,24 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>295.85</v>
+        <v>290</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>292.49</v>
+        <v>292.25</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>284.49</v>
+        <v>284.7</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>258.24</v>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>258.49</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>299.55</v>
+        <v>294.3</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>306.6</v>
+        <v>305.43</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>304.01</v>
+        <v>303.63</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>287.16</v>
+        <v>287.05</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1349.6</v>
+        <v>1354.5</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1372.14</v>
+        <v>1370.46</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1384.17</v>
+        <v>1383.01</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1407.53</v>
+        <v>1406.21</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1859.9</v>
+        <v>1870.7</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1860.59</v>
+        <v>1861.55</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1885.73</v>
+        <v>1885.14</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1885.66</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1886.95</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>914.75</v>
+        <v>941</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>953.3099999999999</v>
+        <v>952.14</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>970.1900000000001</v>
+        <v>969.05</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>880.2</v>
+        <v>881.17</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>950.9</v>
+        <v>949.2</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>994.47</v>
+        <v>990.15</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1025.98</v>
+        <v>1022.97</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>970.83</v>
+        <v>970.7</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1891.3</v>
+        <v>1844.6</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1832.77</v>
+        <v>1833.9</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1784.69</v>
+        <v>1787.04</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1726.81</v>
+        <v>1727.73</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2327.2</v>
+        <v>2317.3</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>2369.74</v>
+        <v>2364.75</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2474.8</v>
+        <v>2468.62</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2839.27</v>
+        <v>2833.52</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1194.9</v>
+        <v>1191.8</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1190.33</v>
+        <v>1190.47</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1156.59</v>
+        <v>1157.97</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1130.38</v>
+        <v>1131.68</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>361.35</v>
+        <v>363.35</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>350.47</v>
+        <v>351.69</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>347.38</v>
+        <v>348</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>362.17</v>
+        <v>362.18</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2675,9 +2675,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>208.58</v>
+        <v>209.19</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>211.64</v>
+        <v>211.41</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>207.07</v>
+        <v>207.15</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>186.52</v>
+        <v>186.84</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1420</v>
+        <v>1422.2</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1428.54</v>
+        <v>1427.94</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1441.23</v>
+        <v>1440.48</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1488.95</v>
+        <v>1488.76</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>4083.1</v>
+        <v>4079.8</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4227.42</v>
+        <v>4213.36</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>4244.1</v>
+        <v>4237.65</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>3983.03</v>
+        <v>3982.86</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>4170.4</v>
+        <v>4296.5</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4118.24</v>
+        <v>4135.22</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4042.13</v>
+        <v>4052.11</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>4321.38</v>
+        <v>4321.52</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>11474</v>
+        <v>11569</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>11643.6</v>
+        <v>11636.49</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>11711.81</v>
+        <v>11706.21</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>11858.54</v>
+        <v>11863.33</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,29 +2914,29 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>199.74</v>
+        <v>203.11</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>196.43</v>
+        <v>197.06</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>201.22</v>
+        <v>201.29</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>225.17</v>
+        <v>224.84</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-May-2026  13:58:07    |    Closing Price Date: 25-May-2026</t>
+          <t>Scan Run: 26-May-2026  13:52:00    |    Closing Price Date: 26-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-May-2026  13:58:07</t>
+          <t>26-May-2026  13:52:00</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 64.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 32 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 28 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2849.7</v>
+        <v>2969.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2571.08</v>
+        <v>2609</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2374.41</v>
+        <v>2397.74</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2286.93</v>
+        <v>2293.72</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1802.9</v>
+        <v>1811.2</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1728.31</v>
+        <v>1736.2</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1626.96</v>
+        <v>1634.19</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1481.79</v>
+        <v>1485.07</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8404</v>
+        <v>8258.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8023.15</v>
+        <v>8045.56</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7794.28</v>
+        <v>7812.49</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7451.93</v>
+        <v>7459.95</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2657.8</v>
+        <v>2647</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2558.7</v>
+        <v>2567.11</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2485.18</v>
+        <v>2491.53</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2479.56</v>
+        <v>2481.23</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1311.2</v>
+        <v>1299.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1274.59</v>
+        <v>1276.94</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1283.85</v>
+        <v>1284.46</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1244.76</v>
+        <v>1245.3</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10491</v>
+        <v>10593</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10264.88</v>
+        <v>10296.13</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9931.190000000001</v>
+        <v>9957.15</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9324.459999999999</v>
+        <v>9337.08</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>941.9</v>
+        <v>930.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>924</v>
+        <v>924.59</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>923.65</v>
+        <v>923.91</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>940.26</v>
+        <v>940.16</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1807.4</v>
+        <v>1800.7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1771.54</v>
+        <v>1774.32</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1798.86</v>
+        <v>1798.93</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1910.16</v>
+        <v>1909.07</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>421.85</v>
+        <v>420.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>427.35</v>
+        <v>426.66</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>431.17</v>
+        <v>430.73</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.34</v>
+        <v>409.45</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,29 +1157,29 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>308.25</v>
+        <v>304.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>297.65</v>
+        <v>298.31</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>306.91</v>
+        <v>306.82</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>319.08</v>
+        <v>318.94</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1874.8</v>
+        <v>1846.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1862.36</v>
+        <v>1860.89</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1867.07</v>
+        <v>1866.27</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1911.38</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1910.73</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5327</v>
+        <v>5338</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5474.02</v>
+        <v>5461.07</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5606.62</v>
+        <v>5596.09</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5707.13</v>
+        <v>5703.46</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1413.9</v>
+        <v>1417.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1364.23</v>
+        <v>1369.31</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1332.08</v>
+        <v>1335.43</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.3</v>
+        <v>1395.52</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>458</v>
+        <v>458.15</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>460</v>
+        <v>459.82</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>453.32</v>
+        <v>453.51</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>415.96</v>
+        <v>416.38</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1331.4</v>
+        <v>1327.9</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1305.39</v>
+        <v>1307.53</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1287.41</v>
+        <v>1289</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1260.79</v>
+        <v>1261.46</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7414</v>
+        <v>7376</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7083.18</v>
+        <v>7111.06</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7132.6</v>
+        <v>7142.14</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6858.44</v>
+        <v>6863.59</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3171.6</v>
+        <v>3165</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2957.54</v>
+        <v>2977.29</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2857.37</v>
+        <v>2869.44</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2778.01</v>
+        <v>2781.86</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1165.7</v>
+        <v>1161.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1190.9</v>
+        <v>1188.13</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1268.72</v>
+        <v>1264.53</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1423.18</v>
+        <v>1420.58</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>786.85</v>
+        <v>778.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>773.21</v>
+        <v>773.76</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>797.76</v>
+        <v>797.02</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>881.86</v>
+        <v>880.83</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>620</v>
+        <v>618.85</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>609.65</v>
+        <v>610.52</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>622.73</v>
+        <v>622.58</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>683.37</v>
+        <v>682.73</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4979</v>
+        <v>4983</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5067.01</v>
+        <v>5059.01</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5180.86</v>
+        <v>5173.1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5163.97</v>
+        <v>5162.17</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1099.6</v>
+        <v>1103.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1062.07</v>
+        <v>1066.05</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1017.58</v>
+        <v>1020.96</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>889.49</v>
+        <v>891.63</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2196.5</v>
+        <v>2209.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2241.24</v>
+        <v>2238.21</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2244.69</v>
+        <v>2243.31</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2313.57</v>
+        <v>2312.53</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1291.8</v>
+        <v>1279.1</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1265.92</v>
+        <v>1267.18</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1287.85</v>
+        <v>1287.5</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1335.49</v>
+        <v>1334.92</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>303.95</v>
+        <v>301.65</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>306.69</v>
+        <v>306.21</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>308.87</v>
+        <v>308.58</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>344.08</v>
+        <v>343.66</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>926.1</v>
+        <v>932.3</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>900.1799999999999</v>
+        <v>903.24</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>884.9400000000001</v>
+        <v>886.79</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>866.49</v>
+        <v>867.15</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1168.5</v>
+        <v>1167.7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1177.79</v>
+        <v>1176.83</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1236.64</v>
+        <v>1233.93</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1410.04</v>
+        <v>1407.63</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1289.4</v>
+        <v>1293.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1272.46</v>
+        <v>1274.47</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1245.07</v>
+        <v>1246.97</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1171.13</v>
+        <v>1172.35</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>392.85</v>
+        <v>388.65</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.04</v>
+        <v>382.67</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.77</v>
+        <v>383.96</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>401.15</v>
+        <v>401.02</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4033.4</v>
+        <v>4037.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3923.04</v>
+        <v>3933.97</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3905.34</v>
+        <v>3910.54</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3812.73</v>
+        <v>3814.97</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3139</v>
+        <v>3107.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3145.04</v>
+        <v>3141.44</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3189.81</v>
+        <v>3186.57</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3300.45</v>
+        <v>3298.53</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13170</v>
+        <v>13208</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13189.02</v>
+        <v>13190.83</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13440.02</v>
+        <v>13430.92</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14144.1</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>14134.79</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>390.05</v>
+        <v>389.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>392.62</v>
+        <v>392.34</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>386.99</v>
+        <v>387.1</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>357.69</v>
+        <v>358</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,24 +2213,24 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1413.6</v>
+        <v>1428.6</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1422.7</v>
+        <v>1423.26</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1369.3</v>
+        <v>1371.62</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1275.36</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1276.88</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>284.95</v>
+        <v>287.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>291.56</v>
+        <v>291.17</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>284.71</v>
+        <v>284.82</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>258.6</v>
+        <v>258.89</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>295.35</v>
+        <v>292.55</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>304.47</v>
+        <v>303.33</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>303.3</v>
+        <v>302.88</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.39</v>
+        <v>287.45</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1367</v>
+        <v>1356.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1370.13</v>
+        <v>1368.81</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1382.38</v>
+        <v>1381.35</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1406.19</v>
+        <v>1405.69</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,34 +2389,34 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1901.9</v>
+        <v>1883.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1865.4</v>
+        <v>1867.09</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1885.8</v>
+        <v>1885.69</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1888.14</v>
+        <v>1888.09</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>961.95</v>
+        <v>952.15</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>953.0700000000001</v>
+        <v>952.98</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>968.77</v>
+        <v>968.12</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>882.12</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>882.8200000000001</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>969.6</v>
+        <v>968.5</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>988.2</v>
+        <v>986.3200000000001</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1020.88</v>
+        <v>1018.82</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>970.47</v>
+        <v>970.45</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1840.6</v>
+        <v>1840.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1834.54</v>
+        <v>1835.13</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1789.14</v>
+        <v>1791.17</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1729.72</v>
+        <v>1730.83</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2308.2</v>
+        <v>2276.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2330.74</v>
+        <v>2325.55</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2430.6</v>
+        <v>2424.54</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2788.86</v>
+        <v>2783.76</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1187.2</v>
+        <v>1187.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1181.12</v>
+        <v>1181.74</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1149.78</v>
+        <v>1151.27</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1122.55</v>
+        <v>1123.2</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>373.25</v>
+        <v>385.6</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>353.75</v>
+        <v>356.78</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>348.99</v>
+        <v>350.43</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>362.29</v>
+        <v>362.53</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.22</v>
+        <v>210.47</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.29</v>
+        <v>211.22</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>207.27</v>
+        <v>207.4</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>187.16</v>
+        <v>187.39</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1435.5</v>
+        <v>1458.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1428.66</v>
+        <v>1431.52</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1440.28</v>
+        <v>1441.01</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1487.58</v>
+        <v>1487.3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4159.2</v>
+        <v>4105.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4208.2</v>
+        <v>4198.46</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4234.58</v>
+        <v>4229.53</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3983.66</v>
+        <v>3984.88</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4300</v>
+        <v>4239.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4150.91</v>
+        <v>4159.36</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4061.83</v>
+        <v>4068.8</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4315.14</v>
+        <v>4314.39</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,29 +2873,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11726</v>
+        <v>11623</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11645.02</v>
+        <v>11642.92</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11706.98</v>
+        <v>11703.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11862.54</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11860.15</v>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>206.84</v>
+        <v>203.73</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>197.99</v>
+        <v>198.54</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.51</v>
+        <v>201.6</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>224.45</v>
+        <v>224.25</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 26-May-2026  13:52:00    |    Closing Price Date: 26-May-2026</t>
+          <t>Scan Run: 27-May-2026  14:24:49    |    Closing Price Date: 27-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>52</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>26-May-2026  13:52:00</t>
+          <t>27-May-2026  14:24:49</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 28 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2969.3</v>
+        <v>2973.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2609</v>
+        <v>2643.68</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2397.74</v>
+        <v>2420.31</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2293.72</v>
+        <v>2300.48</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1811.2</v>
+        <v>1824.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1736.2</v>
+        <v>1744.61</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1634.19</v>
+        <v>1641.65</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1485.07</v>
+        <v>1488.44</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8258.5</v>
+        <v>8272.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8045.56</v>
+        <v>8067.18</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7812.49</v>
+        <v>7830.52</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7459.95</v>
+        <v>7468.04</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2647</v>
+        <v>2671.9</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2567.11</v>
+        <v>2577.09</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2491.53</v>
+        <v>2498.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2481.23</v>
+        <v>2483.13</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1299.3</v>
+        <v>1304.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1276.94</v>
+        <v>1279.53</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1284.46</v>
+        <v>1285.23</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1245.3</v>
+        <v>1245.89</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10593</v>
+        <v>10808.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10296.13</v>
+        <v>10344.93</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9957.15</v>
+        <v>9990.530000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9337.08</v>
+        <v>9351.719999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>930.2</v>
+        <v>931.15</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>924.59</v>
+        <v>925.21</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>923.91</v>
+        <v>924.1900000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>940.16</v>
+        <v>940.0700000000001</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1800.7</v>
+        <v>1809.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1774.32</v>
+        <v>1777.63</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1798.93</v>
+        <v>1799.33</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1909.07</v>
+        <v>1908.08</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>420.1</v>
+        <v>419.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>426.66</v>
+        <v>425.94</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>430.73</v>
+        <v>430.28</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.45</v>
+        <v>409.55</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,29 +1157,29 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>304.6</v>
+        <v>307.15</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>298.31</v>
+        <v>299.15</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>306.82</v>
+        <v>306.83</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>318.94</v>
+        <v>318.82</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1846.9</v>
+        <v>1852.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1860.89</v>
+        <v>1860.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1866.27</v>
+        <v>1865.72</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1910.73</v>
+        <v>1910.15</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5338</v>
+        <v>5335.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5461.07</v>
+        <v>5449.11</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5596.09</v>
+        <v>5585.87</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5703.46</v>
+        <v>5699.79</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1417.5</v>
+        <v>1418.2</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1369.31</v>
+        <v>1373.96</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1335.43</v>
+        <v>1338.68</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.52</v>
+        <v>1395.75</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>458.15</v>
+        <v>463.05</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>459.82</v>
+        <v>460.13</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>453.51</v>
+        <v>453.89</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>416.38</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>416.84</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1327.9</v>
+        <v>1319</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1307.53</v>
+        <v>1308.62</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1289</v>
+        <v>1290.17</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.46</v>
+        <v>1262.03</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7376</v>
+        <v>7419</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7111.06</v>
+        <v>7140.39</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7142.14</v>
+        <v>7153</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6863.59</v>
+        <v>6869.12</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3165</v>
+        <v>3170</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2977.29</v>
+        <v>2995.65</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2869.44</v>
+        <v>2881.22</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2781.86</v>
+        <v>2785.72</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1161.9</v>
+        <v>1165.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1188.13</v>
+        <v>1185.95</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1264.53</v>
+        <v>1260.64</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1420.58</v>
+        <v>1418.04</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,24 +1553,24 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>778.9</v>
+        <v>758.65</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>773.76</v>
+        <v>772.3200000000001</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>797.02</v>
+        <v>795.52</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>880.83</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>879.62</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -1597,24 +1597,24 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>618.85</v>
+        <v>609.6</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>610.52</v>
+        <v>610.4400000000001</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>622.58</v>
+        <v>622.0700000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>682.73</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>682</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4983</v>
+        <v>5075</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5059.01</v>
+        <v>5060.53</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5173.1</v>
+        <v>5169.25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5162.17</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5161.31</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1103.8</v>
+        <v>1149.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1066.05</v>
+        <v>1074.01</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1020.96</v>
+        <v>1026.01</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>891.63</v>
+        <v>894.2</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2209.4</v>
+        <v>2198.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2238.21</v>
+        <v>2234.41</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2243.31</v>
+        <v>2241.55</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2312.53</v>
+        <v>2311.4</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1279.1</v>
+        <v>1272.7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1267.18</v>
+        <v>1267.7</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1287.5</v>
+        <v>1286.92</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1334.92</v>
+        <v>1334.3</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>301.65</v>
+        <v>291.95</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>306.21</v>
+        <v>297.5</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>308.58</v>
+        <v>300.07</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>343.66</v>
+        <v>334.12</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
         <v>932.3</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>903.24</v>
+        <v>906.01</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>886.79</v>
+        <v>888.58</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>867.15</v>
+        <v>867.79</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1167.7</v>
+        <v>1159.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1176.83</v>
+        <v>1175.22</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1233.93</v>
+        <v>1231.03</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1407.63</v>
+        <v>1405.17</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1293.6</v>
+        <v>1309.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1274.47</v>
+        <v>1277.79</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1246.97</v>
+        <v>1249.42</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1172.35</v>
+        <v>1173.71</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>388.65</v>
+        <v>388.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.67</v>
+        <v>383.24</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.96</v>
+        <v>384.15</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>401.02</v>
+        <v>400.9</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4037.8</v>
+        <v>4047.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3933.97</v>
+        <v>3944.78</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3910.54</v>
+        <v>3915.91</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3814.97</v>
+        <v>3817.29</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3107.3</v>
+        <v>3121.6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3141.44</v>
+        <v>3139.55</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3186.57</v>
+        <v>3184.02</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3298.53</v>
+        <v>3296.77</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13208</v>
+        <v>13364</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13190.83</v>
+        <v>13207.32</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13430.92</v>
+        <v>13428.29</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14134.79</v>
+        <v>14127.12</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,24 +2169,24 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>389.7</v>
+        <v>398.15</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>392.34</v>
+        <v>392.89</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>387.1</v>
+        <v>387.53</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>358</v>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>358.4</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1428.6</v>
+        <v>1427.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1423.26</v>
+        <v>1423.66</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1371.62</v>
+        <v>1373.82</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1276.88</v>
+        <v>1278.38</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,29 +2257,29 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>287.5</v>
+        <v>274.05</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>291.17</v>
+        <v>289.54</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>284.82</v>
+        <v>284.4</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>258.89</v>
+        <v>259.04</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>292.55</v>
+        <v>300.15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>303.33</v>
+        <v>303.03</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>302.88</v>
+        <v>302.77</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.45</v>
+        <v>287.57</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1356.3</v>
+        <v>1350.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1368.81</v>
+        <v>1367.07</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1381.35</v>
+        <v>1380.14</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1405.69</v>
+        <v>1405.14</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,24 +2389,24 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1883.2</v>
+        <v>1864.5</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1867.09</v>
+        <v>1866.85</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1885.69</v>
+        <v>1884.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1888.09</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1887.86</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>952.15</v>
+        <v>963.2</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>952.98</v>
+        <v>953.96</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>968.12</v>
+        <v>967.9299999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>882.8200000000001</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>883.62</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>968.5</v>
+        <v>967.8</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>986.3200000000001</v>
+        <v>984.5599999999999</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1018.82</v>
+        <v>1016.82</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>970.45</v>
+        <v>970.42</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1840.8</v>
+        <v>1844.3</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1835.13</v>
+        <v>1836.01</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1791.17</v>
+        <v>1793.25</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1730.83</v>
+        <v>1731.95</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2276.2</v>
+        <v>2284.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2325.55</v>
+        <v>2321.61</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2424.54</v>
+        <v>2419.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2783.76</v>
+        <v>2778.79</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1187.6</v>
+        <v>1204.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1181.74</v>
+        <v>1183.91</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1151.27</v>
+        <v>1153.36</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1123.2</v>
+        <v>1124.01</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>385.6</v>
+        <v>400.95</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>356.78</v>
+        <v>360.94</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>350.43</v>
+        <v>352.34</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>362.53</v>
+        <v>362.59</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.47</v>
+        <v>214.7</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.22</v>
+        <v>211.55</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>207.4</v>
+        <v>207.68</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>187.39</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>187.66</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1458.7</v>
+        <v>1455.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1431.52</v>
+        <v>1433.81</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1441.01</v>
+        <v>1441.58</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1487.3</v>
+        <v>1486.98</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4105.9</v>
+        <v>4137.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4198.46</v>
+        <v>4192.69</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4229.53</v>
+        <v>4225.94</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3984.88</v>
+        <v>3986.4</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4239.6</v>
+        <v>4248.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4159.36</v>
+        <v>4167.86</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4068.8</v>
+        <v>4075.85</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4314.39</v>
+        <v>4313.73</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,24 +2873,24 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11623</v>
+        <v>11689</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11642.92</v>
+        <v>11647.31</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11703.69</v>
+        <v>11703.11</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11860.15</v>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>11858.45</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
@@ -2917,29 +2917,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>27-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>203.73</v>
+        <v>201.58</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>198.54</v>
+        <v>198.83</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>201.6</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>224.25</v>
+        <v>224.02</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 27-May-2026  14:24:49    |    Closing Price Date: 27-May-2026</t>
+          <t>Scan Run: 28-May-2026  14:35:05    |    Closing Price Date: 27-May-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>54</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27-May-2026  14:24:49</t>
+          <t>28-May-2026  14:35:05</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>2420.31</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2300.48</v>
+        <v>2300.33</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1641.65</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1488.44</v>
+        <v>1488.54</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         <v>8067.18</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7830.52</v>
+        <v>7830.53</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7468.04</v>
+        <v>7471.38</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>2498.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2483.13</v>
+        <v>2482.55</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1285.23</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1245.89</v>
+        <v>1245.94</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>9990.530000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9351.719999999999</v>
+        <v>9347.860000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>924.1900000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>940.0700000000001</v>
+        <v>940.24</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1799.33</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1908.08</v>
+        <v>1908.03</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>430.28</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.55</v>
+        <v>409.38</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>306.83</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>318.82</v>
+        <v>318.84</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1865.72</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1910.15</v>
+        <v>1909.86</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>5585.87</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5699.79</v>
+        <v>5696.67</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1338.68</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.75</v>
+        <v>1396.07</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>453.89</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>416.84</v>
+        <v>416.88</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1290.17</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1262.03</v>
+        <v>1261.96</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>7153</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6869.12</v>
+        <v>6868.01</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2881.22</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2785.72</v>
+        <v>2785.69</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>1260.64</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1418.04</v>
+        <v>1418.69</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>795.52</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>879.62</v>
+        <v>879.74</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>622.0700000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>682</v>
+        <v>681.8099999999999</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>5169.25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5161.31</v>
+        <v>5159.79</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1026.01</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>894.2</v>
+        <v>894.22</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>2241.55</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2311.4</v>
+        <v>2309.96</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1286.92</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1334.3</v>
+        <v>1333.95</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>300.07</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>334.12</v>
+        <v>333.98</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>888.58</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>867.79</v>
+        <v>866.74</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1231.03</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1405.17</v>
+        <v>1405.58</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1249.42</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1173.71</v>
+        <v>1173.94</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>384.15</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>400.9</v>
+        <v>401.06</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>3915.91</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3817.29</v>
+        <v>3817.21</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>3184.02</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3296.77</v>
+        <v>3294.95</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>13428.29</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14127.12</v>
+        <v>14128.13</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>387.53</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>358.4</v>
+        <v>358.78</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>1373.82</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1278.38</v>
+        <v>1278.51</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>284.4</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.04</v>
+        <v>259.16</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>302.77</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.57</v>
+        <v>287.73</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1380.14</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1405.14</v>
+        <v>1405.16</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1884.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1887.86</v>
+        <v>1887.82</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>967.9299999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>883.62</v>
+        <v>883.75</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1016.82</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>970.42</v>
+        <v>970.34</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1793.25</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.95</v>
+        <v>1731.41</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>2419.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2778.79</v>
+        <v>2777.49</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1153.36</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.01</v>
+        <v>1124.17</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         <v>360.94</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>352.34</v>
+        <v>352.99</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>362.59</v>
+        <v>425.52</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2678,9 +2678,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J45" s="13" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>207.68</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>187.66</v>
+        <v>187.67</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1441.58</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1486.98</v>
+        <v>1488.68</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>4225.94</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3986.4</v>
+        <v>3985.91</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>4075.85</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4313.73</v>
+        <v>4309.42</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>11703.11</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11858.45</v>
+        <v>11850.58</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>201.6</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>224.02</v>
+        <v>224.31</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -89,7 +89,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,7 +99,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-May-2026  14:35:05    |    Closing Price Date: 27-May-2026</t>
+          <t>Scan Run: 29-May-2026  13:57:24    |    Closing Price Date: 29-May-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>50</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-May-2026  14:35:05</t>
+          <t>29-May-2026  13:57:24</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 19 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 24 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2973.1</v>
+        <v>2937.4</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2643.68</v>
+        <v>2671.65</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2420.31</v>
+        <v>2440.58</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2300.33</v>
+        <v>2304.94</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1824.5</v>
+        <v>1804.6</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1744.61</v>
+        <v>1750.32</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1641.65</v>
+        <v>1648.04</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1488.54</v>
+        <v>1491.59</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8272.5</v>
+        <v>8176.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8067.18</v>
+        <v>8077.59</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7830.53</v>
+        <v>7844.09</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7471.38</v>
+        <v>7480.39</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2671.9</v>
+        <v>2671.6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2577.09</v>
+        <v>2586.09</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2498.6</v>
+        <v>2505.39</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2482.55</v>
+        <v>2484.5</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1304.1</v>
+        <v>1286.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1279.53</v>
+        <v>1280.2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1285.23</v>
+        <v>1285.28</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1245.94</v>
+        <v>1247.09</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10808.5</v>
+        <v>10460</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10344.93</v>
+        <v>10355.89</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9990.530000000001</v>
+        <v>10008.94</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9347.860000000001</v>
+        <v>9360.33</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,29 +1025,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>931.15</v>
+        <v>908.25</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>925.21</v>
+        <v>923.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>924.1900000000001</v>
+        <v>923.5700000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>940.24</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>939.8099999999999</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1809.1</v>
+        <v>1783.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1777.63</v>
+        <v>1778.2</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1799.33</v>
+        <v>1798.72</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1908.03</v>
+        <v>1905.99</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>419.1</v>
+        <v>410.75</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>425.94</v>
+        <v>424.49</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>430.28</v>
+        <v>429.51</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.38</v>
+        <v>409.77</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,29 +1157,29 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>307.15</v>
+        <v>298.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>299.15</v>
+        <v>299.05</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>306.83</v>
+        <v>306.49</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>318.84</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>318.75</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1852.2</v>
+        <v>1829</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1860.06</v>
+        <v>1857.1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1865.72</v>
+        <v>1864.28</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1909.86</v>
+        <v>1908.03</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5335.5</v>
+        <v>5204.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5449.11</v>
+        <v>5425.81</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5585.87</v>
+        <v>5570.91</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5696.67</v>
+        <v>5689.45</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1418.2</v>
+        <v>1401</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1373.96</v>
+        <v>1376.54</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1338.68</v>
+        <v>1341.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1396.07</v>
+        <v>1395.34</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>463.05</v>
+        <v>457.9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>460.13</v>
+        <v>459.92</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>453.89</v>
+        <v>454.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>416.88</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>417.34</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1319</v>
+        <v>1303.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1308.62</v>
+        <v>1308.14</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1290.17</v>
+        <v>1290.7</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.96</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1261.01</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7419</v>
+        <v>7177</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7140.39</v>
+        <v>7143.88</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7153</v>
+        <v>7153.94</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6868.01</v>
+        <v>6875.02</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3170</v>
+        <v>3122.4</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2995.65</v>
+        <v>3007.72</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2881.22</v>
+        <v>2890.68</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2785.69</v>
+        <v>2789.04</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1165.2</v>
+        <v>1183.8</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1185.95</v>
+        <v>1185.75</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1260.64</v>
+        <v>1257.62</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1418.69</v>
+        <v>1415.8</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>758.65</v>
+        <v>744.55</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>772.3200000000001</v>
+        <v>769.67</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>795.52</v>
+        <v>793.52</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>879.74</v>
+        <v>878.48</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>609.6</v>
+        <v>594.8</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>610.4400000000001</v>
+        <v>608.95</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>622.0700000000001</v>
+        <v>621</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>681.8099999999999</v>
+        <v>681.12</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5075</v>
+        <v>4903</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5060.53</v>
+        <v>5045.53</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5169.25</v>
+        <v>5158.81</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5159.79</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5158.86</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1149.7</v>
+        <v>1126.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1074.01</v>
+        <v>1079.03</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1026.01</v>
+        <v>1029.95</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>894.22</v>
+        <v>897.1799999999999</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2198.4</v>
+        <v>2153.5</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2234.41</v>
+        <v>2226.71</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2241.55</v>
+        <v>2238.09</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2309.96</v>
+        <v>2306.45</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,24 +1773,24 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1272.7</v>
+        <v>1256.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1267.7</v>
+        <v>1266.63</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1286.92</v>
+        <v>1285.73</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1333.95</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1333.99</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>291.95</v>
+        <v>286.9</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>297.5</v>
+        <v>296.49</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>300.07</v>
+        <v>299.55</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>333.98</v>
+        <v>333.56</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>932.3</v>
+        <v>914.35</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>906.01</v>
+        <v>906.8</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>888.58</v>
+        <v>889.59</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>866.74</v>
+        <v>867.72</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1159.9</v>
+        <v>1160.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1175.22</v>
+        <v>1173.86</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1231.03</v>
+        <v>1228.28</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1405.58</v>
+        <v>1401.39</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1309.3</v>
+        <v>1278</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1277.79</v>
+        <v>1277.81</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1249.42</v>
+        <v>1250.54</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1173.94</v>
+        <v>1174.91</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>388.7</v>
+        <v>384.2</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>383.24</v>
+        <v>383.33</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>384.15</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>401.06</v>
+        <v>401.08</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4047.5</v>
+        <v>4076.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3944.78</v>
+        <v>3957.32</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3915.91</v>
+        <v>3922.21</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3817.21</v>
+        <v>3822.19</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3121.6</v>
+        <v>3045.6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3139.55</v>
+        <v>3130.61</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3184.02</v>
+        <v>3178.59</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3294.95</v>
+        <v>3291.05</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13364</v>
+        <v>13127</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13207.32</v>
+        <v>13199.67</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13428.29</v>
+        <v>13416.48</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14128.13</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>14113.84</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2169,29 +2169,29 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>398.15</v>
+        <v>386.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>392.89</v>
+        <v>392.32</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>387.53</v>
+        <v>387.5</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>358.78</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>359.21</v>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -2213,24 +2213,24 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1427.5</v>
+        <v>1421.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1423.66</v>
+        <v>1423.46</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1373.82</v>
+        <v>1375.69</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1278.51</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1279.55</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>274.05</v>
+        <v>265.4</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>289.54</v>
+        <v>287.24</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>284.4</v>
+        <v>283.65</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.16</v>
+        <v>259.29</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>300.15</v>
+        <v>290.55</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>303.03</v>
+        <v>301.84</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>302.77</v>
+        <v>302.29</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.73</v>
+        <v>287.59</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1350.5</v>
+        <v>1321.2</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1367.07</v>
+        <v>1362.7</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1380.14</v>
+        <v>1377.83</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1405.16</v>
+        <v>1404.42</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1864.5</v>
+        <v>1830.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1866.85</v>
+        <v>1863.35</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1884.86</v>
+        <v>1882.72</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1887.82</v>
+        <v>1887.26</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>963.2</v>
+        <v>947.15</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>953.96</v>
+        <v>953.3099999999999</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>967.9299999999999</v>
+        <v>967.11</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>883.75</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>884.5700000000001</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>967.8</v>
+        <v>964.4</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>984.5599999999999</v>
+        <v>982.64</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1016.82</v>
+        <v>1014.77</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>970.34</v>
@@ -2521,24 +2521,24 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1844.3</v>
+        <v>1799.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1836.01</v>
+        <v>1832.5</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.25</v>
+        <v>1793.49</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.41</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1731</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2284.2</v>
+        <v>2258.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2321.61</v>
+        <v>2315.64</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2419.04</v>
+        <v>2412.76</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2777.49</v>
+        <v>2768.61</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1204.6</v>
+        <v>1178.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1183.91</v>
+        <v>1183.39</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1153.36</v>
+        <v>1154.34</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.17</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1124.64</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>400.95</v>
+        <v>393.9</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>360.94</v>
+        <v>364.08</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>352.99</v>
+        <v>354.6</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>425.52</v>
+        <v>425.14</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>214.7</v>
+        <v>208.02</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.55</v>
+        <v>211.21</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>207.68</v>
+        <v>207.7</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>187.67</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>187.93</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1455.6</v>
+        <v>1483.9</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1433.81</v>
+        <v>1438.58</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1441.58</v>
+        <v>1443.24</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1488.68</v>
+        <v>1487.82</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4137.9</v>
+        <v>4074.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4192.69</v>
+        <v>4181.47</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4225.94</v>
+        <v>4220.01</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3985.91</v>
+        <v>3986.29</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4248.6</v>
+        <v>4224</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4167.86</v>
+        <v>4173.2</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4075.85</v>
+        <v>4081.66</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4309.42</v>
+        <v>4308.3</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,24 +2873,24 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11689</v>
+        <v>11482</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11647.31</v>
+        <v>11631.57</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11703.11</v>
+        <v>11694.44</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11850.58</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11846.16</v>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
@@ -2917,29 +2917,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>27-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>201.58</v>
+        <v>204.25</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>198.83</v>
+        <v>199.35</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.6</v>
+        <v>201.7</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>224.31</v>
+        <v>224.19</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 29-May-2026  13:57:24    |    Closing Price Date: 29-May-2026</t>
+          <t>Scan Run: 01-Jun-2026  16:35:34    |    Closing Price Date: 01-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>48</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>29-May-2026  13:57:24</t>
+          <t>01-Jun-2026  16:35:34</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 19 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 19 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2937.4</v>
+        <v>2909.4</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2671.65</v>
+        <v>2719.98</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2440.58</v>
+        <v>2478.98</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2304.94</v>
+        <v>2314.66</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1804.6</v>
+        <v>1783.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1750.32</v>
+        <v>1753.48</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1648.04</v>
+        <v>1653.35</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1491.59</v>
+        <v>1493.93</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8176.5</v>
+        <v>8108.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8077.59</v>
+        <v>8096.54</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7844.09</v>
+        <v>7870.46</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7480.39</v>
+        <v>7486.95</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2671.6</v>
+        <v>2632.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2586.09</v>
+        <v>2597.9</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2505.39</v>
+        <v>2516.64</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2484.5</v>
+        <v>2488.12</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,29 +937,29 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1286.6</v>
+        <v>1275.9</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1280.2</v>
+        <v>1279.79</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1285.28</v>
+        <v>1284.91</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1247.09</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1247.32</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10460</v>
+        <v>10376</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10355.89</v>
+        <v>10275.92</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10008.94</v>
+        <v>9924.549999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9360.33</v>
+        <v>9255.83</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>908.25</v>
+        <v>889.05</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>923.6</v>
+        <v>920.77</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>923.5700000000001</v>
+        <v>922.47</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>939.8099999999999</v>
+        <v>938.85</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1783.6</v>
+        <v>1758.9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1778.2</v>
+        <v>1778.81</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1798.72</v>
+        <v>1797.51</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1905.99</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1902.79</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>410.75</v>
+        <v>407.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>424.49</v>
+        <v>422.31</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>429.51</v>
+        <v>428.23</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.77</v>
+        <v>409.96</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1138,9 +1138,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>298.1</v>
+        <v>296.85</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>299.05</v>
+        <v>299.47</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>306.49</v>
+        <v>306.12</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>318.75</v>
+        <v>318.22</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1829</v>
+        <v>1810.6</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1857.1</v>
+        <v>1852.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1864.28</v>
+        <v>1861.69</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1908.03</v>
+        <v>1904.59</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5204.5</v>
+        <v>5157.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5425.81</v>
+        <v>5400.26</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5570.91</v>
+        <v>5554.7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5689.45</v>
+        <v>5682.7</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1401</v>
+        <v>1390.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1376.54</v>
+        <v>1381.3</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1341.12</v>
+        <v>1345.93</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.34</v>
+        <v>1396.06</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1314,9 +1314,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>457.9</v>
+        <v>472.6</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>459.92</v>
+        <v>461.35</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>454.04</v>
+        <v>455.1</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>417.34</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>418.44</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1303.5</v>
+        <v>1290.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1308.14</v>
+        <v>1306.45</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1290.7</v>
+        <v>1290.69</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.01</v>
+        <v>1261.25</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7177</v>
+        <v>7100.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7143.88</v>
+        <v>7139.75</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7153.94</v>
+        <v>7151.84</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6875.02</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6885.97</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3122.4</v>
+        <v>3102.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3007.72</v>
+        <v>3016.75</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2890.68</v>
+        <v>2898.99</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2789.04</v>
+        <v>2789.09</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,24 +1509,24 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1183.8</v>
+        <v>1195.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1185.75</v>
+        <v>1185.02</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1257.62</v>
+        <v>1251.72</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1415.8</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1408.3</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>744.55</v>
+        <v>742.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>769.67</v>
+        <v>766.04</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>793.52</v>
+        <v>790.1900000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>878.48</v>
+        <v>874.88</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>594.8</v>
+        <v>586.55</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>608.95</v>
+        <v>606.8099999999999</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>621</v>
+        <v>619.65</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>681.12</v>
+        <v>679.92</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4903</v>
+        <v>4819.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5045.53</v>
+        <v>5024.04</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5158.81</v>
+        <v>5145.52</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5158.86</v>
+        <v>5155.74</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1126.7</v>
+        <v>1141.3</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1079.03</v>
+        <v>1090.86</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1029.95</v>
+        <v>1038.8</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>897.1799999999999</v>
+        <v>902.76</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2153.5</v>
+        <v>2084.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2226.71</v>
+        <v>2210.34</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2238.09</v>
+        <v>2230.5</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2306.45</v>
+        <v>2302.79</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1256.4</v>
+        <v>1239.7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1266.63</v>
+        <v>1264.06</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1285.73</v>
+        <v>1283.92</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1333.99</v>
+        <v>1331.15</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>286.9</v>
+        <v>279.65</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>296.49</v>
+        <v>294.45</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>299.55</v>
+        <v>298.48</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>333.56</v>
+        <v>332.43</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>914.35</v>
+        <v>901.15</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>906.8</v>
+        <v>908.3200000000001</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>889.59</v>
+        <v>891.62</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>867.72</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>868.39</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1905,24 +1905,24 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1160.9</v>
+        <v>1202.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1173.86</v>
+        <v>1175.39</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1228.28</v>
+        <v>1224.69</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1401.39</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1395.03</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1278</v>
+        <v>1299.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1277.81</v>
+        <v>1282.32</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1250.54</v>
+        <v>1254.62</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1174.91</v>
+        <v>1177.01</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,29 +1993,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>384.2</v>
+        <v>377.4</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>383.33</v>
+        <v>383.19</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>384.15</v>
+        <v>384.05</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>401.08</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>400.56</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4076.5</v>
+        <v>4010.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3957.32</v>
+        <v>3970.43</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3922.21</v>
+        <v>3930.45</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3822.19</v>
+        <v>3825.48</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3045.6</v>
+        <v>2970.2</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3130.61</v>
+        <v>3113.93</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3178.59</v>
+        <v>3168.16</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3291.05</v>
+        <v>3284.08</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13127</v>
+        <v>12946</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13199.67</v>
+        <v>13175.51</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13416.48</v>
+        <v>13398.03</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14113.84</v>
+        <v>14087.44</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>386.9</v>
+        <v>378.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>392.32</v>
+        <v>391.44</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>387.5</v>
+        <v>387.54</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>359.21</v>
+        <v>360.01</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1421.5</v>
+        <v>1391.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1423.46</v>
+        <v>1420.74</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1375.69</v>
+        <v>1378.26</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1279.55</v>
+        <v>1282.46</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>265.4</v>
+        <v>264.3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>287.24</v>
+        <v>283.85</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>283.65</v>
+        <v>282.52</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.29</v>
+        <v>259.32</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>290.55</v>
+        <v>286.15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>301.84</v>
+        <v>300.12</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>302.29</v>
+        <v>301.57</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.59</v>
+        <v>287.53</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2326,9 +2326,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1321.2</v>
+        <v>1320</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1362.7</v>
+        <v>1357.34</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1377.83</v>
+        <v>1374.49</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1404.42</v>
+        <v>1402.47</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1830.1</v>
+        <v>1812.5</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1863.35</v>
+        <v>1858.5</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1882.72</v>
+        <v>1879.96</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1887.26</v>
+        <v>1886.99</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>947.15</v>
+        <v>919.05</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>953.3099999999999</v>
+        <v>950.04</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>967.11</v>
+        <v>965.23</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>884.5700000000001</v>
+        <v>885.75</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>964.4</v>
+        <v>954.1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>982.64</v>
+        <v>979.92</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1014.77</v>
+        <v>1012.39</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>970.34</v>
+        <v>969.72</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1799.2</v>
+        <v>1796.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1832.5</v>
+        <v>1829.07</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.49</v>
+        <v>1793.6</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731</v>
+        <v>1730.03</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2258.9</v>
+        <v>2297.4</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2315.64</v>
+        <v>2310.98</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2412.76</v>
+        <v>2403.35</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2768.61</v>
+        <v>2754.58</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1178.4</v>
+        <v>1143.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1183.39</v>
+        <v>1181.18</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1154.34</v>
+        <v>1155.76</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.64</v>
+        <v>1124.63</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>393.9</v>
+        <v>384.9</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>364.08</v>
+        <v>369.18</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>354.6</v>
+        <v>357.52</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>425.14</v>
+        <v>423.94</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>208.02</v>
+        <v>210.57</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.21</v>
+        <v>211.4</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>207.7</v>
+        <v>208.06</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>187.93</v>
+        <v>188.49</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1483.9</v>
+        <v>1543.2</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1438.58</v>
+        <v>1448.55</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1443.24</v>
+        <v>1447.16</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1487.82</v>
+        <v>1485.27</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4074.9</v>
+        <v>4024.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4181.47</v>
+        <v>4166.53</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4220.01</v>
+        <v>4212.35</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3986.29</v>
+        <v>3985.03</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,24 +2829,24 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4224</v>
+        <v>4157.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4173.2</v>
+        <v>4171.69</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4081.66</v>
+        <v>4084.63</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4308.3</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4310.04</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11482</v>
+        <v>11232</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11631.57</v>
+        <v>11593.51</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11694.44</v>
+        <v>11676.31</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11846.16</v>
+        <v>11829.08</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>204.25</v>
+        <v>206.41</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>199.35</v>
+        <v>200.23</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.7</v>
+        <v>201.89</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>224.19</v>
+        <v>222.99</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-Jun-2026  16:35:34    |    Closing Price Date: 01-Jun-2026</t>
+          <t>Scan Run: 02-Jun-2026  14:49:15    |    Closing Price Date: 02-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>40</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>46</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-Jun-2026  16:35:34</t>
+          <t>02-Jun-2026  14:49:15</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 18 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 19 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 20 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2909.4</v>
+        <v>2968.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2719.98</v>
+        <v>2743.61</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2478.98</v>
+        <v>2498.16</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2314.66</v>
+        <v>2321.16</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1783.5</v>
+        <v>1814.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1753.48</v>
+        <v>1764.93</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1653.35</v>
+        <v>1666.03</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1493.93</v>
+        <v>1500.37</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,24 +849,24 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8108.5</v>
+        <v>8089.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8096.54</v>
+        <v>8095.87</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7870.46</v>
+        <v>7879.05</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7486.95</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>7492.95</v>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2632.4</v>
+        <v>2660.7</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2597.9</v>
+        <v>2603.88</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2516.64</v>
+        <v>2522.29</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2488.12</v>
+        <v>2489.83</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1275.9</v>
+        <v>1251.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1279.79</v>
+        <v>1277.06</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1284.91</v>
+        <v>1283.59</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1247.32</v>
+        <v>1247.36</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10376</v>
+        <v>10281</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10275.92</v>
+        <v>10276.4</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9924.549999999999</v>
+        <v>9938.530000000001</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9255.83</v>
+        <v>9266.030000000001</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>889.05</v>
+        <v>882</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>920.77</v>
+        <v>917.08</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>922.47</v>
+        <v>920.88</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>938.85</v>
+        <v>938.28</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1758.9</v>
+        <v>1741.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1778.81</v>
+        <v>1775.25</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1797.51</v>
+        <v>1795.31</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1902.79</v>
+        <v>1901.18</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>407.2</v>
+        <v>407.85</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>422.31</v>
+        <v>420.94</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>428.23</v>
+        <v>427.43</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.96</v>
+        <v>409.94</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>296.85</v>
+        <v>294.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>299.47</v>
+        <v>298.99</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>306.12</v>
+        <v>305.66</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>318.22</v>
+        <v>317.99</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1810.6</v>
+        <v>1814.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1852.06</v>
+        <v>1848.46</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1861.69</v>
+        <v>1859.83</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1904.59</v>
+        <v>1903.69</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5157.5</v>
+        <v>5117</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5400.26</v>
+        <v>5373.28</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5554.7</v>
+        <v>5537.53</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5682.7</v>
+        <v>5677.07</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1390.3</v>
+        <v>1379.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1381.3</v>
+        <v>1381.11</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1345.93</v>
+        <v>1347.24</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1396.06</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1395.89</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472.6</v>
+        <v>472.15</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>461.35</v>
+        <v>462.38</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>455.1</v>
+        <v>455.77</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>418.44</v>
+        <v>418.97</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1290.4</v>
+        <v>1274</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1306.45</v>
+        <v>1304.09</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1290.69</v>
+        <v>1291.03</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.25</v>
+        <v>1261.94</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7100.5</v>
+        <v>7141.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7139.75</v>
+        <v>7139.91</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7151.84</v>
+        <v>7151.44</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6885.97</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>6888.52</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3102.6</v>
+        <v>3097.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3016.75</v>
+        <v>3024.45</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2898.99</v>
+        <v>2906.78</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2789.09</v>
+        <v>2792.16</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1195.1</v>
+        <v>1243.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1185.02</v>
+        <v>1190.59</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1251.72</v>
+        <v>1251.39</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1408.3</v>
+        <v>1406.66</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>742.7</v>
+        <v>748.25</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>766.04</v>
+        <v>764.34</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>790.1900000000001</v>
+        <v>788.55</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>874.88</v>
+        <v>873.62</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>586.55</v>
+        <v>579.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>606.8099999999999</v>
+        <v>604.25</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>619.65</v>
+        <v>618.09</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>679.92</v>
+        <v>678.92</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4819.9</v>
+        <v>4875</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5024.04</v>
+        <v>5010.87</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5145.52</v>
+        <v>5131.63</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5155.74</v>
+        <v>5152.11</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1141.3</v>
+        <v>1146.3</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1090.86</v>
+        <v>1096.14</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1038.8</v>
+        <v>1043.01</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>902.76</v>
+        <v>905.1799999999999</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2084.3</v>
+        <v>2093.7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2210.34</v>
+        <v>2199.23</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2230.5</v>
+        <v>2225.13</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2302.79</v>
+        <v>2300.71</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1239.7</v>
+        <v>1226.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1264.06</v>
+        <v>1260.85</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1283.92</v>
+        <v>1281.18</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1331.15</v>
+        <v>1329.53</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>279.65</v>
+        <v>283.25</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>294.45</v>
+        <v>293.39</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>298.48</v>
+        <v>297.88</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>332.43</v>
+        <v>331.94</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>901.15</v>
+        <v>912.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>908.3200000000001</v>
+        <v>908.71</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>891.62</v>
+        <v>892.4400000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>868.39</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>868.83</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1905,29 +1905,29 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1202.5</v>
+        <v>1270.8</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1175.39</v>
+        <v>1184.48</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1224.69</v>
+        <v>1226.5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1395.03</v>
+        <v>1393.79</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1299.4</v>
+        <v>1310.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1282.32</v>
+        <v>1285.04</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1254.62</v>
+        <v>1256.83</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1177.01</v>
+        <v>1178.34</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>377.4</v>
+        <v>379.05</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>383.19</v>
+        <v>382.8</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>384.05</v>
+        <v>383.85</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>400.56</v>
+        <v>400.34</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4010.8</v>
+        <v>4000.9</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3970.43</v>
+        <v>3973.33</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3930.45</v>
+        <v>3933.21</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3825.48</v>
+        <v>3827.23</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2970.2</v>
+        <v>2998.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3113.93</v>
+        <v>3102.92</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3168.16</v>
+        <v>3161.5</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3284.08</v>
+        <v>3281.23</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>12946</v>
+        <v>13022</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13175.51</v>
+        <v>13160.89</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13398.03</v>
+        <v>13383.28</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14087.44</v>
+        <v>14076.84</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>378.7</v>
+        <v>367.4</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>391.44</v>
+        <v>389.15</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>387.54</v>
+        <v>386.75</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>360.01</v>
+        <v>360.08</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1391.8</v>
+        <v>1398.7</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1420.74</v>
+        <v>1418.64</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1378.26</v>
+        <v>1379.06</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1282.46</v>
+        <v>1283.62</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>264.3</v>
+        <v>265.05</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>283.85</v>
+        <v>282.06</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>282.52</v>
+        <v>281.84</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.32</v>
+        <v>259.37</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>286.15</v>
+        <v>282.15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>300.12</v>
+        <v>298.41</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>301.57</v>
+        <v>300.8</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.53</v>
+        <v>287.48</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1320</v>
+        <v>1314.6</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1357.34</v>
+        <v>1353.27</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1374.49</v>
+        <v>1372.14</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1402.47</v>
+        <v>1401.6</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1812.5</v>
+        <v>1801.7</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1858.5</v>
+        <v>1852.93</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1879.96</v>
+        <v>1876.19</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1886.99</v>
+        <v>1885.91</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>919.05</v>
+        <v>911.7</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>950.04</v>
+        <v>947.05</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>965.23</v>
+        <v>962.96</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>885.75</v>
+        <v>886.76</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>954.1</v>
+        <v>956.65</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>979.92</v>
+        <v>976.52</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1012.39</v>
+        <v>1008.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>969.72</v>
+        <v>969.5700000000001</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,29 +2521,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1796.5</v>
+        <v>1789.9</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1829.07</v>
+        <v>1825.93</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.6</v>
+        <v>1795.23</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1730.03</v>
+        <v>1731.74</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -2565,29 +2565,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2297.4</v>
+        <v>2446.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2310.98</v>
+        <v>2323.93</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2403.35</v>
+        <v>2405.06</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2754.58</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2751.52</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1143.3</v>
+        <v>1154.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1181.18</v>
+        <v>1178.66</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1155.76</v>
+        <v>1155.72</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.63</v>
+        <v>1124.93</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>384.9</v>
+        <v>390.2</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>369.18</v>
+        <v>371.18</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>357.52</v>
+        <v>358.8</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>423.94</v>
+        <v>423.61</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.57</v>
+        <v>210.6</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.4</v>
+        <v>211.32</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.06</v>
+        <v>208.16</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>188.49</v>
+        <v>188.71</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1543.2</v>
+        <v>1571.4</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1448.55</v>
+        <v>1461.78</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1447.16</v>
+        <v>1452.52</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1485.27</v>
+        <v>1485.85</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4024.6</v>
+        <v>4078.1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4166.53</v>
+        <v>4154.25</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4212.35</v>
+        <v>4204.02</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3985.03</v>
+        <v>3987.45</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,24 +2829,24 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4157.3</v>
+        <v>4210.4</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4171.69</v>
+        <v>4175.37</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4084.63</v>
+        <v>4089.56</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4310.04</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4309.05</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11232</v>
+        <v>11165</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11593.51</v>
+        <v>11555.64</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11676.31</v>
+        <v>11655.76</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11829.08</v>
+        <v>11821.02</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>02-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>206.41</v>
+        <v>209.84</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>200.23</v>
+        <v>201.15</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.89</v>
+        <v>202.2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>222.99</v>
+        <v>222.86</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 02-Jun-2026  14:49:15    |    Closing Price Date: 02-Jun-2026</t>
+          <t>Scan Run: 03-Jun-2026  15:25:59    |    Closing Price Date: 03-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>36</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>40</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>46</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>02-Jun-2026  14:49:15</t>
+          <t>03-Jun-2026  15:25:59</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 18 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 20 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 18 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2968.1</v>
+        <v>2925.6</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2743.61</v>
+        <v>2760.94</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2498.16</v>
+        <v>2514.92</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2321.16</v>
+        <v>2327.18</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1814.5</v>
+        <v>1803.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1764.93</v>
+        <v>1768.63</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1666.03</v>
+        <v>1671.44</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1500.37</v>
+        <v>1503.39</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,24 +849,24 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8089.5</v>
+        <v>8290.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8095.87</v>
+        <v>8114.41</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7879.05</v>
+        <v>7895.19</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7492.95</v>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>7500.89</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2660.7</v>
+        <v>2662.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2603.88</v>
+        <v>2609.45</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2522.29</v>
+        <v>2527.79</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2489.83</v>
+        <v>2491.55</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1251.1</v>
+        <v>1255.2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1277.06</v>
+        <v>1276.55</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1283.59</v>
+        <v>1283.1</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1247.36</v>
+        <v>1247.99</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,24 +981,24 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10281</v>
+        <v>10259</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10276.4</v>
+        <v>10274.75</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9938.530000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9266.030000000001</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>9275.91</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>882</v>
+        <v>876.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>917.08</v>
+        <v>913.24</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>920.88</v>
+        <v>919.15</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>938.28</v>
+        <v>937.67</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1741.4</v>
+        <v>1734.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1775.25</v>
+        <v>1771.36</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1795.31</v>
+        <v>1792.92</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1901.18</v>
+        <v>1899.52</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>407.85</v>
+        <v>406.6</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>420.94</v>
+        <v>419.57</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>427.43</v>
+        <v>426.62</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.94</v>
+        <v>409.91</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>294.4</v>
+        <v>292.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>298.99</v>
+        <v>298.33</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>305.66</v>
+        <v>305.13</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>317.99</v>
+        <v>317.73</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1814.2</v>
+        <v>1824.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1848.46</v>
+        <v>1846.14</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1859.83</v>
+        <v>1858.42</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1903.69</v>
+        <v>1902.9</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5117</v>
+        <v>5064</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5373.28</v>
+        <v>5336.58</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5537.53</v>
+        <v>5510.6</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5677.07</v>
+        <v>5667.56</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1379.3</v>
+        <v>1375.2</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1381.11</v>
+        <v>1380.54</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1347.24</v>
+        <v>1348.33</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.89</v>
+        <v>1395.68</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472.15</v>
+        <v>472.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>462.38</v>
+        <v>463.33</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>455.77</v>
+        <v>456.42</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>418.97</v>
+        <v>419.5</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1274</v>
+        <v>1263.3</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1304.09</v>
+        <v>1300.2</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1291.03</v>
+        <v>1289.95</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.94</v>
+        <v>1261.95</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7141.5</v>
+        <v>7130</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7139.91</v>
+        <v>7138.97</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7151.44</v>
+        <v>7150.6</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6888.52</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6890.92</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3097.6</v>
+        <v>3101.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3024.45</v>
+        <v>3042.93</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2906.78</v>
+        <v>2924.07</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2792.16</v>
+        <v>2798.95</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,24 +1509,24 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1243.5</v>
+        <v>1179</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1190.59</v>
+        <v>1189.48</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1251.39</v>
+        <v>1248.55</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1406.66</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1404.39</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>748.25</v>
+        <v>753.65</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>764.34</v>
+        <v>763.33</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>788.55</v>
+        <v>787.1799999999999</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>873.62</v>
+        <v>872.42</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>579.9</v>
+        <v>574.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>604.25</v>
+        <v>601.41</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>618.09</v>
+        <v>616.37</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>678.92</v>
+        <v>677.88</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4875</v>
+        <v>4840.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>5010.87</v>
+        <v>4994.68</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5131.63</v>
+        <v>5120.23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5152.11</v>
+        <v>5149.01</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1146.3</v>
+        <v>1138.9</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1096.14</v>
+        <v>1100.21</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1043.01</v>
+        <v>1046.77</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>905.1799999999999</v>
+        <v>907.51</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2093.7</v>
+        <v>2090.6</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2199.23</v>
+        <v>2188.88</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2225.13</v>
+        <v>2219.86</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2300.71</v>
+        <v>2298.62</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1226.6</v>
+        <v>1242</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1260.85</v>
+        <v>1259.05</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1281.18</v>
+        <v>1279.64</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1329.53</v>
+        <v>1328.66</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>283.25</v>
+        <v>277</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>293.39</v>
+        <v>291.83</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>297.88</v>
+        <v>297.06</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>331.94</v>
+        <v>331.39</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>912.5</v>
+        <v>899.95</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>908.71</v>
+        <v>907.88</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>892.4400000000001</v>
+        <v>892.74</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>868.83</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>869.14</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1905,29 +1905,29 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1270.8</v>
+        <v>1222.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1184.48</v>
+        <v>1188.11</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1226.5</v>
+        <v>1226.35</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1393.79</v>
+        <v>1392.09</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1310.8</v>
+        <v>1312.9</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1285.04</v>
+        <v>1287.69</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1256.83</v>
+        <v>1259.02</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1178.34</v>
+        <v>1179.68</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>379.05</v>
+        <v>381</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.8</v>
+        <v>382.63</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.85</v>
+        <v>383.74</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>400.34</v>
+        <v>400.15</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,24 +2037,24 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4000.9</v>
+        <v>3953.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3973.33</v>
+        <v>3971.41</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3933.21</v>
+        <v>3933.99</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3827.23</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3828.48</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2998.3</v>
+        <v>3011.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3102.92</v>
+        <v>3094.17</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3161.5</v>
+        <v>3155.6</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3281.23</v>
+        <v>3278.55</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13022</v>
+        <v>13044</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13160.89</v>
+        <v>13159.76</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13383.28</v>
+        <v>13367.83</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14076.84</v>
+        <v>14059.44</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>367.4</v>
+        <v>366.8</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>389.15</v>
+        <v>387.02</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>386.75</v>
+        <v>385.97</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>360.08</v>
+        <v>360.15</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1398.7</v>
+        <v>1391.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1418.64</v>
+        <v>1416.06</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1379.06</v>
+        <v>1379.55</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1283.62</v>
+        <v>1284.69</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>265.05</v>
+        <v>267.75</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>282.06</v>
+        <v>280.7</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>281.84</v>
+        <v>281.28</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.37</v>
+        <v>259.46</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>282.15</v>
+        <v>285.05</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>298.41</v>
+        <v>297.14</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>300.8</v>
+        <v>300.19</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.48</v>
+        <v>287.46</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1314.6</v>
+        <v>1313.2</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1353.27</v>
+        <v>1349.46</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1372.14</v>
+        <v>1369.83</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1401.6</v>
+        <v>1400.72</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1801.7</v>
+        <v>1784.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1852.93</v>
+        <v>1846.38</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1876.19</v>
+        <v>1872.58</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1885.91</v>
+        <v>1884.9</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>911.7</v>
+        <v>912.95</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>947.05</v>
+        <v>943.8</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>962.96</v>
+        <v>961</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>886.76</v>
+        <v>887.02</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,17 +2477,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>956.65</v>
+        <v>970.45</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>976.52</v>
+        <v>975.9400000000001</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1008.5</v>
+        <v>1007.01</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>969.5700000000001</v>
@@ -2502,9 +2502,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1789.9</v>
+        <v>1788.5</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1825.93</v>
+        <v>1822.36</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1795.23</v>
+        <v>1794.97</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.74</v>
+        <v>1732.31</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,29 +2565,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2446.9</v>
+        <v>2241.7</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2323.93</v>
+        <v>2316.1</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2405.06</v>
+        <v>2398.66</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2751.52</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2746.45</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1154.7</v>
+        <v>1144</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1178.66</v>
+        <v>1175.36</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1155.72</v>
+        <v>1155.26</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1124.93</v>
+        <v>1125.12</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>390.2</v>
+        <v>398.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>371.18</v>
+        <v>373.75</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>358.8</v>
+        <v>360.35</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>423.61</v>
+        <v>423.35</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.6</v>
+        <v>211.89</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.32</v>
+        <v>211.37</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.16</v>
+        <v>208.31</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>188.71</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>188.95</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1571.4</v>
+        <v>1472.3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1461.78</v>
+        <v>1462.79</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1452.52</v>
+        <v>1453.29</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1485.85</v>
+        <v>1485.71</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4078.1</v>
+        <v>4088.8</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4154.25</v>
+        <v>4148.01</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4204.02</v>
+        <v>4199.51</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3987.45</v>
+        <v>3988.46</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4210.4</v>
+        <v>4257.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4175.37</v>
+        <v>4183.21</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4089.56</v>
+        <v>4096.15</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4309.05</v>
+        <v>4308.54</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11165</v>
+        <v>11101</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11555.64</v>
+        <v>11512.34</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11655.76</v>
+        <v>11634.01</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11821.02</v>
+        <v>11813.86</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>03-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>209.84</v>
+        <v>204.1</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.15</v>
+        <v>201.43</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>202.2</v>
+        <v>202.27</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>222.86</v>
+        <v>222.67</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 03-Jun-2026  15:25:59    |    Closing Price Date: 03-Jun-2026</t>
+          <t>Scan Run: 04-Jun-2026  13:56:58    |    Closing Price Date: 04-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>36</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>03-Jun-2026  15:25:59</t>
+          <t>04-Jun-2026  13:56:58</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2925.6</v>
+        <v>2972.8</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2760.94</v>
+        <v>2781.12</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2514.92</v>
+        <v>2532.88</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2327.18</v>
+        <v>2334.24</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1803.8</v>
+        <v>1790.9</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1768.63</v>
+        <v>1770.75</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1671.44</v>
+        <v>1676.12</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1503.39</v>
+        <v>1506.68</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8290.5</v>
+        <v>8249</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8114.41</v>
+        <v>8127.22</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7895.19</v>
+        <v>7909.06</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7500.89</v>
+        <v>7508.33</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2662.4</v>
+        <v>2661.6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2609.45</v>
+        <v>2614.42</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2527.79</v>
+        <v>2533.03</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2491.55</v>
+        <v>2492.32</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1255.2</v>
+        <v>1253.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1276.55</v>
+        <v>1274.33</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1283.1</v>
+        <v>1281.94</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1247.99</v>
+        <v>1248</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,24 +981,24 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10259</v>
+        <v>10362</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10274.75</v>
+        <v>10283.06</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9951.1</v>
+        <v>9967.209999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9275.91</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>9285.51</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>876.8</v>
+        <v>874.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>913.24</v>
+        <v>909.54</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>919.15</v>
+        <v>917.39</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.67</v>
+        <v>937.62</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1734.4</v>
+        <v>1709.8</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1771.36</v>
+        <v>1765.5</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1792.92</v>
+        <v>1789.66</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1899.52</v>
+        <v>1898.39</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>406.6</v>
+        <v>409.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>419.57</v>
+        <v>418.65</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>426.62</v>
+        <v>425.96</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.91</v>
+        <v>409.92</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>292.1</v>
+        <v>295.15</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>298.33</v>
+        <v>298.03</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>305.13</v>
+        <v>304.74</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>317.73</v>
+        <v>317.4</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1824.1</v>
+        <v>1818.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1846.14</v>
+        <v>1843.54</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1858.42</v>
+        <v>1856.87</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1902.9</v>
+        <v>1903.78</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5064</v>
+        <v>5090</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5336.58</v>
+        <v>5313.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5510.6</v>
+        <v>5494.1</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5667.56</v>
+        <v>5661.54</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1375.2</v>
+        <v>1398.7</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1380.54</v>
+        <v>1382.27</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1348.33</v>
+        <v>1350.31</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.68</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1395.14</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1314,9 +1314,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472.3</v>
+        <v>481.65</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>463.33</v>
+        <v>465.07</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>456.42</v>
+        <v>457.41</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>419.5</v>
+        <v>419.97</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1263.3</v>
+        <v>1267.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1300.2</v>
+        <v>1297.09</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1289.95</v>
+        <v>1289.07</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1261.95</v>
+        <v>1260.44</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7130</v>
+        <v>7110</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7138.97</v>
+        <v>7152.3</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7150.6</v>
+        <v>7157.55</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6890.92</v>
+        <v>6897.3</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3101.6</v>
+        <v>3103.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3042.93</v>
+        <v>3048.7</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2924.07</v>
+        <v>2931.11</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2798.95</v>
+        <v>2801.36</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1179</v>
+        <v>1168.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1189.48</v>
+        <v>1187.47</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1248.55</v>
+        <v>1245.41</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1404.39</v>
+        <v>1401.72</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>753.65</v>
+        <v>754.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>763.33</v>
+        <v>762.46</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>787.1799999999999</v>
+        <v>785.89</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>872.42</v>
+        <v>871.36</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>574.4</v>
+        <v>573.75</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>601.41</v>
+        <v>598.73</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>616.37</v>
+        <v>614.3</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>677.88</v>
+        <v>676.38</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4840.9</v>
+        <v>4882.3</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4994.68</v>
+        <v>4983.98</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5120.23</v>
+        <v>5110.9</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5149.01</v>
+        <v>5143.99</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1138.9</v>
+        <v>1125.6</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1100.21</v>
+        <v>1102.63</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1046.77</v>
+        <v>1049.87</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>907.51</v>
+        <v>908.71</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2090.6</v>
+        <v>2079.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2188.88</v>
+        <v>2178.46</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2219.86</v>
+        <v>2214.35</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2298.62</v>
+        <v>2297.19</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1242</v>
+        <v>1251.7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1259.05</v>
+        <v>1258.35</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1279.64</v>
+        <v>1278.55</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1328.66</v>
+        <v>1328.14</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>277</v>
+        <v>280.3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>291.83</v>
+        <v>290.73</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>297.06</v>
+        <v>296.4</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>331.39</v>
+        <v>331.01</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>899.95</v>
+        <v>903.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>907.88</v>
+        <v>907.4299999999999</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>892.74</v>
+        <v>893.15</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>869.14</v>
+        <v>869.7</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1222.6</v>
+        <v>1201.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1188.11</v>
+        <v>1189.36</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1226.35</v>
+        <v>1225.37</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1392.09</v>
+        <v>1390.34</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1312.9</v>
+        <v>1301.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1287.69</v>
+        <v>1288.97</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1259.02</v>
+        <v>1260.67</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1179.68</v>
+        <v>1180.54</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>381</v>
+        <v>381.5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.63</v>
+        <v>382.52</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.74</v>
+        <v>383.65</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>400.15</v>
+        <v>399.98</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3953.2</v>
+        <v>3942.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3971.41</v>
+        <v>3968.62</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3933.99</v>
+        <v>3934.31</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3828.48</v>
+        <v>3828.26</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3011.1</v>
+        <v>3016.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3094.17</v>
+        <v>3086.74</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3155.6</v>
+        <v>3150.13</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3278.55</v>
+        <v>3278.88</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13044</v>
+        <v>13064</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13159.76</v>
+        <v>13150.64</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13367.83</v>
+        <v>13355.91</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14059.44</v>
+        <v>14055.15</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>366.8</v>
+        <v>366.4</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>387.02</v>
+        <v>385.05</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>385.97</v>
+        <v>385.2</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>360.15</v>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1391.5</v>
+        <v>1382.9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1416.06</v>
+        <v>1412.9</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1379.55</v>
+        <v>1379.68</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1284.69</v>
+        <v>1286.31</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>267.75</v>
+        <v>267.55</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>280.7</v>
+        <v>279.44</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>281.28</v>
+        <v>280.75</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.46</v>
+        <v>259.48</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>285.05</v>
+        <v>284.6</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>297.14</v>
+        <v>295.94</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>300.19</v>
+        <v>299.57</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.46</v>
+        <v>287.29</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1313.2</v>
+        <v>1303.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1349.46</v>
+        <v>1345.1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1369.83</v>
+        <v>1367.24</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1400.72</v>
+        <v>1399.3</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1784.2</v>
+        <v>1764.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1846.38</v>
+        <v>1838.62</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1872.58</v>
+        <v>1868.36</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1884.9</v>
+        <v>1883.07</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>912.95</v>
+        <v>915.8</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>943.8</v>
+        <v>941.13</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>961</v>
+        <v>959.23</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>887.02</v>
+        <v>887.1799999999999</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,24 +2477,24 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>970.45</v>
+        <v>979.25</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>975.9400000000001</v>
+        <v>976.26</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1007.01</v>
+        <v>1005.92</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>969.5700000000001</v>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>969.4400000000001</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1788.5</v>
+        <v>1780.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1822.36</v>
+        <v>1818.34</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1794.97</v>
+        <v>1794.39</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1732.31</v>
+        <v>1731.67</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2241.7</v>
+        <v>2241</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2316.1</v>
+        <v>2308.94</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2398.66</v>
+        <v>2392.47</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2746.45</v>
+        <v>2739.52</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1144</v>
+        <v>1149.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1175.36</v>
+        <v>1172.88</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1155.26</v>
+        <v>1155.03</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1125.12</v>
+        <v>1125.46</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>398.15</v>
+        <v>399.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>373.75</v>
+        <v>376.22</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>360.35</v>
+        <v>361.89</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>423.35</v>
+        <v>422.83</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>211.89</v>
+        <v>210.57</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.37</v>
+        <v>211.3</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.31</v>
+        <v>208.4</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>188.95</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>189.14</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1472.3</v>
+        <v>1487.3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1462.79</v>
+        <v>1465.12</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1453.29</v>
+        <v>1454.63</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1485.71</v>
+        <v>1484.9</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4088.8</v>
+        <v>4231</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4148.01</v>
+        <v>4155.92</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4199.51</v>
+        <v>4200.74</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3988.46</v>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3991.98</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -2829,29 +2829,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>4257.6</v>
+        <v>2837.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4183.21</v>
+        <v>3730.26</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4096.15</v>
+        <v>3899.86</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4308.54</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4247.79</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>11101</v>
+        <v>10997</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11512.34</v>
+        <v>11463.26</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11634.01</v>
+        <v>11609.03</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11813.86</v>
+        <v>11802.36</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>03-Jun-2026</t>
+          <t>04-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>204.1</v>
+        <v>204.32</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.43</v>
+        <v>201.7</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>202.27</v>
+        <v>202.35</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>222.67</v>
+        <v>222.33</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 04-Jun-2026  13:56:58    |    Closing Price Date: 04-Jun-2026</t>
+          <t>Scan Run: 05-Jun-2026  13:50:47    |    Closing Price Date: 05-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>36</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>04-Jun-2026  13:56:58</t>
+          <t>05-Jun-2026  13:50:47</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 18 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2972.8</v>
+        <v>3048.2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2781.12</v>
+        <v>2806.55</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2532.88</v>
+        <v>2553.09</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2334.24</v>
+        <v>2340.52</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1790.9</v>
+        <v>1824.2</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1770.75</v>
+        <v>1775.84</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1676.12</v>
+        <v>1681.93</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1506.68</v>
+        <v>1509.77</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8249</v>
+        <v>8304.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8127.22</v>
+        <v>8144.11</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7909.06</v>
+        <v>7924.57</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7508.33</v>
+        <v>7513.39</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2661.6</v>
+        <v>2686.7</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2614.42</v>
+        <v>2621.3</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2533.03</v>
+        <v>2539.06</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2492.32</v>
+        <v>2493.78</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1253.3</v>
+        <v>1272.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1274.33</v>
+        <v>1274.14</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1281.94</v>
+        <v>1281.56</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1248</v>
+        <v>1248.57</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10362</v>
+        <v>10342</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10283.06</v>
+        <v>10288.67</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9967.209999999999</v>
+        <v>9981.91</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9285.51</v>
+        <v>9288.299999999999</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>874.4</v>
+        <v>889.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>909.54</v>
+        <v>907.62</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>917.39</v>
+        <v>916.3</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.62</v>
+        <v>938.0700000000001</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1709.8</v>
+        <v>1703.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1765.5</v>
+        <v>1759.56</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1789.66</v>
+        <v>1786.27</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1898.39</v>
+        <v>1898.63</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>409.9</v>
+        <v>408.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>418.65</v>
+        <v>417.65</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>425.96</v>
+        <v>425.26</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.92</v>
+        <v>409.72</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>295.15</v>
+        <v>295</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>298.03</v>
+        <v>297.74</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>304.74</v>
+        <v>304.36</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>317.4</v>
+        <v>317.03</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1818.9</v>
+        <v>1798.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1843.54</v>
+        <v>1839.22</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1856.87</v>
+        <v>1854.57</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1903.78</v>
+        <v>1903.12</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5090</v>
+        <v>5120.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5313.09</v>
+        <v>5294.75</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5494.1</v>
+        <v>5479.45</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5661.54</v>
+        <v>5655.51</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1398.7</v>
+        <v>1401.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1382.27</v>
+        <v>1372.46</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1350.31</v>
+        <v>1340.25</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1395.14</v>
+        <v>1381.42</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>481.65</v>
+        <v>472.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>465.07</v>
+        <v>465.76</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>457.41</v>
+        <v>457.99</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>419.97</v>
+        <v>420.6</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1267.5</v>
+        <v>1278.2</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1297.09</v>
+        <v>1295.29</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1289.07</v>
+        <v>1288.64</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1260.44</v>
+        <v>1260.51</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7110</v>
+        <v>7070</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7152.3</v>
+        <v>7144.46</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7157.55</v>
+        <v>7154.11</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6897.3</v>
+        <v>6896.69</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3103.5</v>
+        <v>3087.7</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3048.7</v>
+        <v>3052.41</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2931.11</v>
+        <v>2937.25</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2801.36</v>
+        <v>2802.51</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1168.3</v>
+        <v>1154.7</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1187.47</v>
+        <v>1184.35</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1245.41</v>
+        <v>1241.85</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1401.72</v>
+        <v>1398.97</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>754.2</v>
+        <v>747.05</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>762.46</v>
+        <v>760.99</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>785.89</v>
+        <v>784.36</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>871.36</v>
+        <v>870.51</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>573.75</v>
+        <v>575.3</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>598.73</v>
+        <v>596.49</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>614.3</v>
+        <v>612.77</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>676.38</v>
+        <v>675.22</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4882.3</v>
+        <v>4835</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4983.98</v>
+        <v>4969.79</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5110.9</v>
+        <v>5100.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5143.99</v>
+        <v>5138.04</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1125.6</v>
+        <v>1092.6</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1102.63</v>
+        <v>1101.68</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1049.87</v>
+        <v>1051.54</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>908.71</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>911.08</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2079.4</v>
+        <v>2121.5</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2178.46</v>
+        <v>2173.03</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2214.35</v>
+        <v>2210.71</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2297.19</v>
+        <v>2294.84</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,24 +1773,24 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1251.7</v>
+        <v>1262.1</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1258.35</v>
+        <v>1258.71</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1278.55</v>
+        <v>1277.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1328.14</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1327.41</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>280.3</v>
+        <v>280.7</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>290.73</v>
+        <v>289.77</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>296.4</v>
+        <v>295.79</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>331.01</v>
+        <v>330.37</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>903.2</v>
+        <v>904.8</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>907.4299999999999</v>
+        <v>907.1799999999999</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>893.15</v>
+        <v>893.61</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>869.7</v>
+        <v>870.58</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1201.3</v>
+        <v>1197.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1189.36</v>
+        <v>1190.14</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1225.37</v>
+        <v>1224.27</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1390.34</v>
+        <v>1388.28</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,24 +1949,24 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1301.1</v>
+        <v>1284</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1288.97</v>
+        <v>1288.49</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1260.67</v>
+        <v>1261.59</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1180.54</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1182.27</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>381.5</v>
+        <v>377.45</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.52</v>
+        <v>382.04</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.65</v>
+        <v>383.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>399.98</v>
+        <v>399.58</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3942.1</v>
+        <v>3953.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3968.62</v>
+        <v>3967.15</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3934.31</v>
+        <v>3935.05</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3828.26</v>
+        <v>3828.81</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3016.1</v>
+        <v>3040.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3086.74</v>
+        <v>3082.33</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3150.13</v>
+        <v>3145.83</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3278.88</v>
+        <v>3274.31</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13064</v>
+        <v>13050</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13150.64</v>
+        <v>13141.05</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13355.91</v>
+        <v>13343.92</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14055.15</v>
+        <v>14041.05</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>366.4</v>
+        <v>361.65</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>385.05</v>
+        <v>382.83</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>385.2</v>
+        <v>384.28</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>360.15</v>
+        <v>360.04</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1382.9</v>
+        <v>1386.2</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1412.9</v>
+        <v>1410.36</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1379.68</v>
+        <v>1379.94</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1286.31</v>
+        <v>1287.9</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>267.55</v>
+        <v>264.75</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>279.44</v>
+        <v>278.04</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>280.75</v>
+        <v>280.12</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.48</v>
+        <v>259.45</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>284.6</v>
+        <v>285.65</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>295.94</v>
+        <v>294.96</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>299.57</v>
+        <v>299.03</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>287.29</v>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1303.7</v>
+        <v>1291</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1345.1</v>
+        <v>1334.34</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1367.24</v>
+        <v>1358.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1399.3</v>
+        <v>1391.98</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1764.9</v>
+        <v>1782.8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1838.62</v>
+        <v>1833.31</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1868.36</v>
+        <v>1865</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1883.07</v>
+        <v>1881.98</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>915.8</v>
+        <v>923.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>941.13</v>
+        <v>939.4299999999999</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>959.23</v>
+        <v>957.8200000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>887.1799999999999</v>
+        <v>888.9400000000001</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>979.25</v>
+        <v>977.7</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>976.26</v>
+        <v>976.4</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1005.92</v>
+        <v>1004.81</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>969.4400000000001</v>
+        <v>969.23</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1780.1</v>
+        <v>1782.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1818.34</v>
+        <v>1814.9</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1794.39</v>
+        <v>1793.91</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.67</v>
+        <v>1733.63</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2241</v>
+        <v>2198.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2308.94</v>
+        <v>2298.46</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2392.47</v>
+        <v>2384.88</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2739.52</v>
+        <v>2733.43</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1149.3</v>
+        <v>1130.9</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1172.88</v>
+        <v>1168.88</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1155.03</v>
+        <v>1154.08</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1125.46</v>
+        <v>1125.65</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>399.7</v>
+        <v>397.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>376.22</v>
+        <v>378.28</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>361.89</v>
+        <v>363.3</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>422.83</v>
+        <v>422.02</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>210.57</v>
+        <v>206.77</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>211.3</v>
+        <v>210.87</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.4</v>
+        <v>208.33</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>189.14</v>
+        <v>189.38</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1487.3</v>
+        <v>1483.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1465.12</v>
+        <v>1466.87</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1454.63</v>
+        <v>1455.76</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1484.9</v>
+        <v>1484.65</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4231</v>
+        <v>4260.2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4155.92</v>
+        <v>4165.85</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4200.74</v>
+        <v>4203.07</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3991.98</v>
+        <v>3995.7</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2837.6</v>
+        <v>2774.2</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3730.26</v>
+        <v>3639.21</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3899.86</v>
+        <v>3855.72</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4247.79</v>
+        <v>4226.44</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10997</v>
+        <v>10912</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11463.26</v>
+        <v>11410.76</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11609.03</v>
+        <v>11581.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11802.36</v>
+        <v>11771.28</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,29 +2917,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>04-Jun-2026</t>
+          <t>05-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>204.32</v>
+        <v>198.37</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.7</v>
+        <v>201.39</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>202.35</v>
+        <v>202.2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>222.33</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>222.23</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 05-Jun-2026  13:50:47    |    Closing Price Date: 05-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  03:45:01    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>32</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>05-Jun-2026  13:50:47</t>
+          <t>08-Jun-2026  03:45:01</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3048.2</v>
+        <v>3004.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2806.55</v>
+        <v>2825.37</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2553.09</v>
+        <v>2570.77</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2340.52</v>
+        <v>2347.4</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1824.2</v>
+        <v>1809.6</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1775.84</v>
+        <v>1779.06</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1681.93</v>
+        <v>1686.93</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1509.77</v>
+        <v>1511.64</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8304.5</v>
+        <v>8212.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8144.11</v>
+        <v>8150.62</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7924.57</v>
+        <v>7935.86</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7513.39</v>
+        <v>7519.77</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2686.7</v>
+        <v>2642.8</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2621.3</v>
+        <v>2623.35</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2539.06</v>
+        <v>2543.13</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2493.78</v>
+        <v>2493.24</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1272.3</v>
+        <v>1264.4</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1274.14</v>
+        <v>1273.21</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1281.56</v>
+        <v>1280.88</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1248.57</v>
+        <v>1248.31</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,24 +981,24 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10342</v>
+        <v>10277</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10288.67</v>
+        <v>10287.56</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9981.91</v>
+        <v>9993.48</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9288.299999999999</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>9276.52</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>889.4</v>
+        <v>873.15</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>907.62</v>
+        <v>904.34</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>916.3</v>
+        <v>914.61</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>938.0700000000001</v>
+        <v>937.09</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1703.2</v>
+        <v>1690.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1759.56</v>
+        <v>1752.99</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1786.27</v>
+        <v>1782.51</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1898.63</v>
+        <v>1892.78</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>408.2</v>
+        <v>402.35</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>417.65</v>
+        <v>416.2</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>425.26</v>
+        <v>424.36</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.72</v>
+        <v>409.87</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>295</v>
+        <v>291.25</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>297.74</v>
+        <v>297.12</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>304.36</v>
+        <v>303.84</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>317.03</v>
+        <v>316.68</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1798.2</v>
+        <v>1779.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1839.22</v>
+        <v>1833.57</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1854.57</v>
+        <v>1851.65</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1903.12</v>
+        <v>1899.56</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5120.5</v>
+        <v>5053.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5294.75</v>
+        <v>5271.77</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5479.45</v>
+        <v>5462.75</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5655.51</v>
+        <v>5641.56</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1401.3</v>
+        <v>1391.1</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1372.46</v>
+        <v>1374.24</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1340.25</v>
+        <v>1342.24</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1381.42</v>
+        <v>1380.09</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472.3</v>
+        <v>467.55</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>465.76</v>
+        <v>465.93</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>457.99</v>
+        <v>458.37</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>420.6</v>
+        <v>420.93</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1278.2</v>
+        <v>1275.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1295.29</v>
+        <v>1293.4</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1288.64</v>
+        <v>1288.12</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1260.51</v>
+        <v>1260.4</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7070</v>
+        <v>6970</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7144.46</v>
+        <v>7127.84</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7154.11</v>
+        <v>7146.89</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6896.69</v>
+        <v>6896.25</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,24 +1465,24 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3087.7</v>
+        <v>3042.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3052.41</v>
+        <v>3051.5</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2937.25</v>
+        <v>2941.39</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2802.51</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2806.55</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1154.7</v>
+        <v>1144.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1184.35</v>
+        <v>1180.53</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1241.85</v>
+        <v>1238.02</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1398.97</v>
+        <v>1394.11</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>747.05</v>
+        <v>740.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>760.99</v>
+        <v>759.03</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>784.36</v>
+        <v>782.64</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>870.51</v>
+        <v>869.23</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>575.3</v>
+        <v>569.15</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>596.49</v>
+        <v>593.89</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>612.77</v>
+        <v>611.0599999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>675.22</v>
+        <v>674.15</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4835</v>
+        <v>4807.6</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4969.79</v>
+        <v>4954.34</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5100.08</v>
+        <v>5088.61</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5138.04</v>
+        <v>5129.34</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1092.6</v>
+        <v>1067.6</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1101.68</v>
+        <v>1098.43</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1051.54</v>
+        <v>1052.17</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>911.08</v>
+        <v>912.84</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2121.5</v>
+        <v>2101.7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2173.03</v>
+        <v>2166.24</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2210.71</v>
+        <v>2206.43</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2294.84</v>
+        <v>2290.01</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,24 +1773,24 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1262.1</v>
+        <v>1248.5</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1258.71</v>
+        <v>1257.74</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1277.9</v>
+        <v>1276.75</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1327.41</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1325.93</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>280.7</v>
+        <v>278</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>289.77</v>
+        <v>288.65</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>295.79</v>
+        <v>295.09</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>330.37</v>
+        <v>329.68</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,29 +1861,29 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>904.8</v>
+        <v>889</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>907.1799999999999</v>
+        <v>905.45</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>893.61</v>
+        <v>893.42</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>870.58</v>
+        <v>868.05</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
@@ -1905,24 +1905,24 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1197.5</v>
+        <v>1184.7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1190.14</v>
+        <v>1189.62</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1224.27</v>
+        <v>1222.72</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1388.28</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1383.92</v>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1284</v>
+        <v>1267</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1288.49</v>
+        <v>1286.45</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1261.59</v>
+        <v>1261.8</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1182.27</v>
+        <v>1183.17</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>377.45</v>
+        <v>374.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>382.04</v>
+        <v>381.34</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.41</v>
+        <v>383.07</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>399.58</v>
+        <v>399.05</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,29 +2037,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3953.2</v>
+        <v>3905</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3967.15</v>
+        <v>3961.23</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3935.05</v>
+        <v>3933.87</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3828.81</v>
+        <v>3829.06</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3040.5</v>
+        <v>2993.3</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3082.33</v>
+        <v>3073.85</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3145.83</v>
+        <v>3139.85</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3274.31</v>
+        <v>3266.6</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>13050</v>
+        <v>12889</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13141.05</v>
+        <v>13117.05</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13343.92</v>
+        <v>13326.07</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14041.05</v>
+        <v>14003.61</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>361.65</v>
+        <v>355.75</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>382.83</v>
+        <v>380.25</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>384.28</v>
+        <v>383.16</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>360.04</v>
+        <v>359.95</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2194,9 +2194,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J34" s="13" t="inlineStr">
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1386.2</v>
+        <v>1381.7</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1410.36</v>
+        <v>1407.63</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1379.94</v>
+        <v>1380.01</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1287.9</v>
+        <v>1286.85</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>264.75</v>
+        <v>263.85</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>278.04</v>
+        <v>276.69</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>280.12</v>
+        <v>279.48</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.45</v>
+        <v>259.26</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>285.65</v>
+        <v>283.35</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>294.96</v>
+        <v>293.86</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>299.03</v>
+        <v>298.41</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.29</v>
+        <v>287.1</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1291</v>
+        <v>1278.2</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1334.34</v>
+        <v>1329</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1358.2</v>
+        <v>1355.07</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1391.98</v>
+        <v>1389.29</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1782.8</v>
+        <v>1776</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1833.31</v>
+        <v>1827.85</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1865</v>
+        <v>1861.51</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1881.98</v>
+        <v>1878.28</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>923.3</v>
+        <v>904.25</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>939.4299999999999</v>
+        <v>936.08</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>957.8200000000001</v>
+        <v>955.72</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>888.9400000000001</v>
+        <v>889.71</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,24 +2477,24 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>977.7</v>
+        <v>968.95</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>976.4</v>
+        <v>975.6900000000001</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1004.81</v>
+        <v>1003.4</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>969.23</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>968.87</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1782.2</v>
+        <v>1785.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1814.9</v>
+        <v>1812.06</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.91</v>
+        <v>1793.56</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1733.63</v>
+        <v>1731.46</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2198.9</v>
+        <v>2167</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2298.46</v>
+        <v>2285.94</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2384.88</v>
+        <v>2376.34</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2733.43</v>
+        <v>2722.87</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1130.9</v>
+        <v>1114.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1168.88</v>
+        <v>1163.68</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1154.08</v>
+        <v>1152.52</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1125.65</v>
+        <v>1123.23</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2634,9 +2634,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>397.8</v>
+        <v>390.25</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>378.28</v>
+        <v>379.42</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>363.3</v>
+        <v>364.35</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>422.02</v>
+        <v>420.53</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>206.77</v>
+        <v>202.93</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>210.87</v>
+        <v>210.11</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.33</v>
+        <v>208.12</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>189.38</v>
+        <v>189.51</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1483.5</v>
+        <v>1486.3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1466.87</v>
+        <v>1468.72</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1455.76</v>
+        <v>1456.96</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1484.65</v>
+        <v>1480.66</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4260.2</v>
+        <v>4218</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4165.85</v>
+        <v>4170.82</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4203.07</v>
+        <v>4203.66</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3995.7</v>
+        <v>3991.83</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2774.2</v>
+        <v>2730.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>3639.21</v>
+        <v>2788.4</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3855.72</v>
+        <v>2759.79</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4226.44</v>
+        <v>3420.5</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10912</v>
+        <v>10768</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11410.76</v>
+        <v>11349.55</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11581.69</v>
+        <v>11549.78</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11771.28</v>
+        <v>11756.8</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>198.37</v>
+        <v>192.01</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>201.39</v>
+        <v>200.49</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>222.23</v>
+        <v>221.48</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  03:45:01    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  04:27:40    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>46</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  03:45:01</t>
+          <t>08-Jun-2026  04:27:40</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 12 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 14 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3004.1</v>
+        <v>3032</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2825.37</v>
+        <v>2828.03</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2570.77</v>
+        <v>2571.87</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2347.4</v>
+        <v>2347.68</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1809.6</v>
+        <v>1823.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1779.06</v>
+        <v>1780.38</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1686.93</v>
+        <v>1687.48</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1511.64</v>
+        <v>1511.77</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8212.5</v>
+        <v>8397</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8150.62</v>
+        <v>8168.19</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7935.86</v>
+        <v>7943.09</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7519.77</v>
+        <v>7521.61</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2642.8</v>
+        <v>2655.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2623.35</v>
+        <v>2624.55</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2543.13</v>
+        <v>2543.62</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2493.24</v>
+        <v>2493.36</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -941,20 +941,20 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1264.4</v>
+        <v>1275.4</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1273.21</v>
+        <v>1274.26</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1280.88</v>
+        <v>1281.32</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1248.31</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1248.42</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -985,16 +985,16 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10277</v>
+        <v>10284</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10287.56</v>
+        <v>10288.23</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9993.48</v>
+        <v>9993.75</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9276.52</v>
+        <v>9276.59</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>873.15</v>
+        <v>873.9</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>904.34</v>
+        <v>904.41</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>914.61</v>
+        <v>914.63</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.09</v>
+        <v>937.1</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1690.5</v>
+        <v>1687.1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1752.99</v>
+        <v>1752.66</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1782.51</v>
+        <v>1782.38</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1892.78</v>
+        <v>1892.74</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>402.35</v>
+        <v>407.6</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>416.2</v>
+        <v>416.7</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>424.36</v>
+        <v>424.57</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.87</v>
+        <v>409.92</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>291.25</v>
+        <v>289.25</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>297.12</v>
+        <v>296.93</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>303.84</v>
+        <v>303.76</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>316.68</v>
+        <v>316.66</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1779.9</v>
+        <v>1794.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1833.57</v>
+        <v>1835</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1851.65</v>
+        <v>1852.23</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1899.56</v>
+        <v>1899.71</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5053.5</v>
+        <v>5083</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5271.77</v>
+        <v>5274.58</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5462.75</v>
+        <v>5463.9</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5641.56</v>
+        <v>5641.86</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1391.1</v>
+        <v>1396</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1374.24</v>
+        <v>1374.7</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1342.24</v>
+        <v>1342.44</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1380.09</v>
+        <v>1380.14</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>467.55</v>
+        <v>465.9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>465.93</v>
+        <v>465.77</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>458.37</v>
+        <v>458.3</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>420.93</v>
+        <v>420.91</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1275.4</v>
+        <v>1286</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1293.4</v>
+        <v>1294.41</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1288.12</v>
+        <v>1288.54</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1260.4</v>
+        <v>1260.5</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>6970</v>
+        <v>7048</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7127.84</v>
+        <v>7135.27</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7146.89</v>
+        <v>7149.95</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6896.25</v>
+        <v>6897.02</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1469,20 +1469,20 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3042.8</v>
+        <v>3062.3</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3051.5</v>
+        <v>3053.35</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2941.39</v>
+        <v>2942.15</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2806.55</v>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2806.74</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1144.3</v>
+        <v>1145.8</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1180.53</v>
+        <v>1180.68</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1238.02</v>
+        <v>1238.08</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1394.11</v>
+        <v>1394.12</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>740.4</v>
+        <v>739.55</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>759.03</v>
+        <v>758.95</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>782.64</v>
+        <v>782.61</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>869.23</v>
+        <v>869.22</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>569.15</v>
+        <v>571.85</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>593.89</v>
+        <v>594.15</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>611.0599999999999</v>
+        <v>611.17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>674.15</v>
+        <v>674.1799999999999</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1645,16 +1645,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4807.6</v>
+        <v>4828.8</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4954.34</v>
+        <v>4956.36</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5088.61</v>
+        <v>5089.44</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5129.34</v>
+        <v>5129.56</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1067.6</v>
+        <v>1069.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1098.43</v>
+        <v>1098.63</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1052.17</v>
+        <v>1052.25</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>912.84</v>
+        <v>912.86</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2101.7</v>
+        <v>2114</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2166.24</v>
+        <v>2167.41</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2206.43</v>
+        <v>2206.92</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2290.01</v>
+        <v>2290.14</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1248.5</v>
+        <v>1248.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1257.74</v>
+        <v>1257.73</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1276.75</v>
+        <v>1276.74</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>1325.93</v>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>278</v>
+        <v>280.55</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>288.65</v>
+        <v>288.9</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>295.09</v>
+        <v>295.19</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>329.68</v>
+        <v>329.71</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1865,25 +1865,25 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>889</v>
+        <v>896.05</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>905.45</v>
+        <v>906.12</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>893.42</v>
+        <v>893.7</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>868.05</v>
+        <v>868.12</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1184.7</v>
+        <v>1185.2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1189.62</v>
+        <v>1189.67</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1222.72</v>
+        <v>1222.74</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>1383.92</v>
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1267</v>
+        <v>1267.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1286.45</v>
+        <v>1286.48</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1261.8</v>
+        <v>1261.82</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>1183.17</v>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>374.7</v>
+        <v>375.3</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>381.34</v>
+        <v>381.4</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.07</v>
+        <v>383.09</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>399.05</v>
+        <v>399.06</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3905</v>
+        <v>3890.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3961.23</v>
+        <v>3959.88</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3933.87</v>
+        <v>3933.32</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3829.06</v>
+        <v>3828.92</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2993.3</v>
+        <v>2985</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3073.85</v>
+        <v>3073.06</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3139.85</v>
+        <v>3139.53</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3266.6</v>
+        <v>3266.52</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>12889</v>
+        <v>12954</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13117.05</v>
+        <v>13123.24</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13326.07</v>
+        <v>13328.62</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14003.61</v>
+        <v>14004.26</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>355.75</v>
+        <v>359.5</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>380.25</v>
+        <v>380.6</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>383.16</v>
+        <v>383.31</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>359.95</v>
+        <v>359.98</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1381.7</v>
+        <v>1391.9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1407.63</v>
+        <v>1408.6</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1380.01</v>
+        <v>1380.41</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1286.85</v>
+        <v>1286.95</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>263.85</v>
+        <v>264.25</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>276.69</v>
+        <v>276.73</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>279.48</v>
+        <v>279.5</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>259.26</v>
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>283.35</v>
+        <v>288.25</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>293.86</v>
+        <v>294.32</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>298.41</v>
+        <v>298.61</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.1</v>
+        <v>287.14</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2326,9 +2326,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1278.2</v>
+        <v>1280.9</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1329</v>
+        <v>1329.25</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1355.07</v>
+        <v>1355.17</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1389.29</v>
+        <v>1389.32</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1776</v>
+        <v>1776.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1827.85</v>
+        <v>1827.87</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1861.51</v>
+        <v>1861.52</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>1878.28</v>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>904.25</v>
+        <v>907.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>936.08</v>
+        <v>936.39</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>955.72</v>
+        <v>955.85</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>889.71</v>
+        <v>889.74</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2481,20 +2481,20 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>968.95</v>
+        <v>987.6</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>975.6900000000001</v>
+        <v>977.46</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1003.4</v>
+        <v>1004.14</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>968.87</v>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>969.0599999999999</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -2525,25 +2525,25 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1785.1</v>
+        <v>1795.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1812.06</v>
+        <v>1813.02</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.56</v>
+        <v>1793.96</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.46</v>
+        <v>1731.57</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2285.94</v>
+        <v>2285.75</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2376.34</v>
+        <v>2376.26</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2722.87</v>
+        <v>2722.85</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1114.3</v>
+        <v>1121.8</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1163.68</v>
+        <v>1164.4</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1152.52</v>
+        <v>1152.81</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1123.23</v>
+        <v>1123.31</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>390.25</v>
+        <v>391.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>379.42</v>
+        <v>379.5</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>364.35</v>
+        <v>364.39</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>420.53</v>
+        <v>420.54</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>202.93</v>
+        <v>204.56</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>210.11</v>
+        <v>210.27</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.12</v>
+        <v>208.19</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>189.51</v>
+        <v>189.53</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1486.3</v>
+        <v>1471.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1468.72</v>
+        <v>1467.33</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1456.96</v>
+        <v>1456.38</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1480.66</v>
+        <v>1480.51</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4218</v>
+        <v>4233</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4170.82</v>
+        <v>4172.24</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4203.66</v>
+        <v>4204.25</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3991.83</v>
+        <v>3991.98</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2730.8</v>
+        <v>2754.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>2788.4</v>
+        <v>2790.64</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>2759.79</v>
+        <v>2760.72</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3420.5</v>
+        <v>3420.73</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10768</v>
+        <v>10810</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11349.55</v>
+        <v>11353.55</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11549.78</v>
+        <v>11551.43</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11756.8</v>
+        <v>11757.21</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>192.01</v>
+        <v>187.96</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>200.49</v>
+        <v>200.11</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.8</v>
+        <v>201.64</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>221.48</v>
+        <v>221.44</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  04:27:40    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  10:25:42    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -598,20 +598,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  04:27:40</t>
+          <t>08-Jun-2026  10:25:42</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
@@ -765,42 +765,42 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3032</v>
+        <v>1263.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2828.03</v>
+        <v>1327.58</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2571.87</v>
+        <v>1354.48</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2347.68</v>
+        <v>1389.15</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -809,42 +809,42 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1823.5</v>
+        <v>738.65</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1780.38</v>
+        <v>758.86</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1687.48</v>
+        <v>782.5700000000001</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1511.77</v>
+        <v>869.21</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -853,42 +853,42 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8397</v>
+        <v>2151.4</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8168.19</v>
+        <v>2284.46</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7943.09</v>
+        <v>2375.73</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7521.61</v>
+        <v>2722.71</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -897,42 +897,42 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2655.4</v>
+        <v>181.76</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2624.55</v>
+        <v>199.52</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>2543.62</v>
+        <v>201.39</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2493.36</v>
+        <v>221.37</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -941,42 +941,42 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1275.4</v>
+        <v>1250.2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1274.26</v>
+        <v>1257.9</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1281.32</v>
+        <v>1276.81</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1248.42</v>
+        <v>1325.95</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -985,42 +985,42 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10284</v>
+        <v>981.95</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>10288.23</v>
+        <v>976.92</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9993.75</v>
+        <v>1003.91</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9276.59</v>
+        <v>969</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -1029,42 +1029,42 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>873.9</v>
+        <v>1813.3</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>904.41</v>
+        <v>1836.76</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>914.63</v>
+        <v>1852.95</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>937.1</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+        <v>1899.89</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -1073,42 +1073,42 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1687.1</v>
+        <v>1187.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1752.66</v>
+        <v>1189.9</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1782.38</v>
+        <v>1222.84</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1892.74</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
+        <v>1383.95</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1117,42 +1117,42 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>407.6</v>
+        <v>2966</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>416.7</v>
+        <v>3071.25</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>424.57</v>
+        <v>3138.78</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>409.92</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
+        <v>3266.33</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1161,42 +1161,42 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>289.25</v>
+        <v>3875.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>296.93</v>
+        <v>3958.42</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>303.76</v>
+        <v>3932.72</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>316.66</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
+        <v>3828.77</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>LT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -1205,42 +1205,42 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1794.9</v>
+        <v>1268.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1835</v>
+        <v>1273.56</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1852.23</v>
+        <v>1281.03</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1899.71</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
+        <v>1248.35</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -1249,42 +1249,42 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5083</v>
+        <v>202.72</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5274.58</v>
+        <v>210.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5463.9</v>
+        <v>208.11</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5641.86</v>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
+        <v>189.51</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -1293,42 +1293,42 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1396</v>
+        <v>248.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1374.7</v>
+        <v>249.61</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1342.44</v>
+        <v>249.75</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1380.14</v>
+        <v>264.42</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -1337,42 +1337,42 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>465.9</v>
+        <v>1788.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>465.77</v>
+        <v>1812.41</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>458.3</v>
+        <v>1793.71</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>420.91</v>
+        <v>1731.5</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -1381,42 +1381,42 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1286</v>
+        <v>1007.45</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1294.41</v>
+        <v>995.45</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1288.54</v>
+        <v>1004.58</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1260.5</v>
+        <v>1049.69</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1425,42 +1425,42 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>7048</v>
+        <v>377.1</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7135.27</v>
+        <v>381.57</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7149.95</v>
+        <v>383.16</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6897.02</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
+        <v>399.07</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -1469,42 +1469,42 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3062.3</v>
+        <v>362.4</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3053.35</v>
+        <v>380.88</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2942.15</v>
+        <v>383.42</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2806.74</v>
+        <v>360.01</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1513,42 +1513,42 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1145.8</v>
+        <v>871.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1180.68</v>
+        <v>904.15</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1238.08</v>
+        <v>914.52</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1394.12</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
+        <v>937.0700000000001</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -1557,42 +1557,42 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>739.55</v>
+        <v>1062.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>758.95</v>
+        <v>1097.94</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>782.61</v>
+        <v>1051.97</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>869.22</v>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
+        <v>912.79</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -1601,42 +1601,42 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>571.85</v>
+        <v>2970</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>594.15</v>
+        <v>2822.12</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>611.17</v>
+        <v>2569.44</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>674.1799999999999</v>
+        <v>2347.06</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -1645,42 +1645,42 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4828.8</v>
+        <v>412.95</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4956.36</v>
+        <v>417.21</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>5089.44</v>
+        <v>424.78</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5129.56</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
+        <v>409.97</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -1689,42 +1689,42 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1069.7</v>
+        <v>12912</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1098.63</v>
+        <v>13119.24</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1052.25</v>
+        <v>13326.98</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>912.86</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
+        <v>14003.84</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -1733,42 +1733,42 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2114</v>
+        <v>464.9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2167.41</v>
+        <v>465.68</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2206.92</v>
+        <v>458.26</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2290.14</v>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
+        <v>420.9</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -1777,42 +1777,42 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1248.4</v>
+        <v>1805</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1257.73</v>
+        <v>1778.62</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1276.74</v>
+        <v>1686.75</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1325.93</v>
+        <v>1511.59</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -1821,42 +1821,42 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>280.55</v>
+        <v>8358.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>288.9</v>
+        <v>8164.53</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>295.19</v>
+        <v>7941.59</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>329.71</v>
+        <v>7521.22</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -1865,42 +1865,42 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>896.05</v>
+        <v>279.45</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>906.12</v>
+        <v>288.79</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>893.7</v>
+        <v>295.15</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>868.12</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
+        <v>329.7</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -1909,42 +1909,42 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1185.2</v>
+        <v>896.65</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1189.67</v>
+        <v>935.36</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1222.74</v>
+        <v>955.42</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1383.92</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
+        <v>889.63</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -1953,42 +1953,42 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1267.4</v>
+        <v>1503.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1286.48</v>
+        <v>1470.35</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1261.82</v>
+        <v>1457.63</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1183.17</v>
+        <v>1480.83</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -1997,42 +1997,42 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>375.3</v>
+        <v>4359.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>381.4</v>
+        <v>4436.25</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>383.09</v>
+        <v>4454.51</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>399.06</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
+        <v>4830.94</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -2041,42 +2041,42 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3890.8</v>
+        <v>2110.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>3959.88</v>
+        <v>2167.04</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3933.32</v>
+        <v>2206.76</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3828.92</v>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
+        <v>2290.1</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -2085,42 +2085,42 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2985</v>
+        <v>2659.2</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>3073.06</v>
+        <v>2624.91</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>3139.53</v>
+        <v>2543.77</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3266.52</v>
+        <v>2493.4</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -2129,42 +2129,42 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>12954</v>
+        <v>10795</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>13123.24</v>
+        <v>11352.12</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13328.62</v>
+        <v>11550.84</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>14004.26</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
+        <v>11757.06</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -2173,42 +2173,42 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>359.5</v>
+        <v>228.86</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>380.6</v>
+        <v>237.51</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>383.31</v>
+        <v>241.38</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>359.98</v>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
+        <v>261.09</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -2217,42 +2217,42 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1391.9</v>
+        <v>389</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1408.6</v>
+        <v>379.3</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1380.41</v>
+        <v>364.31</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1286.95</v>
+        <v>420.52</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TMPV</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -2261,42 +2261,42 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>264.25</v>
+        <v>7050</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>276.73</v>
+        <v>7135.46</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>279.5</v>
+        <v>7150.03</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>259.26</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
+        <v>6897.04</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -2305,42 +2305,42 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>288.25</v>
+        <v>4192.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>294.32</v>
+        <v>4168.38</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>298.61</v>
+        <v>4202.65</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>287.14</v>
+        <v>3991.57</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -2349,42 +2349,42 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1280.9</v>
+        <v>2724.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1329.25</v>
+        <v>2787.76</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1355.17</v>
+        <v>2759.53</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1389.32</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
+        <v>3420.43</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -2393,42 +2393,42 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1776.2</v>
+        <v>290.3</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1827.87</v>
+        <v>294.52</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1861.52</v>
+        <v>298.69</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1878.28</v>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
+        <v>287.16</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -2437,42 +2437,42 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>907.5</v>
+        <v>3050.1</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>936.39</v>
+        <v>3052.19</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>955.85</v>
+        <v>2941.67</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>889.74</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
+        <v>2806.62</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -2481,42 +2481,42 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>987.6</v>
+        <v>264.65</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>977.46</v>
+        <v>276.77</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1004.14</v>
+        <v>279.51</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>969.0599999999999</v>
+        <v>259.26</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ONGC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -2525,42 +2525,42 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1795.2</v>
+        <v>1151.3</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1813.02</v>
+        <v>1181.2</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1793.96</v>
+        <v>1238.3</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1731.57</v>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
+        <v>1394.18</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -2569,42 +2569,42 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2165</v>
+        <v>1398.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2285.75</v>
+        <v>1409.27</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2376.26</v>
+        <v>1380.68</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2722.85</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
+        <v>1287.02</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -2613,42 +2613,42 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1121.8</v>
+        <v>1260.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1164.4</v>
+        <v>1285.85</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1152.81</v>
+        <v>1261.55</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1123.31</v>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
+        <v>1183.1</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -2657,42 +2657,42 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>391.15</v>
+        <v>564.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>379.5</v>
+        <v>593.45</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>364.39</v>
+        <v>610.88</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>420.54</v>
+        <v>674.1</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -2701,42 +2701,42 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>204.56</v>
+        <v>10231</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>210.27</v>
+        <v>10283.18</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>208.19</v>
+        <v>9991.67</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>189.53</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
+        <v>9276.059999999999</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -2745,42 +2745,42 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1471.7</v>
+        <v>1674.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1467.33</v>
+        <v>1751.47</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1456.38</v>
+        <v>1781.89</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1480.51</v>
+        <v>1892.62</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -2789,42 +2789,42 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4233</v>
+        <v>1275.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>4172.24</v>
+        <v>1293.42</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4204.25</v>
+        <v>1288.13</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3991.98</v>
+        <v>1260.4</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -2833,42 +2833,42 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2754.3</v>
+        <v>1387.9</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>2790.64</v>
+        <v>1373.93</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>2760.72</v>
+        <v>1342.12</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3420.73</v>
+        <v>1380.06</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -2877,42 +2877,42 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10810</v>
+        <v>1107</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>11353.55</v>
+        <v>1162.99</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>11551.43</v>
+        <v>1152.23</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11757.21</v>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
+        <v>1123.16</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -2921,35 +2921,35 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>187.96</v>
+        <v>1764.4</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>200.11</v>
+        <v>1826.74</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>201.64</v>
+        <v>1861.05</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>221.44</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
+        <v>1878.16</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  10:25:42    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  10:46:16    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  10:25:42</t>
+          <t>08-Jun-2026  10:46:16</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  10:46:16    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  14:46:10    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  10:46:16</t>
+          <t>08-Jun-2026  14:46:10</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  14:46:10    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  05:44:30    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  14:46:10</t>
+          <t>09-Jun-2026  05:44:30</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 15 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1263.3</v>
+        <v>1264.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1327.58</v>
+        <v>1321.53</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1354.48</v>
+        <v>1350.94</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1389.15</v>
+        <v>1387.9</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>738.65</v>
+        <v>735.25</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>758.86</v>
+        <v>756.61</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>782.5700000000001</v>
+        <v>780.71</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>869.21</v>
+        <v>867.88</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2151.4</v>
+        <v>2149</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2284.46</v>
+        <v>2271.56</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2375.73</v>
+        <v>2366.83</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2722.71</v>
+        <v>2717.01</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>181.76</v>
+        <v>181.28</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>199.52</v>
+        <v>197.78</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>201.39</v>
+        <v>200.61</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>221.37</v>
+        <v>220.97</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,24 +937,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1250.2</v>
+        <v>1259.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1257.9</v>
+        <v>1258.05</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1276.81</v>
+        <v>1276.14</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.95</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1325.29</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>981.95</v>
+        <v>989.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>976.92</v>
+        <v>978.14</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1003.91</v>
+        <v>1003.36</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>969</v>
+        <v>969.21</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1813.3</v>
+        <v>1798.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1836.76</v>
+        <v>1833.1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1852.95</v>
+        <v>1850.82</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1899.89</v>
+        <v>1898.88</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1187.6</v>
+        <v>1175</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1189.9</v>
+        <v>1188.48</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1222.84</v>
+        <v>1220.96</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1383.95</v>
+        <v>1381.87</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2966</v>
+        <v>3010.4</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3071.25</v>
+        <v>3065.46</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3138.78</v>
+        <v>3133.75</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3266.33</v>
+        <v>3263.78</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3875.5</v>
+        <v>3900.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3958.42</v>
+        <v>3952.87</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3932.72</v>
+        <v>3931.44</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3828.77</v>
+        <v>3829.48</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1268.1</v>
+        <v>1276.6</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1273.56</v>
+        <v>1273.85</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1281.03</v>
+        <v>1280.86</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1248.35</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1248.63</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>202.72</v>
+        <v>202.85</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>210.09</v>
+        <v>209.4</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>208.11</v>
+        <v>207.91</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>189.51</v>
+        <v>189.64</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>248.3</v>
+        <v>244.9</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>249.61</v>
+        <v>249.16</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.75</v>
+        <v>249.56</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>264.42</v>
+        <v>264.22</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1788.8</v>
+        <v>1791.4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1812.41</v>
+        <v>1810.41</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1793.71</v>
+        <v>1793.62</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1731.5</v>
+        <v>1732.1</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1007.45</v>
+        <v>1010</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>995.45</v>
+        <v>996.84</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1004.58</v>
+        <v>1004.8</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1049.69</v>
+        <v>1049.3</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>377.1</v>
+        <v>378.45</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>381.57</v>
+        <v>381.27</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>383.16</v>
+        <v>382.98</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399.07</v>
+        <v>398.87</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>362.4</v>
+        <v>357.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>380.88</v>
+        <v>378.65</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>383.42</v>
+        <v>382.41</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.01</v>
+        <v>359.99</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1490,9 +1490,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>871.1</v>
+        <v>881.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>904.15</v>
+        <v>901.96</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>914.52</v>
+        <v>913.22</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>937.0700000000001</v>
+        <v>936.52</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1062.4</v>
+        <v>1060.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1097.94</v>
+        <v>1094.39</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1051.97</v>
+        <v>1052.31</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>912.79</v>
+        <v>914.26</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2970</v>
+        <v>2963</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2822.12</v>
+        <v>2835.54</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2569.44</v>
+        <v>2584.87</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2347.06</v>
+        <v>2353.19</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>412.95</v>
+        <v>410.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>417.21</v>
+        <v>416.61</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>424.78</v>
+        <v>424.24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>409.97</v>
+        <v>409.98</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12912</v>
+        <v>12906</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13119.24</v>
+        <v>13098.93</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13326.98</v>
+        <v>13310.47</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>14003.84</v>
+        <v>13992.92</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>464.9</v>
+        <v>464.15</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>465.68</v>
+        <v>465.53</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>458.26</v>
+        <v>458.49</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>420.9</v>
+        <v>421.33</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1805</v>
+        <v>1798.7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1778.62</v>
+        <v>1780.53</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1686.75</v>
+        <v>1691.14</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1511.59</v>
+        <v>1514.45</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8358.5</v>
+        <v>8457.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8164.53</v>
+        <v>8192.43</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>7941.59</v>
+        <v>7961.82</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7521.22</v>
+        <v>7530.54</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
         <v>279.45</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>288.79</v>
+        <v>287.9</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>295.15</v>
+        <v>294.53</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>329.7</v>
+        <v>329.2</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>896.65</v>
+        <v>903.1</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>935.36</v>
+        <v>932.29</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>955.42</v>
+        <v>953.37</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>889.63</v>
+        <v>889.77</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1503.4</v>
+        <v>1487.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1470.35</v>
+        <v>1471.99</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1457.63</v>
+        <v>1458.8</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1480.83</v>
+        <v>1480.9</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,24 +1993,24 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4359.7</v>
+        <v>4437.1</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4436.25</v>
+        <v>4436.33</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4454.51</v>
+        <v>4453.83</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4830.94</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4827.02</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2110.1</v>
+        <v>2112.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2167.04</v>
+        <v>2161.84</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2206.76</v>
+        <v>2203.07</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2290.1</v>
+        <v>2288.33</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2659.2</v>
+        <v>2673.9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2624.91</v>
+        <v>2629.58</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2543.77</v>
+        <v>2548.87</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2493.4</v>
+        <v>2495.2</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10795</v>
+        <v>10817</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11352.12</v>
+        <v>11301.15</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11550.84</v>
+        <v>11522.06</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11757.06</v>
+        <v>11747.71</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>228.86</v>
+        <v>232.54</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>237.51</v>
+        <v>237.04</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>241.38</v>
+        <v>241.04</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>261.09</v>
+        <v>260.81</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>389</v>
+        <v>389.45</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>379.3</v>
+        <v>380.26</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>364.31</v>
+        <v>365.29</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>420.52</v>
+        <v>420.21</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,24 +2257,24 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7050</v>
+        <v>7140</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7135.46</v>
+        <v>7135.9</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7150.03</v>
+        <v>7149.64</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6897.04</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>6899.46</v>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4192.4</v>
+        <v>4121.3</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4168.38</v>
+        <v>4163.89</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4202.65</v>
+        <v>4199.46</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3991.57</v>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3992.86</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2345,29 +2345,29 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2724.1</v>
+        <v>2779</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2787.76</v>
+        <v>2786.93</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2759.53</v>
+        <v>2760.3</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3420.43</v>
+        <v>3414.05</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>290.3</v>
+        <v>286.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>294.52</v>
+        <v>293.73</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>298.69</v>
+        <v>298.2</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.16</v>
+        <v>287.15</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2414,9 +2414,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3050.1</v>
+        <v>3095.6</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3052.19</v>
+        <v>3056.33</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2941.67</v>
+        <v>2947.71</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2806.62</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2809.5</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>264.65</v>
+        <v>263.25</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>276.77</v>
+        <v>275.48</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>279.51</v>
+        <v>278.87</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>259.26</v>
+        <v>259.3</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1151.3</v>
+        <v>1142</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1181.2</v>
+        <v>1177.47</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1238.3</v>
+        <v>1234.52</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1394.18</v>
+        <v>1391.67</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1398.9</v>
+        <v>1405.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1409.27</v>
+        <v>1408.88</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1380.68</v>
+        <v>1381.64</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1287.02</v>
+        <v>1288.2</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1260.7</v>
+        <v>1271.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1285.85</v>
+        <v>1284.5</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1261.55</v>
+        <v>1261.95</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1183.1</v>
+        <v>1183.99</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>564.55</v>
+        <v>561.25</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>593.45</v>
+        <v>590.39</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>610.88</v>
+        <v>608.9400000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>674.1</v>
+        <v>672.98</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10231</v>
+        <v>10315</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10283.18</v>
+        <v>10286.21</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9991.67</v>
+        <v>10004.35</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9276.059999999999</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>9286.4</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1674.6</v>
+        <v>1694.3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1751.47</v>
+        <v>1746.03</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1781.89</v>
+        <v>1778.45</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1892.62</v>
+        <v>1890.64</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1275.6</v>
+        <v>1282.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1293.42</v>
+        <v>1292.38</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1288.13</v>
+        <v>1287.91</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1260.4</v>
+        <v>1260.62</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1387.9</v>
+        <v>1389.4</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1373.93</v>
+        <v>1375.41</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1342.12</v>
+        <v>1343.97</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1380.06</v>
+        <v>1380.15</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1107</v>
+        <v>1097.8</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1162.99</v>
+        <v>1156.78</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1152.23</v>
+        <v>1150.1</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1123.16</v>
+        <v>1122.91</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1764.4</v>
+        <v>1777</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1826.74</v>
+        <v>1822.01</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1861.05</v>
+        <v>1857.76</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1878.16</v>
+        <v>1877.16</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  05:44:30    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  06:01:18    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>46</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  05:44:30</t>
+          <t>09-Jun-2026  06:01:18</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1264.1</v>
+        <v>1263.5</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1321.53</v>
+        <v>1321.48</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1350.94</v>
+        <v>1350.91</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>1387.9</v>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>735.25</v>
+        <v>733.55</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>756.61</v>
+        <v>756.45</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>780.71</v>
+        <v>780.65</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>867.88</v>
+        <v>867.86</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2149</v>
+        <v>2149.6</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2271.56</v>
+        <v>2271.61</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2366.83</v>
+        <v>2366.86</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2717.01</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>181.28</v>
+        <v>181.45</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>197.78</v>
+        <v>197.8</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>200.61</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>220.97</v>
+        <v>220.98</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1259.5</v>
+        <v>1259.7</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1258.05</v>
+        <v>1258.07</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>1276.14</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>989.7</v>
+        <v>989.55</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>978.14</v>
+        <v>978.13</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1003.36</v>
+        <v>1003.35</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>969.21</v>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1798.4</v>
+        <v>1796</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1833.1</v>
+        <v>1832.87</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1850.82</v>
+        <v>1850.72</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1898.88</v>
+        <v>1898.86</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1175</v>
+        <v>1173.9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1188.48</v>
+        <v>1188.37</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1220.96</v>
+        <v>1220.92</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1381.87</v>
+        <v>1381.86</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3010.4</v>
+        <v>3012</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3065.46</v>
+        <v>3065.61</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3133.75</v>
+        <v>3133.81</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3263.78</v>
+        <v>3263.8</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3900.1</v>
+        <v>3905</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3952.87</v>
+        <v>3953.33</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3931.44</v>
+        <v>3931.63</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3829.48</v>
+        <v>3829.52</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1276.6</v>
+        <v>1276.7</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1273.85</v>
+        <v>1273.86</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>1280.86</v>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>202.85</v>
+        <v>202.21</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>209.4</v>
+        <v>209.34</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>207.91</v>
+        <v>207.88</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>189.64</v>
+        <v>189.63</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>244.9</v>
+        <v>244.65</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>249.16</v>
+        <v>249.14</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.56</v>
+        <v>249.55</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>264.22</v>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1791.4</v>
+        <v>1788.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1810.41</v>
+        <v>1810.11</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1793.62</v>
+        <v>1793.5</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1732.1</v>
+        <v>1732.07</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1010</v>
+        <v>1006.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>996.84</v>
+        <v>996.49</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1004.8</v>
+        <v>1004.65</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1049.3</v>
+        <v>1049.26</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>378.45</v>
+        <v>378.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>381.27</v>
+        <v>381.28</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>382.98</v>
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>357.5</v>
+        <v>356.9</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>378.65</v>
+        <v>378.6</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>382.41</v>
+        <v>382.38</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>359.99</v>
+        <v>359.98</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>881.2</v>
+        <v>876.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>901.96</v>
+        <v>901.51</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>913.22</v>
+        <v>913.03</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>936.52</v>
+        <v>936.47</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1060.7</v>
+        <v>1060.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1094.39</v>
+        <v>1094.34</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1052.31</v>
+        <v>1052.29</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>914.26</v>
+        <v>914.25</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2963</v>
+        <v>2972.3</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2835.54</v>
+        <v>2836.42</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2584.87</v>
+        <v>2585.24</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2353.19</v>
+        <v>2353.28</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1645,16 +1645,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>410.9</v>
+        <v>412.05</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>416.61</v>
+        <v>416.71</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>424.24</v>
+        <v>424.28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>409.98</v>
+        <v>409.99</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12906</v>
+        <v>12907</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13098.93</v>
+        <v>13099.02</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13310.47</v>
+        <v>13310.51</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13992.92</v>
+        <v>13992.93</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>464.15</v>
+        <v>463.1</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>465.53</v>
+        <v>465.43</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>458.49</v>
+        <v>458.45</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>421.33</v>
+        <v>421.32</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1777,16 +1777,16 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1798.7</v>
+        <v>1795</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1780.53</v>
+        <v>1780.18</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1691.14</v>
+        <v>1691</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1514.45</v>
+        <v>1514.41</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8457.5</v>
+        <v>8445</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8192.43</v>
+        <v>8191.24</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>7961.82</v>
+        <v>7961.33</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7530.54</v>
+        <v>7530.42</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>279.45</v>
+        <v>279.65</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.9</v>
+        <v>287.92</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>294.53</v>
+        <v>294.54</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>329.2</v>
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>903.1</v>
+        <v>898.4</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>932.29</v>
+        <v>931.84</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>953.37</v>
+        <v>953.1900000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>889.77</v>
+        <v>889.72</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1487.6</v>
+        <v>1485.5</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1471.99</v>
+        <v>1471.79</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1458.8</v>
+        <v>1458.72</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1480.9</v>
+        <v>1480.88</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4437.1</v>
+        <v>4448</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4436.33</v>
+        <v>4437.37</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4453.83</v>
+        <v>4454.26</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4827.02</v>
+        <v>4827.13</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2112.5</v>
+        <v>2122</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2161.84</v>
+        <v>2162.75</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2203.07</v>
+        <v>2203.44</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2288.33</v>
+        <v>2288.42</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2673.9</v>
+        <v>2675.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2629.58</v>
+        <v>2629.76</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2548.87</v>
+        <v>2548.95</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2495.2</v>
+        <v>2495.21</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10817</v>
+        <v>10828</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11301.15</v>
+        <v>11302.2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11522.06</v>
+        <v>11522.49</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11747.71</v>
+        <v>11747.82</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>232.54</v>
+        <v>232.61</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>237.04</v>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>389.45</v>
+        <v>388.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>380.26</v>
+        <v>380.2</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>365.29</v>
+        <v>365.27</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>420.21</v>
+        <v>420.2</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7140</v>
+        <v>7145.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7135.9</v>
+        <v>7136.42</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7149.64</v>
+        <v>7149.85</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6899.46</v>
+        <v>6899.51</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4121.3</v>
+        <v>4121.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4163.89</v>
+        <v>4163.9</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4199.46</v>
+        <v>4199.47</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>3992.86</v>
@@ -2349,25 +2349,25 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2779</v>
+        <v>2750.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2786.93</v>
+        <v>2784.18</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2760.3</v>
+        <v>2759.16</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3414.05</v>
+        <v>3413.76</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>286.2</v>
+        <v>286.65</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>293.73</v>
+        <v>293.77</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>298.2</v>
+        <v>298.21</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.15</v>
+        <v>287.16</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3095.6</v>
+        <v>3094.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3056.33</v>
+        <v>3056.21</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2947.71</v>
+        <v>2947.66</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2809.5</v>
+        <v>2809.48</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>263.25</v>
+        <v>262.55</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>275.48</v>
+        <v>275.41</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>278.87</v>
+        <v>278.85</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>259.3</v>
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1142</v>
+        <v>1141.3</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1177.47</v>
+        <v>1177.4</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1234.52</v>
+        <v>1234.5</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1391.67</v>
+        <v>1391.66</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1405.2</v>
+        <v>1405</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1408.88</v>
+        <v>1408.86</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1381.64</v>
+        <v>1381.63</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1288.2</v>
+        <v>1288.19</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1271.7</v>
+        <v>1266.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1284.5</v>
+        <v>1283.98</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1261.95</v>
+        <v>1261.74</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1183.99</v>
+        <v>1183.93</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>561.25</v>
+        <v>562.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>590.39</v>
+        <v>590.51</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>608.9400000000001</v>
+        <v>608.99</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>672.98</v>
+        <v>672.99</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10315</v>
+        <v>10311</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10286.21</v>
+        <v>10285.83</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10004.35</v>
+        <v>10004.2</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9286.4</v>
+        <v>9286.360000000001</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1694.3</v>
+        <v>1686.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1746.03</v>
+        <v>1745.29</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1778.45</v>
+        <v>1778.15</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1890.64</v>
+        <v>1890.57</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1282.5</v>
+        <v>1278.1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1292.38</v>
+        <v>1291.96</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1287.91</v>
+        <v>1287.73</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1260.62</v>
+        <v>1260.58</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1389.4</v>
+        <v>1389.5</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>1375.41</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1343.97</v>
+        <v>1343.98</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>1380.15</v>
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1097.8</v>
+        <v>1098.7</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1156.78</v>
+        <v>1156.86</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1150.1</v>
+        <v>1150.13</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>1122.91</v>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  06:01:18    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  10:16:21    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -598,20 +598,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  06:01:18</t>
+          <t>09-Jun-2026  10:16:21</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 18 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 14 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 17 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1263.5</v>
+        <v>1269.2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1321.48</v>
+        <v>1322.02</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1350.91</v>
+        <v>1351.14</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1387.9</v>
+        <v>1387.95</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>733.55</v>
+        <v>738.35</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>756.45</v>
+        <v>756.91</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>780.65</v>
+        <v>780.84</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>867.86</v>
+        <v>867.91</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2149.6</v>
+        <v>2151</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2271.61</v>
+        <v>2271.75</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2366.86</v>
+        <v>2366.91</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2717.01</v>
+        <v>2717.03</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>181.45</v>
+        <v>181.67</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>197.8</v>
+        <v>197.82</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>200.61</v>
+        <v>200.62</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>220.98</v>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1259.7</v>
+        <v>1275</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1258.07</v>
+        <v>1259.53</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1276.14</v>
+        <v>1276.74</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.29</v>
+        <v>1325.44</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -985,16 +985,16 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>989.55</v>
+        <v>1002.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>978.13</v>
+        <v>979.38</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1003.35</v>
+        <v>1003.87</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>969.21</v>
+        <v>969.34</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1832.87</v>
+        <v>1833.16</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1850.72</v>
+        <v>1850.84</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1898.86</v>
+        <v>1898.89</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1173.9</v>
+        <v>1180.3</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1188.37</v>
+        <v>1188.98</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1220.92</v>
+        <v>1221.17</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1381.86</v>
+        <v>1381.92</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3012</v>
+        <v>2990.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3065.61</v>
+        <v>3063.53</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3133.81</v>
+        <v>3132.95</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3263.8</v>
+        <v>3263.58</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3905</v>
+        <v>3900.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3953.33</v>
+        <v>3952.92</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3931.63</v>
+        <v>3931.46</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3829.52</v>
+        <v>3829.48</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1276.7</v>
+        <v>1292.4</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1273.86</v>
+        <v>1275.36</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1280.86</v>
+        <v>1281.48</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1248.63</v>
+        <v>1248.79</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>202.21</v>
+        <v>203.18</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>209.34</v>
+        <v>209.43</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>207.88</v>
+        <v>207.92</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>189.63</v>
+        <v>189.64</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>244.65</v>
+        <v>245.65</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>249.14</v>
+        <v>249.24</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.55</v>
+        <v>249.59</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>264.22</v>
+        <v>264.23</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1788.3</v>
+        <v>1779</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1810.11</v>
+        <v>1809.23</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1793.5</v>
+        <v>1793.13</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1732.07</v>
+        <v>1731.97</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1381,25 +1381,25 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1006.4</v>
+        <v>1003.1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>996.49</v>
+        <v>996.1799999999999</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1004.65</v>
+        <v>1004.52</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1049.26</v>
+        <v>1049.23</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -1425,20 +1425,20 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>378.5</v>
+        <v>381.7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>381.28</v>
+        <v>381.58</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>382.98</v>
+        <v>383.11</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.87</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>398.9</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>356.9</v>
+        <v>355.65</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>378.6</v>
+        <v>378.48</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>382.38</v>
+        <v>382.33</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>359.98</v>
+        <v>359.97</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>876.5</v>
+        <v>886.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>901.51</v>
+        <v>902.5</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>913.03</v>
+        <v>913.4400000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>936.47</v>
+        <v>936.5700000000001</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1060.2</v>
+        <v>1076.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1094.34</v>
+        <v>1095.91</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1052.29</v>
+        <v>1052.94</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>914.25</v>
+        <v>914.42</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2972.3</v>
+        <v>2979.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2836.42</v>
+        <v>2837.15</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2585.24</v>
+        <v>2585.53</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2353.28</v>
+        <v>2353.36</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1689,20 +1689,20 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12907</v>
+        <v>13120</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13099.02</v>
+        <v>13119.31</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13310.51</v>
+        <v>13318.86</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13992.93</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>13995.05</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -1733,20 +1733,20 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>463.1</v>
+        <v>466.9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>465.43</v>
+        <v>465.79</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>458.45</v>
+        <v>458.6</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>421.32</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>421.36</v>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
@@ -1777,16 +1777,16 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1795</v>
+        <v>1826.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1780.18</v>
+        <v>1783.17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1691</v>
+        <v>1692.23</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1514.41</v>
+        <v>1514.72</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8445</v>
+        <v>8524</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8191.24</v>
+        <v>8198.76</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>7961.33</v>
+        <v>7964.42</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7530.42</v>
+        <v>7531.2</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>279.65</v>
+        <v>280</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.92</v>
+        <v>287.95</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>294.54</v>
+        <v>294.55</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>329.2</v>
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>898.4</v>
+        <v>911.7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>931.84</v>
+        <v>933.11</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>953.1900000000001</v>
+        <v>953.71</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>889.72</v>
+        <v>889.85</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1485.5</v>
+        <v>1483.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1471.79</v>
+        <v>1471.63</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1458.72</v>
+        <v>1458.65</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1480.88</v>
+        <v>1480.86</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4448</v>
+        <v>4537.6</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4437.37</v>
+        <v>4445.9</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4454.26</v>
+        <v>4457.77</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4827.13</v>
+        <v>4828.02</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2122</v>
+        <v>2132.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2162.75</v>
+        <v>2163.78</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2203.44</v>
+        <v>2203.86</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2288.42</v>
+        <v>2288.53</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2675.8</v>
+        <v>2708.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2629.76</v>
+        <v>2632.83</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2548.95</v>
+        <v>2550.21</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2495.21</v>
+        <v>2495.54</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10828</v>
+        <v>10911</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11302.2</v>
+        <v>11310.11</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11522.49</v>
+        <v>11525.75</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11747.82</v>
+        <v>11748.65</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>232.61</v>
+        <v>234.21</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>237.04</v>
+        <v>237.2</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>241.04</v>
+        <v>241.1</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.81</v>
+        <v>260.82</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>388.8</v>
+        <v>387.8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>380.2</v>
+        <v>380.11</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>365.27</v>
+        <v>365.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>420.2</v>
+        <v>420.19</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7145.5</v>
+        <v>7203</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7136.42</v>
+        <v>7141.9</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7149.85</v>
+        <v>7152.11</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6899.51</v>
+        <v>6900.09</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4121.4</v>
+        <v>4104.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4163.9</v>
+        <v>4162.33</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4199.47</v>
+        <v>4198.82</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3992.86</v>
+        <v>3992.7</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2750.1</v>
+        <v>2771.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2784.18</v>
+        <v>2786.2</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2759.16</v>
+        <v>2759.99</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3413.76</v>
+        <v>3413.97</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>286.65</v>
+        <v>285.7</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>293.77</v>
+        <v>293.68</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>298.21</v>
+        <v>298.18</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.16</v>
+        <v>287.15</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3094.4</v>
+        <v>3095.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3056.21</v>
+        <v>3056.32</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2947.66</v>
+        <v>2947.71</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2809.48</v>
+        <v>2809.49</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>262.55</v>
+        <v>259</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>275.41</v>
+        <v>275.08</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>278.85</v>
+        <v>278.71</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>259.3</v>
+        <v>259.26</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2502,9 +2502,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1141.3</v>
+        <v>1146.3</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1177.4</v>
+        <v>1177.88</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1234.5</v>
+        <v>1234.69</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1391.66</v>
+        <v>1391.71</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2569,20 +2569,20 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1405</v>
+        <v>1410.4</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1408.86</v>
+        <v>1409.37</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1381.63</v>
+        <v>1381.85</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1288.19</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1288.25</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1266.2</v>
+        <v>1261.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1283.98</v>
+        <v>1283.55</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1261.74</v>
+        <v>1261.56</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1183.93</v>
+        <v>1183.89</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>562.55</v>
+        <v>560.6</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>590.51</v>
+        <v>590.3200000000001</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>608.99</v>
+        <v>608.91</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>672.99</v>
+        <v>672.97</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,20 +2701,20 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10311</v>
+        <v>10184</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10285.83</v>
+        <v>10273.73</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10004.2</v>
+        <v>9999.219999999999</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9286.360000000001</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>9285.09</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1686.6</v>
+        <v>1693.1</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1745.29</v>
+        <v>1745.91</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1778.15</v>
+        <v>1778.41</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1890.57</v>
+        <v>1890.63</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1278.1</v>
+        <v>1268.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1291.96</v>
+        <v>1291.04</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1287.73</v>
+        <v>1287.36</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1260.58</v>
+        <v>1260.48</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1389.5</v>
+        <v>1376.5</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1375.41</v>
+        <v>1374.18</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1343.98</v>
+        <v>1343.47</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1380.15</v>
+        <v>1380.02</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1098.7</v>
+        <v>1106.5</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1156.86</v>
+        <v>1157.61</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1150.13</v>
+        <v>1150.44</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.91</v>
+        <v>1122.99</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1777</v>
+        <v>1769.1</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1822.01</v>
+        <v>1821.25</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1857.76</v>
+        <v>1857.45</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1877.16</v>
+        <v>1877.08</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  10:16:21    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  10:42:12    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  10:16:21</t>
+          <t>09-Jun-2026  10:42:12</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  10:42:12    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  13:42:34    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  10:42:12</t>
+          <t>09-Jun-2026  13:42:34</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  13:42:34    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 10-Jun-2026  14:20:29    |    Closing Price Date: 10-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>34</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  13:42:34</t>
+          <t>10-Jun-2026  14:20:29</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 18 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 17 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1269.2</v>
+        <v>1258.8</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1322.02</v>
+        <v>1316</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1351.14</v>
+        <v>1347.52</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1387.95</v>
+        <v>1386.67</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>738.35</v>
+        <v>746.85</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>756.91</v>
+        <v>755.95</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>780.84</v>
+        <v>779.5</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>867.91</v>
+        <v>866.71</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2151</v>
+        <v>2153.9</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2271.75</v>
+        <v>2260.52</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2366.91</v>
+        <v>2358.56</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2717.03</v>
+        <v>2711.42</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>181.67</v>
+        <v>178.93</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>197.82</v>
+        <v>196.02</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>200.62</v>
+        <v>199.77</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>220.98</v>
+        <v>220.56</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,29 +937,29 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1275</v>
+        <v>1293.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1259.53</v>
+        <v>1262.74</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1276.74</v>
+        <v>1277.39</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.44</v>
+        <v>1325.12</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1002.7</v>
+        <v>1003.25</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>979.38</v>
+        <v>981.65</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1003.87</v>
+        <v>1003.84</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>969.34</v>
+        <v>969.6799999999999</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1799</v>
+        <v>1775.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1833.16</v>
+        <v>1827.64</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1850.84</v>
+        <v>1847.87</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1898.89</v>
+        <v>1897.66</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1180.3</v>
+        <v>1145.3</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1188.98</v>
+        <v>1162.04</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1221.17</v>
+        <v>1193.34</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1381.92</v>
+        <v>1350.59</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2990.1</v>
+        <v>2952.5</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3063.53</v>
+        <v>3052.95</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3132.95</v>
+        <v>3125.87</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3263.58</v>
+        <v>3260.48</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3900.6</v>
+        <v>3917.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3952.92</v>
+        <v>3949.54</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3931.46</v>
+        <v>3930.91</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3829.48</v>
+        <v>3830.36</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1292.4</v>
+        <v>1314.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1275.36</v>
+        <v>1279.09</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1281.48</v>
+        <v>1282.77</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1248.79</v>
+        <v>1249.44</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>203.18</v>
+        <v>199.31</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>209.43</v>
+        <v>208.47</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>207.92</v>
+        <v>207.58</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>189.64</v>
+        <v>189.74</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>245.65</v>
+        <v>239.8</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>249.24</v>
+        <v>248.34</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.59</v>
+        <v>249.2</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>264.23</v>
+        <v>263.99</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1779</v>
+        <v>1786.4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1809.23</v>
+        <v>1807.05</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1793.13</v>
+        <v>1792.87</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1731.97</v>
+        <v>1732.52</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1003.1</v>
+        <v>1010.1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>996.1799999999999</v>
+        <v>997.51</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1004.52</v>
+        <v>1004.74</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1049.23</v>
+        <v>1048.84</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -1421,29 +1421,29 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>381.7</v>
+        <v>388.1</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>381.58</v>
+        <v>382.2</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>383.11</v>
+        <v>383.3</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.9</v>
+        <v>398.79</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>355.65</v>
+        <v>351.65</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>378.48</v>
+        <v>375.92</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>382.33</v>
+        <v>381.13</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>359.97</v>
+        <v>359.89</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>886.9</v>
+        <v>884.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>902.5</v>
+        <v>900.75</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>913.4400000000001</v>
+        <v>912.29</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>936.5700000000001</v>
+        <v>936.05</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,29 +1553,29 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1076.7</v>
+        <v>1039.3</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1095.91</v>
+        <v>1090.52</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1052.94</v>
+        <v>1052.4</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>914.42</v>
+        <v>915.66</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2979.9</v>
+        <v>2931.1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2837.15</v>
+        <v>2846.1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2585.53</v>
+        <v>2599.09</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2353.36</v>
+        <v>2359.11</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>412.05</v>
+        <v>408.35</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>416.71</v>
+        <v>415.92</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>424.28</v>
+        <v>423.66</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>409.99</v>
+        <v>409.98</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1666,9 +1666,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13120</v>
+        <v>13073</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13119.31</v>
+        <v>13114.9</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13318.86</v>
+        <v>13309.22</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13995.05</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>13985.87</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -1729,29 +1729,29 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>466.9</v>
+        <v>451</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>465.79</v>
+        <v>464.39</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>458.6</v>
+        <v>458.3</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>421.36</v>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>421.65</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1826.4</v>
+        <v>1821.2</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1783.17</v>
+        <v>1786.79</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1692.23</v>
+        <v>1697.29</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1514.72</v>
+        <v>1517.77</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8524</v>
+        <v>8488.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8198.76</v>
+        <v>8226.360000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>7964.42</v>
+        <v>7984.98</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7531.2</v>
+        <v>7540.73</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>280</v>
+        <v>283.65</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.95</v>
+        <v>287.54</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>294.55</v>
+        <v>294.13</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>329.2</v>
+        <v>328.75</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>911.7</v>
+        <v>897.35</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>933.11</v>
+        <v>929.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>953.71</v>
+        <v>951.5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>889.85</v>
+        <v>889.9299999999999</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1483.8</v>
+        <v>1478.9</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1471.63</v>
+        <v>1472.32</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1458.65</v>
+        <v>1459.45</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1480.86</v>
+        <v>1480.84</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1974,9 +1974,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4537.6</v>
+        <v>4524.9</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4445.9</v>
+        <v>4453.43</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4457.77</v>
+        <v>4460.4</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4828.02</v>
+        <v>4825.01</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,24 +2037,24 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2132.8</v>
+        <v>2169.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2163.78</v>
+        <v>2164.32</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2203.86</v>
+        <v>2202.52</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2288.53</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2287.35</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2708.1</v>
+        <v>2715.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2632.83</v>
+        <v>2640.67</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2550.21</v>
+        <v>2556.68</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2495.54</v>
+        <v>2497.72</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10911</v>
+        <v>10866</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11310.11</v>
+        <v>11267.81</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11525.75</v>
+        <v>11499.88</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11748.65</v>
+        <v>11739.86</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>234.21</v>
+        <v>230.17</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>237.2</v>
+        <v>236.53</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>241.1</v>
+        <v>240.67</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.82</v>
+        <v>260.52</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>387.8</v>
+        <v>381</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>380.11</v>
+        <v>380.19</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>365.23</v>
+        <v>365.85</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>420.19</v>
+        <v>419.8</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7203</v>
+        <v>7219.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7141.9</v>
+        <v>7149.29</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7152.11</v>
+        <v>7154.75</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6900.09</v>
+        <v>6903.26</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4104.9</v>
+        <v>4042.1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4162.33</v>
+        <v>4150.88</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4198.82</v>
+        <v>4192.67</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3992.7</v>
+        <v>3993.19</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,29 +2345,29 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2771.3</v>
+        <v>2754.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2786.2</v>
+        <v>2783.2</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2759.99</v>
+        <v>2759.79</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3413.97</v>
+        <v>3407.42</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -2389,17 +2389,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>285.7</v>
+        <v>287.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>293.68</v>
+        <v>293.06</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>298.18</v>
+        <v>297.75</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>287.15</v>
@@ -2414,9 +2414,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3095.5</v>
+        <v>3071.2</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3056.32</v>
+        <v>3057.73</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2947.71</v>
+        <v>2952.55</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2809.49</v>
+        <v>2812.1</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>259</v>
+        <v>251.9</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>275.08</v>
+        <v>272.87</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>278.71</v>
+        <v>277.66</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>259.26</v>
+        <v>259.19</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1146.3</v>
+        <v>1132.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1177.88</v>
+        <v>1173.52</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1234.69</v>
+        <v>1230.67</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1391.71</v>
+        <v>1389.13</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1410.4</v>
+        <v>1438.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1409.37</v>
+        <v>1412.13</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1381.85</v>
+        <v>1384.06</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1288.25</v>
+        <v>1289.74</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1261.7</v>
+        <v>1269.8</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1283.55</v>
+        <v>1282.24</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1261.56</v>
+        <v>1261.88</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1183.89</v>
+        <v>1184.74</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>560.6</v>
+        <v>549.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>590.3200000000001</v>
+        <v>586.4400000000001</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>608.91</v>
+        <v>606.58</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>672.97</v>
+        <v>671.75</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10184</v>
+        <v>10144</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10273.73</v>
+        <v>10261.38</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9999.219999999999</v>
+        <v>10004.89</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9285.09</v>
+        <v>9293.639999999999</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1693.1</v>
+        <v>1664.2</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1745.91</v>
+        <v>1738.13</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1778.41</v>
+        <v>1773.93</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1890.63</v>
+        <v>1888.38</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1268.5</v>
+        <v>1271.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1291.04</v>
+        <v>1289.2</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1287.36</v>
+        <v>1286.74</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1260.48</v>
+        <v>1260.59</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1376.5</v>
+        <v>1377</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1374.18</v>
+        <v>1374.45</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1343.47</v>
+        <v>1344.78</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1380.02</v>
+        <v>1379.99</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1106.5</v>
+        <v>1108</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1157.61</v>
+        <v>1152.88</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1150.44</v>
+        <v>1148.78</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.99</v>
+        <v>1122.84</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>10-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1769.1</v>
+        <v>1728.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1821.25</v>
+        <v>1812.44</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1857.45</v>
+        <v>1852.4</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1877.08</v>
+        <v>1875.6</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 10-Jun-2026  14:20:29    |    Closing Price Date: 10-Jun-2026</t>
+          <t>Scan Run: 11-Jun-2026  05:33:29    |    Closing Price Date: 11-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>40</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>10-Jun-2026  14:20:29</t>
+          <t>11-Jun-2026  05:33:29</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 17 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 17 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1258.8</v>
+        <v>1265.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1316</v>
+        <v>1311.15</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1347.52</v>
+        <v>1344.28</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1386.67</v>
+        <v>1385.06</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>746.85</v>
+        <v>743.3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>755.95</v>
+        <v>754.75</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>779.5</v>
+        <v>778.08</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>866.71</v>
+        <v>865.66</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2153.9</v>
+        <v>2138.3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2260.52</v>
+        <v>2248.88</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2358.56</v>
+        <v>2349.92</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2711.42</v>
+        <v>2707.31</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>178.93</v>
+        <v>177.29</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>196.02</v>
+        <v>194.24</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>199.77</v>
+        <v>198.89</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>220.56</v>
+        <v>219.98</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1293.3</v>
+        <v>1322.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1262.74</v>
+        <v>1268.43</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1277.39</v>
+        <v>1279.16</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.12</v>
+        <v>1325.27</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1003.25</v>
+        <v>1000.45</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>981.65</v>
+        <v>983.4400000000001</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1003.84</v>
+        <v>1003.71</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>969.6799999999999</v>
+        <v>970.84</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1775.2</v>
+        <v>1788.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1827.64</v>
+        <v>1823.93</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1847.87</v>
+        <v>1845.55</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1897.66</v>
+        <v>1895.71</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1145.3</v>
+        <v>1119.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1162.04</v>
+        <v>1158</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1193.34</v>
+        <v>1190.45</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1350.59</v>
+        <v>1347.46</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2952.5</v>
+        <v>2946.5</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3052.95</v>
+        <v>3042.81</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3125.87</v>
+        <v>3118.84</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3260.48</v>
+        <v>3257.42</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3917.5</v>
+        <v>3862.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3949.54</v>
+        <v>3941.25</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3930.91</v>
+        <v>3928.23</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3830.36</v>
+        <v>3831.34</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1314.5</v>
+        <v>1325.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1279.09</v>
+        <v>1283.47</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1282.77</v>
+        <v>1284.43</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1249.44</v>
+        <v>1249.96</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>199.31</v>
+        <v>198.07</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>208.47</v>
+        <v>207.48</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>207.58</v>
+        <v>207.21</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>189.74</v>
+        <v>189.86</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>239.8</v>
+        <v>234.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>248.34</v>
+        <v>247.02</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.2</v>
+        <v>248.63</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>263.99</v>
+        <v>263.93</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1786.4</v>
+        <v>1792.2</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1807.05</v>
+        <v>1805.64</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1792.87</v>
+        <v>1792.84</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1732.52</v>
+        <v>1732.32</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1010.1</v>
+        <v>1009</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>997.51</v>
+        <v>998.6</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1004.74</v>
+        <v>1004.91</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1048.84</v>
+        <v>1049.07</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>388.1</v>
+        <v>389.1</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>382.2</v>
+        <v>382.86</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>383.3</v>
+        <v>383.53</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.79</v>
+        <v>398.64</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>351.65</v>
+        <v>351.4</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>375.92</v>
+        <v>373.59</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>381.13</v>
+        <v>379.96</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>359.89</v>
+        <v>359.77</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>884.1</v>
+        <v>873.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>900.75</v>
+        <v>898.1900000000001</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>912.29</v>
+        <v>910.79</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>936.05</v>
+        <v>935.25</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1039.3</v>
+        <v>1031.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1090.52</v>
+        <v>1084.94</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1052.4</v>
+        <v>1051.6</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>915.66</v>
+        <v>917.03</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2931.1</v>
+        <v>2943.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2846.1</v>
+        <v>2855.34</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2599.09</v>
+        <v>2612.58</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2359.11</v>
+        <v>2366.1</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>408.35</v>
+        <v>404.3</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>415.92</v>
+        <v>414.81</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>423.66</v>
+        <v>422.9</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>409.98</v>
+        <v>410.23</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13073</v>
+        <v>13026</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13114.9</v>
+        <v>13106.43</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13309.22</v>
+        <v>13298.11</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13985.87</v>
+        <v>13969.56</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>451</v>
+        <v>448.7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>464.39</v>
+        <v>462.89</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>458.3</v>
+        <v>457.93</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>421.65</v>
+        <v>422.06</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1821.2</v>
+        <v>1796.5</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1786.79</v>
+        <v>1787.72</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1697.29</v>
+        <v>1701.18</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1517.77</v>
+        <v>1520.75</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8488.5</v>
+        <v>8457.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8226.360000000001</v>
+        <v>8248.370000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>7984.98</v>
+        <v>8003.51</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7540.73</v>
+        <v>7550.6</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>283.65</v>
+        <v>281.85</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.54</v>
+        <v>287</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>294.13</v>
+        <v>293.64</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>328.75</v>
+        <v>328.18</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>897.35</v>
+        <v>881.4</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>929.7</v>
+        <v>925.1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>951.5</v>
+        <v>948.75</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>889.9299999999999</v>
+        <v>890.34</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1930,9 +1930,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
@@ -1949,24 +1949,24 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1478.9</v>
+        <v>1466</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1472.32</v>
+        <v>1471.72</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1459.45</v>
+        <v>1459.7</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1480.84</v>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1480.49</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4524.9</v>
+        <v>4506.6</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4453.43</v>
+        <v>4458.49</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4460.4</v>
+        <v>4462.22</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4825.01</v>
+        <v>4827.63</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,24 +2037,24 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2169.5</v>
+        <v>2139.9</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2164.32</v>
+        <v>2162</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2202.52</v>
+        <v>2200.06</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2287.35</v>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2285.06</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2715.1</v>
+        <v>2691</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2640.67</v>
+        <v>2645.46</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2556.68</v>
+        <v>2561.95</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2497.72</v>
+        <v>2498.19</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10866</v>
+        <v>10808</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11267.81</v>
+        <v>11224.02</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11499.88</v>
+        <v>11472.74</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11739.86</v>
+        <v>11731.84</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>230.17</v>
+        <v>227.25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>236.53</v>
+        <v>235.64</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.67</v>
+        <v>240.15</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.52</v>
+        <v>260.42</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,24 +2213,24 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>381</v>
+        <v>376.25</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>380.19</v>
+        <v>379.82</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>365.85</v>
+        <v>366.25</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>419.8</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>419.29</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2257,29 +2257,29 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7219.5</v>
+        <v>7134.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7149.29</v>
+        <v>7147.88</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7154.75</v>
+        <v>7153.96</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6903.26</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6901.69</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4042.1</v>
+        <v>4024.2</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4150.88</v>
+        <v>4138.82</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4192.67</v>
+        <v>4186.07</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3993.19</v>
+        <v>3992.07</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2754.7</v>
+        <v>2680.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2783.2</v>
+        <v>2773.42</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2759.79</v>
+        <v>2756.68</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3407.42</v>
+        <v>3402.45</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>287.2</v>
+        <v>288.6</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>293.06</v>
+        <v>292.64</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>297.75</v>
+        <v>297.39</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.15</v>
+        <v>287.23</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3071.2</v>
+        <v>3086.7</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3057.73</v>
+        <v>3060.49</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2952.55</v>
+        <v>2957.81</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2812.1</v>
+        <v>2815.56</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>251.9</v>
+        <v>253.6</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>272.87</v>
+        <v>271.03</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>277.66</v>
+        <v>276.71</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>259.19</v>
+        <v>259.2</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1132.1</v>
+        <v>1103.7</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1173.52</v>
+        <v>1166.87</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1230.67</v>
+        <v>1225.69</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1389.13</v>
+        <v>1384.79</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1438.3</v>
+        <v>1439.9</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1412.13</v>
+        <v>1414.77</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1384.06</v>
+        <v>1386.25</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1289.74</v>
+        <v>1290.41</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1269.8</v>
+        <v>1275.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1282.24</v>
+        <v>1281.61</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1261.88</v>
+        <v>1262.42</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1184.74</v>
+        <v>1185.56</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>549.55</v>
+        <v>546.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>586.4400000000001</v>
+        <v>582.66</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>606.58</v>
+        <v>604.23</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>671.75</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10144</v>
+        <v>10149</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10261.38</v>
+        <v>10250.67</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10004.89</v>
+        <v>10010.54</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9293.639999999999</v>
+        <v>9286.43</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1664.2</v>
+        <v>1651</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1738.13</v>
+        <v>1729.83</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1773.93</v>
+        <v>1769.11</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1888.38</v>
+        <v>1883.95</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1271.7</v>
+        <v>1276.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1289.2</v>
+        <v>1288.03</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1286.74</v>
+        <v>1286.36</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1260.59</v>
+        <v>1260.78</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1377</v>
+        <v>1383.6</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1374.45</v>
+        <v>1375.32</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1344.78</v>
+        <v>1346.3</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1379.99</v>
+        <v>1379.79</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1108</v>
+        <v>1111.4</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1152.88</v>
+        <v>1148.93</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1148.78</v>
+        <v>1147.31</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.84</v>
+        <v>1122.76</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>10-Jun-2026</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1728.7</v>
+        <v>1717.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1812.44</v>
+        <v>1803.42</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1852.4</v>
+        <v>1847.12</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1875.6</v>
+        <v>1873.37</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,13 +157,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 11-Jun-2026  14:33:38    |    Closing Price Date: 11-Jun-2026</t>
+          <t>Scan Run: 12-Jun-2026  14:07:55    |    Closing Price Date: 12-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>11-Jun-2026  14:33:38</t>
+          <t>12-Jun-2026  14:07:55</t>
         </is>
       </c>
     </row>
@@ -617,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 24 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 18 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 22 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 19 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 22 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1263</v>
+        <v>1293</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1310.95</v>
+        <v>1309.24</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1344.2</v>
+        <v>1342.19</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1385.04</v>
+        <v>1384.71</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,24 +802,24 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>744.6</v>
+        <v>772.45</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>754.87</v>
+        <v>756.54</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>778.13</v>
+        <v>777.91</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>865.67</v>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>864.3200000000001</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -841,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2135.6</v>
+        <v>2161.4</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2248.63</v>
+        <v>2240.32</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2349.82</v>
+        <v>2342.43</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2707.29</v>
+        <v>2702.47</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>177.37</v>
+        <v>180.14</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>194.24</v>
+        <v>192.9</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>198.89</v>
+        <v>198.16</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>219.98</v>
+        <v>219.8</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1317</v>
+        <v>1340.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1267.91</v>
+        <v>1274.85</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1278.95</v>
+        <v>1281.37</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1325.22</v>
+        <v>1325.6</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -954,9 +959,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -973,29 +978,29 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1000.7</v>
+        <v>1017.15</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>983.47</v>
+        <v>986.67</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1003.72</v>
+        <v>1004.25</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>970.84</v>
+        <v>971.89</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -1017,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1782.6</v>
+        <v>1822.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1823.35</v>
+        <v>1823.27</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1845.31</v>
+        <v>1844.42</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1895.65</v>
+        <v>1896.74</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1114.6</v>
+        <v>1116.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1157.52</v>
+        <v>1153.6</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1190.25</v>
+        <v>1187.36</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1347.41</v>
+        <v>1346.06</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3000.9</v>
+        <v>3042.9</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3047.99</v>
+        <v>3047.51</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3120.97</v>
+        <v>3117.91</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3257.96</v>
+        <v>3260.64</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,29 +1154,29 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3862</v>
+        <v>4049.3</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3941.2</v>
+        <v>3951.5</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3928.21</v>
+        <v>3932.96</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3831.33</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3834.62</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -1193,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1317.3</v>
+        <v>1356.3</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1282.72</v>
+        <v>1289.73</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1284.12</v>
+        <v>1286.96</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1249.89</v>
+        <v>1251.49</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>197.96</v>
+        <v>197.86</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>207.47</v>
+        <v>202.76</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>207.21</v>
+        <v>202.82</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>189.85</v>
+        <v>186.41</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>235.2</v>
+        <v>243.8</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>247.09</v>
+        <v>246.77</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>248.65</v>
+        <v>248.46</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>263.93</v>
+        <v>263.71</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,24 +1330,24 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1794.2</v>
+        <v>1807.7</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1805.83</v>
+        <v>1806.01</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1792.92</v>
+        <v>1793.5</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1732.34</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1733.77</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -1369,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1009.6</v>
+        <v>1012.45</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>998.66</v>
+        <v>999.97</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1004.93</v>
+        <v>1005.23</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1049.08</v>
+        <v>1050.14</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1413,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>393.35</v>
+        <v>403.3</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>383.26</v>
+        <v>385.17</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>383.7</v>
+        <v>384.46</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>398.68</v>
+        <v>398.94</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1438,9 +1443,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -1457,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>351.85</v>
+        <v>353.9</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>373.63</v>
+        <v>371.75</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>379.98</v>
+        <v>378.96</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>359.78</v>
+        <v>360.24</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,29 +1506,29 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>870.55</v>
+        <v>918.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>897.87</v>
+        <v>899.8200000000001</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>910.65</v>
+        <v>910.95</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>935.22</v>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>933.83</v>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -1545,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1024.3</v>
+        <v>1021.6</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1084.21</v>
+        <v>1078.25</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1051.3</v>
+        <v>1050.14</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>916.96</v>
+        <v>918.67</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2908.8</v>
+        <v>2921.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2852.07</v>
+        <v>2857.54</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2611.23</v>
+        <v>2622.28</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2365.76</v>
+        <v>2374.57</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1633,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>402.3</v>
+        <v>406.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>414.62</v>
+        <v>413.85</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>422.82</v>
+        <v>422.18</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>410.21</v>
+        <v>410.61</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,29 +1682,29 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>13098</v>
+        <v>13366</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13113.29</v>
+        <v>13137.36</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13300.93</v>
+        <v>13303.49</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13970.28</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>13964.31</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -1721,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>446.2</v>
+        <v>443.5</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>462.65</v>
+        <v>460.83</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>457.83</v>
+        <v>457.27</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>422.04</v>
+        <v>422.43</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1787.1</v>
+        <v>1812.9</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1786.82</v>
+        <v>1782.52</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1700.81</v>
+        <v>1698.35</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1520.66</v>
+        <v>1519.57</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8493</v>
+        <v>8498</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8251.75</v>
+        <v>8275.200000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8004.9</v>
+        <v>8024.24</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7550.95</v>
+        <v>7561.5</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>282.4</v>
+        <v>285.1</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>287.05</v>
+        <v>286.87</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>293.67</v>
+        <v>293.33</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>328.19</v>
+        <v>328.17</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,34 +1902,34 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>886.25</v>
+        <v>954.95</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>925.5599999999999</v>
+        <v>928.36</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>948.9400000000001</v>
+        <v>949.17</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>890.38</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>890.96</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,29 +1946,29 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1465.1</v>
+        <v>1429.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1471.63</v>
+        <v>1467.59</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1459.67</v>
+        <v>1458.47</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1480.48</v>
+        <v>1482.05</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -1985,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4502.4</v>
+        <v>4709.7</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4458.09</v>
+        <v>4482.05</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4462.05</v>
+        <v>4471.76</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4827.59</v>
+        <v>4830.71</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2029,24 +2034,24 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2139.8</v>
+        <v>2168.8</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2161.99</v>
+        <v>2162.64</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2200.06</v>
+        <v>2198.83</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2285.06</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2284.45</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2073,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2690.9</v>
+        <v>2747.4</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2645.45</v>
+        <v>2655.16</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2561.94</v>
+        <v>2569.22</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2498.19</v>
+        <v>2502.03</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2117,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10830</v>
+        <v>11117</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11226.11</v>
+        <v>11215.72</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11473.61</v>
+        <v>11459.62</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11732.06</v>
+        <v>11729.94</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,24 +2166,24 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>228.02</v>
+        <v>235.89</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>235.72</v>
+        <v>235.73</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>240.18</v>
+        <v>240.01</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>260.43</v>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>260.64</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2205,24 +2210,24 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>375.9</v>
+        <v>390</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>379.78</v>
+        <v>380.76</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>366.24</v>
+        <v>367.17</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>419.28</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>419.91</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -2249,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7179.5</v>
+        <v>7312</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7152.16</v>
+        <v>7167.39</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7155.72</v>
+        <v>7161.85</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>6902.14</v>
+        <v>6913.55</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -2293,24 +2298,24 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4025.2</v>
+        <v>4184</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4138.91</v>
+        <v>4143.21</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4186.11</v>
+        <v>4186.02</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>3992.08</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3995.61</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2337,29 +2342,29 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2710.9</v>
+        <v>2755.3</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2776.31</v>
+        <v>2770.6</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2757.87</v>
+        <v>2753.86</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3402.75</v>
+        <v>3395.88</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -2381,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>286.65</v>
+        <v>284.8</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>292.45</v>
+        <v>291.72</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>297.31</v>
+        <v>296.82</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>287.21</v>
+        <v>287.62</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3089.5</v>
+        <v>3105.5</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3060.76</v>
+        <v>3065.02</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>2957.92</v>
+        <v>2963.71</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>2815.59</v>
+        <v>2818.35</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2469,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>252.6</v>
+        <v>246.2</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>270.94</v>
+        <v>268.58</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>276.67</v>
+        <v>275.48</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>259.19</v>
+        <v>259.15</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1110.2</v>
+        <v>1109.6</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1167.49</v>
+        <v>1161.97</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1225.94</v>
+        <v>1221.38</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1384.85</v>
+        <v>1383.64</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,29 +2562,29 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1422.5</v>
+        <v>1375.7</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1413.12</v>
+        <v>1409.55</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1385.57</v>
+        <v>1385.18</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1290.23</v>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1292.16</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
@@ -2601,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1282.3</v>
+        <v>1297.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1282.24</v>
+        <v>1283.71</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1262.68</v>
+        <v>1264.05</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1185.63</v>
+        <v>1187.96</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2645,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>545.25</v>
+        <v>555.35</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>582.52</v>
+        <v>579.9299999999999</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>604.1799999999999</v>
+        <v>602.26</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>670.42</v>
+        <v>669.48</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10114</v>
+        <v>10063</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10247.34</v>
+        <v>10229.78</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10009.17</v>
+        <v>10011.28</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>9286.08</v>
+        <v>9297.4</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1645.1</v>
+        <v>1689.1</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1729.27</v>
+        <v>1725.45</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1768.88</v>
+        <v>1765.75</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1883.89</v>
+        <v>1882.45</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1276</v>
+        <v>1275.4</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1287.94</v>
+        <v>1286.75</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1286.32</v>
+        <v>1285.89</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1260.77</v>
+        <v>1261.18</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -2821,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1383.3</v>
+        <v>1389.4</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1375.29</v>
+        <v>1376.63</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1346.29</v>
+        <v>1347.98</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1379.79</v>
+        <v>1380.63</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2865,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1108.6</v>
+        <v>1100.7</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1148.67</v>
+        <v>1144.1</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1147.2</v>
+        <v>1145.38</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1122.73</v>
+        <v>1122.6</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1719.1</v>
+        <v>1706</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1803.55</v>
+        <v>1794.26</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1847.17</v>
+        <v>1841.64</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1873.39</v>
+        <v>1872.9</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 15-Jun-2026  16:14:10    |    Closing Price Date: 15-Jun-2026</t>
+          <t>Scan Run: 16-Jun-2026  15:50:21    |    Closing Price Date: 16-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>50</v>
+      <c r="C5" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>15-Jun-2026  16:14:10</t>
+          <t>16-Jun-2026  15:50:21</t>
         </is>
       </c>
     </row>
@@ -632,14 +632,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -660,14 +660,14 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,37 +761,37 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1307</v>
+        <v>1328.8</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1309.03</v>
+        <v>1310.91</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1340.81</v>
+        <v>1340.34</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1386.61</v>
+        <v>1386.03</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -805,37 +805,37 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>777.35</v>
+        <v>784.9</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>758.53</v>
+        <v>761.04</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>777.89</v>
+        <v>778.16</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>863.4</v>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
+        <v>862.62</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -849,37 +849,37 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2162</v>
+        <v>2199</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2232.86</v>
+        <v>2229.64</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2335.35</v>
+        <v>2330</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2698.82</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+        <v>2693.84</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -893,37 +893,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>181.38</v>
+        <v>182.67</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>191.8</v>
+        <v>190.93</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>197.5</v>
+        <v>196.92</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>219.24</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+        <v>218.88</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -937,37 +937,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1327.6</v>
+        <v>1334.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1279.88</v>
+        <v>1285.06</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1283.18</v>
+        <v>1285.19</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.58</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+        <v>1325.67</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -981,37 +981,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1020.85</v>
+        <v>1015.3</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>989.9299999999999</v>
+        <v>992.35</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1004.9</v>
+        <v>1005.31</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>972.3200000000001</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+        <v>972.74</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1841.2</v>
+        <v>1853</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1824.98</v>
+        <v>1827.65</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1844.29</v>
+        <v>1844.63</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1896.73</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+        <v>1896.29</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1134.9</v>
+        <v>1143.6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1151.82</v>
+        <v>1151.04</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1185.3</v>
+        <v>1183.66</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1343.55</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+        <v>1341.56</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1113,37 +1113,37 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3134.3</v>
+        <v>3137.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3055.77</v>
+        <v>3063.6</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3118.55</v>
+        <v>3119.31</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3258.33</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+        <v>3257.13</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4169.8</v>
+        <v>4186.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3972.29</v>
+        <v>3992.68</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3942.24</v>
+        <v>3951.82</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3835.29</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+        <v>3838.78</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1368.3</v>
+        <v>1365.7</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1297.21</v>
+        <v>1303.74</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1290.15</v>
+        <v>1293.11</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1253.56</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+        <v>1254.68</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>197.28</v>
+        <v>196</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>202.24</v>
+        <v>201.64</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>202.6</v>
+        <v>202.34</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>186.72</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+        <v>186.82</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>252</v>
+        <v>253.6</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>247.27</v>
+        <v>247.87</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>248.6</v>
+        <v>248.8</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.91</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+        <v>262.82</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1333,37 +1333,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1806</v>
+        <v>1800.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1806.01</v>
+        <v>1805.5</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1793.99</v>
+        <v>1794.25</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1735.72</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+        <v>1736.36</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1028.9</v>
+        <v>1024.1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1002.73</v>
+        <v>1004.76</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1006.16</v>
+        <v>1006.86</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1047.45</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+        <v>1047.21</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>405.75</v>
+        <v>407.85</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>387.13</v>
+        <v>389.1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>385.3</v>
+        <v>386.18</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.91</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>348.1</v>
+        <v>355.55</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>369.5</v>
+        <v>368.17</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>377.75</v>
+        <v>376.88</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.25</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+        <v>360.2</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>942.3</v>
+        <v>959.65</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>903.87</v>
+        <v>909.1799999999999</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>912.1799999999999</v>
+        <v>914.04</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>934.09</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+        <v>934.35</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1013.9</v>
+        <v>982.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1072.12</v>
+        <v>1063.58</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1048.72</v>
+        <v>1046.11</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>920.97</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+        <v>921.58</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2942.5</v>
+        <v>2943.6</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2865.63</v>
+        <v>2873.05</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2634.84</v>
+        <v>2646.95</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2379.45</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+        <v>2385.07</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1641,37 +1641,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>409.55</v>
+        <v>407.55</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>413.44</v>
+        <v>412.88</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>421.68</v>
+        <v>421.13</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>410.48</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+        <v>410.45</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1685,37 +1685,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13805</v>
+        <v>13691</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13200.94</v>
+        <v>13247.62</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13323.15</v>
+        <v>13337.58</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13961.33</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+        <v>13958.65</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>444.05</v>
+        <v>450.95</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>459.23</v>
+        <v>458.44</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>456.75</v>
+        <v>456.52</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>422.91</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+        <v>423.19</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1773,37 +1773,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1804.8</v>
+        <v>1822</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1784.64</v>
+        <v>1788.2</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1702.52</v>
+        <v>1707.21</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1523.7</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+        <v>1526.67</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8468.5</v>
+        <v>8390.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8293.610000000001</v>
+        <v>8302.84</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8041.66</v>
+        <v>8055.34</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7567.67</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+        <v>7575.86</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1861,37 +1861,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>287.9</v>
+        <v>291.65</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>286.97</v>
+        <v>287.41</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>293.12</v>
+        <v>293.06</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>327.76</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+        <v>327.4</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1000.65</v>
+        <v>1005.75</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>935.25</v>
+        <v>941.96</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>951.1900000000001</v>
+        <v>953.33</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+        <v>892.9299999999999</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1425.6</v>
+        <v>1446.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1463.59</v>
+        <v>1461.99</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1457.19</v>
+        <v>1456.78</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1479.34</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+        <v>1479.02</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4880.4</v>
+        <v>4840</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4519.99</v>
+        <v>4550.47</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4487.79</v>
+        <v>4501.6</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4828.08</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+        <v>4828.2</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2156.1</v>
+        <v>2199.9</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2162.01</v>
+        <v>2165.62</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2197.15</v>
+        <v>2197.26</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2286.46</v>
+        <v>2285.6</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2739.3</v>
+        <v>2748.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2663.17</v>
+        <v>2671.26</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2575.89</v>
+        <v>2582.64</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2509.25</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+        <v>2511.63</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11466</v>
+        <v>11391</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11239.56</v>
+        <v>11253.98</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11459.87</v>
+        <v>11457.17</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11729.68</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+        <v>11726.31</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2169,37 +2169,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>239.52</v>
+        <v>241.95</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>236.09</v>
+        <v>236.65</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>239.99</v>
+        <v>240.07</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
+        <v>260.22</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2213,37 +2213,37 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>396.4</v>
+        <v>393.6</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>382.25</v>
+        <v>383.33</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>368.32</v>
+        <v>369.31</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+        <v>419.73</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7624.5</v>
+        <v>7560.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7210.92</v>
+        <v>7244.21</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7179.99</v>
+        <v>7194.91</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6917.57</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+        <v>6926.99</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2301,37 +2301,37 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4283.5</v>
+        <v>4338</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4156.57</v>
+        <v>4173.85</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4189.85</v>
+        <v>4195.66</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3995.86</v>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+        <v>3999.27</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2901.1</v>
+        <v>2897.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2783.03</v>
+        <v>2793.96</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2759.63</v>
+        <v>2765.05</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3377.65</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+        <v>3372.88</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>285.7</v>
+        <v>285.15</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>291.15</v>
+        <v>290.58</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>296.38</v>
+        <v>295.94</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.89</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+        <v>287.86</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3164.5</v>
+        <v>3140.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3074.49</v>
+        <v>3080.76</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2971.58</v>
+        <v>2978.2</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2821.45</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+        <v>2824.62</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>243.65</v>
+        <v>248.2</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>266.21</v>
+        <v>264.49</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>274.23</v>
+        <v>273.21</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>258.75</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+        <v>258.65</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1119.3</v>
+        <v>1159</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1157.91</v>
+        <v>1158.01</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1217.38</v>
+        <v>1215.09</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1380.03</v>
+        <v>1377.83</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1374.7</v>
+        <v>1391.7</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1406.23</v>
+        <v>1404.85</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1384.77</v>
+        <v>1385.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1294.08</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
+        <v>1295.05</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1296.5</v>
+        <v>1274.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1284.92</v>
+        <v>1283.91</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1265.33</v>
+        <v>1265.68</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1189.51</v>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+        <v>1190.35</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2653,37 +2653,37 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>581.2</v>
+        <v>574.4</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>580.05</v>
+        <v>579.51</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>601.4400000000001</v>
+        <v>600.38</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>668.8</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+        <v>667.87</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9943</v>
+        <v>9939</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10202.47</v>
+        <v>10177.38</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10008.6</v>
+        <v>10005.87</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9302.190000000001</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+        <v>9308.52</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2741,37 +2741,37 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1750.2</v>
+        <v>1787.3</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1727.8</v>
+        <v>1733.47</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1765.14</v>
+        <v>1766.01</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1882.78</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
+        <v>1881.83</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2785,37 +2785,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1279.5</v>
+        <v>1276.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1286.06</v>
+        <v>1285.19</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1285.64</v>
+        <v>1285.3</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1261.09</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+        <v>1261.24</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2829,37 +2829,37 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1381.3</v>
+        <v>1373.2</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1377.08</v>
+        <v>1376.71</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1349.29</v>
+        <v>1350.23</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1382.45</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+        <v>1382.36</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2873,37 +2873,37 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1100.4</v>
+        <v>1130.9</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1139.94</v>
+        <v>1139.07</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1143.61</v>
+        <v>1143.11</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.4</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
+        <v>1122.49</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1759.5</v>
+        <v>1767.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1790.95</v>
+        <v>1788.73</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1838.42</v>
+        <v>1835.64</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1871.84</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+        <v>1870.8</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 16-Jun-2026  15:50:21    |    Closing Price Date: 16-Jun-2026</t>
+          <t>Scan Run: 17-Jun-2026  14:25:08    |    Closing Price Date: 17-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>16-Jun-2026  15:50:21</t>
+          <t>17-Jun-2026  14:25:08</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 74.0% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 37 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1328.8</v>
+        <v>1332.7</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1310.91</v>
+        <v>1312.99</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1340.34</v>
+        <v>1340.04</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1386.03</v>
+        <v>1385.5</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>784.9</v>
+        <v>787.1</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>761.04</v>
+        <v>763.52</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>778.16</v>
+        <v>778.52</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>862.62</v>
+        <v>861.87</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2199</v>
+        <v>2223</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2229.64</v>
+        <v>2229</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2330</v>
+        <v>2325.81</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2693.84</v>
+        <v>2689.16</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>182.67</v>
+        <v>184.47</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>190.93</v>
+        <v>190.32</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>196.92</v>
+        <v>196.43</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>218.88</v>
+        <v>218.53</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1334.3</v>
+        <v>1336.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1285.06</v>
+        <v>1289.99</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1285.19</v>
+        <v>1287.21</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.67</v>
+        <v>1325.78</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1015.3</v>
+        <v>1026.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>992.35</v>
+        <v>995.6</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1005.31</v>
+        <v>1006.14</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>972.74</v>
+        <v>973.28</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1853</v>
+        <v>1875.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1827.65</v>
+        <v>1832.22</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1844.63</v>
+        <v>1845.85</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1896.29</v>
+        <v>1896.09</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1143.6</v>
+        <v>1157.7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1151.04</v>
+        <v>1151.67</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1183.66</v>
+        <v>1182.65</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1341.56</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1339.73</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3137.9</v>
+        <v>3132.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3063.6</v>
+        <v>3070.2</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3119.31</v>
+        <v>3119.85</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3257.13</v>
+        <v>3255.9</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4186.4</v>
+        <v>4207.7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3992.68</v>
+        <v>4013.16</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3951.82</v>
+        <v>3961.85</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3838.78</v>
+        <v>3842.45</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1365.7</v>
+        <v>1350.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1303.74</v>
+        <v>1308.23</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1293.11</v>
+        <v>1295.37</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1254.68</v>
+        <v>1255.64</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>196</v>
+        <v>199.01</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>201.64</v>
+        <v>201.39</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>202.34</v>
+        <v>202.21</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>186.82</v>
+        <v>186.94</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>253.6</v>
+        <v>258.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>247.87</v>
+        <v>248.88</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>248.8</v>
+        <v>249.17</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.82</v>
+        <v>262.77</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1800.7</v>
+        <v>1820.4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1805.5</v>
+        <v>1806.92</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1794.25</v>
+        <v>1795.28</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1736.36</v>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1737.2</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1024.1</v>
+        <v>1026.15</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1004.76</v>
+        <v>1006.8</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1006.86</v>
+        <v>1007.62</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1047.21</v>
+        <v>1047</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>407.85</v>
+        <v>404.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>389.1</v>
+        <v>390.57</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>386.18</v>
+        <v>386.9</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399</v>
+        <v>399.06</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
         <v>355.55</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>368.17</v>
+        <v>366.97</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>376.88</v>
+        <v>376.04</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.2</v>
+        <v>360.16</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>959.65</v>
+        <v>958.4</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>909.1799999999999</v>
+        <v>913.87</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>914.04</v>
+        <v>915.78</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>934.35</v>
+        <v>934.59</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>982.4</v>
+        <v>1007.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1063.58</v>
+        <v>1058.28</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1046.11</v>
+        <v>1044.62</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>921.58</v>
+        <v>922.4400000000001</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2943.6</v>
+        <v>2951.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2873.05</v>
+        <v>2880.56</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2646.95</v>
+        <v>2658.91</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2385.07</v>
+        <v>2390.71</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>407.55</v>
+        <v>419.85</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>412.88</v>
+        <v>413.54</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>421.13</v>
+        <v>421.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>410.45</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>410.55</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -1666,9 +1666,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13691</v>
+        <v>13630</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13247.62</v>
+        <v>13284.03</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13337.58</v>
+        <v>13349.05</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13958.65</v>
+        <v>13955.37</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>450.95</v>
+        <v>455.75</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>458.44</v>
+        <v>458.19</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>456.52</v>
+        <v>456.49</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>423.19</v>
+        <v>423.52</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1822</v>
+        <v>1828.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1788.2</v>
+        <v>1792.05</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1707.21</v>
+        <v>1711.97</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1526.67</v>
+        <v>1529.67</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8390.5</v>
+        <v>8427.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8302.84</v>
+        <v>8314.709999999999</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8055.34</v>
+        <v>8069.93</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7575.86</v>
+        <v>7584.33</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>291.65</v>
+        <v>290.75</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.41</v>
+        <v>287.73</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>293.06</v>
+        <v>292.97</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>327.4</v>
+        <v>327.04</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1005.75</v>
+        <v>1007.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>941.96</v>
+        <v>948.2</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>953.33</v>
+        <v>955.46</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>892.9299999999999</v>
+        <v>894.0700000000001</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1446.8</v>
+        <v>1462.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1461.99</v>
+        <v>1462.03</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1456.78</v>
+        <v>1457</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1479.02</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1478.85</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4840</v>
+        <v>4878.4</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4550.47</v>
+        <v>4581.7</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4501.6</v>
+        <v>4516.38</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4828.2</v>
+        <v>4828.7</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2199.9</v>
+        <v>2197.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2165.62</v>
+        <v>2168.67</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2197.26</v>
+        <v>2197.28</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2285.6</v>
+        <v>2284.72</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2748.1</v>
+        <v>2738</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2671.26</v>
+        <v>2677.62</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2582.64</v>
+        <v>2588.73</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2511.63</v>
+        <v>2513.88</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11391</v>
+        <v>11373</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11253.98</v>
+        <v>11265.32</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11457.17</v>
+        <v>11453.87</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11726.31</v>
+        <v>11722.8</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>241.95</v>
+        <v>242.98</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>236.65</v>
+        <v>237.25</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.07</v>
+        <v>240.18</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.22</v>
+        <v>260.05</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,29 +2213,29 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>393.6</v>
+        <v>360.95</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>383.33</v>
+        <v>381.2</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>369.31</v>
+        <v>368.98</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>419.73</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>419.14</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7560.5</v>
+        <v>7509</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7244.21</v>
+        <v>7269.43</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7194.91</v>
+        <v>7207.23</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6926.99</v>
+        <v>6932.78</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4338</v>
+        <v>4380.5</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4173.85</v>
+        <v>4193.53</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4195.66</v>
+        <v>4202.91</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3999.27</v>
+        <v>4003.06</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2897.8</v>
+        <v>3102.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2793.96</v>
+        <v>2823.37</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2765.05</v>
+        <v>2778.3</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3372.88</v>
+        <v>3370.19</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>285.15</v>
+        <v>286.35</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>290.58</v>
+        <v>290.18</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>295.94</v>
+        <v>295.57</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.86</v>
+        <v>287.85</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3140.3</v>
+        <v>3150.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3080.76</v>
+        <v>3087.39</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2978.2</v>
+        <v>2984.95</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2824.62</v>
+        <v>2827.86</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>248.2</v>
+        <v>245</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>264.49</v>
+        <v>262.64</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>273.21</v>
+        <v>272.1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>258.65</v>
+        <v>258.51</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1159</v>
+        <v>1166.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1158.01</v>
+        <v>1158.85</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1215.09</v>
+        <v>1213.2</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1377.83</v>
+        <v>1375.73</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,24 +2565,24 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1391.7</v>
+        <v>1407.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1404.85</v>
+        <v>1405.08</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1385.04</v>
+        <v>1385.91</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1295.05</v>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1296.17</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1274.3</v>
+        <v>1287.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1283.91</v>
+        <v>1284.23</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1265.68</v>
+        <v>1266.52</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1190.35</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1191.32</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>574.4</v>
+        <v>581.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>579.51</v>
+        <v>579.73</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>600.38</v>
+        <v>599.65</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>667.87</v>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>667.01</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -2697,29 +2697,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9939</v>
+        <v>10042</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10177.38</v>
+        <v>10164.49</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10005.87</v>
+        <v>10007.29</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9308.52</v>
+        <v>9315.82</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1787.3</v>
+        <v>1764.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1733.47</v>
+        <v>1736.43</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1766.01</v>
+        <v>1765.95</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1881.83</v>
+        <v>1880.66</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1276.9</v>
+        <v>1269</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1285.19</v>
+        <v>1283.64</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1285.3</v>
+        <v>1284.66</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1261.24</v>
+        <v>1261.32</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1373.2</v>
+        <v>1350.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1376.71</v>
+        <v>1374.24</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1350.23</v>
+        <v>1350.25</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1382.36</v>
+        <v>1382.04</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1130.9</v>
+        <v>1124.5</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1139.07</v>
+        <v>1137.69</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1143.11</v>
+        <v>1142.38</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.49</v>
+        <v>1122.51</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2917,24 +2917,24 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1767.6</v>
+        <v>1793.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1788.73</v>
+        <v>1789.19</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1835.64</v>
+        <v>1833.99</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1870.8</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1870.03</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Jun-2026  14:25:08    |    Closing Price Date: 17-Jun-2026</t>
+          <t>Scan Run: 18-Jun-2026  14:07:51    |    Closing Price Date: 18-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Jun-2026  14:25:08</t>
+          <t>18-Jun-2026  14:07:51</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 74.0% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 37 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1332.7</v>
+        <v>1328.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1312.99</v>
+        <v>1314.43</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1340.04</v>
+        <v>1339.57</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1385.5</v>
+        <v>1385.31</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>787.1</v>
+        <v>799</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>763.52</v>
+        <v>766.9</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>778.52</v>
+        <v>779.3200000000001</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>861.87</v>
+        <v>861.2</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2223</v>
+        <v>2203.3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2229</v>
+        <v>2226.56</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2325.81</v>
+        <v>2321</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2689.16</v>
+        <v>2683.74</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>184.47</v>
+        <v>182.84</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>190.32</v>
+        <v>189.61</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>196.43</v>
+        <v>195.9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>218.53</v>
+        <v>218.05</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1336.8</v>
+        <v>1342.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1289.99</v>
+        <v>1294.97</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1287.21</v>
+        <v>1289.37</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1325.78</v>
+        <v>1327.24</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1026.5</v>
+        <v>1042.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>995.6</v>
+        <v>1000.08</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1006.14</v>
+        <v>1007.57</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>973.28</v>
+        <v>974.01</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1875.7</v>
+        <v>1874.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1832.22</v>
+        <v>1836.28</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1845.85</v>
+        <v>1846.99</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1896.09</v>
+        <v>1897.24</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1157.7</v>
+        <v>1127.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1151.67</v>
+        <v>1149.37</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1182.65</v>
+        <v>1180.48</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1339.73</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1336</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3132.9</v>
+        <v>3136.5</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3070.2</v>
+        <v>3076.51</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3119.85</v>
+        <v>3120.5</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3255.9</v>
+        <v>3252.29</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4207.7</v>
+        <v>4190</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4013.16</v>
+        <v>4030</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3961.85</v>
+        <v>3970.8</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3842.45</v>
+        <v>3846.66</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1350.9</v>
+        <v>1360.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1308.23</v>
+        <v>1313.17</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1295.37</v>
+        <v>1297.91</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1255.64</v>
+        <v>1256.24</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>199.01</v>
+        <v>200.52</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>201.39</v>
+        <v>201.31</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>202.21</v>
+        <v>202.14</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>186.94</v>
+        <v>187.06</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>258.4</v>
+        <v>258.55</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>248.88</v>
+        <v>249.8</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.17</v>
+        <v>249.54</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.77</v>
+        <v>262.59</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1820.4</v>
+        <v>1824.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1806.92</v>
+        <v>1808.62</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1795.28</v>
+        <v>1796.44</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1737.2</v>
+        <v>1739.93</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1026.15</v>
+        <v>1090.45</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1006.8</v>
+        <v>1014.77</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1007.62</v>
+        <v>1010.87</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1047</v>
+        <v>1048.25</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1402,9 +1402,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>404.5</v>
+        <v>402.95</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>390.57</v>
+        <v>391.75</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>386.9</v>
+        <v>387.53</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399.06</v>
+        <v>399.21</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>355.55</v>
+        <v>361.95</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>366.97</v>
+        <v>366.49</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>376.04</v>
+        <v>375.49</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.16</v>
+        <v>360.21</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -1490,9 +1490,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>958.4</v>
+        <v>958.85</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>913.87</v>
+        <v>918.15</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>915.78</v>
+        <v>917.47</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>934.59</v>
+        <v>934.8200000000001</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1007.9</v>
+        <v>1008.5</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1058.28</v>
+        <v>1053.53</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1044.62</v>
+        <v>1043.2</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>922.4400000000001</v>
+        <v>923.5599999999999</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2951.9</v>
+        <v>3013.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2880.56</v>
+        <v>2893.21</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2658.91</v>
+        <v>2672.81</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2390.71</v>
+        <v>2397.86</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>419.85</v>
+        <v>428.6</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>413.54</v>
+        <v>414.98</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>421.08</v>
+        <v>421.37</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>410.55</v>
+        <v>411</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13630</v>
+        <v>13484</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13284.03</v>
+        <v>13303.08</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13349.05</v>
+        <v>13354.34</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13955.37</v>
+        <v>13953.27</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>455.75</v>
+        <v>452</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>458.19</v>
+        <v>457.6</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>456.49</v>
+        <v>456.32</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>423.52</v>
+        <v>423.96</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1828.6</v>
+        <v>1842.1</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1792.05</v>
+        <v>1796.81</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1711.97</v>
+        <v>1717.07</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1529.67</v>
+        <v>1532.44</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8427.5</v>
+        <v>8411.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8314.709999999999</v>
+        <v>8323.93</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8069.93</v>
+        <v>8083.33</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7584.33</v>
+        <v>7591.93</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>290.75</v>
+        <v>291.15</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>287.73</v>
+        <v>288.06</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>292.97</v>
+        <v>292.9</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>327.04</v>
+        <v>326.73</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1007.5</v>
+        <v>1002.7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>948.2</v>
+        <v>953.39</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>955.46</v>
+        <v>957.3099999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>894.0700000000001</v>
+        <v>895.6900000000001</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1462.4</v>
+        <v>1447.7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1462.03</v>
+        <v>1460.67</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1457</v>
+        <v>1456.63</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1478.85</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1478.23</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4878.4</v>
+        <v>5011.8</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4581.7</v>
+        <v>4622.66</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4516.38</v>
+        <v>4535.81</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4828.7</v>
+        <v>4831.56</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2197.6</v>
+        <v>2218.5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2168.67</v>
+        <v>2173.41</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2197.28</v>
+        <v>2198.11</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2284.72</v>
+        <v>2282.77</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2738</v>
+        <v>2755</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2677.62</v>
+        <v>2684.99</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2588.73</v>
+        <v>2595.25</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2513.88</v>
+        <v>2516.65</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11373</v>
+        <v>11430</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11265.32</v>
+        <v>11281</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11453.87</v>
+        <v>11452.93</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11722.8</v>
+        <v>11716.44</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>242.98</v>
+        <v>244.1</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>237.25</v>
+        <v>237.91</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.18</v>
+        <v>240.33</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>260.05</v>
+        <v>259.93</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>360.95</v>
+        <v>364.65</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>381.2</v>
+        <v>379.62</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>368.98</v>
+        <v>368.81</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>419.14</v>
+        <v>418.6</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7509</v>
+        <v>7601</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7269.43</v>
+        <v>7301.01</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7207.23</v>
+        <v>7222.67</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6932.78</v>
+        <v>6939.22</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4380.5</v>
+        <v>4387.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4193.53</v>
+        <v>4212.04</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4202.91</v>
+        <v>4210.16</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4003.06</v>
+        <v>4007.73</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3102.8</v>
+        <v>3179.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2823.37</v>
+        <v>2857.31</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2778.3</v>
+        <v>2794.04</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3370.19</v>
+        <v>3376.67</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>286.35</v>
+        <v>288.7</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>290.18</v>
+        <v>290.03</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>295.57</v>
+        <v>295.3</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.85</v>
+        <v>287.69</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2414,9 +2414,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3150.4</v>
+        <v>3145.1</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3087.39</v>
+        <v>3092.89</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2984.95</v>
+        <v>2991.23</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2827.86</v>
+        <v>2832.29</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>245</v>
+        <v>245.3</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>262.64</v>
+        <v>260.99</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>272.1</v>
+        <v>271.05</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>258.51</v>
+        <v>258.52</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1166.8</v>
+        <v>1161.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1158.85</v>
+        <v>1159.13</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1213.2</v>
+        <v>1211.18</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1375.73</v>
+        <v>1374.35</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,24 +2565,24 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1407.3</v>
+        <v>1400.4</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1405.08</v>
+        <v>1404.64</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1385.91</v>
+        <v>1386.48</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1296.17</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1297.27</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1287.2</v>
+        <v>1293.9</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1284.23</v>
+        <v>1285.15</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1266.52</v>
+        <v>1267.6</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1191.32</v>
+        <v>1192.56</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>581.8</v>
+        <v>591.3</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>579.73</v>
+        <v>580.83</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>599.65</v>
+        <v>599.3200000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>667.01</v>
+        <v>666.73</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10042</v>
+        <v>10077</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10164.49</v>
+        <v>10156.15</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10007.29</v>
+        <v>10010.03</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9315.82</v>
+        <v>9328.200000000001</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1764.6</v>
+        <v>1771.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1736.43</v>
+        <v>1739.79</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1765.95</v>
+        <v>1766.18</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1880.66</v>
+        <v>1878.08</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1269</v>
+        <v>1267.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1283.64</v>
+        <v>1282.11</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1284.66</v>
+        <v>1283.99</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1261.32</v>
+        <v>1261.23</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1350.8</v>
+        <v>1355.5</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1374.24</v>
+        <v>1372.46</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1350.25</v>
+        <v>1350.46</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1382.04</v>
+        <v>1381.07</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1124.5</v>
+        <v>1111.4</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1137.69</v>
+        <v>1135.18</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1142.38</v>
+        <v>1141.17</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.51</v>
+        <v>1122.5</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2898,9 +2898,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1793.6</v>
+        <v>1807.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1789.19</v>
+        <v>1790.94</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1833.99</v>
+        <v>1832.95</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1870.03</v>
+        <v>1869.32</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-Jun-2026  14:07:51    |    Closing Price Date: 18-Jun-2026</t>
+          <t>Scan Run: 19-Jun-2026  14:12:18    |    Closing Price Date: 19-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-Jun-2026  14:07:51</t>
+          <t>19-Jun-2026  14:12:18</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,37 +761,37 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1328.1</v>
+        <v>1309.5</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1314.43</v>
+        <v>1313.96</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1339.57</v>
+        <v>1338.4</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1385.31</v>
+        <v>1384.97</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -805,37 +805,37 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>799</v>
+        <v>779.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>766.9</v>
+        <v>756.84</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>779.3200000000001</v>
+        <v>767.15</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>861.2</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="14" t="inlineStr">
+        <v>847.05</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -849,37 +849,37 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2203.3</v>
+        <v>2125</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2226.56</v>
+        <v>2216.88</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2321</v>
+        <v>2313.32</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2683.74</v>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
+        <v>2675.35</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -893,37 +893,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>182.84</v>
+        <v>180.8</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>189.61</v>
+        <v>188.77</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>195.9</v>
+        <v>195.3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>218.05</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
+        <v>217.3</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -937,37 +937,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1342.3</v>
+        <v>1346.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1294.97</v>
+        <v>1299.88</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1289.37</v>
+        <v>1291.61</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1327.24</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
+        <v>1327.37</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -981,37 +981,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1042.7</v>
+        <v>1035.1</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1000.08</v>
+        <v>1003.42</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1007.57</v>
+        <v>1008.65</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>974.01</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+        <v>974.34</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1874.8</v>
+        <v>1910.8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1836.28</v>
+        <v>1843.37</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1846.99</v>
+        <v>1849.49</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1897.24</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
+        <v>1896.52</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1127.5</v>
+        <v>1051.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1149.37</v>
+        <v>1140.04</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1180.48</v>
+        <v>1175.42</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1336</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
+        <v>1330.28</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1113,37 +1113,37 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3136.5</v>
+        <v>3074.8</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3076.51</v>
+        <v>3076.35</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3120.5</v>
+        <v>3118.71</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3252.29</v>
+        <v>3250.85</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4190</v>
+        <v>4209.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4030</v>
+        <v>4047.09</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3970.8</v>
+        <v>3980.16</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3846.66</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+        <v>3850.19</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1360.1</v>
+        <v>1357.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1313.17</v>
+        <v>1317.43</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1297.91</v>
+        <v>1300.27</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1256.24</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+        <v>1256.63</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>200.52</v>
+        <v>198.96</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>201.31</v>
+        <v>201.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>202.14</v>
+        <v>202.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.06</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+        <v>187.16</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>258.55</v>
+        <v>264.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>249.8</v>
+        <v>251.18</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>249.54</v>
+        <v>250.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.59</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+        <v>262.5</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1333,37 +1333,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1824.8</v>
+        <v>1838.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1808.62</v>
+        <v>1811.45</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1796.44</v>
+        <v>1798.08</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1739.93</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
+        <v>1741.82</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1090.45</v>
+        <v>1094.75</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1014.77</v>
+        <v>1022.38</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1010.87</v>
+        <v>1014.16</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1048.25</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
+        <v>1048.99</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>402.95</v>
+        <v>399.25</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>391.75</v>
+        <v>392.46</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>387.53</v>
+        <v>387.99</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399.21</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
+        <v>399.62</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>361.95</v>
+        <v>365.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>366.49</v>
+        <v>366.42</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>375.49</v>
+        <v>375.11</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.21</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+        <v>360.26</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>958.85</v>
+        <v>961.8</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>918.15</v>
+        <v>922.3099999999999</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>917.47</v>
+        <v>919.21</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>934.8200000000001</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
+        <v>935.7</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1008.5</v>
+        <v>1010</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1053.53</v>
+        <v>1049.39</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1043.2</v>
+        <v>1041.9</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>923.5599999999999</v>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
+        <v>924.1799999999999</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3013.4</v>
+        <v>3038.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2893.21</v>
+        <v>2907.04</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2672.81</v>
+        <v>2687.14</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2397.86</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
+        <v>2403.85</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1641,37 +1641,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>428.6</v>
+        <v>426.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>414.98</v>
+        <v>416.11</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>421.37</v>
+        <v>421.59</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>411</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
+        <v>411.14</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1685,37 +1685,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13484</v>
+        <v>13395</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13303.08</v>
+        <v>13311.83</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13354.34</v>
+        <v>13355.93</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13953.27</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
+        <v>13947.42</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>452</v>
+        <v>451.3</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>457.6</v>
+        <v>457</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>456.32</v>
+        <v>456.12</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>423.96</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
+        <v>424.29</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1773,37 +1773,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1842.1</v>
+        <v>1835.3</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1796.81</v>
+        <v>1800.48</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1717.07</v>
+        <v>1721.71</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1532.44</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
+        <v>1535.17</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8411.5</v>
+        <v>8489.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8323.93</v>
+        <v>8339.700000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8083.33</v>
+        <v>8099.26</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7591.93</v>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
+        <v>7601.24</v>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1861,37 +1861,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>291.15</v>
+        <v>292.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>288.06</v>
+        <v>288.48</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>292.9</v>
+        <v>292.88</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>326.73</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
+        <v>326.64</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1002.7</v>
+        <v>1001.9</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>953.39</v>
+        <v>958.01</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>957.3099999999999</v>
+        <v>959.0599999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>895.6900000000001</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
+        <v>896.6900000000001</v>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1447.7</v>
+        <v>1409.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1460.67</v>
+        <v>1455.8</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1456.63</v>
+        <v>1454.79</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1478.23</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
+        <v>1475.84</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5011.8</v>
+        <v>5021.5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4622.66</v>
+        <v>4660.65</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4535.81</v>
+        <v>4554.85</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4831.56</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
+        <v>4836.81</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2218.5</v>
+        <v>2194.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2173.41</v>
+        <v>2175.43</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2198.11</v>
+        <v>2197.97</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2282.77</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
+        <v>2280.88</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2755</v>
+        <v>2732.9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2684.99</v>
+        <v>2689.55</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2595.25</v>
+        <v>2600.65</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2516.65</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
+        <v>2517.27</v>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11430</v>
+        <v>11367</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11281</v>
+        <v>11289.19</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11452.93</v>
+        <v>11449.57</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11716.44</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
+        <v>11716.42</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2169,37 +2169,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>244.1</v>
+        <v>244.45</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>237.91</v>
+        <v>238.53</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.33</v>
+        <v>240.5</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>259.93</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
+        <v>260.12</v>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2213,37 +2213,37 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>364.65</v>
+        <v>359.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>379.62</v>
+        <v>374.88</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>368.81</v>
+        <v>365.53</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>418.6</v>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
+        <v>415.45</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7601</v>
+        <v>7611</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7301.01</v>
+        <v>7330.53</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7222.67</v>
+        <v>7237.9</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6939.22</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
+        <v>6947.25</v>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2301,37 +2301,37 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4387.9</v>
+        <v>4419.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4212.04</v>
+        <v>4231.84</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4210.16</v>
+        <v>4218.38</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4007.73</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="14" t="inlineStr">
+        <v>4010.66</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3179.7</v>
+        <v>3205.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2857.31</v>
+        <v>2890.5</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2794.04</v>
+        <v>2810.19</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3376.67</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
+        <v>3375.82</v>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>288.7</v>
+        <v>292.25</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>290.03</v>
+        <v>290.25</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>295.3</v>
+        <v>295.18</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.69</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
+        <v>287.72</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3145.1</v>
+        <v>3149.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3092.89</v>
+        <v>3098.28</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2991.23</v>
+        <v>2997.44</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2832.29</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
+        <v>2834.82</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>245.3</v>
+        <v>246.25</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>260.99</v>
+        <v>259.58</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>271.05</v>
+        <v>270.08</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>258.52</v>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="14" t="inlineStr">
+        <v>258.31</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1161.8</v>
+        <v>1131.7</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1159.13</v>
+        <v>1156.52</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1211.18</v>
+        <v>1208.06</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1374.35</v>
+        <v>1370.83</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1400.4</v>
+        <v>1414.8</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1404.64</v>
+        <v>1405.6</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1386.48</v>
+        <v>1387.59</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1297.27</v>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
+        <v>1297.25</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1293.9</v>
+        <v>1287.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1285.15</v>
+        <v>1285.39</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1267.6</v>
+        <v>1268.38</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1192.56</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
+        <v>1193.15</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2653,37 +2653,37 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>591.3</v>
+        <v>591.85</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>580.83</v>
+        <v>580.02</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>599.3200000000001</v>
+        <v>596.98</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>666.73</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
+        <v>663.4299999999999</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10077</v>
+        <v>10066</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10156.15</v>
+        <v>10147.57</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10010.03</v>
+        <v>10012.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9328.200000000001</v>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
+        <v>9336.16</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2741,37 +2741,37 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1771.7</v>
+        <v>1769.4</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1739.79</v>
+        <v>1742.61</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1766.18</v>
+        <v>1766.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1878.08</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
+        <v>1877.6</v>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2785,37 +2785,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1267.5</v>
+        <v>1272.1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1282.11</v>
+        <v>1281.15</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1283.99</v>
+        <v>1283.52</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1261.23</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" s="14" t="inlineStr">
+        <v>1260.85</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2829,37 +2829,37 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1355.5</v>
+        <v>1351.8</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1372.46</v>
+        <v>1370.49</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1350.46</v>
+        <v>1350.51</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1381.07</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
+        <v>1381.13</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2873,37 +2873,37 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1111.4</v>
+        <v>1111.5</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1135.18</v>
+        <v>1132.93</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1141.17</v>
+        <v>1140.01</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1122.5</v>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="14" t="inlineStr">
+        <v>1121.79</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1807.6</v>
+        <v>1800.2</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1790.94</v>
+        <v>1791.82</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1832.95</v>
+        <v>1831.67</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1869.32</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
+        <v>1868.28</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -90,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -146,9 +141,6 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -160,13 +152,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-Jun-2026  14:12:18    |    Closing Price Date: 19-Jun-2026</t>
+          <t>Scan Run: 22-Jun-2026  15:49:01    |    Closing Price Date: 22-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,80 +586,80 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>56</v>
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-Jun-2026  14:12:18</t>
+          <t>22-Jun-2026  15:49:01</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Market Breadth Interpretation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 66.0% stocks above EMA</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Above 20 EMA : 33 of 50 stocks</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Above 200 EMA: 30 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -754,31 +746,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>1309.5</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>1313.96</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>1338.4</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>1384.97</v>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>1326.5</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>1315.15</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1337.93</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1383.61</v>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -798,34 +790,34 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>779.8</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>756.84</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>767.15</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>847.05</v>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>786.4</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>759.65</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>767.91</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>846.4299999999999</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -842,27 +834,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>2125</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>2216.88</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>2313.32</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>2675.35</v>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>2127.8</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>2208.4</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>2306.04</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>2669.55</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -886,27 +878,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>180.8</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>188.77</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>195.3</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>217.3</v>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>180.18</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>187.95</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>194.71</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>216.57</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -930,39 +922,39 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>1346.5</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>1299.88</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>1291.61</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>1327.37</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>1352.4</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1304.88</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1294</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1328.7</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -974,39 +966,39 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>1035.1</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>1003.42</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>1008.65</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>974.34</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1040.75</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1006.97</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1009.91</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>975</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1018,39 +1010,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>1910.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>1843.37</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>1849.49</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>1896.52</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1916.6</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1850.35</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1852.12</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1896.56</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1062,27 +1054,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>1051.4</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>1140.04</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>1175.42</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1330.28</v>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1065.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1132.93</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1171.11</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1327.62</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1106,27 +1098,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>3074.8</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>3076.35</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>3118.71</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>3250.85</v>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>3063.4</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>3075.12</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>3116.54</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3251.21</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1150,39 +1142,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>4209.4</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>4047.09</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>3980.16</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>3850.19</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>4201.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>4061.77</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>3988.83</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>3852.83</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1194,39 +1186,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>1357.9</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>1317.43</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1300.27</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>1256.63</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>1358.6</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1321.35</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1302.55</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1258.64</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1238,27 +1230,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>198.96</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>201.09</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>202.02</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>187.16</v>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>198.97</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>200.88</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>187.34</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1270,7 +1262,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1282,39 +1274,39 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>264.3</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>251.18</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>250.12</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>262.5</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>263.65</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>252.37</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>250.65</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>262.43</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1326,39 +1318,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>1838.3</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>1811.45</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>1798.08</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>1741.82</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1862.9</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1816.35</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1800.62</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>1744.2</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1370,39 +1362,39 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>1094.75</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>1022.38</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>1014.16</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>1048.99</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>1095.05</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1029.3</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1017.33</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1049.8</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1414,41 +1406,41 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>399.25</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>392.46</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>387.99</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>399.62</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>399.73</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
@@ -1458,31 +1450,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>365.8</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>366.42</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>375.11</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>360.26</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>360.39</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1490,7 +1482,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1502,39 +1494,39 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>961.8</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>922.3099999999999</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>919.21</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>935.7</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>968.3</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>926.6900000000001</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>921.14</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>936.4400000000001</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1546,27 +1538,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>1049.39</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>1041.9</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>924.1799999999999</v>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>1014.2</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1046.04</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1040.81</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>924.6900000000001</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1578,7 +1570,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1590,39 +1582,39 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>2907.04</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>2687.14</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>2403.85</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>3059.6</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>2921.57</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>2701.75</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>2410.86</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1634,39 +1626,39 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>426.9</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>416.11</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>421.59</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>411.14</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>431.5</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>417.58</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>421.98</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1678,34 +1670,34 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>13395</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>13311.83</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>13355.93</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>13947.42</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>13421</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>13322.23</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>13358.48</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>13938.54</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1722,27 +1714,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>451.3</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>457</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>456.12</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>424.29</v>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>449</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>456.24</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>455.84</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>424.74</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1754,7 +1746,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1766,39 +1758,39 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>1835.3</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>1800.48</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>1721.71</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>1535.17</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>1827.2</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1803.02</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1725.84</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>1538.46</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1810,39 +1802,39 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>8489.5</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>8339.700000000001</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>8099.26</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>7601.24</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>8469</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>8352.01</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>8113.76</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>7610.45</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1854,29 +1846,29 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>288.48</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>292.88</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>326.64</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>288.74</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>292.82</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>326.11</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1898,39 +1890,39 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>1001.9</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>958.01</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>959.0599999999999</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>896.6900000000001</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>992.85</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>961.33</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>960.38</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>897.0700000000001</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1942,27 +1934,27 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>1409.6</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>1455.8</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>1454.79</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>1475.84</v>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>1435.2</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>1453.84</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>1454.02</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>1475.51</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1986,39 +1978,39 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>5021.5</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>4660.65</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>4554.85</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>4836.81</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>5021.1</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>4694.98</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>4573.14</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>4840.89</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2030,29 +2022,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>2194.6</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>2175.43</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>2197.97</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>2280.88</v>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>2184.9</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>2176.33</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>2197.46</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>2279.01</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2074,39 +2066,39 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>2732.9</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>2689.55</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>2600.65</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>2517.27</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>2674</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>2688.07</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>2603.53</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>2517.48</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2118,29 +2110,29 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>11367</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>11289.19</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>11449.57</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>11716.42</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>11402</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>11299.93</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>11447.7</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>11714.47</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2162,34 +2154,34 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>244.45</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>238.53</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>240.5</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>260.12</v>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>243.38</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>238.99</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>240.61</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2206,27 +2198,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>374.88</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>365.53</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>415.45</v>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>365.37</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>414.61</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2250,39 +2242,39 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>7611</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>7330.53</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>7237.9</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>6947.25</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>7639.5</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>7359.96</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>7253.65</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>6955.54</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2294,39 +2286,39 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>4419.9</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>4231.84</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>4218.38</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>4010.66</v>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>4372.5</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>4245.23</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>4224.43</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>4014.19</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2338,34 +2330,34 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>3205.8</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>2890.5</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>2810.19</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>3375.82</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>3180.6</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>2918.13</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>2824.71</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>3380.1</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2382,31 +2374,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>292.25</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>290.25</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>295.18</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>287.72</v>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>290.2</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>294.97</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>287.76</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -2414,7 +2406,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2426,39 +2418,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>3149.5</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>3098.28</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>2997.44</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>2834.82</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>3175.2</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>3105.61</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>3004.41</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>2838.23</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2470,27 +2462,27 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>246.25</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>259.58</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>270.08</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>258.31</v>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>245.45</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>258.24</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>258.4</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2514,27 +2506,27 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>1131.7</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>1156.52</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>1208.06</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>1370.83</v>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>1130.5</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>1154.04</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1205.02</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1368.63</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2558,39 +2550,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>1414.8</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>1405.6</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>1387.59</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>1297.25</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>1401.9</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>1405.25</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>1388.15</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>1297.84</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2602,39 +2594,39 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>1287.7</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>1285.39</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>1268.38</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>1193.15</v>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>1282.4</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>1285.11</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>1268.93</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>1193.84</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2646,36 +2638,36 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>591.85</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>580.02</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>596.98</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>663.4299999999999</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>597.15</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>581.65</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>596.99</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>662.6799999999999</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
@@ -2690,39 +2682,39 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>10066</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>10147.57</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10012.22</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>9336.16</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>10191</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>10019.23</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>9343.459999999999</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2734,34 +2726,34 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>1769.4</v>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>1742.61</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>1766.3</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>1877.6</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>1782.2</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>1746.38</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>1766.93</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>1878.91</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2778,39 +2770,39 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>1272.1</v>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>1281.15</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>1283.52</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>1260.85</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>1290.7</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>1282.06</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>1283.8</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1263.1</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2822,41 +2814,41 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>1351.8</v>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>1370.49</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>1350.51</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>1381.13</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>1415.7</v>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>1374.79</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>1353.06</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>1383.1</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
@@ -2866,27 +2858,27 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>1111.5</v>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>1132.93</v>
-      </c>
-      <c r="E50" s="11" t="n">
-        <v>1140.01</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>1121.79</v>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>1131.02</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1138.94</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>1121.49</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2910,29 +2902,29 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>1800.2</v>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>1791.82</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>1831.67</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>1868.28</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>1793.13</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>1830.64</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>1868.75</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +89,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,13 +157,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Jun-2026  15:49:01    |    Closing Price Date: 22-Jun-2026</t>
+          <t>Scan Run: 23-Jun-2026  13:42:16    |    Closing Price Date: 23-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Jun-2026  15:49:01</t>
+          <t>23-Jun-2026  13:42:16</t>
         </is>
       </c>
     </row>
@@ -617,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 29 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 27 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 29 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,37 +758,37 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1326.5</v>
+        <v>1309.5</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1315.15</v>
+        <v>1314.61</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1337.93</v>
+        <v>1336.81</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1383.61</v>
+        <v>1382.87</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -797,37 +802,37 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>786.4</v>
+        <v>774.65</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>759.65</v>
+        <v>761.08</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>767.91</v>
+        <v>768.17</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>846.4299999999999</v>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+        <v>845.72</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -841,37 +846,37 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2127.8</v>
+        <v>2059.6</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2208.4</v>
+        <v>2194.23</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2306.04</v>
+        <v>2296.38</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2669.55</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+        <v>2663.48</v>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -885,37 +890,37 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>180.18</v>
+        <v>174.49</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>187.95</v>
+        <v>186.67</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>194.71</v>
+        <v>193.92</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>216.57</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+        <v>216.16</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -929,37 +934,37 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1352.4</v>
+        <v>1338.3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1304.88</v>
+        <v>1308.06</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1294</v>
+        <v>1295.73</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1328.7</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+        <v>1328.79</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -973,37 +978,37 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1040.75</v>
+        <v>1024.2</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1006.97</v>
+        <v>1008.61</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1009.91</v>
+        <v>1010.47</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>975</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+        <v>975.49</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1017,37 +1022,37 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1916.6</v>
+        <v>1901.6</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1850.35</v>
+        <v>1855.23</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1852.12</v>
+        <v>1854.06</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1896.56</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+        <v>1896.61</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1061,37 +1066,37 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1065.4</v>
+        <v>1029.3</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1132.93</v>
+        <v>1123.06</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1171.11</v>
+        <v>1165.55</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1327.62</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+        <v>1324.65</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1105,37 +1110,37 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3063.4</v>
+        <v>3037.3</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3075.12</v>
+        <v>3071.51</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3116.54</v>
+        <v>3113.43</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3251.21</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+        <v>3249.08</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1149,37 +1154,37 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4201.3</v>
+        <v>4179.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>4061.77</v>
+        <v>4072.98</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3988.83</v>
+        <v>3996.3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3852.83</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+        <v>3856.08</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1193,37 +1198,37 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1358.6</v>
+        <v>1363.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1321.35</v>
+        <v>1325.36</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1302.55</v>
+        <v>1304.94</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1258.64</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+        <v>1259.68</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1237,37 +1242,37 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>198.97</v>
+        <v>193.56</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>200.88</v>
+        <v>200.19</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>201.9</v>
+        <v>201.57</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.34</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+        <v>187.4</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1281,37 +1286,37 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>263.65</v>
+        <v>258.95</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>252.37</v>
+        <v>252.99</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>250.65</v>
+        <v>250.98</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>262.43</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
+        <v>262.4</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1325,37 +1330,37 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1862.9</v>
+        <v>1868</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1816.35</v>
+        <v>1821.27</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1800.62</v>
+        <v>1803.26</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1744.2</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+        <v>1745.43</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1369,37 +1374,37 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1095.05</v>
+        <v>1078.05</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1029.3</v>
+        <v>1033.95</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1017.33</v>
+        <v>1019.71</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1049.8</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+        <v>1050.08</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1413,37 +1418,37 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>402.15</v>
+        <v>401.65</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>393.39</v>
+        <v>394.17</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>388.55</v>
+        <v>389.06</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>399.73</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+        <v>399.75</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1457,37 +1462,37 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>367.05</v>
+        <v>364.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>366.48</v>
+        <v>366.3</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>374.79</v>
+        <v>374.39</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>360.39</v>
+        <v>360.43</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1501,37 +1506,37 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>968.3</v>
+        <v>962.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>926.6900000000001</v>
+        <v>930.09</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>921.14</v>
+        <v>922.75</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>936.4400000000001</v>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+        <v>936.7</v>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1545,37 +1550,37 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1014.2</v>
+        <v>986.8</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1046.04</v>
+        <v>1040.4</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1040.81</v>
+        <v>1038.69</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>924.6900000000001</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+        <v>925.3099999999999</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1589,37 +1594,37 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>3059.6</v>
+        <v>2962.9</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2921.57</v>
+        <v>2925.51</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2701.75</v>
+        <v>2711.99</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2410.86</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+        <v>2416.35</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1633,37 +1638,37 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>431.5</v>
+        <v>420</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>417.58</v>
+        <v>417.81</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>421.98</v>
+        <v>421.9</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.47</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
+        <v>411.56</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1677,37 +1682,37 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>13421</v>
+        <v>13451</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13322.23</v>
+        <v>13334.49</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13358.48</v>
+        <v>13362.11</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13938.54</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+        <v>13933.69</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1721,37 +1726,37 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>449</v>
+        <v>444.35</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>456.24</v>
+        <v>455.1</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>455.84</v>
+        <v>455.39</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>424.74</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+        <v>424.94</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1765,37 +1770,37 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1827.2</v>
+        <v>1784</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1803.02</v>
+        <v>1801.21</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1725.84</v>
+        <v>1728.13</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1538.46</v>
+        <v>1540.9</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1809,37 +1814,37 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8469</v>
+        <v>8487.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8352.01</v>
+        <v>8364.92</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8113.76</v>
+        <v>8128.41</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7610.45</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+        <v>7619.18</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1853,37 +1858,37 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>291.25</v>
+        <v>290</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>288.74</v>
+        <v>288.86</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>292.82</v>
+        <v>292.71</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>326.11</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+        <v>325.75</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1897,37 +1902,37 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>992.85</v>
+        <v>993.35</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>961.33</v>
+        <v>964.38</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>960.38</v>
+        <v>961.6799999999999</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>897.0700000000001</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+        <v>898.03</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1941,37 +1946,37 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1435.2</v>
+        <v>1415.6</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1453.84</v>
+        <v>1450.2</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1454.02</v>
+        <v>1452.51</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1475.51</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+        <v>1474.91</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1985,37 +1990,37 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>5021.1</v>
+        <v>4961.4</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4694.98</v>
+        <v>4720.35</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4573.14</v>
+        <v>4588.36</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4840.89</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+        <v>4842.09</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2029,37 +2034,37 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2184.9</v>
+        <v>2160.1</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2176.33</v>
+        <v>2154.96</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2197.46</v>
+        <v>2174.73</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2279.01</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+        <v>2255.11</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2073,37 +2078,37 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2674</v>
+        <v>2661.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2688.07</v>
+        <v>2664.59</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2603.53</v>
+        <v>2584.27</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2517.48</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+        <v>2497.47</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2117,37 +2122,37 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11402</v>
+        <v>11307</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11299.93</v>
+        <v>11300.61</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11447.7</v>
+        <v>11442.18</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11714.47</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+        <v>11710.41</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2161,37 +2166,37 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>243.38</v>
+        <v>237.81</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>238.99</v>
+        <v>238.88</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>240.61</v>
+        <v>240.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>259.7</v>
+        <v>259.48</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2205,37 +2210,37 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>361.5</v>
+        <v>354.55</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>373.6</v>
+        <v>371.79</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>365.37</v>
+        <v>364.95</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>414.61</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+        <v>414.02</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2249,37 +2254,37 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7639.5</v>
+        <v>7578</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7359.96</v>
+        <v>7380.72</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7253.65</v>
+        <v>7266.37</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>6955.54</v>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+        <v>6961.74</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2293,37 +2298,37 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4372.5</v>
+        <v>4305.3</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4245.23</v>
+        <v>4250.95</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4224.43</v>
+        <v>4227.6</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4014.19</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+        <v>4017.09</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2337,37 +2342,37 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>3180.6</v>
+        <v>3142.9</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2918.13</v>
+        <v>2939.54</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2824.71</v>
+        <v>2837.19</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3380.1</v>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+        <v>3377.74</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2381,37 +2386,37 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>289.75</v>
+        <v>291.95</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>290.2</v>
+        <v>290.37</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>294.97</v>
+        <v>294.85</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>287.76</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+        <v>287.8</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2425,37 +2430,37 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3175.2</v>
+        <v>3144.3</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3105.61</v>
+        <v>3109.29</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3004.41</v>
+        <v>3009.89</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>2838.23</v>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+        <v>2841.28</v>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2469,37 +2474,37 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>245.45</v>
+        <v>244.35</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>258.24</v>
+        <v>256.91</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>269.11</v>
+        <v>268.14</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>258.4</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+        <v>258.26</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2513,37 +2518,37 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1130.5</v>
+        <v>1109.5</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1154.04</v>
+        <v>1149.8</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1205.02</v>
+        <v>1201.28</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1368.63</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+        <v>1366.05</v>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2557,37 +2562,37 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1401.9</v>
+        <v>1392.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1405.25</v>
+        <v>1404.01</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1388.15</v>
+        <v>1388.31</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1297.84</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+        <v>1298.78</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2601,37 +2606,37 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1282.4</v>
+        <v>1242.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1285.11</v>
+        <v>1281.02</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1268.93</v>
+        <v>1267.89</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1193.84</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
+        <v>1194.32</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2645,37 +2650,37 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>597.15</v>
+        <v>597.45</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>581.65</v>
+        <v>583.15</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>596.99</v>
+        <v>597.01</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>662.6799999999999</v>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+        <v>662.03</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2689,37 +2694,37 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10191</v>
+        <v>10025</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10151.7</v>
+        <v>10139.64</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10019.23</v>
+        <v>10019.46</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>9343.459999999999</v>
+        <v>9350.25</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2733,37 +2738,37 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1782.2</v>
+        <v>1765</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1746.38</v>
+        <v>1748.16</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1766.93</v>
+        <v>1766.85</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1878.91</v>
-      </c>
-      <c r="G47" s="11" t="inlineStr">
+        <v>1877.78</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2777,37 +2782,37 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1290.7</v>
+        <v>1301.3</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1282.06</v>
+        <v>1283.9</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1283.8</v>
+        <v>1284.49</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1263.1</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+        <v>1263.48</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2821,37 +2826,37 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1415.7</v>
+        <v>1433.1</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1374.79</v>
+        <v>1380.35</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1353.06</v>
+        <v>1356.2</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1383.1</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+        <v>1383.6</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2865,37 +2870,37 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1112.9</v>
+        <v>1103.8</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1131.02</v>
+        <v>1128.43</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1138.94</v>
+        <v>1137.57</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1121.49</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+        <v>1121.31</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2909,37 +2914,37 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1805.5</v>
+        <v>1786.2</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1793.13</v>
+        <v>1792.47</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1830.64</v>
+        <v>1828.9</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1868.75</v>
+        <v>1867.93</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 24-Jun-2026  13:18:10    |    Closing Price Date: 24-Jun-2026</t>
+          <t>Scan Run: 25-Jun-2026  13:13:35    |    Closing Price Date: 25-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24-Jun-2026  13:18:10</t>
+          <t>25-Jun-2026  13:13:35</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 27 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,37 +761,37 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1313.6</v>
+        <v>1318.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1314.52</v>
+        <v>1314.86</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1335.9</v>
+        <v>1335.21</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1382.18</v>
+        <v>1381.55</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -805,37 +805,37 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>793.2</v>
+        <v>796.3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>764.14</v>
+        <v>767.2</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>769.16</v>
+        <v>770.22</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>845.2</v>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+        <v>844.71</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -849,37 +849,37 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2109</v>
+        <v>2094.7</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2186.11</v>
+        <v>2177.41</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2289.03</v>
+        <v>2281.41</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2657.97</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+        <v>2652.36</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -893,37 +893,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>174.48</v>
+        <v>175</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>185.51</v>
+        <v>184.51</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>193.16</v>
+        <v>192.44</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>215.74</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+        <v>215.33</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -937,37 +937,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1373.6</v>
+        <v>1387.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1314.3</v>
+        <v>1321.27</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1298.79</v>
+        <v>1302.27</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1329.24</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+        <v>1329.82</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -981,37 +981,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1034.6</v>
+        <v>1045.4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1011.09</v>
+        <v>1014.36</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1011.42</v>
+        <v>1012.75</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>976.08</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+        <v>976.77</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1877.3</v>
+        <v>1850.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1857.33</v>
+        <v>1856.7</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1854.97</v>
+        <v>1854.81</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1896.42</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+        <v>1895.97</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1056.6</v>
+        <v>1041.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1116.73</v>
+        <v>1109.54</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1161.27</v>
+        <v>1156.56</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1321.98</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+        <v>1319.19</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1113,37 +1113,37 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3064.5</v>
+        <v>3182.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3070.85</v>
+        <v>3081.45</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3111.51</v>
+        <v>3114.28</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3247.25</v>
+        <v>3246.6</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4181.7</v>
+        <v>4216.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4083.33</v>
+        <v>4096</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4003.57</v>
+        <v>4011.92</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3859.32</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+        <v>3862.87</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1384.5</v>
+        <v>1377.2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1331</v>
+        <v>1335.4</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1308.06</v>
+        <v>1310.77</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1260.93</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+        <v>1262.08</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>190.16</v>
+        <v>188.71</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>199.23</v>
+        <v>198.23</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>201.12</v>
+        <v>200.64</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.43</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+        <v>187.44</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>256.35</v>
+        <v>255.15</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>253.31</v>
+        <v>253.49</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>251.19</v>
+        <v>251.34</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.34</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+        <v>262.27</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1333,37 +1333,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1874.4</v>
+        <v>1862.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1826.33</v>
+        <v>1829.8</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1806.05</v>
+        <v>1808.28</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1746.72</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+        <v>1747.87</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1081.7</v>
+        <v>1123.35</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1038.49</v>
+        <v>1046.58</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1022.14</v>
+        <v>1026.11</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1050.39</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+        <v>1051.12</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>405.95</v>
+        <v>409</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>395.3</v>
+        <v>396.6</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>389.72</v>
+        <v>390.48</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399.81</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+        <v>399.9</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>357.05</v>
+        <v>352.05</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>365.42</v>
+        <v>364.15</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>373.71</v>
+        <v>372.86</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.4</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+        <v>360.32</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>990.95</v>
+        <v>980.4</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>935.88</v>
+        <v>940.12</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>925.4299999999999</v>
+        <v>927.58</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>937.24</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+        <v>937.67</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>976.6</v>
+        <v>953.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1034.32</v>
+        <v>1026.59</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1036.26</v>
+        <v>1033</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>925.8200000000001</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+        <v>926.1</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3069.7</v>
+        <v>3038</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2939.24</v>
+        <v>2948.65</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2726.02</v>
+        <v>2738.25</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2422.85</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+        <v>2428.97</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1641,37 +1641,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>413.55</v>
+        <v>407.2</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>417.4</v>
+        <v>416.43</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>421.57</v>
+        <v>421.01</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>411.58</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+        <v>411.54</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1685,37 +1685,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13248</v>
+        <v>13745</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13326.26</v>
+        <v>13366.14</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13357.64</v>
+        <v>13372.83</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13926.86</v>
+        <v>13925.05</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>441.75</v>
+        <v>435.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>453.83</v>
+        <v>452.08</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>454.85</v>
+        <v>454.09</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>425.11</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+        <v>425.21</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1773,37 +1773,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1813.3</v>
+        <v>1796</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1802.36</v>
+        <v>1801.76</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1731.47</v>
+        <v>1734</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1543.62</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+        <v>1546.13</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8573.5</v>
+        <v>8592</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8384.780000000001</v>
+        <v>8404.52</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8145.87</v>
+        <v>8163.36</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7628.67</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+        <v>7638.26</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1861,37 +1861,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>290.35</v>
+        <v>290</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>289</v>
+        <v>289.1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>292.61</v>
+        <v>292.51</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>325.4</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+        <v>325.09</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1019</v>
+        <v>1031.8</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>969.58</v>
+        <v>975.51</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>963.92</v>
+        <v>966.59</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>899.23</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+        <v>900.55</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1461.6</v>
+        <v>1437.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1451.29</v>
+        <v>1449.93</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1452.87</v>
+        <v>1452.25</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1474.78</v>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+        <v>1474.41</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5207.2</v>
+        <v>5450</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4766.72</v>
+        <v>4831.79</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4612.63</v>
+        <v>4645.47</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4845.72</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+        <v>4851.73</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2157.8</v>
+        <v>2174.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2155.23</v>
+        <v>2157.04</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>2174.07</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2254.14</v>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+        <v>2253.34</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2667.5</v>
+        <v>2645.2</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2664.87</v>
+        <v>2663</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2587.54</v>
+        <v>2589.8</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2499.16</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+        <v>2500.62</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11430</v>
+        <v>11489</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11312.93</v>
+        <v>11329.7</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11441.7</v>
+        <v>11443.56</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11707.62</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
+        <v>11705.45</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2169,37 +2169,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>238.87</v>
+        <v>239.43</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>238.88</v>
+        <v>238.93</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.43</v>
+        <v>240.4</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>259.27</v>
+        <v>259.08</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2213,37 +2213,37 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>349.7</v>
+        <v>353.2</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>369.69</v>
+        <v>368.12</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>364.35</v>
+        <v>363.91</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>413.38</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+        <v>412.78</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7572</v>
+        <v>7598</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7398.94</v>
+        <v>7417.9</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7278.36</v>
+        <v>7290.89</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6967.81</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+        <v>6974.08</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2301,37 +2301,37 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4323.8</v>
+        <v>4291.3</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4257.89</v>
+        <v>4261.07</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4231.37</v>
+        <v>4233.72</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4020.14</v>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+        <v>4022.84</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3247</v>
+        <v>3216.2</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2968.82</v>
+        <v>2992.38</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2853.26</v>
+        <v>2867.49</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3376.44</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+        <v>3374.85</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>290.9</v>
+        <v>283.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>290.42</v>
+        <v>289.8</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>294.69</v>
+        <v>294.27</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.83</v>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+        <v>287.79</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3127.9</v>
+        <v>3126.6</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3111.06</v>
+        <v>3112.54</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3014.52</v>
+        <v>3018.92</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2844.13</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+        <v>2846.94</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>240</v>
+        <v>233.1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>255.3</v>
+        <v>253.19</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>267.04</v>
+        <v>265.71</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>258.08</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+        <v>257.83</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1113.9</v>
+        <v>1100.7</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1146.38</v>
+        <v>1142.03</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1197.85</v>
+        <v>1194.04</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1363.54</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+        <v>1360.93</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1382.6</v>
+        <v>1402.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1401.97</v>
+        <v>1402.03</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1388.09</v>
+        <v>1388.66</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1299.61</v>
+        <v>1300.64</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1231.2</v>
+        <v>1231</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1276.27</v>
+        <v>1271.96</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1266.45</v>
+        <v>1265.06</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1194.69</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+        <v>1195.05</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2653,37 +2653,37 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>591.75</v>
+        <v>585.45</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>583.97</v>
+        <v>584.11</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>596.8</v>
+        <v>596.36</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>661.33</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+        <v>660.5700000000001</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9750</v>
+        <v>9843</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10102.53</v>
+        <v>10077.81</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10008.89</v>
+        <v>10002.38</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9354.219999999999</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+        <v>9359.09</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2741,37 +2741,37 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1780.5</v>
+        <v>1764.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1751.24</v>
+        <v>1752.51</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1767.39</v>
+        <v>1767.28</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1876.81</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+        <v>1875.69</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2785,37 +2785,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1328.4</v>
+        <v>1350.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1288.13</v>
+        <v>1294.07</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1286.21</v>
+        <v>1288.73</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1264.13</v>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+        <v>1264.99</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2829,37 +2829,37 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1437.9</v>
+        <v>1440.1</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1385.83</v>
+        <v>1391</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1359.41</v>
+        <v>1362.57</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1384.14</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+        <v>1384.69</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2873,37 +2873,37 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1098.1</v>
+        <v>1131.3</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1125.54</v>
+        <v>1126.09</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1136.02</v>
+        <v>1135.83</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1121.08</v>
+        <v>1121.18</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1767.7</v>
+        <v>1744.9</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1790.11</v>
+        <v>1785.8</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1826.5</v>
+        <v>1823.3</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1866.93</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+        <v>1865.72</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Jun-2026  13:13:35    |    Closing Price Date: 25-Jun-2026</t>
+          <t>Scan Run: 26-Jun-2026  13:08:27    |    Closing Price Date: 25-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Jun-2026  13:13:35</t>
+          <t>26-Jun-2026  13:08:27</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1335.21</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1381.55</v>
+        <v>1381.9</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>770.22</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>844.71</v>
+        <v>845.41</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>2281.41</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2652.36</v>
+        <v>2652.34</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>192.44</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>215.33</v>
+        <v>215.57</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1302.27</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1329.82</v>
+        <v>1331.69</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1012.75</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>976.77</v>
+        <v>977.67</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>1854.81</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1895.97</v>
+        <v>1895.88</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1156.56</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1319.19</v>
+        <v>1319.05</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>3114.28</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3246.6</v>
+        <v>3250.17</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>4011.92</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3862.87</v>
+        <v>3869.01</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1310.77</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1262.08</v>
+        <v>1262.85</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>200.64</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.44</v>
+        <v>187.72</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>251.34</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.27</v>
+        <v>263.12</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>1808.28</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1747.87</v>
+        <v>1749.06</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1026.11</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1051.12</v>
+        <v>1054.95</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>390.48</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>399.9</v>
+        <v>400.15</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>372.86</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.32</v>
+        <v>360.72</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>927.58</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>937.67</v>
+        <v>938.3099999999999</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1033</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>926.1</v>
+        <v>926.85</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>2738.25</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2428.97</v>
+        <v>2431.8</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>421.01</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>411.54</v>
+        <v>411.96</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>13372.83</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13925.05</v>
+        <v>13927.68</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>454.09</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>425.21</v>
+        <v>425.61</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>1734</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1546.13</v>
+        <v>1547.67</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>8163.36</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7638.26</v>
+        <v>7649.84</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>292.51</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>325.09</v>
+        <v>324.85</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>966.59</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>900.55</v>
+        <v>902.4400000000001</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1452.25</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1474.41</v>
+        <v>1472.58</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>4645.47</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4851.73</v>
+        <v>4860.38</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         <v>2157.04</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2174.07</v>
+        <v>2174.08</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2253.34</v>
+        <v>2254.54</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>2589.8</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2500.62</v>
+        <v>2503.19</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>11443.56</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11705.45</v>
+        <v>11721.89</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>240.4</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>259.08</v>
+        <v>259.47</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>363.91</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>412.78</v>
+        <v>413.67</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>7290.89</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6974.08</v>
+        <v>6976.22</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>4233.72</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4022.84</v>
+        <v>4025.36</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>2867.49</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3374.85</v>
+        <v>3377.89</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>294.27</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>287.79</v>
+        <v>288.2</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>3018.92</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2846.94</v>
+        <v>2849.46</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>265.71</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>257.83</v>
+        <v>257.94</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>1194.04</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1360.93</v>
+        <v>1360.9</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>1388.66</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1300.64</v>
+        <v>1300.84</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1265.06</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1195.05</v>
+        <v>1196.23</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>596.36</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>660.5700000000001</v>
+        <v>662.05</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         <v>10077.81</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10002.38</v>
+        <v>10002.39</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9359.09</v>
+        <v>9368.799999999999</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>1767.28</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1875.69</v>
+        <v>1874.44</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1288.73</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1264.99</v>
+        <v>1265.9</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1362.57</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1384.69</v>
+        <v>1384.97</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>1135.83</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1121.18</v>
+        <v>1121.58</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>1823.3</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1865.72</v>
+        <v>1867.89</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 29-Jun-2026  14:45:42    |    Closing Price Date: 29-Jun-2026</t>
+          <t>Scan Run: 30-Jun-2026  13:08:07    |    Closing Price Date: 30-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>29-Jun-2026  14:45:42</t>
+          <t>30-Jun-2026  13:08:07</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 24 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1301</v>
+        <v>1293.9</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1313.54</v>
+        <v>1311.92</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1333.86</v>
+        <v>1331.68</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1383.45</v>
+        <v>1381.92</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>798.9</v>
+        <v>797.95</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>770.22</v>
+        <v>775.13</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>771.34</v>
+        <v>773.33</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>846.12</v>
+        <v>845.15</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2097.9</v>
+        <v>2031.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2169.83</v>
+        <v>2150.21</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2274.21</v>
+        <v>2257.94</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2652.26</v>
+        <v>2640.59</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>175.48</v>
+        <v>170.39</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>183.65</v>
+        <v>181.64</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>191.78</v>
+        <v>190.31</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>215.33</v>
+        <v>214.49</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1387.6</v>
+        <v>1375.2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1327.59</v>
+        <v>1337.29</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1305.61</v>
+        <v>1311.43</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1334.19</v>
+        <v>1335.12</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1036.1</v>
+        <v>1026.9</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1016.43</v>
+        <v>1019.85</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1013.66</v>
+        <v>1015.37</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>979.75</v>
+        <v>980.87</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1841.1</v>
+        <v>1852</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1855.21</v>
+        <v>1854.91</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1854.27</v>
+        <v>1854.18</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1898.81</v>
+        <v>1898.34</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1036.7</v>
+        <v>1000.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1102.6</v>
+        <v>1087.54</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1151.86</v>
+        <v>1141.75</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1316.48</v>
+        <v>1310.62</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3093</v>
+        <v>3068.8</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3082.55</v>
+        <v>3089.1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3113.45</v>
+        <v>3114.16</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3247.96</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3245.52</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4165.2</v>
+        <v>4143.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>4102.59</v>
+        <v>4115.87</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>4017.93</v>
+        <v>4030.25</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3878.87</v>
+        <v>3884.82</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1356.8</v>
+        <v>1345.7</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1337.44</v>
+        <v>1341.48</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1312.58</v>
+        <v>1316.28</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1265.78</v>
+        <v>1267.67</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>189.57</v>
+        <v>188.06</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>197.41</v>
+        <v>195.77</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>200.2</v>
+        <v>199.3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.73</v>
+        <v>187.75</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>259.4</v>
+        <v>264.6</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>254.05</v>
+        <v>255.19</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>251.66</v>
+        <v>252.3</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>263.05</v>
+        <v>262.98</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1311,9 +1311,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1874.8</v>
+        <v>1862.5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1834.09</v>
+        <v>1839.37</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1810.89</v>
+        <v>1814.88</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1752.55</v>
+        <v>1754.74</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1149.9</v>
+        <v>1129.25</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1056.42</v>
+        <v>1063.35</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1030.96</v>
+        <v>1034.82</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.41</v>
+        <v>1059.11</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>395.5</v>
+        <v>392.25</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>396.5</v>
+        <v>397.06</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>390.68</v>
+        <v>391.41</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.45</v>
+        <v>401.43</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>356.1</v>
+        <v>356.65</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>363.38</v>
+        <v>361.8</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>372.21</v>
+        <v>370.84</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>361.76</v>
+        <v>361.61</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>982.05</v>
+        <v>1004.75</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>944.12</v>
+        <v>947.79</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>929.72</v>
+        <v>929.11</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>940.3</v>
+        <v>935.65</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>963.8</v>
+        <v>956.6</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1020.61</v>
+        <v>1008.8</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1030.29</v>
+        <v>1024.51</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>927.35</v>
+        <v>927.89</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2962.5</v>
+        <v>3036</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2949.96</v>
+        <v>2965.12</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2747.05</v>
+        <v>2769.23</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2439.24</v>
+        <v>2451.06</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>411.6</v>
+        <v>411.8</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>415.97</v>
+        <v>414.85</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>420.64</v>
+        <v>419.79</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.48</v>
+        <v>412.42</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>13412</v>
+        <v>14115</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13370.5</v>
+        <v>13470.94</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13374.37</v>
+        <v>13416.88</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13935.71</v>
+        <v>13935.58</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1707,9 +1707,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>444.85</v>
+        <v>439.05</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>451.39</v>
+        <v>448.91</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>453.73</v>
+        <v>452.48</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>426.22</v>
+        <v>426.43</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,24 +1770,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1776.1</v>
+        <v>1810.2</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1799.31</v>
+        <v>1799.9</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1735.65</v>
+        <v>1740.82</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1551.12</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1556.11</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8655</v>
+        <v>8682</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8428.370000000001</v>
+        <v>8452.530000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8182.64</v>
+        <v>8202.23</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7667.95</v>
+        <v>7678.04</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1858,24 +1858,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>290.7</v>
+        <v>286.95</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>289.25</v>
+        <v>289.1</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>292.44</v>
+        <v>292.13</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>324.83</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>324.11</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1032.65</v>
+        <v>1042.15</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>980.95</v>
+        <v>986.78</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>969.1799999999999</v>
+        <v>972.04</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>904.34</v>
+        <v>905.72</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1433.8</v>
+        <v>1404.7</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1448.4</v>
+        <v>1443.24</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1451.53</v>
+        <v>1449.14</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1474.83</v>
+        <v>1473.76</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>5315.2</v>
+        <v>5368.4</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4877.83</v>
+        <v>4972.75</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4671.73</v>
+        <v>4728.18</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4864.38</v>
+        <v>4875.15</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2151.3</v>
+        <v>2118.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2156.49</v>
+        <v>2154.18</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2173.18</v>
+        <v>2171.03</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2255.87</v>
+        <v>2253.69</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2656.9</v>
+        <v>2635.7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2662.42</v>
+        <v>2658.48</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2592.43</v>
+        <v>2596.13</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2506.5</v>
+        <v>2509.15</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,24 +2122,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11336</v>
+        <v>11253</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11330.3</v>
+        <v>11322.94</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11439.34</v>
+        <v>11432.04</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11723.15</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11718.47</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>236.71</v>
+        <v>236.44</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>238.72</v>
+        <v>238.54</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>240.25</v>
+        <v>240.07</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>259.41</v>
+        <v>258.99</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>345.05</v>
+        <v>352.2</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>365.92</v>
+        <v>363.45</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>363.17</v>
+        <v>362.36</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>414.32</v>
+        <v>413.1</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2254,29 +2254,29 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7426</v>
+        <v>7073.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7418.67</v>
+        <v>7385.8</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7296.19</v>
+        <v>7287.46</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>6994.51</v>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6995.3</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4277.2</v>
+        <v>4404</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4262.61</v>
+        <v>4278.43</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4235.43</v>
+        <v>4244.12</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4027.9</v>
+        <v>4034.23</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>3258.3</v>
+        <v>3282.6</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>3017.7</v>
+        <v>3042.93</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2882.82</v>
+        <v>2898.5</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3369.06</v>
+        <v>3368.2</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>286.25</v>
+        <v>286.3</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>289.46</v>
+        <v>288.7</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>293.96</v>
+        <v>293.28</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>288.79</v>
+        <v>288.72</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3080.2</v>
+        <v>3100</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3109.46</v>
+        <v>3109.66</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3021.32</v>
+        <v>3028.3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>2854.14</v>
+        <v>2859.26</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>234.05</v>
+        <v>234.9</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>251.37</v>
+        <v>248.23</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>264.47</v>
+        <v>262.13</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>258.17</v>
+        <v>257.69</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1102.4</v>
+        <v>1071.8</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1138.25</v>
+        <v>1128.7</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1190.45</v>
+        <v>1182.41</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1360.78</v>
+        <v>1355.35</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,29 +2562,29 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1387.3</v>
+        <v>1405.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1400.63</v>
+        <v>1401.11</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1388.6</v>
+        <v>1389.76</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1303.4</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1305.39</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1232.4</v>
+        <v>1226.4</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1268.19</v>
+        <v>1261.02</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1263.78</v>
+        <v>1261.08</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1197.79</v>
+        <v>1198.41</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>583.25</v>
+        <v>575.85</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>584.03</v>
+        <v>583.36</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>595.84</v>
+        <v>594.66</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>661.9299999999999</v>
+        <v>660.3200000000001</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>9630</v>
+        <v>9716</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10035.16</v>
+        <v>9986.459999999999</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>9987.780000000001</v>
+        <v>9971.360000000001</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>9388.15</v>
+        <v>9395.870000000001</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,29 +2738,29 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1759.3</v>
+        <v>1780.2</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1753.16</v>
+        <v>1754.38</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1766.97</v>
+        <v>1766.04</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1875.55</v>
+        <v>1873.02</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1375.7</v>
+        <v>1357.1</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1301.85</v>
+        <v>1311.51</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1292.14</v>
+        <v>1296.93</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1268.63</v>
+        <v>1270.32</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1454.1</v>
+        <v>1465.4</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1397.01</v>
+        <v>1407.35</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1366.16</v>
+        <v>1372.86</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1386.71</v>
+        <v>1388.02</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1112.8</v>
+        <v>1075.6</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1124.82</v>
+        <v>1120.54</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1134.93</v>
+        <v>1132.44</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1122.36</v>
+        <v>1121.98</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1755.4</v>
+        <v>1765.7</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1782.91</v>
+        <v>1778.08</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1820.64</v>
+        <v>1815.65</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1870.44</v>
+        <v>1868.16</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-Jul-2026  13:32:19    |    Closing Price Date: 01-Jul-2026</t>
+          <t>Scan Run: 02-Jul-2026  12:54:22    |    Closing Price Date: 02-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026  13:32:19</t>
+          <t>02-Jul-2026  12:54:22</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 64.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 32 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 28 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1308</v>
+        <v>1303.5</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1311.55</v>
+        <v>1310.78</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1330.75</v>
+        <v>1329.68</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1381.18</v>
+        <v>1379.71</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>796.15</v>
+        <v>795.9</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>777.13</v>
+        <v>778.92</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>774.23</v>
+        <v>775.08</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>844.67</v>
+        <v>844.62</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>1982.6</v>
+        <v>2068.1</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2134.25</v>
+        <v>2127.95</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2247.14</v>
+        <v>2240.12</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2634.04</v>
+        <v>2629.58</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>170.13</v>
+        <v>174</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>180.55</v>
+        <v>179.92</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>189.52</v>
+        <v>188.91</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>214.04</v>
+        <v>213.71</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1379.8</v>
+        <v>1400</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1341.34</v>
+        <v>1346.92</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1314.11</v>
+        <v>1317.48</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1335.56</v>
+        <v>1335.6</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1047.4</v>
+        <v>1051.6</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1022.47</v>
+        <v>1025.24</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1016.62</v>
+        <v>1017.99</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>981.53</v>
+        <v>981.9</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1871</v>
+        <v>1875</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1856.02</v>
+        <v>1857.83</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1854.7</v>
+        <v>1855.49</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1897.6</v>
+        <v>1897.87</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>985.3</v>
+        <v>1040.9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1077.8</v>
+        <v>1074.29</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1135.61</v>
+        <v>1131.9</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1307.38</v>
+        <v>1306.17</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3130</v>
+        <v>3175.4</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3092.99</v>
+        <v>3071.34</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3114.78</v>
+        <v>3085.6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3244.37</v>
+        <v>3208.21</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4092.6</v>
+        <v>4059.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4113.65</v>
+        <v>4108.48</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4032.7</v>
+        <v>4033.75</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3886.89</v>
+        <v>3888.1</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1368.7</v>
+        <v>1362.6</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1344.07</v>
+        <v>1345.84</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1318.34</v>
+        <v>1320.07</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1268.67</v>
+        <v>1270.48</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>185.17</v>
+        <v>187.67</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>194.76</v>
+        <v>194.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>198.74</v>
+        <v>198.31</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.72</v>
+        <v>187.65</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1270,9 +1270,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
         <v>279.7</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>257.52</v>
+        <v>259.63</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>253.38</v>
+        <v>254.41</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>263.15</v>
+        <v>262.76</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1866.2</v>
+        <v>1871</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1841.92</v>
+        <v>1844.69</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1816.9</v>
+        <v>1819.02</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1755.85</v>
+        <v>1756.15</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1139.9</v>
+        <v>1127.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1070.64</v>
+        <v>1076.05</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1038.94</v>
+        <v>1042.41</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1059.92</v>
+        <v>1061.72</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>400.45</v>
+        <v>399.3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>397.38</v>
+        <v>397.56</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>391.76</v>
+        <v>392.06</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>401.42</v>
+        <v>401.34</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>357.9</v>
+        <v>358.25</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>361.43</v>
+        <v>361.12</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>370.34</v>
+        <v>369.86</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>361.58</v>
+        <v>361.54</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1014.9</v>
+        <v>1018.4</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>954.1799999999999</v>
+        <v>960.3</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>932.47</v>
+        <v>935.84</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>936.4299999999999</v>
+        <v>937.15</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>939.7</v>
+        <v>949.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1002.21</v>
+        <v>997.17</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1021.18</v>
+        <v>1018.36</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>928.01</v>
+        <v>927.88</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3143.6</v>
+        <v>3177.5</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2982.12</v>
+        <v>3000.73</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2783.91</v>
+        <v>2799.35</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2457.96</v>
+        <v>2463.07</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>416.25</v>
+        <v>415.05</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>414.99</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>419.66</v>
+        <v>419.48</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.46</v>
+        <v>412.4</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>14395</v>
+        <v>14348</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13558.95</v>
+        <v>13634.1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13455.24</v>
+        <v>13490.25</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13940.15</v>
+        <v>13941.97</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>434.75</v>
+        <v>438.9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>447.56</v>
+        <v>446.74</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>451.78</v>
+        <v>451.28</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>426.52</v>
+        <v>426.34</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1848.2</v>
+        <v>1883.2</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1804.5</v>
+        <v>1812</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1745.03</v>
+        <v>1750.45</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1559.01</v>
+        <v>1561.47</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8618.5</v>
+        <v>8696</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8468.33</v>
+        <v>8490.02</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8218.549999999999</v>
+        <v>8237.27</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7687.4</v>
+        <v>7698.67</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>290.3</v>
+        <v>289.9</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>289.22</v>
+        <v>289.28</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>292.06</v>
+        <v>291.98</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>323.77</v>
+        <v>323.39</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1048.1</v>
+        <v>1066.7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>992.62</v>
+        <v>999.67</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>975.02</v>
+        <v>978.62</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>907.13</v>
+        <v>908.5700000000001</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1362.2</v>
+        <v>1421.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1435.52</v>
+        <v>1399.84</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1445.73</v>
+        <v>1408.07</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1472.65</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1433.48</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5399</v>
+        <v>5444</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5013.34</v>
+        <v>5054.36</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4754.48</v>
+        <v>4781.52</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4880.36</v>
+        <v>4887.53</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2182</v>
+        <v>2210.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2156.83</v>
+        <v>2161.95</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2171.46</v>
+        <v>2173</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2252.98</v>
+        <v>2253.18</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2716.4</v>
+        <v>2744.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2664</v>
+        <v>2671.67</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2600.85</v>
+        <v>2606.48</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2511.21</v>
+        <v>2513.88</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11456</v>
+        <v>11536</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11346.85</v>
+        <v>11364.86</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11434.56</v>
+        <v>11438.53</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11713.56</v>
+        <v>11727.39</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>240.01</v>
+        <v>239.73</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>238.68</v>
+        <v>238.78</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.06</v>
+        <v>240.05</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>258.8</v>
+        <v>258.39</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>347.8</v>
+        <v>345.95</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>361.96</v>
+        <v>360.43</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>361.78</v>
+        <v>361.16</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>412.45</v>
+        <v>411.65</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7139</v>
+        <v>7250</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7375</v>
+        <v>7363.09</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7292.32</v>
+        <v>7290.66</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7002.59</v>
+        <v>7005.35</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4398.6</v>
+        <v>4481.1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4289.88</v>
+        <v>4308.09</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4250.18</v>
+        <v>4259.24</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4037.86</v>
+        <v>4041.19</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3290.3</v>
+        <v>3317.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3082.28</v>
+        <v>3104.71</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2925.99</v>
+        <v>2941.36</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3365.94</v>
+        <v>3370.98</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>287.55</v>
+        <v>288.2</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>288.59</v>
+        <v>288.55</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>293.06</v>
+        <v>292.86</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>288.71</v>
+        <v>288.67</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3140.4</v>
+        <v>3169.2</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3112.59</v>
+        <v>3117.98</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3032.7</v>
+        <v>3038.05</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2862.06</v>
+        <v>2867.49</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>234.99</v>
+        <v>235.96</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>246.97</v>
+        <v>245.92</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>261.06</v>
+        <v>260.08</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>257.46</v>
+        <v>257.19</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1034.2</v>
+        <v>1078.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1119.7</v>
+        <v>1115.74</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1176.6</v>
+        <v>1172.74</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1352.15</v>
+        <v>1350.26</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1453.8</v>
+        <v>1446.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1406.13</v>
+        <v>1409.94</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1392.27</v>
+        <v>1394.39</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1306.87</v>
+        <v>1308.07</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1216.2</v>
+        <v>1223.8</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1256.75</v>
+        <v>1253.61</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1259.32</v>
+        <v>1257.92</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1198.58</v>
+        <v>1198.85</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>569.95</v>
+        <v>571.35</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>582.08</v>
+        <v>581.0599999999999</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>593.6900000000001</v>
+        <v>592.8200000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>659.42</v>
+        <v>658.25</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9842</v>
+        <v>9857</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>9972.700000000001</v>
+        <v>9961.68</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9966.280000000001</v>
+        <v>9962</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9400.309999999999</v>
+        <v>9399.98</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1797.6</v>
+        <v>1855.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1759.35</v>
+        <v>1768.52</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1767.18</v>
+        <v>1770.65</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1871.19</v>
+        <v>1873.19</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1339.9</v>
+        <v>1345.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1314.21</v>
+        <v>1317.21</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1298.61</v>
+        <v>1300.46</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1271.02</v>
+        <v>1270.39</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1456.7</v>
+        <v>1456</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1412.05</v>
+        <v>1416.23</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1376.15</v>
+        <v>1379.28</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1388.7</v>
+        <v>1388.84</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1090.9</v>
+        <v>1107.2</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1117.72</v>
+        <v>1116.72</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1130.81</v>
+        <v>1129.88</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1121.68</v>
+        <v>1121.54</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1790.9</v>
+        <v>1784.4</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1779.3</v>
+        <v>1779.79</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1814.68</v>
+        <v>1813.49</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1867.39</v>
+        <v>1866.03</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 02-Jul-2026  12:54:22    |    Closing Price Date: 02-Jul-2026</t>
+          <t>Scan Run: 03-Jul-2026  12:54:12    |    Closing Price Date: 03-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>58</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>02-Jul-2026  12:54:22</t>
+          <t>03-Jul-2026  12:54:12</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 64.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 54.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 32 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 27 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 29 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1303.5</v>
+        <v>1304</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1310.78</v>
+        <v>1310.13</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1329.68</v>
+        <v>1328.67</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1379.71</v>
+        <v>1378.43</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>795.9</v>
+        <v>801.05</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>778.92</v>
+        <v>781.03</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>775.08</v>
+        <v>776.1</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>844.62</v>
+        <v>843.88</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2068.1</v>
+        <v>2093.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2127.95</v>
+        <v>2124.67</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2240.12</v>
+        <v>2234.37</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2629.58</v>
+        <v>2623.35</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>174</v>
+        <v>176.08</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>179.92</v>
+        <v>179.56</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>188.91</v>
+        <v>188.41</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>213.71</v>
+        <v>213.19</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1400</v>
+        <v>1411.4</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1346.92</v>
+        <v>1353.06</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1317.48</v>
+        <v>1321.16</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1335.6</v>
+        <v>1336.02</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1051.6</v>
+        <v>1040</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1025.24</v>
+        <v>1026.65</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1017.99</v>
+        <v>1018.86</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>981.9</v>
+        <v>982.12</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1875</v>
+        <v>1910.4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1857.83</v>
+        <v>1862.83</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1855.49</v>
+        <v>1857.65</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1897.87</v>
+        <v>1898.33</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1040.9</v>
+        <v>1047.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1074.29</v>
+        <v>1071.71</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1131.9</v>
+        <v>1128.58</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1306.17</v>
+        <v>1302.43</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3175.4</v>
+        <v>3136.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3071.34</v>
+        <v>3077.58</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3085.6</v>
+        <v>3087.62</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3208.21</v>
+        <v>3207.76</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1157,29 +1157,29 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4059.4</v>
+        <v>4026.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4108.48</v>
+        <v>4100.69</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4033.75</v>
+        <v>4033.47</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3888.1</v>
+        <v>3888.44</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1362.6</v>
+        <v>1342.1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1345.84</v>
+        <v>1345.48</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1320.07</v>
+        <v>1320.94</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1270.48</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1270.25</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>187.67</v>
+        <v>189.8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>194.09</v>
+        <v>193.68</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>198.31</v>
+        <v>197.97</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.65</v>
+        <v>187.63</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>279.7</v>
+        <v>281.65</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>259.63</v>
+        <v>261.73</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>254.41</v>
+        <v>255.48</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.76</v>
+        <v>262.68</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1871</v>
+        <v>1904.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1844.69</v>
+        <v>1850.42</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1819.02</v>
+        <v>1822.38</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1756.15</v>
+        <v>1757.38</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1127.4</v>
+        <v>1153.4</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1076.05</v>
+        <v>1081.69</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1042.41</v>
+        <v>1044.98</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1061.72</v>
+        <v>1058.63</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>399.3</v>
+        <v>396.75</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>397.56</v>
+        <v>397.49</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.06</v>
+        <v>392.24</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>401.34</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>401.09</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>358.25</v>
+        <v>356.45</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>361.12</v>
+        <v>360.68</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>369.86</v>
+        <v>369.34</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>361.54</v>
+        <v>360.99</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1018.4</v>
+        <v>1031.4</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>960.3</v>
+        <v>967.0700000000001</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>935.84</v>
+        <v>939.59</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>937.15</v>
+        <v>937.25</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>949.2</v>
+        <v>953.2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>997.17</v>
+        <v>992.98</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1018.36</v>
+        <v>1015.8</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>927.88</v>
+        <v>928.04</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3177.5</v>
+        <v>3212.1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>3000.73</v>
+        <v>3020.86</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2799.35</v>
+        <v>2815.53</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2463.07</v>
+        <v>2470.19</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>415.05</v>
+        <v>418.05</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>414.99</v>
+        <v>415.28</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>419.48</v>
+        <v>419.42</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.4</v>
+        <v>412.43</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>14348</v>
+        <v>14366</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13634.1</v>
+        <v>13703.8</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13490.25</v>
+        <v>13524.59</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13941.97</v>
+        <v>13940.54</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>438.9</v>
+        <v>438.7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>446.74</v>
+        <v>445.97</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>451.28</v>
+        <v>450.78</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>426.34</v>
+        <v>426.32</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1883.2</v>
+        <v>1874.2</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1812</v>
+        <v>1817.92</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1750.45</v>
+        <v>1755.3</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1561.47</v>
+        <v>1564.54</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8696</v>
+        <v>8893.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8490.02</v>
+        <v>8528.440000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8237.27</v>
+        <v>8263.01</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7698.67</v>
+        <v>7705.22</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>289.9</v>
+        <v>289.95</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>289.28</v>
+        <v>289.35</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>291.98</v>
+        <v>291.9</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>323.39</v>
+        <v>322.96</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1066.7</v>
+        <v>1063.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>999.67</v>
+        <v>1003.91</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>978.62</v>
+        <v>978.74</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>908.5700000000001</v>
+        <v>906</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1421.3</v>
+        <v>1410.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1399.84</v>
+        <v>1400.82</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1408.07</v>
+        <v>1408.15</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1433.48</v>
+        <v>1431.68</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5444</v>
+        <v>5426.5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5054.36</v>
+        <v>5089.8</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4781.52</v>
+        <v>4806.82</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4887.53</v>
+        <v>4893.68</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2210.6</v>
+        <v>2201.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2161.95</v>
+        <v>2165.69</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2173</v>
+        <v>2174.1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2253.18</v>
+        <v>2251.61</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2744.5</v>
+        <v>2737.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2671.67</v>
+        <v>2677.96</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2606.48</v>
+        <v>2611.63</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2513.88</v>
+        <v>2515.79</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11536</v>
+        <v>11723</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11364.86</v>
+        <v>11398.97</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11438.53</v>
+        <v>11449.69</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11727.39</v>
+        <v>11726.54</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>239.73</v>
+        <v>239.35</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>238.78</v>
+        <v>238.83</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>240.05</v>
+        <v>240.02</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>258.39</v>
+        <v>258</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>345.95</v>
+        <v>344.1</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>360.43</v>
+        <v>358.88</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>361.16</v>
+        <v>360.49</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>411.65</v>
+        <v>410.9</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,29 +2257,29 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7250</v>
+        <v>7339.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7363.09</v>
+        <v>7360.84</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7290.66</v>
+        <v>7292.57</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7005.35</v>
+        <v>7007.51</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4481.1</v>
+        <v>4461.1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4308.09</v>
+        <v>4322.66</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4259.24</v>
+        <v>4267.15</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4041.19</v>
+        <v>4045.53</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3317.8</v>
+        <v>3340.6</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3104.71</v>
+        <v>3127.17</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2941.36</v>
+        <v>2957.01</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3370.98</v>
+        <v>3376.47</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>288.2</v>
+        <v>287.85</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>288.55</v>
+        <v>288.48</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>292.86</v>
+        <v>292.67</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>288.67</v>
+        <v>288.66</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3169.2</v>
+        <v>3180.9</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3117.98</v>
+        <v>3123.97</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3038.05</v>
+        <v>3043.66</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2867.49</v>
+        <v>2871.13</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>235.96</v>
+        <v>237.84</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>245.92</v>
+        <v>245.15</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>260.08</v>
+        <v>259.21</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>257.19</v>
+        <v>256.89</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,24 +2521,24 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1078.1</v>
+        <v>1139</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1115.74</v>
+        <v>1117.96</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1172.74</v>
+        <v>1171.42</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1350.26</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1348.5</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1446.2</v>
+        <v>1459.8</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1409.94</v>
+        <v>1414.69</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1394.39</v>
+        <v>1396.95</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1308.07</v>
+        <v>1309.34</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1223.8</v>
+        <v>1230.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1253.61</v>
+        <v>1251.38</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1257.92</v>
+        <v>1256.84</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1198.85</v>
+        <v>1198.94</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>571.35</v>
+        <v>567.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>581.0599999999999</v>
+        <v>579.78</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>592.8200000000001</v>
+        <v>591.83</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>658.25</v>
+        <v>657.15</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9857</v>
+        <v>9785.5</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>9961.68</v>
+        <v>9944.9</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9962</v>
+        <v>9955.08</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9399.98</v>
+        <v>9402.629999999999</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1855.7</v>
+        <v>1895.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1768.52</v>
+        <v>1780.63</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1770.65</v>
+        <v>1775.55</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1873.19</v>
+        <v>1873.34</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1345.7</v>
+        <v>1374.1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1317.21</v>
+        <v>1322.63</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1300.46</v>
+        <v>1303.35</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1270.39</v>
+        <v>1270.86</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1456</v>
+        <v>1458.2</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1416.23</v>
+        <v>1420.23</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1379.28</v>
+        <v>1382.37</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1388.84</v>
+        <v>1388.07</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1107.2</v>
+        <v>1116.7</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1116.72</v>
+        <v>1116.71</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1129.88</v>
+        <v>1129.37</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1121.54</v>
+        <v>1121.03</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1784.4</v>
+        <v>1788.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1779.79</v>
+        <v>1780.64</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1813.49</v>
+        <v>1812.52</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1866.03</v>
+        <v>1864.59</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 03-Jul-2026  12:54:12    |    Closing Price Date: 03-Jul-2026</t>
+          <t>Scan Run: 06-Jul-2026  14:21:59    |    Closing Price Date: 06-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>03-Jul-2026  12:54:12</t>
+          <t>06-Jul-2026  14:21:59</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 29 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 29 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 28 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,37 +761,37 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1304</v>
+        <v>1321.3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1310.13</v>
+        <v>1311.2</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1328.67</v>
+        <v>1328.38</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1378.43</v>
+        <v>1376.98</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -805,37 +805,37 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>801.05</v>
+        <v>829.85</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>781.03</v>
+        <v>785.6799999999999</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>776.1</v>
+        <v>778.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>843.88</v>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+        <v>842.92</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -849,37 +849,37 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2093.5</v>
+        <v>2057.6</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2124.67</v>
+        <v>2118.28</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2234.37</v>
+        <v>2227.44</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2623.35</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+        <v>2614.22</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -893,37 +893,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>176.08</v>
+        <v>174.32</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>179.56</v>
+        <v>179.06</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>188.41</v>
+        <v>187.85</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>213.19</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+        <v>212.6</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -937,37 +937,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1411.4</v>
+        <v>1426.9</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1353.06</v>
+        <v>1360.1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1321.16</v>
+        <v>1325.31</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1336.02</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+        <v>1336.17</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -981,37 +981,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1040</v>
+        <v>1037.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1026.65</v>
+        <v>1027.7</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1018.86</v>
+        <v>1019.59</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>982.12</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+        <v>982.98</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1910.4</v>
+        <v>1925.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1862.83</v>
+        <v>1868.82</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1857.65</v>
+        <v>1860.31</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1898.33</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+        <v>1897.99</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1047.2</v>
+        <v>1042.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1071.71</v>
+        <v>1068.9</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1128.58</v>
+        <v>1125.19</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1302.43</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+        <v>1296.85</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1113,37 +1113,37 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3136.9</v>
+        <v>3201.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3077.58</v>
+        <v>3087.13</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3087.62</v>
+        <v>3091.29</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3207.76</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+        <v>3203.45</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4026.6</v>
+        <v>4041</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4100.69</v>
+        <v>4095</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4033.47</v>
+        <v>4033.76</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3888.44</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+        <v>3889.58</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1342.1</v>
+        <v>1339.6</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1345.48</v>
+        <v>1344.92</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1320.94</v>
+        <v>1321.67</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1270.25</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+        <v>1270.48</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>189.8</v>
+        <v>190.87</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>193.68</v>
+        <v>193.41</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>197.97</v>
+        <v>197.7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.63</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+        <v>187.56</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>281.65</v>
+        <v>283.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>261.73</v>
+        <v>263.79</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>255.48</v>
+        <v>256.57</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>262.68</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+        <v>262.83</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1333,37 +1333,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1904.8</v>
+        <v>1912.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1850.42</v>
+        <v>1856.36</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1822.38</v>
+        <v>1825.93</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1757.38</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+        <v>1756.36</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1153.4</v>
+        <v>1132.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1081.69</v>
+        <v>1090.53</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1044.98</v>
+        <v>1051.41</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1058.63</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+        <v>1058.31</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>396.75</v>
+        <v>381.3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>397.49</v>
+        <v>395.94</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.24</v>
+        <v>391.81</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>401.09</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+        <v>400.9</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>356.45</v>
+        <v>356.25</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>360.68</v>
+        <v>360.26</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>369.34</v>
+        <v>368.82</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>360.99</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+        <v>360.83</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1031.4</v>
+        <v>1029.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>967.0700000000001</v>
+        <v>972.98</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>939.59</v>
+        <v>943.1</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>937.25</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+        <v>937.4400000000001</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>953.2</v>
+        <v>980.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>992.98</v>
+        <v>991.78</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1015.8</v>
+        <v>1014.42</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>928.04</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+        <v>927.38</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3212.1</v>
+        <v>3206.6</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>3020.86</v>
+        <v>3038.55</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2815.53</v>
+        <v>2830.87</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2470.19</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+        <v>2478.47</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1641,37 +1641,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>418.05</v>
+        <v>425.55</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>415.28</v>
+        <v>416.26</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>419.42</v>
+        <v>419.66</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.43</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
+        <v>412.24</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1685,37 +1685,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>14366</v>
+        <v>14456</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13703.8</v>
+        <v>13775.44</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13524.59</v>
+        <v>13561.12</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13940.54</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+        <v>13934.93</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>438.7</v>
+        <v>432.35</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>445.97</v>
+        <v>444.68</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>450.78</v>
+        <v>450.06</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>426.32</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+        <v>426.49</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1773,37 +1773,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1874.2</v>
+        <v>1864.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1817.92</v>
+        <v>1822.35</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1755.3</v>
+        <v>1759.58</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1564.54</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+        <v>1567.23</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8893.5</v>
+        <v>8888.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8528.440000000001</v>
+        <v>8572.530000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8263.01</v>
+        <v>8300.76</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7705.22</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+        <v>7730.61</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1861,37 +1861,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>289.95</v>
+        <v>288.25</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>289.35</v>
+        <v>289.24</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>291.9</v>
+        <v>291.76</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>322.96</v>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+        <v>322.58</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1063.6</v>
+        <v>1062.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1003.91</v>
+        <v>1009.47</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>978.74</v>
+        <v>982.02</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>906</v>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+        <v>906.08</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1410.1</v>
+        <v>1406.5</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1400.82</v>
+        <v>1399.72</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1408.15</v>
+        <v>1408.19</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1431.68</v>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+        <v>1431.77</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5426.5</v>
+        <v>5408.5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5089.8</v>
+        <v>5120.15</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4806.82</v>
+        <v>4830.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4893.68</v>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+        <v>4898.84</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2201.2</v>
+        <v>2202</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2165.69</v>
+        <v>2169.15</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2174.1</v>
+        <v>2175.2</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2251.61</v>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+        <v>2250.61</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2737.8</v>
+        <v>2754.9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2677.96</v>
+        <v>2685.29</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2611.63</v>
+        <v>2617.25</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2515.79</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+        <v>2517.85</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11723</v>
+        <v>11661</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11398.97</v>
+        <v>11423.92</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11449.69</v>
+        <v>11457.98</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11726.54</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+        <v>11724.75</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2169,37 +2169,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>239.35</v>
+        <v>240</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>238.83</v>
+        <v>238.95</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>240.02</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>258</v>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+        <v>258.15</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2213,37 +2213,37 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>344.1</v>
+        <v>347.05</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>358.88</v>
+        <v>357.75</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>360.49</v>
+        <v>359.97</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>410.9</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+        <v>408.74</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7339.5</v>
+        <v>7471.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7360.84</v>
+        <v>7371.38</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7292.57</v>
+        <v>7299.59</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7007.51</v>
+        <v>7008.06</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2301,37 +2301,37 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4461.1</v>
+        <v>4484.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4322.66</v>
+        <v>4338.06</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4267.15</v>
+        <v>4275.67</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4045.53</v>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+        <v>4046.84</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3340.6</v>
+        <v>3343.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3127.17</v>
+        <v>3147.81</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2957.01</v>
+        <v>2972.18</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3376.47</v>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+        <v>3387.11</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>287.85</v>
+        <v>285.4</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>288.48</v>
+        <v>288.19</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>292.67</v>
+        <v>292.38</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>288.66</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+        <v>288.56</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3180.9</v>
+        <v>3213</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3123.97</v>
+        <v>3132.45</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3043.66</v>
+        <v>3050.3</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2871.13</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+        <v>2876.11</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>237.84</v>
+        <v>243.9</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>245.15</v>
+        <v>245.03</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>259.21</v>
+        <v>258.61</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>256.89</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+        <v>257.1</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1139</v>
+        <v>1134.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1117.96</v>
+        <v>1119.5</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1171.42</v>
+        <v>1169.96</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1348.5</v>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+        <v>1342.16</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1459.8</v>
+        <v>1473.7</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1414.69</v>
+        <v>1420.31</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1396.95</v>
+        <v>1399.96</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1309.34</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+        <v>1310.77</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1230.2</v>
+        <v>1243.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1251.38</v>
+        <v>1250.6</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1256.84</v>
+        <v>1256.3</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1198.94</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+        <v>1199.37</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2653,37 +2653,37 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>567.7</v>
+        <v>564.2</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>579.78</v>
+        <v>578.3</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>591.83</v>
+        <v>590.75</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>657.15</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+        <v>657.27</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>9785.5</v>
+        <v>10036.5</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>9944.9</v>
+        <v>9953.629999999999</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9955.08</v>
+        <v>9958.27</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>9402.629999999999</v>
+        <v>9409.65</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2741,37 +2741,37 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1895.6</v>
+        <v>1870.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1780.63</v>
+        <v>1789.2</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1775.55</v>
+        <v>1779.28</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1873.34</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+        <v>1872.99</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2785,37 +2785,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1374.1</v>
+        <v>1367.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1322.63</v>
+        <v>1326.94</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1303.35</v>
+        <v>1305.88</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1270.86</v>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+        <v>1271.31</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2829,37 +2829,37 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1458.2</v>
+        <v>1472.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1420.23</v>
+        <v>1425.19</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1382.37</v>
+        <v>1385.9</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1388.07</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+        <v>1387.57</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2873,37 +2873,37 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1116.7</v>
+        <v>1117.9</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1116.71</v>
+        <v>1116.83</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1129.37</v>
+        <v>1128.92</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1121.03</v>
+        <v>1122.37</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1788.7</v>
+        <v>1787.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1780.64</v>
+        <v>1781.31</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1812.52</v>
+        <v>1811.54</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1864.59</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+        <v>1863.99</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +89,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +163,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 07-Jul-2026  13:15:58    |    Closing Price Date: 07-Jul-2026</t>
+          <t>Scan Run: 08-Jul-2026  12:17:33    |    Closing Price Date: 08-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07-Jul-2026  13:15:58</t>
+          <t>08-Jul-2026  12:17:33</t>
         </is>
       </c>
     </row>
@@ -617,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BULLISH — 68.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BULLISH — 60.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 62.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -645,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 34 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 30 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 24 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 31 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1308.4</v>
+        <v>1275.9</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1310.93</v>
+        <v>1307.6</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1327.6</v>
+        <v>1325.57</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1376.3</v>
+        <v>1375.3</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>829.3</v>
+        <v>810.3</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>789.83</v>
+        <v>791.78</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>780.21</v>
+        <v>781.39</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>842.78</v>
+        <v>842.46</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -841,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2096.1</v>
+        <v>2057.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2116.17</v>
+        <v>2110.58</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2222.28</v>
+        <v>2215.82</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2609.07</v>
+        <v>2603.58</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>173</v>
+        <v>172.72</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>178.48</v>
+        <v>177.93</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>187.27</v>
+        <v>186.7</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>212.21</v>
+        <v>211.82</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1414.7</v>
+        <v>1380.6</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1365.3</v>
+        <v>1366.75</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1328.81</v>
+        <v>1330.84</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1336.95</v>
+        <v>1337.39</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,29 +978,29 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1038.1</v>
+        <v>1016.9</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1028.69</v>
+        <v>1027.57</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1020.32</v>
+        <v>1020.19</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>983.53</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>983.86</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -1017,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1925.8</v>
+        <v>1888.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1874.25</v>
+        <v>1875.57</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1862.88</v>
+        <v>1863.87</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1898.27</v>
+        <v>1898.17</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1042,9 +1047,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1061,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1071.8</v>
+        <v>1069.3</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1069.17</v>
+        <v>1069.19</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1123.1</v>
+        <v>1120.99</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1294.61</v>
+        <v>1292.36</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1105,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3196.4</v>
+        <v>3102.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3097.53</v>
+        <v>3098.01</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3095.41</v>
+        <v>3095.69</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3203.38</v>
+        <v>3202.37</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1149,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3991.9</v>
+        <v>3892.1</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>4085.18</v>
+        <v>4066.79</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>4032.12</v>
+        <v>4026.63</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3890.59</v>
+        <v>3890.61</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,29 +1198,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1341</v>
+        <v>1309.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1344.55</v>
+        <v>1341.21</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1322.43</v>
+        <v>1321.92</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1271.18</v>
+        <v>1271.56</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1237,17 +1242,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>189.79</v>
+        <v>188.2</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>193.07</v>
+        <v>192.6</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>197.39</v>
+        <v>197.03</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>187.58</v>
@@ -1281,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>289.4</v>
+        <v>286.7</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>266.23</v>
+        <v>268.18</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>257.86</v>
+        <v>258.99</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>263.09</v>
+        <v>263.33</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1903.4</v>
+        <v>1888.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1856.45</v>
+        <v>1859.47</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1824.38</v>
+        <v>1826.88</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1753.27</v>
+        <v>1754.62</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1369,24 +1374,24 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1118.4</v>
+        <v>1084.8</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1093.19</v>
+        <v>1092.39</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1054.04</v>
+        <v>1055.24</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.91</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1059.17</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -1413,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>381.7</v>
+        <v>370.1</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>394.59</v>
+        <v>392.26</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>391.42</v>
+        <v>390.58</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.71</v>
+        <v>400.4</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1457,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>354.2</v>
+        <v>348.7</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>359.68</v>
+        <v>358.63</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>368.25</v>
+        <v>367.48</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>360.76</v>
+        <v>360.64</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1042.5</v>
+        <v>1010.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>979.6</v>
+        <v>982.53</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>947</v>
+        <v>949.48</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>938.48</v>
+        <v>939.2</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1545,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>969.5</v>
+        <v>971.65</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>989.66</v>
+        <v>987.9400000000001</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1012.65</v>
+        <v>1011.05</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>927.8</v>
+        <v>928.24</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>3107.2</v>
+        <v>3046.9</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>3045.09</v>
+        <v>3045.26</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2841.71</v>
+        <v>2849.75</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2484.73</v>
+        <v>2490.32</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1633,24 +1638,24 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>419.15</v>
+        <v>407.6</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>416.54</v>
+        <v>415.69</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>419.64</v>
+        <v>419.17</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.31</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>412.26</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -1658,9 +1663,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -1677,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>14538</v>
+        <v>13951</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13848.07</v>
+        <v>13857.87</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13599.43</v>
+        <v>13613.21</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13940.93</v>
+        <v>13941.03</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1721,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>428.95</v>
+        <v>429.05</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>443.18</v>
+        <v>441.83</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>449.23</v>
+        <v>448.44</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>426.52</v>
+        <v>426.54</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,24 +1770,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1833.9</v>
+        <v>1791.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1823.45</v>
+        <v>1820.42</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1762.49</v>
+        <v>1763.64</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1569.88</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1572.09</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1809,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8837</v>
+        <v>8753.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8597.719999999999</v>
+        <v>8612.549999999999</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8321.790000000001</v>
+        <v>8338.719999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7741.62</v>
+        <v>7751.69</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>288.75</v>
+        <v>280.65</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>289.19</v>
+        <v>288.38</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>291.64</v>
+        <v>291.21</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>322.25</v>
+        <v>321.83</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,24 +1902,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1066.8</v>
+        <v>1014.4</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1014.93</v>
+        <v>1014.88</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>985.34</v>
+        <v>986.48</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>907.6799999999999</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>908.75</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -1941,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1447.5</v>
+        <v>1428.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1404.27</v>
+        <v>1406.61</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1409.73</v>
+        <v>1410.48</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1431.93</v>
+        <v>1431.9</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1966,9 +1971,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -1985,24 +1990,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>5395</v>
+        <v>5124</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5146.33</v>
+        <v>5144.2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4852.55</v>
+        <v>4863.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4903.78</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4905.97</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -2029,29 +2034,29 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2208.8</v>
+        <v>2135.8</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2172.92</v>
+        <v>2169.39</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2176.51</v>
+        <v>2174.92</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2250.19</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2249.05</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2073,24 +2078,24 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2731.4</v>
+        <v>2665.9</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2689.68</v>
+        <v>2687.42</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2621.73</v>
+        <v>2623.46</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2519.98</v>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2521.43</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -2117,29 +2122,29 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11649</v>
+        <v>11353</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11445.36</v>
+        <v>11436.56</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11465.47</v>
+        <v>11461.06</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11724</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11720.31</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -2161,29 +2166,29 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>243.07</v>
+        <v>229.99</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>239.34</v>
+        <v>238.45</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>240.14</v>
+        <v>239.74</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>258</v>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>257.72</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -2205,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>342.3</v>
+        <v>332.05</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>356.28</v>
+        <v>353.97</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>359.27</v>
+        <v>358.21</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>408.08</v>
+        <v>407.32</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7536</v>
+        <v>7418.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7387.06</v>
+        <v>7390.06</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7308.86</v>
+        <v>7313.16</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7013.32</v>
+        <v>7017.35</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -2293,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4604.2</v>
+        <v>4586.4</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4363.41</v>
+        <v>4384.65</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4288.56</v>
+        <v>4300.24</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4052.39</v>
+        <v>4057.7</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2337,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2927.8</v>
+        <v>2924</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>3126.85</v>
+        <v>3107.53</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2970.44</v>
+        <v>2968.62</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3382.54</v>
+        <v>3377.97</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>284.35</v>
+        <v>279.7</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>287.83</v>
+        <v>287.05</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>292.07</v>
+        <v>291.58</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>288.51</v>
+        <v>288.43</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,24 +2430,24 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3190.9</v>
+        <v>3134.8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3138.02</v>
+        <v>3137.71</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3055.81</v>
+        <v>3058.91</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>2879.25</v>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2881.79</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -2469,24 +2474,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>244.18</v>
+        <v>247</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>244.95</v>
+        <v>245.15</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>258.04</v>
+        <v>257.61</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>256.97</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>256.87</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1168.2</v>
+        <v>1145.6</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1124.14</v>
+        <v>1126.18</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1169.89</v>
+        <v>1168.93</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1340.43</v>
+        <v>1338.49</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1471.8</v>
+        <v>1450.5</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1425.21</v>
+        <v>1427.62</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1402.78</v>
+        <v>1404.65</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1312.37</v>
+        <v>1313.75</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2601,24 +2606,24 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1246.4</v>
+        <v>1219.5</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1243.74</v>
+        <v>1241.43</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1249.02</v>
+        <v>1247.86</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1193.05</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1193.32</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -2645,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>572.45</v>
+        <v>555.7</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>577.74</v>
+        <v>575.64</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>590.03</v>
+        <v>588.6900000000001</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>656.4299999999999</v>
+        <v>655.42</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10109.5</v>
+        <v>10164</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>9968.469999999999</v>
+        <v>9987.09</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>9964.200000000001</v>
+        <v>9972.030000000001</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>9416.610000000001</v>
+        <v>9424.049999999999</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2733,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1885.3</v>
+        <v>1854.9</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1798.36</v>
+        <v>1803.74</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1783.44</v>
+        <v>1786.24</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1873.11</v>
+        <v>1872.93</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2758,9 +2763,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -2777,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1354.6</v>
+        <v>1349</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1329.57</v>
+        <v>1331.42</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1307.79</v>
+        <v>1309.4</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1272.14</v>
+        <v>1272.9</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1451.8</v>
+        <v>1431.8</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1427.72</v>
+        <v>1428.11</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1388.48</v>
+        <v>1390.18</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1388.21</v>
+        <v>1388.64</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2865,24 +2870,24 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1125</v>
+        <v>1089.8</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1117.61</v>
+        <v>1114.96</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1128.76</v>
+        <v>1127.24</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1122.39</v>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1122.07</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2890,9 +2895,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
@@ -2909,29 +2914,29 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1832.3</v>
+        <v>1789</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1786.16</v>
+        <v>1786.43</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1812.36</v>
+        <v>1811.44</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1863.68</v>
+        <v>1862.93</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jul-2026  12:17:33    |    Closing Price Date: 08-Jul-2026</t>
+          <t>Scan Run: 09-Jul-2026  13:46:23    |    Closing Price Date: 09-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jul-2026  12:17:33</t>
+          <t>09-Jul-2026  13:46:23</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 48.0% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 22 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 24 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 25 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 26 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 25 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1275.9</v>
+        <v>1279.8</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1307.6</v>
+        <v>1304.95</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1325.57</v>
+        <v>1323.78</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1375.3</v>
+        <v>1374.35</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>810.3</v>
+        <v>817.55</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>791.78</v>
+        <v>794.24</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>781.39</v>
+        <v>782.8099999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>842.46</v>
+        <v>842.21</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2057.5</v>
+        <v>2049.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2110.58</v>
+        <v>2104.76</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2215.82</v>
+        <v>2209.3</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2603.58</v>
+        <v>2598.06</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>172.72</v>
+        <v>172.76</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>177.93</v>
+        <v>177.44</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>186.7</v>
+        <v>186.15</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>211.82</v>
+        <v>211.43</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1380.6</v>
+        <v>1380.7</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1366.75</v>
+        <v>1368.08</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1330.84</v>
+        <v>1332.8</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1337.39</v>
+        <v>1337.82</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,29 +978,29 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1016.9</v>
+        <v>1022.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1027.57</v>
+        <v>1027.05</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1020.19</v>
+        <v>1020.26</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>983.86</v>
+        <v>984.24</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1888.1</v>
+        <v>1931.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1875.57</v>
+        <v>1880.85</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1863.87</v>
+        <v>1866.51</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1898.17</v>
+        <v>1898.5</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1047,9 +1047,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1066,24 +1066,24 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1069.3</v>
+        <v>1050.8</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1069.19</v>
+        <v>1067.44</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1120.99</v>
+        <v>1118.23</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1292.36</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1289.96</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1110,29 +1110,29 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3102.5</v>
+        <v>3085.4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3098.01</v>
+        <v>3096.81</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3095.69</v>
+        <v>3095.29</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3202.37</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3201.21</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3892.1</v>
+        <v>3886</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>4066.79</v>
+        <v>4049.57</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>4026.63</v>
+        <v>4021.11</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3890.61</v>
+        <v>3890.56</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1179,9 +1179,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1309.5</v>
+        <v>1297.6</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1341.21</v>
+        <v>1337.06</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1321.92</v>
+        <v>1320.97</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1271.56</v>
+        <v>1271.82</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>188.2</v>
+        <v>187.91</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>192.6</v>
+        <v>192.16</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>197.03</v>
+        <v>196.67</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.58</v>
+        <v>187.59</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>286.7</v>
+        <v>292.45</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>268.18</v>
+        <v>270.49</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>258.99</v>
+        <v>260.3</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>263.33</v>
+        <v>263.62</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1888.2</v>
+        <v>1938.7</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1859.47</v>
+        <v>1867.02</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1826.88</v>
+        <v>1831.27</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1754.62</v>
+        <v>1756.45</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,24 +1374,24 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1084.8</v>
+        <v>1101.3</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1092.39</v>
+        <v>1093.24</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1055.24</v>
+        <v>1057.05</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1059.17</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1059.59</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>370.1</v>
+        <v>377.15</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>392.26</v>
+        <v>390.82</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>390.58</v>
+        <v>390.05</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.4</v>
+        <v>400.17</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>348.7</v>
+        <v>343.7</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>358.63</v>
+        <v>357.21</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>367.48</v>
+        <v>366.55</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>360.64</v>
+        <v>360.47</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1010.4</v>
+        <v>1003.8</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>982.53</v>
+        <v>984.5599999999999</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>949.48</v>
+        <v>951.61</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>939.2</v>
+        <v>939.84</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>971.65</v>
+        <v>963.45</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>987.9400000000001</v>
+        <v>985.61</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1011.05</v>
+        <v>1009.18</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>928.24</v>
+        <v>928.59</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>3046.9</v>
+        <v>3083.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>3045.26</v>
+        <v>3048.91</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2849.75</v>
+        <v>2858.92</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2490.32</v>
+        <v>2496.23</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>407.6</v>
+        <v>406.2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>415.69</v>
+        <v>414.78</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>419.17</v>
+        <v>418.66</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.26</v>
+        <v>412.2</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,24 +1682,24 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>13951</v>
+        <v>13728</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13857.87</v>
+        <v>13845.5</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13613.21</v>
+        <v>13617.72</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13941.03</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>13938.91</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -1707,9 +1707,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>429.05</v>
+        <v>429.9</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>441.83</v>
+        <v>440.7</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>448.44</v>
+        <v>447.71</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>426.54</v>
+        <v>426.58</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1791.7</v>
+        <v>1800.1</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1820.42</v>
+        <v>1818.49</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1763.64</v>
+        <v>1765.07</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1572.09</v>
+        <v>1574.35</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8753.5</v>
+        <v>8845.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8612.549999999999</v>
+        <v>8634.74</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8338.719999999999</v>
+        <v>8358.59</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7751.69</v>
+        <v>7762.57</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>280.65</v>
+        <v>282.05</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>288.38</v>
+        <v>287.78</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>291.21</v>
+        <v>290.85</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>321.83</v>
+        <v>321.44</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,24 +1902,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1014.4</v>
+        <v>1031.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1014.88</v>
+        <v>1016.48</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>986.48</v>
+        <v>988.26</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>908.75</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>909.97</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1428.8</v>
+        <v>1426.3</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1406.61</v>
+        <v>1408.48</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1410.48</v>
+        <v>1411.1</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1431.9</v>
+        <v>1431.84</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1990,24 +1990,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>5124</v>
+        <v>5229.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5144.2</v>
+        <v>5152.33</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4863.2</v>
+        <v>4877.56</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4905.97</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4909.19</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2135.8</v>
+        <v>2144.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2169.39</v>
+        <v>2167.02</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2174.92</v>
+        <v>2173.72</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2249.05</v>
+        <v>2248.01</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2665.9</v>
+        <v>2673.8</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2687.42</v>
+        <v>2686.12</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2623.46</v>
+        <v>2625.43</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2521.43</v>
+        <v>2522.94</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,29 +2122,29 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11353</v>
+        <v>11524</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11436.56</v>
+        <v>11444.89</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11461.06</v>
+        <v>11463.53</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11720.31</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>11718.36</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>229.99</v>
+        <v>233.37</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>238.45</v>
+        <v>237.96</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>239.74</v>
+        <v>239.49</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>257.72</v>
+        <v>257.48</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>332.05</v>
+        <v>331.5</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>353.97</v>
+        <v>351.83</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>358.21</v>
+        <v>357.16</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>407.32</v>
+        <v>406.57</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2254,24 +2254,24 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7418.5</v>
+        <v>7361</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7390.06</v>
+        <v>7387.29</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7313.16</v>
+        <v>7315.04</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7017.35</v>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>7020.77</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+         